--- a/Status.xlsx
+++ b/Status.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Springer_Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mac014886\Documents\GitHub\sn-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="241">
   <si>
     <t>S. no</t>
   </si>
@@ -898,6 +898,9 @@
 CE : 00 Chapters;
 Comp : 00 Chapters;
 Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>testing</t>
   </si>
 </sst>
 </file>
@@ -908,7 +911,7 @@
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1078,6 +1081,18 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1474,7 +1489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2035,6 +2050,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4400,7 +4424,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H34" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4720,8 +4744,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:S33" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
-  <autoFilter ref="A1:S33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:S34" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
+  <autoFilter ref="A1:S34"/>
   <tableColumns count="19">
     <tableColumn id="1" name="S. no" dataDxfId="66"/>
     <tableColumn id="2" name="Book ID" dataDxfId="65"/>
@@ -5665,7 +5689,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" style="53" customWidth="1"/>
@@ -7296,7 +7320,7 @@
       <c r="S32" s="111"/>
     </row>
     <row r="33" spans="1:19" ht="29">
-      <c r="A33" s="56">
+      <c r="A33" s="35">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -7325,11 +7349,44 @@
       </c>
       <c r="O33" s="120"/>
       <c r="P33" s="120"/>
-      <c r="Q33" s="184"/>
+      <c r="Q33" s="120"/>
       <c r="R33" s="111"/>
       <c r="S33" s="111" t="s">
         <v>174</v>
       </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" s="35">
+        <v>33</v>
+      </c>
+      <c r="B34" s="197">
+        <v>6789</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="132"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="129"/>
+      <c r="J34" s="129"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="129"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="132"/>
+      <c r="O34" s="195"/>
+      <c r="P34" s="195"/>
+      <c r="Q34" s="195"/>
+      <c r="R34" s="111"/>
+      <c r="S34" s="111"/>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="R35" s="196"/>
+      <c r="S35" s="196"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8590,7 +8647,7 @@
       </c>
       <c r="B3" s="98">
         <f>COUNTA(Table2[MPS ID])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="101">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2048,17 +2048,17 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4424,7 +4424,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H34" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -7310,9 +7310,7 @@
       <c r="K32" s="129"/>
       <c r="L32" s="129"/>
       <c r="M32" s="35"/>
-      <c r="N32" s="132">
-        <v>150</v>
-      </c>
+      <c r="N32" s="132"/>
       <c r="O32" s="120"/>
       <c r="P32" s="120"/>
       <c r="Q32" s="184"/>
@@ -7359,7 +7357,7 @@
       <c r="A34" s="35">
         <v>33</v>
       </c>
-      <c r="B34" s="197">
+      <c r="B34" s="196">
         <v>6789</v>
       </c>
       <c r="C34" s="36" t="s">
@@ -7378,15 +7376,15 @@
       <c r="L34" s="129"/>
       <c r="M34" s="35"/>
       <c r="N34" s="132"/>
-      <c r="O34" s="195"/>
-      <c r="P34" s="195"/>
-      <c r="Q34" s="195"/>
+      <c r="O34" s="194"/>
+      <c r="P34" s="194"/>
+      <c r="Q34" s="194"/>
       <c r="R34" s="111"/>
       <c r="S34" s="111"/>
     </row>
     <row r="35" spans="1:19">
-      <c r="R35" s="196"/>
-      <c r="S35" s="196"/>
+      <c r="R35" s="195"/>
+      <c r="S35" s="195"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8718,10 +8716,10 @@
       <c r="J2" s="83"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="194" t="s">
+      <c r="B3" s="197" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="194"/>
+      <c r="C3" s="197"/>
       <c r="E3" s="83"/>
       <c r="F3" s="84"/>
       <c r="G3" s="83"/>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId7"/>
+    <pivotCache cacheId="3" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="241">
   <si>
     <t>S. no</t>
   </si>
@@ -900,7 +900,7 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>testing</t>
+    <t>S650A</t>
   </si>
 </sst>
 </file>
@@ -911,7 +911,7 @@
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,18 +1081,6 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1489,7 +1477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2048,14 +2036,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4424,7 +4406,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H34" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4744,8 +4726,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:S34" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
-  <autoFilter ref="A1:S34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:S33" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
+  <autoFilter ref="A1:S33"/>
   <tableColumns count="19">
     <tableColumn id="1" name="S. no" dataDxfId="66"/>
     <tableColumn id="2" name="Book ID" dataDxfId="65"/>
@@ -5689,7 +5671,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" style="53" customWidth="1"/>
@@ -5784,7 +5766,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="E2" s="57">
         <v>46258</v>
@@ -5798,11 +5780,17 @@
         <v>26</v>
       </c>
       <c r="H2" s="56">
-        <f ca="1">TODAY()-DATE(2026,9,19)</f>
-        <v>37</v>
-      </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="35"/>
+        <f>DATE(2026,10,22)-DATE(2026,9,19)</f>
+        <v>33</v>
+      </c>
+      <c r="I2" s="56">
+        <f>DATE(2026,10,24)-DATE(2026,10,22)</f>
+        <v>2</v>
+      </c>
+      <c r="J2" s="35">
+        <f ca="1">TODAY()-DATE(2026,10,25)</f>
+        <v>1</v>
+      </c>
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
       <c r="M2" s="35">
@@ -6452,7 +6440,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="E14" s="37">
         <v>46286</v>
@@ -6474,10 +6462,13 @@
         <v>3</v>
       </c>
       <c r="J14" s="113">
-        <f ca="1">TODAY()-DATE(2026,10,23)</f>
-        <v>3</v>
-      </c>
-      <c r="K14" s="111"/>
+        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="113">
+        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <v>0</v>
+      </c>
       <c r="L14" s="111"/>
       <c r="M14" s="35">
         <v>7</v>
@@ -6511,7 +6502,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="E15" s="37">
         <v>46282</v>
@@ -6533,10 +6524,13 @@
         <v>1</v>
       </c>
       <c r="J15" s="165">
-        <f ca="1">TODAY()-DATE(2026,10,23)</f>
-        <v>3</v>
-      </c>
-      <c r="K15" s="114"/>
+        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
+        <v>1</v>
+      </c>
+      <c r="K15" s="113">
+        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <v>0</v>
+      </c>
       <c r="L15" s="114"/>
       <c r="M15" s="35">
         <v>41</v>
@@ -7354,37 +7348,8 @@
       </c>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="35">
-        <v>33</v>
-      </c>
-      <c r="B34" s="196">
-        <v>6789</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="132"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="129"/>
-      <c r="J34" s="129"/>
-      <c r="K34" s="129"/>
-      <c r="L34" s="129"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="132"/>
-      <c r="O34" s="194"/>
-      <c r="P34" s="194"/>
-      <c r="Q34" s="194"/>
-      <c r="R34" s="111"/>
-      <c r="S34" s="111"/>
-    </row>
-    <row r="35" spans="1:19">
-      <c r="R35" s="195"/>
-      <c r="S35" s="195"/>
+      <c r="R34" s="194"/>
+      <c r="S34" s="194"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8645,7 +8610,7 @@
       </c>
       <c r="B3" s="98">
         <f>COUNTA(Table2[MPS ID])</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="101">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>
@@ -8716,10 +8681,10 @@
       <c r="J2" s="83"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="195" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="197"/>
+      <c r="C3" s="195"/>
       <c r="E3" s="83"/>
       <c r="F3" s="84"/>
       <c r="G3" s="83"/>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="242">
   <si>
     <t>S. no</t>
   </si>
@@ -901,6 +901,9 @@
   </si>
   <si>
     <t>S650A</t>
+  </si>
+  <si>
+    <t>Pawan</t>
   </si>
 </sst>
 </file>
@@ -911,7 +914,7 @@
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,6 +1084,18 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1477,7 +1492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2036,11 +2051,32 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4406,7 +4442,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H34" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4726,8 +4762,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:S33" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
-  <autoFilter ref="A1:S33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:S34" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
+  <autoFilter ref="A1:S34"/>
   <tableColumns count="19">
     <tableColumn id="1" name="S. no" dataDxfId="66"/>
     <tableColumn id="2" name="Book ID" dataDxfId="65"/>
@@ -7348,8 +7384,31 @@
       </c>
     </row>
     <row r="34" spans="1:19">
-      <c r="R34" s="194"/>
-      <c r="S34" s="194"/>
+      <c r="A34" s="195"/>
+      <c r="B34" s="196">
+        <v>6454</v>
+      </c>
+      <c r="C34" s="197" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="198" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="199"/>
+      <c r="F34" s="199"/>
+      <c r="G34" s="200"/>
+      <c r="H34" s="133"/>
+      <c r="I34" s="201"/>
+      <c r="J34" s="201"/>
+      <c r="K34" s="201"/>
+      <c r="L34" s="201"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="200"/>
+      <c r="O34" s="202"/>
+      <c r="P34" s="202"/>
+      <c r="Q34" s="202"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="114"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8610,7 +8669,7 @@
       </c>
       <c r="B3" s="98">
         <f>COUNTA(Table2[MPS ID])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="101">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>
@@ -8681,10 +8740,10 @@
       <c r="J2" s="83"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="195" t="s">
+      <c r="B3" s="194" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="195"/>
+      <c r="C3" s="194"/>
       <c r="E3" s="83"/>
       <c r="F3" s="84"/>
       <c r="G3" s="83"/>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="8" r:id="rId1"/>
@@ -20,12 +20,12 @@
     <sheet name="MISC" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current Status'!$A$1:$S$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current Status'!$A$1:$S$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MISC!$D$48:$E$74</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="253">
   <si>
     <t>S. no</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>703192_1_En</t>
-  </si>
-  <si>
-    <t>S50</t>
   </si>
   <si>
     <t>S650</t>
@@ -553,9 +550,6 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>(blank)</t>
-  </si>
-  <si>
     <t>Count of S200 TAT</t>
   </si>
   <si>
@@ -634,21 +628,12 @@
     <t>713564_1_En</t>
   </si>
   <si>
-    <t>Ihalanayake, Ranjith</t>
-  </si>
-  <si>
-    <t>PERARNAU-DMD</t>
-  </si>
-  <si>
     <t>Tex</t>
   </si>
   <si>
     <t>Word</t>
   </si>
   <si>
-    <t xml:space="preserve">Package received on 12 oct </t>
-  </si>
-  <si>
     <t>HOLD</t>
   </si>
   <si>
@@ -704,15 +689,6 @@
   </si>
   <si>
     <t>SL. No</t>
-  </si>
-  <si>
-    <t>F reciprterror</t>
-  </si>
-  <si>
-    <t>AL-Emran</t>
-  </si>
-  <si>
-    <t>As per discussion with PE, It will move today to Author</t>
   </si>
   <si>
     <t>S200 - 
@@ -737,9 +713,6 @@
     <t>Books should be spilit in Two vol-I and II in S600 stage</t>
   </si>
   <si>
-    <t xml:space="preserve">S600 uploaded from our side. As per discussion with PE, it wll move to Author once Bflux will start working. </t>
-  </si>
-  <si>
     <t>Hold  for Manuscript</t>
   </si>
   <si>
@@ -785,9 +758,6 @@
     <t>MS Pages</t>
   </si>
   <si>
-    <t>8 Chaps in Eproof, 7 chaps in Revises</t>
-  </si>
-  <si>
     <t>PRR sent on 17th Sep. Query-Reference missing and content mismatch, One new manuscript approval</t>
   </si>
   <si>
@@ -810,12 +780,6 @@
     <t>28 Chaps-Rev.delivered, 3 Part in Eproof, FM-recept error</t>
   </si>
   <si>
-    <t>109 chaps in revises and rest in Eproof Receipt error</t>
-  </si>
-  <si>
-    <t>6 in revises, rest online delivery</t>
-  </si>
-  <si>
     <t>11 in revises. 13 in eproof, FM in 200 comp</t>
   </si>
   <si>
@@ -825,48 +789,13 @@
     <t>All in revises</t>
   </si>
   <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 00 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 03 Chapters</t>
-  </si>
-  <si>
     <t>All in  Revises</t>
   </si>
   <si>
     <t>Part, FM in s200 online delivery so not moved to 300</t>
   </si>
   <si>
-    <t>11 chap in Eproof,17 Chaps in Revises.</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 01 Chapters;
-CE : 24 Chapters;
-Comp : 23 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 01 Chapters;
-PE : 24 Chapters;
-CE : 15 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>S200Login</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 01 Chapters;
-CE : 15 Chapters;
-Comp : 20 Chapters;
-Online Delivery : 00 Chapters</t>
   </si>
   <si>
     <t>S200 - 
@@ -883,27 +812,146 @@
     <t>704476_1_En</t>
   </si>
   <si>
-    <t>Zi,-PIC Yunlong</t>
-  </si>
-  <si>
-    <t>Zhan-Ventura, Michele Della</t>
-  </si>
-  <si>
     <t>Preface &amp; TOC(FM components missing)</t>
   </si>
   <si>
+    <t>S650A</t>
+  </si>
+  <si>
+    <t>All are in revises</t>
+  </si>
+  <si>
+    <t>S300 completed</t>
+  </si>
+  <si>
+    <t>Only 8 chaps in Revises. Rest completed</t>
+  </si>
+  <si>
+    <t>MetSoc-Vol9-8771159</t>
+  </si>
+  <si>
+    <t>PageProof-S200</t>
+  </si>
+  <si>
+    <t>PMApproval</t>
+  </si>
+  <si>
+    <t>etSoc-Vol9-8771159</t>
+  </si>
+  <si>
     <t>S200 - 
-Login : 13 Chapters;
-PE : 114 Chapters;
+Login : 00 Chapters;
+PE : 00 Chapters;
+CE : 00 Chapters;
+Comp : 01 Chapters;
+Online Delivery : 03 Chapters</t>
+  </si>
+  <si>
+    <t>20 chap in Revises, rest in eproof</t>
+  </si>
+  <si>
+    <t>15 chap in Eproof,13 Chaps in Revises.</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 129 Chapters;
+PE : 00 Chapters;
 CE : 00 Chapters;
 Comp : 00 Chapters;
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>S650A</t>
-  </si>
-  <si>
-    <t>Pawan</t>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 00 Chapters;
+CE : 13 Chapters;
+Comp : 35 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 01 Chapters;
+PE : 21 Chapters;
+CE : 18 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 00 Chapters;
+CE : 04 Chapters;
+Comp : 24 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 47 Chapters;
+PE : 09 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 36 Chapters;
+PE : 33 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 33 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>Zi,-PIC Yunlong 8770448</t>
+  </si>
+  <si>
+    <t>Zhan-Ventura, Michele Della-8770452</t>
+  </si>
+  <si>
+    <t>707996_1_En</t>
+  </si>
+  <si>
+    <t>Ullah, Abrar</t>
+  </si>
+  <si>
+    <t>704485_1_En</t>
+  </si>
+  <si>
+    <t>González, Carina S. González</t>
+  </si>
+  <si>
+    <t>FM &amp; TOC will be recd in S200 stage</t>
+  </si>
+  <si>
+    <t>Month/No Of Titles</t>
+  </si>
+  <si>
+    <t>Sep, 9 Books</t>
+  </si>
+  <si>
+    <t>Aug, 1 Book</t>
+  </si>
+  <si>
+    <t>Oct 7 Books</t>
+  </si>
+  <si>
+    <t>Average Aging  Days for past months</t>
+  </si>
+  <si>
+    <t>Total Monthly Avg. Aging days</t>
+  </si>
+  <si>
+    <t>Shortest TAT</t>
+  </si>
+  <si>
+    <t>Longest TAT</t>
   </si>
 </sst>
 </file>
@@ -914,7 +962,7 @@
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1098,6 +1146,12 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF393939"/>
+      <name val="Open Sans"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1179,7 +1233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1431,34 +1485,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1488,11 +1514,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1574,12 +1613,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1612,9 +1645,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1647,9 +1677,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1762,18 +1789,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1825,14 +1846,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1874,12 +1889,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1891,65 +1900,23 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2003,9 +1970,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2051,33 +2015,111 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4442,8 +4484,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
-  <location ref="A3:H34" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="A3:H17" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4495,14 +4537,14 @@
     </pivotField>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="8">
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item x="1"/>
         <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item m="1" x="7"/>
-        <item x="6"/>
-        <item x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" m="1" x="7"/>
+        <item h="1" x="6"/>
+        <item h="1" x="3"/>
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4564,26 +4606,11 @@
     <field x="3"/>
     <field x="5"/>
   </rowFields>
-  <rowItems count="30">
+  <rowItems count="13">
     <i>
       <x/>
       <x v="2"/>
       <x v="11"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x/>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x v="7"/>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x v="7"/>
-      <x v="7"/>
     </i>
     <i>
       <x v="5"/>
@@ -4591,79 +4618,14 @@
       <x v="32"/>
     </i>
     <i>
-      <x v="6"/>
-      <x v="3"/>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="7"/>
-      <x/>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="8"/>
-      <x v="4"/>
-      <x/>
-    </i>
-    <i>
-      <x v="9"/>
-      <x v="7"/>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="19"/>
-      <x v="7"/>
-      <x v="6"/>
-    </i>
-    <i>
       <x v="20"/>
       <x v="2"/>
       <x v="29"/>
     </i>
     <i>
-      <x v="21"/>
-      <x v="4"/>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="23"/>
-      <x/>
-      <x v="8"/>
-    </i>
-    <i>
       <x v="25"/>
       <x v="1"/>
       <x v="30"/>
-    </i>
-    <i>
-      <x v="26"/>
-      <x/>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="27"/>
-      <x v="4"/>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="29"/>
-      <x v="3"/>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="30"/>
-      <x v="3"/>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="31"/>
-      <x v="3"/>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="32"/>
-      <x v="6"/>
-      <x v="17"/>
     </i>
     <i>
       <x v="33"/>
@@ -4704,11 +4666,6 @@
       <x v="40"/>
       <x v="2"/>
       <x v="10"/>
-    </i>
-    <i>
-      <x v="41"/>
-      <x/>
-      <x v="6"/>
     </i>
     <i t="grand">
       <x/>
@@ -4790,14 +4747,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S21" totalsRowShown="0">
-  <autoFilter ref="A1:S21">
-    <filterColumn colId="17">
-      <filters>
-        <dateGroupItem year="2026" month="8" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
   <tableColumns count="19">
     <tableColumn id="1" name="S. no" dataDxfId="49"/>
     <tableColumn id="2" name="Book ID" dataDxfId="48"/>
@@ -5117,7 +5067,7 @@
   <cols>
     <col min="1" max="1" width="29.1796875" customWidth="1"/>
     <col min="2" max="2" width="13.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="63" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" style="59" customWidth="1"/>
     <col min="4" max="4" width="16.1796875" customWidth="1"/>
     <col min="5" max="5" width="17.453125" customWidth="1"/>
     <col min="6" max="7" width="16.1796875" customWidth="1"/>
@@ -5125,34 +5075,35 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:8">
-      <c r="D3" s="93" t="s">
+      <c r="C3"/>
+      <c r="D3" s="89" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="29">
+      <c r="A4" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="29">
-      <c r="A4" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="140" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>147</v>
-      </c>
-      <c r="F4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5160,544 +5111,310 @@
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="63">
+        <v>72</v>
+      </c>
+      <c r="C5">
         <v>24</v>
       </c>
-      <c r="D5" s="94">
+      <c r="D5" s="90">
         <v>1</v>
       </c>
-      <c r="E5" s="94">
+      <c r="E5" s="90">
         <v>1</v>
       </c>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="63">
-        <v>19</v>
-      </c>
-      <c r="D6" s="94">
+        <v>72</v>
+      </c>
+      <c r="C6">
+        <v>28</v>
+      </c>
+      <c r="D6" s="90">
         <v>1</v>
       </c>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
+      <c r="E6" s="90">
+        <v>1</v>
+      </c>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C7" s="63">
-        <v>3</v>
-      </c>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
+        <v>72</v>
+      </c>
+      <c r="C7">
+        <v>52</v>
+      </c>
+      <c r="D7" s="90">
+        <v>1</v>
+      </c>
+      <c r="E7" s="90">
+        <v>1</v>
+      </c>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="63">
-        <v>16</v>
-      </c>
-      <c r="D8" s="94">
+        <v>137</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8" s="90">
         <v>1</v>
       </c>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
+      <c r="E8" s="90">
+        <v>1</v>
+      </c>
+      <c r="F8" s="90">
+        <v>1</v>
+      </c>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="63">
-        <v>28</v>
-      </c>
-      <c r="D9" s="94">
+        <v>72</v>
+      </c>
+      <c r="C9" s="191">
+        <v>46291</v>
+      </c>
+      <c r="D9" s="90">
         <v>1</v>
       </c>
-      <c r="E9" s="94">
+      <c r="E9" s="90">
         <v>1</v>
       </c>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="63">
+        <v>72</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10" s="90">
         <v>1</v>
       </c>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
+      <c r="E10" s="90">
+        <v>1</v>
+      </c>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="63">
-        <v>15</v>
-      </c>
-      <c r="D11" s="94">
+        <v>72</v>
+      </c>
+      <c r="C11">
+        <v>22</v>
+      </c>
+      <c r="D11" s="90">
         <v>1</v>
       </c>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
+      <c r="E11" s="90">
+        <v>1</v>
+      </c>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="90"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="63">
-        <v>3</v>
-      </c>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
+        <v>72</v>
+      </c>
+      <c r="C12">
+        <v>22</v>
+      </c>
+      <c r="D12" s="90">
+        <v>1</v>
+      </c>
+      <c r="E12" s="90">
+        <v>1</v>
+      </c>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13" s="63">
-        <v>8</v>
-      </c>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
+        <v>72</v>
+      </c>
+      <c r="C13">
+        <v>27</v>
+      </c>
+      <c r="D13" s="90">
+        <v>1</v>
+      </c>
+      <c r="E13" s="90">
+        <v>1</v>
+      </c>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
-      </c>
-      <c r="C14" s="63">
-        <v>15</v>
-      </c>
-      <c r="D14" s="94">
+        <v>72</v>
+      </c>
+      <c r="C14">
+        <v>27</v>
+      </c>
+      <c r="D14" s="90">
         <v>1</v>
       </c>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
+      <c r="E14" s="90">
+        <v>1</v>
+      </c>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="63">
-        <v>52</v>
-      </c>
-      <c r="D15" s="94">
+        <v>72</v>
+      </c>
+      <c r="C15">
+        <v>27</v>
+      </c>
+      <c r="D15" s="90">
         <v>1</v>
       </c>
-      <c r="E15" s="94">
+      <c r="E15" s="90">
         <v>1</v>
       </c>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="63">
+        <v>72</v>
+      </c>
+      <c r="C16">
+        <v>21</v>
+      </c>
+      <c r="D16" s="90">
         <v>1</v>
       </c>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
+      <c r="E16" s="90">
+        <v>1</v>
+      </c>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="63">
-        <v>18</v>
-      </c>
-      <c r="D17" s="94">
+        <v>142</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17" s="90">
+        <v>12</v>
+      </c>
+      <c r="E17" s="90">
+        <v>12</v>
+      </c>
+      <c r="F17" s="90">
         <v>1</v>
       </c>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="63">
-        <v>41</v>
-      </c>
-      <c r="D18" s="94">
-        <v>1</v>
-      </c>
-      <c r="E18" s="94">
-        <v>1</v>
-      </c>
-      <c r="F18" s="94">
-        <v>1</v>
-      </c>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
+      <c r="C18"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="63">
-        <v>17</v>
-      </c>
-      <c r="D19" s="94">
-        <v>1</v>
-      </c>
-      <c r="E19" s="94"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
+      <c r="C19"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="63">
-        <v>8</v>
-      </c>
-      <c r="D20" s="94"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="94"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
+      <c r="C20"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="63">
-        <v>1</v>
-      </c>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
+      <c r="C21"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="63">
-        <v>1</v>
-      </c>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
+      <c r="C22"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>172</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="63">
-        <v>2</v>
-      </c>
-      <c r="D23" s="94"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
+      <c r="C23"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="63" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
+      <c r="C24"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="134">
-        <v>46291</v>
-      </c>
-      <c r="D25" s="94">
-        <v>1</v>
-      </c>
-      <c r="E25" s="94">
-        <v>1</v>
-      </c>
-      <c r="F25" s="94"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
+      <c r="C25"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>179</v>
-      </c>
-      <c r="B26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="63">
-        <v>19</v>
-      </c>
-      <c r="D26" s="94">
-        <v>1</v>
-      </c>
-      <c r="E26" s="94">
-        <v>1</v>
-      </c>
-      <c r="F26" s="94"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
+      <c r="C26"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="63">
-        <v>22</v>
-      </c>
-      <c r="D27" s="94">
-        <v>1</v>
-      </c>
-      <c r="E27" s="94">
-        <v>1</v>
-      </c>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="94"/>
+      <c r="C27"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="63">
-        <v>22</v>
-      </c>
-      <c r="D28" s="94">
-        <v>1</v>
-      </c>
-      <c r="E28" s="94">
-        <v>1</v>
-      </c>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
+      <c r="C28"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>182</v>
-      </c>
-      <c r="B29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="63">
-        <v>27</v>
-      </c>
-      <c r="D29" s="94">
-        <v>1</v>
-      </c>
-      <c r="E29" s="94">
-        <v>1</v>
-      </c>
-      <c r="F29" s="94"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
+      <c r="C29"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>184</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="63">
-        <v>27</v>
-      </c>
-      <c r="D30" s="94">
-        <v>1</v>
-      </c>
-      <c r="E30" s="94">
-        <v>1</v>
-      </c>
-      <c r="F30" s="94"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
+      <c r="C30"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>183</v>
-      </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="63">
-        <v>27</v>
-      </c>
-      <c r="D31" s="94">
-        <v>1</v>
-      </c>
-      <c r="E31" s="94">
-        <v>1</v>
-      </c>
-      <c r="F31" s="94"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="94"/>
+      <c r="C31"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="63">
-        <v>21</v>
-      </c>
-      <c r="D32" s="94">
-        <v>1</v>
-      </c>
-      <c r="E32" s="94">
-        <v>1</v>
-      </c>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>186</v>
-      </c>
-      <c r="B33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="63">
-        <v>15</v>
-      </c>
-      <c r="D33" s="94">
-        <v>1</v>
-      </c>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="94">
-        <v>19</v>
-      </c>
-      <c r="E34" s="94">
-        <v>12</v>
-      </c>
-      <c r="F34" s="94">
-        <v>1</v>
-      </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
+      <c r="C32"/>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33"/>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5707,35 +5424,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7" style="53" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" style="73" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" style="73" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" style="53" customWidth="1"/>
+    <col min="1" max="1" width="7" style="50" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" style="69" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" style="69" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" style="50" customWidth="1"/>
     <col min="5" max="5" width="18.81640625" style="27" customWidth="1"/>
     <col min="6" max="6" width="23.90625" style="27" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" style="53" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" style="50" customWidth="1"/>
     <col min="8" max="8" width="10" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="8.7265625" style="27" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="27" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7265625" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08984375" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6328125" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.54296875" style="123" customWidth="1"/>
-    <col min="16" max="16" width="16" style="123" customWidth="1"/>
-    <col min="17" max="17" width="15.81640625" style="123" customWidth="1"/>
+    <col min="13" max="13" width="17.08984375" style="55" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" style="50" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.54296875" style="115" customWidth="1"/>
+    <col min="16" max="16" width="16" style="115" customWidth="1"/>
+    <col min="17" max="17" width="15.81640625" style="115" customWidth="1"/>
     <col min="18" max="18" width="19.26953125" style="26" customWidth="1"/>
     <col min="19" max="19" width="15.81640625" style="26"/>
     <col min="20" max="16384" width="15.81640625" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" thickBot="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="22" t="s">
@@ -5748,1667 +5465,1696 @@
         <v>4</v>
       </c>
       <c r="F1" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="21" t="s">
-        <v>54</v>
-      </c>
       <c r="N1" s="21" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="O1" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="P1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="Q1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="27" t="s">
-        <v>58</v>
-      </c>
       <c r="R1" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S1" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="240">
-      <c r="A2" s="56">
-        <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
+      <c r="A2" s="52">
+        <f t="shared" ref="A2:A10" si="0">ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="126" t="s">
+      <c r="C2" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="56" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="57">
+      <c r="D2" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" s="53">
         <v>46258</v>
       </c>
-      <c r="F2" s="92">
+      <c r="F2" s="88">
         <f ca="1">TODAY()-E2</f>
-        <v>63</v>
-      </c>
-      <c r="G2" s="56">
+        <v>64</v>
+      </c>
+      <c r="G2" s="52">
         <f>DATE(2026,9,19)-DATE(2026,8,24)</f>
         <v>26</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="52">
         <f>DATE(2026,10,22)-DATE(2026,9,19)</f>
         <v>33</v>
       </c>
-      <c r="I2" s="56">
+      <c r="I2" s="52">
         <f>DATE(2026,10,24)-DATE(2026,10,22)</f>
         <v>2</v>
       </c>
-      <c r="J2" s="35">
+      <c r="J2" s="33">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>1</v>
-      </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35">
+        <v>2</v>
+      </c>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33">
         <v>32</v>
       </c>
-      <c r="N2" s="35">
+      <c r="N2" s="33">
         <v>500</v>
       </c>
-      <c r="O2" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q2" s="177" t="s">
-        <v>210</v>
-      </c>
-      <c r="R2" s="111" t="s">
-        <v>102</v>
-      </c>
-      <c r="S2" s="111" t="s">
-        <v>174</v>
+      <c r="O2" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q2" s="153" t="s">
+        <v>201</v>
+      </c>
+      <c r="R2" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="S2" s="105" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="60">
-      <c r="A3" s="56">
+      <c r="A3" s="52">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B3" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="127" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="37">
-        <v>46269</v>
-      </c>
-      <c r="F3" s="35">
-        <f ca="1">TODAY()-E3</f>
-        <v>52</v>
-      </c>
-      <c r="G3" s="35">
-        <f>DATE(2026,9,26)-DATE(2026,9,4)</f>
-        <v>22</v>
-      </c>
-      <c r="H3" s="56">
-        <f>DATE(2026,10,11)-DATE(2026,9,26)</f>
+      <c r="B3" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="35">
+        <v>46291</v>
+      </c>
+      <c r="F3" s="33">
+        <f t="shared" ref="F3:F8" ca="1" si="1">TODAY()-E3</f>
+        <v>31</v>
+      </c>
+      <c r="G3" s="33">
+        <f>DATE(2026,10,10)-DATE(2026,9,26)</f>
+        <v>14</v>
+      </c>
+      <c r="H3" s="104">
+        <f>DATE(2026,10,24)-DATE(2026,10,10)</f>
+        <v>14</v>
+      </c>
+      <c r="I3" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,25)</f>
+        <v>2</v>
+      </c>
+      <c r="J3" s="54"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="33">
         <v>15</v>
       </c>
-      <c r="I3" s="35">
-        <f>DATE(2026,10,16)-DATE(2026,10,12)</f>
-        <v>4</v>
-      </c>
-      <c r="J3" s="35">
-        <f ca="1">TODAY()-DATE(2026,10,16)</f>
-        <v>10</v>
-      </c>
-      <c r="K3" s="35">
-        <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>4</v>
-      </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35">
-        <v>14</v>
-      </c>
-      <c r="N3" s="35">
-        <v>189</v>
-      </c>
-      <c r="O3" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="178" t="s">
-        <v>197</v>
-      </c>
-      <c r="R3" s="111" t="s">
-        <v>195</v>
-      </c>
-      <c r="S3" s="111" t="s">
-        <v>189</v>
+      <c r="N3" s="33">
+        <v>200</v>
+      </c>
+      <c r="O3" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P3" s="113" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q3" s="154" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" s="160" t="s">
+        <v>100</v>
+      </c>
+      <c r="S3" s="105" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="60">
-      <c r="A4" s="56">
+      <c r="A4" s="52">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="62" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" s="37">
+      <c r="B4" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="35">
         <v>46291</v>
       </c>
-      <c r="F4" s="35">
-        <f t="shared" ref="F4:F9" ca="1" si="1">TODAY()-E4</f>
-        <v>30</v>
-      </c>
-      <c r="G4" s="35">
-        <f>DATE(2026,10,10)-DATE(2026,9,26)</f>
-        <v>14</v>
-      </c>
-      <c r="H4" s="110">
-        <f>DATE(2026,10,24)-DATE(2026,10,10)</f>
-        <v>14</v>
-      </c>
-      <c r="I4" s="110">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="35">
+      <c r="F4" s="33">
+        <f t="shared" ca="1" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="G4" s="33">
+        <f>DATE(2026,10,12)-DATE(2026,9,26)</f>
+        <v>16</v>
+      </c>
+      <c r="H4" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,12)</f>
         <v>15</v>
       </c>
-      <c r="N4" s="35">
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="33">
+        <v>15</v>
+      </c>
+      <c r="N4" s="33">
         <v>200</v>
       </c>
-      <c r="O4" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="121" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q4" s="179" t="s">
-        <v>75</v>
-      </c>
-      <c r="R4" s="185" t="s">
-        <v>101</v>
-      </c>
-      <c r="S4" s="111" t="s">
-        <v>174</v>
+      <c r="O4" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P4" s="113" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q4" s="154" t="s">
+        <v>74</v>
+      </c>
+      <c r="R4" s="105"/>
+      <c r="S4" s="105" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="60">
-      <c r="A5" s="56">
+      <c r="A5" s="52">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="D5" s="62" t="s">
+      <c r="B5" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="35">
+        <v>46288</v>
+      </c>
+      <c r="F5" s="33">
+        <f t="shared" ca="1" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="G5" s="68">
+        <f>DATE(2026,10,8)-DATE(2026,9,23)</f>
+        <v>15</v>
+      </c>
+      <c r="H5" s="54">
+        <f>DATE(2026,10,24)-DATE(2026,10,8)</f>
+        <v>16</v>
+      </c>
+      <c r="I5" s="54">
+        <f>DATE(2026,10,26)-DATE(2026,10,25)</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="54">
+        <f ca="1">TODAY()-DATE(2026,10,27)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="33">
+        <v>31</v>
+      </c>
+      <c r="N5" s="33">
+        <v>280</v>
+      </c>
+      <c r="O5" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" s="113" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q5" s="154" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="37">
-        <v>46291</v>
-      </c>
-      <c r="F5" s="35">
-        <f t="shared" ca="1" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="G5" s="35">
-        <f>DATE(2026,10,12)-DATE(2026,9,26)</f>
-        <v>16</v>
-      </c>
-      <c r="H5" s="110">
-        <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>14</v>
-      </c>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="35">
-        <v>15</v>
-      </c>
-      <c r="N5" s="35">
-        <v>200</v>
-      </c>
-      <c r="O5" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="121" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q5" s="179" t="s">
-        <v>75</v>
-      </c>
-      <c r="R5" s="111"/>
-      <c r="S5" s="111" t="s">
-        <v>174</v>
+      <c r="R5" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="S5" s="105" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="60">
-      <c r="A6" s="56">
+      <c r="A6" s="52">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="35">
+        <v>46288</v>
+      </c>
+      <c r="F6" s="33">
+        <f t="shared" ca="1" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="G6" s="104">
+        <f>DATE(2026,10,14)-DATE(2026,10,12)</f>
+        <v>2</v>
+      </c>
+      <c r="H6" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,14)</f>
+        <v>13</v>
+      </c>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="33">
         <v>25</v>
       </c>
-      <c r="C6" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="37">
-        <v>46288</v>
-      </c>
-      <c r="F6" s="35">
-        <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="G6" s="72">
-        <f>DATE(2026,10,8)-DATE(2026,9,23)</f>
-        <v>15</v>
-      </c>
-      <c r="H6" s="58">
-        <f>DATE(2026,10,24)-DATE(2026,10,8)</f>
-        <v>16</v>
-      </c>
-      <c r="I6" s="58">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="35">
-        <v>31</v>
-      </c>
-      <c r="N6" s="35">
-        <v>280</v>
-      </c>
-      <c r="O6" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="121" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q6" s="179" t="s">
-        <v>74</v>
-      </c>
-      <c r="R6" s="111" t="s">
-        <v>102</v>
-      </c>
-      <c r="S6" s="111" t="s">
-        <v>174</v>
+      <c r="N6" s="33">
+        <v>240</v>
+      </c>
+      <c r="O6" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" s="113" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q6" s="154" t="s">
+        <v>155</v>
+      </c>
+      <c r="R6" s="161" t="s">
+        <v>192</v>
+      </c>
+      <c r="S6" s="105" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="60">
-      <c r="A7" s="56">
+      <c r="A7" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="76" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="37">
-        <v>46288</v>
-      </c>
-      <c r="F7" s="35">
+      <c r="B7" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="35">
+        <v>46283</v>
+      </c>
+      <c r="F7" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="G7" s="110">
-        <f>DATE(2026,10,14)-DATE(2026,10,12)</f>
+        <v>39</v>
+      </c>
+      <c r="G7" s="33">
+        <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
+        <v>16</v>
+      </c>
+      <c r="H7" s="54">
+        <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
+        <v>12</v>
+      </c>
+      <c r="I7" s="150">
+        <f ca="1">TODAY()-DATE(2026,10,25)</f>
         <v>2</v>
       </c>
-      <c r="H7" s="110">
-        <f ca="1">TODAY()-DATE(2026,10,14)</f>
-        <v>12</v>
-      </c>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="35">
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="33">
         <v>25</v>
       </c>
-      <c r="N7" s="35">
-        <v>240</v>
-      </c>
-      <c r="O7" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" s="121" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q7" s="179" t="s">
-        <v>157</v>
-      </c>
-      <c r="R7" s="186" t="s">
-        <v>200</v>
-      </c>
-      <c r="S7" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="60">
-      <c r="A8" s="56">
+      <c r="N7" s="33">
+        <v>244</v>
+      </c>
+      <c r="O7" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P7" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q7" s="154" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="105" t="s">
+        <v>138</v>
+      </c>
+      <c r="S7" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="149" customFormat="1" ht="60">
+      <c r="A8" s="142">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" s="37">
+      <c r="B8" s="143" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="142" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="144">
         <v>46283</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="142">
         <f t="shared" ca="1" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="G8" s="35">
+        <v>39</v>
+      </c>
+      <c r="G8" s="142">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H8" s="58">
+      <c r="H8" s="145">
+        <f>DATE(2026,10,19)-DATE(2026,10,12)</f>
+        <v>7</v>
+      </c>
+      <c r="I8" s="145">
+        <f ca="1">TODAY()-DATE(2026,10,20)</f>
+        <v>7</v>
+      </c>
+      <c r="J8" s="145">
+        <f>DATE(2026,10,26)-DATE(2026,10,22)</f>
+        <v>4</v>
+      </c>
+      <c r="K8" s="146">
+        <f ca="1">TODAY()-DATE(2026,10,27)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="146"/>
+      <c r="M8" s="142">
+        <v>9</v>
+      </c>
+      <c r="N8" s="142">
+        <v>100</v>
+      </c>
+      <c r="O8" s="147" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8" s="148"/>
+      <c r="Q8" s="155" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="146"/>
+      <c r="S8" s="146" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="60">
+      <c r="A9" s="33">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="35">
+        <v>46283</v>
+      </c>
+      <c r="F9" s="33">
+        <f t="shared" ref="F9:F19" ca="1" si="2">TODAY()-E9</f>
+        <v>39</v>
+      </c>
+      <c r="G9" s="33">
+        <f>DATE(2026,10,9)-DATE(2026,9,21)</f>
+        <v>18</v>
+      </c>
+      <c r="H9" s="54">
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I8" s="174">
+      <c r="I9" s="150">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="35">
-        <v>25</v>
-      </c>
-      <c r="N8" s="35">
-        <v>244</v>
-      </c>
-      <c r="O8" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="33">
+        <v>13</v>
+      </c>
+      <c r="N9" s="33">
+        <v>120</v>
+      </c>
+      <c r="O9" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P9" s="113" t="s">
         <v>223</v>
       </c>
-      <c r="Q8" s="179" t="s">
-        <v>129</v>
-      </c>
-      <c r="R8" s="111" t="s">
-        <v>139</v>
-      </c>
-      <c r="S8" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" s="173" customFormat="1" ht="60">
-      <c r="A9" s="166">
+      <c r="Q9" s="154" t="s">
+        <v>73</v>
+      </c>
+      <c r="R9" s="105"/>
+      <c r="S9" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="60">
+      <c r="A10" s="52">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="167" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="127" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="166" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="35">
+        <v>46289</v>
+      </c>
+      <c r="F10" s="58">
+        <f t="shared" ca="1" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="G10" s="33">
+        <f ca="1">TODAY()-DATE(2026,9,25)</f>
+        <v>32</v>
+      </c>
+      <c r="H10" s="54">
+        <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
+        <v>12</v>
+      </c>
+      <c r="I10" s="150">
+        <f ca="1">TODAY()-DATE(2026,10,25)</f>
+        <v>2</v>
+      </c>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="33">
+        <v>37</v>
+      </c>
+      <c r="N10" s="33">
+        <v>200</v>
+      </c>
+      <c r="O10" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P10" s="113" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q10" s="154" t="s">
+        <v>75</v>
+      </c>
+      <c r="R10" s="160" t="s">
+        <v>100</v>
+      </c>
+      <c r="S10" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="60">
+      <c r="A11" s="52">
+        <f t="shared" ref="A11" si="3">ROW()-1</f>
+        <v>10</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="35">
+        <v>46295</v>
+      </c>
+      <c r="F11" s="8">
+        <f ca="1">TODAY()-E11</f>
+        <v>27</v>
+      </c>
+      <c r="G11" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,12)</f>
+        <v>15</v>
+      </c>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="33">
+        <v>78</v>
+      </c>
+      <c r="N11" s="33">
+        <v>750</v>
+      </c>
+      <c r="O11" s="114" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="168">
-        <v>46283</v>
-      </c>
-      <c r="F9" s="166">
-        <f t="shared" ca="1" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="G9" s="166">
+      <c r="P11" s="113" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" s="154" t="s">
+        <v>167</v>
+      </c>
+      <c r="R11" s="105"/>
+      <c r="S11" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="60">
+      <c r="A12" s="52">
+        <f t="shared" ref="A12:A34" si="4">ROW()-1</f>
+        <v>11</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="35">
+        <v>46293</v>
+      </c>
+      <c r="F12" s="33">
+        <f t="shared" ca="1" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="G12" s="104">
+        <f>DATE(2026,10,26)-DATE(2026,9,30)</f>
+        <v>26</v>
+      </c>
+      <c r="H12" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,27)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="33">
+        <v>81</v>
+      </c>
+      <c r="N12" s="33">
+        <v>600</v>
+      </c>
+      <c r="O12" s="114" t="s">
+        <v>228</v>
+      </c>
+      <c r="P12" s="113" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q12" s="154" t="s">
+        <v>76</v>
+      </c>
+      <c r="R12" s="105"/>
+      <c r="S12" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="60">
+      <c r="A13" s="52">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="87" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="119" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="35">
+        <v>46286</v>
+      </c>
+      <c r="F13" s="33">
+        <f t="shared" ca="1" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="G13" s="33">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H9" s="169">
-        <f>DATE(2026,10,19)-DATE(2026,10,12)</f>
+      <c r="H13" s="107">
+        <f ca="1">TODAY()-DATE(2026,10,7)</f>
+        <v>20</v>
+      </c>
+      <c r="I13" s="107">
+        <f ca="1">TODAY()-DATE(2026,10,23)</f>
+        <v>4</v>
+      </c>
+      <c r="J13" s="107">
+        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
+        <v>1</v>
+      </c>
+      <c r="K13" s="107">
+        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="105"/>
+      <c r="M13" s="33">
         <v>7</v>
       </c>
-      <c r="I9" s="169">
-        <f ca="1">TODAY()-DATE(2026,10,20)</f>
-        <v>6</v>
-      </c>
-      <c r="J9" s="169">
-        <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>4</v>
-      </c>
-      <c r="K9" s="170"/>
-      <c r="L9" s="170"/>
-      <c r="M9" s="166">
-        <v>9</v>
-      </c>
-      <c r="N9" s="166">
+      <c r="N13" s="33">
         <v>100</v>
       </c>
-      <c r="O9" s="171" t="s">
-        <v>70</v>
-      </c>
-      <c r="P9" s="172"/>
-      <c r="Q9" s="180" t="s">
-        <v>74</v>
-      </c>
-      <c r="R9" s="170"/>
-      <c r="S9" s="170" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="60">
-      <c r="A10" s="35">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="90" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10" s="37">
-        <v>46283</v>
-      </c>
-      <c r="F10" s="35">
-        <f t="shared" ref="F10:F20" ca="1" si="2">TODAY()-E10</f>
-        <v>38</v>
-      </c>
-      <c r="G10" s="35">
-        <f>DATE(2026,10,9)-DATE(2026,9,21)</f>
-        <v>18</v>
-      </c>
-      <c r="H10" s="58">
-        <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
-        <v>12</v>
-      </c>
-      <c r="I10" s="174">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
+      <c r="O13" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P13" s="113" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q13" s="154" t="s">
+        <v>206</v>
+      </c>
+      <c r="R13" s="105"/>
+      <c r="S13" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="60">
+      <c r="A14" s="52">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E14" s="35">
+        <v>46282</v>
+      </c>
+      <c r="F14" s="33">
+        <f ca="1">TODAY()-DATE(2026,9,17)</f>
+        <v>40</v>
+      </c>
+      <c r="G14" s="33">
+        <f>DATE(2026,10,6)-DATE(2026,9,17)</f>
+        <v>19</v>
+      </c>
+      <c r="H14" s="104">
+        <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
+        <v>13</v>
+      </c>
+      <c r="I14" s="104">
+        <f>DATE(2026,10,22)-DATE(2026,10,21)</f>
         <v>1</v>
       </c>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="111"/>
-      <c r="M10" s="35">
-        <v>13</v>
-      </c>
-      <c r="N10" s="35">
-        <v>120</v>
-      </c>
-      <c r="O10" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P10" s="121" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q10" s="179" t="s">
-        <v>74</v>
-      </c>
-      <c r="R10" s="111"/>
-      <c r="S10" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="60">
-      <c r="A11" s="56">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="62" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="37">
-        <v>46289</v>
-      </c>
-      <c r="F11" s="62">
-        <f t="shared" ca="1" si="2"/>
-        <v>32</v>
-      </c>
-      <c r="G11" s="35">
-        <f ca="1">TODAY()-DATE(2026,9,25)</f>
-        <v>31</v>
-      </c>
-      <c r="H11" s="58">
-        <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
-        <v>12</v>
-      </c>
-      <c r="I11" s="174">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
+      <c r="J14" s="141">
+        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="111"/>
-      <c r="K11" s="111"/>
-      <c r="L11" s="111"/>
-      <c r="M11" s="35">
+      <c r="K14" s="107">
+        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <v>1</v>
+      </c>
+      <c r="L14" s="108"/>
+      <c r="M14" s="33">
+        <v>41</v>
+      </c>
+      <c r="N14" s="33">
+        <v>500</v>
+      </c>
+      <c r="O14" s="114" t="s">
+        <v>69</v>
+      </c>
+      <c r="P14" s="113"/>
+      <c r="Q14" s="156" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" s="105"/>
+      <c r="S14" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="60">
+      <c r="A15" s="52">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="35">
-        <v>200</v>
-      </c>
-      <c r="O11" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" s="121" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q11" s="179" t="s">
-        <v>76</v>
-      </c>
-      <c r="R11" s="185" t="s">
-        <v>101</v>
-      </c>
-      <c r="S11" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="60">
-      <c r="A12" s="56">
-        <f t="shared" ref="A12" si="3">ROW()-1</f>
-        <v>11</v>
-      </c>
-      <c r="B12" s="71" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="C15" s="164" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="37">
-        <v>46295</v>
-      </c>
-      <c r="F12" s="8">
-        <f ca="1">TODAY()-E12</f>
-        <v>26</v>
-      </c>
-      <c r="G12" s="110">
-        <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>14</v>
-      </c>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="35">
-        <v>78</v>
-      </c>
-      <c r="N12" s="35">
-        <v>750</v>
-      </c>
-      <c r="O12" s="122" t="s">
-        <v>198</v>
-      </c>
-      <c r="P12" s="121" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q12" s="179" t="s">
-        <v>169</v>
-      </c>
-      <c r="R12" s="111"/>
-      <c r="S12" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="60">
-      <c r="A13" s="56">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="71" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="37">
-        <v>46293</v>
-      </c>
-      <c r="F13" s="35">
+      <c r="E15" s="35">
+        <v>46294</v>
+      </c>
+      <c r="F15" s="46">
         <f t="shared" ca="1" si="2"/>
         <v>28</v>
       </c>
-      <c r="G13" s="110">
-        <f ca="1">TODAY()-DATE(2026,9,30)</f>
-        <v>26</v>
-      </c>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="35">
-        <v>81</v>
-      </c>
-      <c r="N13" s="35">
-        <v>600</v>
-      </c>
-      <c r="O13" s="122" t="s">
-        <v>225</v>
-      </c>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="179" t="s">
-        <v>77</v>
-      </c>
-      <c r="R13" s="111"/>
-      <c r="S13" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="60">
-      <c r="A14" s="56">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="127" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="E14" s="37">
-        <v>46286</v>
-      </c>
-      <c r="F14" s="35">
+      <c r="G15" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,3)</f>
+        <v>24</v>
+      </c>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="33">
+        <v>36</v>
+      </c>
+      <c r="N15" s="33">
+        <v>500</v>
+      </c>
+      <c r="O15" s="114" t="s">
+        <v>207</v>
+      </c>
+      <c r="P15" s="113" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q15" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="R15" s="105"/>
+      <c r="S15" s="105" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="60">
+      <c r="A16" s="52">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="35">
+        <v>46292</v>
+      </c>
+      <c r="F16" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
-      </c>
-      <c r="G14" s="35">
-        <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
+        <v>30</v>
+      </c>
+      <c r="G16" s="52">
+        <f ca="1">TODAY()-DATE(2026,9,28)</f>
+        <v>29</v>
+      </c>
+      <c r="H16" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,19)</f>
+        <v>8</v>
+      </c>
+      <c r="I16" s="105"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="105"/>
+      <c r="M16" s="33">
+        <v>31</v>
+      </c>
+      <c r="N16" s="104">
+        <v>500</v>
+      </c>
+      <c r="O16" s="114" t="s">
+        <v>196</v>
+      </c>
+      <c r="P16" s="113" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q16" s="154"/>
+      <c r="R16" s="105"/>
+      <c r="S16" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="60">
+      <c r="A17" s="52">
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="H14" s="113">
-        <f ca="1">TODAY()-DATE(2026,10,7)</f>
+      <c r="B17" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="35">
+        <v>46291</v>
+      </c>
+      <c r="F17" s="33">
+        <f t="shared" ca="1" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="G17" s="52">
+        <f>DATE(2026,10,22)-DATE(2026,9,28)</f>
+        <v>24</v>
+      </c>
+      <c r="H17" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,22)</f>
+        <v>5</v>
+      </c>
+      <c r="I17" s="105"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
+      <c r="L17" s="105"/>
+      <c r="M17" s="33">
+        <v>28</v>
+      </c>
+      <c r="N17" s="104">
+        <v>500</v>
+      </c>
+      <c r="O17" s="117" t="s">
+        <v>69</v>
+      </c>
+      <c r="P17" s="116" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q17" s="156"/>
+      <c r="R17" s="105"/>
+      <c r="S17" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="60">
+      <c r="A18" s="52">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="166" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="113">
-        <f ca="1">TODAY()-DATE(2026,10,23)</f>
-        <v>3</v>
-      </c>
-      <c r="J14" s="113">
-        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="113">
-        <f ca="1">TODAY()-DATE(2026,10,26)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="111"/>
-      <c r="M14" s="35">
-        <v>7</v>
-      </c>
-      <c r="N14" s="35">
-        <v>100</v>
-      </c>
-      <c r="O14" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="121" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q14" s="179" t="s">
-        <v>216</v>
-      </c>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="60">
-      <c r="A15" s="56">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="91" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="127" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="E15" s="37">
-        <v>46282</v>
-      </c>
-      <c r="F15" s="35">
-        <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>39</v>
-      </c>
-      <c r="G15" s="35">
-        <f>DATE(2026,10,6)-DATE(2026,9,17)</f>
+      <c r="E18" s="35">
+        <v>46302</v>
+      </c>
+      <c r="F18" s="33">
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="G18" s="87">
+        <f ca="1">TODAY()-DATE(2026,10,21)</f>
+        <v>6</v>
+      </c>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105"/>
+      <c r="M18" s="33">
+        <f>129+6</f>
+        <v>135</v>
+      </c>
+      <c r="N18" s="104">
+        <v>1500</v>
+      </c>
+      <c r="O18" s="117" t="s">
+        <v>231</v>
+      </c>
+      <c r="P18" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q18" s="157" t="s">
+        <v>193</v>
+      </c>
+      <c r="R18" s="105"/>
+      <c r="S18" s="105" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="33.5" customHeight="1">
+      <c r="A19" s="52">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="162" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="164" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="110">
-        <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
-        <v>13</v>
-      </c>
-      <c r="I15" s="110">
-        <f>DATE(2026,10,22)-DATE(2026,10,21)</f>
-        <v>1</v>
-      </c>
-      <c r="J15" s="165">
-        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
-        <v>1</v>
-      </c>
-      <c r="K15" s="113">
-        <f ca="1">TODAY()-DATE(2026,10,26)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="114"/>
-      <c r="M15" s="35">
-        <v>41</v>
-      </c>
-      <c r="N15" s="35">
-        <v>500</v>
-      </c>
-      <c r="O15" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" s="121"/>
-      <c r="Q15" s="181" t="s">
-        <v>77</v>
-      </c>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="60">
-      <c r="A16" s="56">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="188" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="189" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="190" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="37">
-        <v>46294</v>
-      </c>
-      <c r="F16" s="49">
+      <c r="E19" s="35">
+        <v>46295</v>
+      </c>
+      <c r="F19" s="33">
         <f t="shared" ca="1" si="2"/>
         <v>27</v>
       </c>
-      <c r="G16" s="110">
-        <f ca="1">TODAY()-DATE(2026,10,3)</f>
+      <c r="G19" s="106">
+        <f ca="1">TODAY()-DATE(2026,10,13)</f>
+        <v>14</v>
+      </c>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="105"/>
+      <c r="M19" s="33">
+        <v>48</v>
+      </c>
+      <c r="N19" s="104">
+        <v>550</v>
+      </c>
+      <c r="O19" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="P19" s="113" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="105"/>
+      <c r="S19" s="105" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="60">
+      <c r="A20" s="52">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="162" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="164" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="167" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="35">
+        <v>46295</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" ref="F20" ca="1" si="5">TODAY()-E20</f>
+        <v>27</v>
+      </c>
+      <c r="G20" s="106">
+        <f ca="1">TODAY()-DATE(2026,10,12)</f>
+        <v>15</v>
+      </c>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="33">
+        <v>40</v>
+      </c>
+      <c r="N20" s="104">
+        <v>450</v>
+      </c>
+      <c r="O20" s="114" t="s">
+        <v>233</v>
+      </c>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="154" t="s">
+        <v>172</v>
+      </c>
+      <c r="R20" s="105"/>
+      <c r="S20" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="32.5">
+      <c r="A21" s="52">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" s="35">
+        <v>46307</v>
+      </c>
+      <c r="F21" s="8">
+        <f ca="1">TODAY()-E21</f>
+        <v>15</v>
+      </c>
+      <c r="G21" s="106"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="105"/>
+      <c r="M21" s="33">
+        <v>30</v>
+      </c>
+      <c r="N21" s="104">
+        <v>350</v>
+      </c>
+      <c r="O21" s="113" t="s">
+        <v>171</v>
+      </c>
+      <c r="P21" s="113" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q21" s="154" t="s">
+        <v>149</v>
+      </c>
+      <c r="R21" s="105" t="s">
+        <v>244</v>
+      </c>
+      <c r="S21" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="60">
+      <c r="A22" s="52">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="35">
+        <v>46307</v>
+      </c>
+      <c r="F22" s="107">
+        <f ca="1">TODAY()-E22</f>
+        <v>15</v>
+      </c>
+      <c r="G22" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,19)</f>
+        <v>8</v>
+      </c>
+      <c r="H22" s="175"/>
+      <c r="I22" s="175"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="33">
+        <v>28</v>
+      </c>
+      <c r="N22" s="104">
+        <v>500</v>
+      </c>
+      <c r="O22" s="114" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" s="113"/>
+      <c r="Q22" s="158"/>
+      <c r="R22" s="105"/>
+      <c r="S22" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="60">
+      <c r="A23" s="52">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9">
+        <v>46302</v>
+      </c>
+      <c r="F23" s="176">
+        <f ca="1">TODAY()-E23</f>
+        <v>20</v>
+      </c>
+      <c r="G23" s="104" t="str">
+        <f ca="1">TRIM(TODAY()-DATE(2026,10,19))</f>
+        <v>8</v>
+      </c>
+      <c r="H23" s="175"/>
+      <c r="I23" s="175"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="33">
+        <v>36</v>
+      </c>
+      <c r="N23" s="104">
+        <v>450</v>
+      </c>
+      <c r="O23" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="P23" s="113"/>
+      <c r="Q23" s="158"/>
+      <c r="R23" s="105"/>
+      <c r="S23" s="105"/>
+    </row>
+    <row r="24" spans="1:19" ht="60">
+      <c r="A24" s="52">
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="35">
-        <v>36</v>
-      </c>
-      <c r="N16" s="35">
+      <c r="B24" s="177" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="151">
+        <v>46309</v>
+      </c>
+      <c r="F24" s="176">
+        <f ca="1">TODAY()-E24</f>
+        <v>13</v>
+      </c>
+      <c r="G24" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,22)</f>
+        <v>5</v>
+      </c>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="33">
+        <v>42</v>
+      </c>
+      <c r="N24" s="104">
         <v>500</v>
       </c>
-      <c r="O16" s="122" t="s">
-        <v>217</v>
-      </c>
-      <c r="P16" s="121" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q16" s="179" t="s">
-        <v>166</v>
-      </c>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="60">
-      <c r="A17" s="56">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" s="71" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="35" t="s">
+      <c r="O24" s="114" t="s">
+        <v>216</v>
+      </c>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="154"/>
+      <c r="R24" s="105"/>
+      <c r="S24" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="60">
+      <c r="A25" s="52">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="168" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="164" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="37">
-        <v>46292</v>
-      </c>
-      <c r="F17" s="35">
-        <f t="shared" ca="1" si="2"/>
-        <v>29</v>
-      </c>
-      <c r="G17" s="56">
-        <f ca="1">TODAY()-DATE(2026,9,28)</f>
+      <c r="E25" s="151">
+        <v>46312</v>
+      </c>
+      <c r="F25" s="110">
+        <f ca="1">TODAY()-E25</f>
+        <v>10</v>
+      </c>
+      <c r="G25" s="106">
+        <f ca="1">TODAY()-DATE(2026,10,22)</f>
+        <v>5</v>
+      </c>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="104">
+        <v>23</v>
+      </c>
+      <c r="N25" s="106">
+        <v>350</v>
+      </c>
+      <c r="O25" s="114" t="s">
+        <v>208</v>
+      </c>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="154"/>
+      <c r="R25" s="105"/>
+      <c r="S25" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="60">
+      <c r="A26" s="52">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="178" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" s="111">
+        <v>46312</v>
+      </c>
+      <c r="F26" s="110">
+        <f t="shared" ref="F26" ca="1" si="6">TODAY()-E26</f>
+        <v>10</v>
+      </c>
+      <c r="G26" s="106"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="105"/>
+      <c r="K26" s="105"/>
+      <c r="L26" s="105"/>
+      <c r="M26" s="33">
+        <v>56</v>
+      </c>
+      <c r="N26" s="106">
+        <v>300</v>
+      </c>
+      <c r="O26" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="159"/>
+      <c r="R26" s="105"/>
+      <c r="S26" s="105" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="52">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="122" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="111">
+        <v>46316</v>
+      </c>
+      <c r="F27" s="110">
+        <f ca="1">TODAY()-E27</f>
+        <v>6</v>
+      </c>
+      <c r="G27" s="106"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="33">
+        <v>109</v>
+      </c>
+      <c r="N27" s="106">
+        <v>350</v>
+      </c>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="159"/>
+      <c r="R27" s="105"/>
+      <c r="S27" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="60">
+      <c r="A28" s="52">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="122" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="151">
+        <v>46316</v>
+      </c>
+      <c r="F28" s="176">
+        <f ca="1">TODAY()-E28</f>
+        <v>6</v>
+      </c>
+      <c r="G28" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,25)</f>
+        <v>2</v>
+      </c>
+      <c r="H28" s="175"/>
+      <c r="I28" s="175"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="33">
+        <v>69</v>
+      </c>
+      <c r="N28" s="104">
+        <v>400</v>
+      </c>
+      <c r="O28" s="114" t="s">
+        <v>236</v>
+      </c>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="159"/>
+      <c r="R28" s="105"/>
+      <c r="S28" s="105" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="60">
+      <c r="A29" s="52">
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="H17" s="110">
-        <f ca="1">TODAY()-DATE(2026,10,19)</f>
-        <v>7</v>
-      </c>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="35">
-        <v>31</v>
-      </c>
-      <c r="N17" s="110">
-        <v>500</v>
-      </c>
-      <c r="O17" s="122" t="s">
-        <v>205</v>
-      </c>
-      <c r="P17" s="121" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q17" s="179"/>
-      <c r="R17" s="111"/>
-      <c r="S17" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="60">
-      <c r="A18" s="56">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="37">
-        <v>46291</v>
-      </c>
-      <c r="F18" s="35">
-        <f t="shared" ca="1" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="G18" s="56">
-        <f>DATE(2026,10,22)-DATE(2026,9,28)</f>
-        <v>24</v>
-      </c>
-      <c r="H18" s="110">
-        <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>4</v>
-      </c>
-      <c r="I18" s="111"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="35">
-        <v>28</v>
-      </c>
-      <c r="N18" s="110">
-        <v>500</v>
-      </c>
-      <c r="O18" s="125" t="s">
-        <v>70</v>
-      </c>
-      <c r="P18" s="124" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q18" s="181"/>
-      <c r="R18" s="111"/>
-      <c r="S18" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="60">
-      <c r="A19" s="56">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="188" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="191" t="s">
-        <v>160</v>
-      </c>
-      <c r="D19" s="192" t="s">
-        <v>161</v>
-      </c>
-      <c r="E19" s="37">
-        <v>46302</v>
-      </c>
-      <c r="F19" s="35">
-        <f t="shared" ca="1" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="G19" s="91">
-        <f ca="1">TODAY()-DATE(2026,10,21)</f>
-        <v>5</v>
-      </c>
-      <c r="H19" s="111"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="35">
-        <f>129+6</f>
-        <v>135</v>
-      </c>
-      <c r="N19" s="110">
-        <v>1500</v>
-      </c>
-      <c r="O19" s="125" t="s">
-        <v>239</v>
-      </c>
-      <c r="P19" s="121" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q19" s="182" t="s">
-        <v>201</v>
-      </c>
-      <c r="R19" s="111"/>
-      <c r="S19" s="111" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="33.5" customHeight="1">
-      <c r="A20" s="56">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B20" s="187" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="189" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="37">
-        <v>46295</v>
-      </c>
-      <c r="F20" s="35">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
-      </c>
-      <c r="G20" s="112">
-        <f ca="1">TODAY()-DATE(2026,10,13)</f>
-        <v>13</v>
-      </c>
-      <c r="H20" s="111"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="35">
-        <v>48</v>
-      </c>
-      <c r="N20" s="110">
-        <v>550</v>
-      </c>
-      <c r="O20" s="122" t="s">
-        <v>229</v>
-      </c>
-      <c r="P20" s="121" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q20" s="179"/>
-      <c r="R20" s="111"/>
-      <c r="S20" s="111" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="60">
-      <c r="A21" s="56">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B21" s="187" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="189" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="37">
-        <v>46295</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" ref="F21" ca="1" si="4">TODAY()-E21</f>
-        <v>26</v>
-      </c>
-      <c r="G21" s="112">
-        <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>14</v>
-      </c>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="35">
-        <v>40</v>
-      </c>
-      <c r="N21" s="112">
-        <v>450</v>
-      </c>
-      <c r="O21" s="122" t="s">
-        <v>230</v>
-      </c>
-      <c r="P21" s="121"/>
-      <c r="Q21" s="179" t="s">
-        <v>177</v>
-      </c>
-      <c r="R21" s="111"/>
-      <c r="S21" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="32.5">
-      <c r="A22" s="56">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B22" s="91" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E22" s="37">
-        <v>46307</v>
-      </c>
-      <c r="F22" s="8">
-        <f ca="1">TODAY()-E22</f>
-        <v>14</v>
-      </c>
-      <c r="G22" s="112"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="35">
-        <v>30</v>
-      </c>
-      <c r="N22" s="112">
-        <v>350</v>
-      </c>
-      <c r="O22" s="121" t="s">
-        <v>176</v>
-      </c>
-      <c r="P22" s="121" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q22" s="179" t="s">
-        <v>151</v>
-      </c>
-      <c r="R22" s="111"/>
-      <c r="S22" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="60">
-      <c r="A23" s="56">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B23" s="187" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="189" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" s="192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="37">
-        <v>46307</v>
-      </c>
-      <c r="F23" s="116">
-        <f ca="1">TODAY()-E23</f>
-        <v>14</v>
-      </c>
-      <c r="G23" s="112">
-        <f ca="1">TODAY()-DATE(2026,10,19)</f>
-        <v>7</v>
-      </c>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="35">
-        <v>28</v>
-      </c>
-      <c r="N23" s="112">
-        <v>500</v>
-      </c>
-      <c r="O23" s="122" t="s">
-        <v>199</v>
-      </c>
-      <c r="P23" s="121"/>
-      <c r="Q23" s="183"/>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="60">
-      <c r="A24" s="56">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B24" s="187" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="189" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="9">
-        <v>46302</v>
-      </c>
-      <c r="F24" s="117">
-        <f ca="1">TODAY()-E24</f>
-        <v>19</v>
-      </c>
-      <c r="G24" s="112" t="str">
-        <f ca="1">TRIM(TODAY()-DATE(2026,10,19))</f>
-        <v>7</v>
-      </c>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="35">
-        <v>36</v>
-      </c>
-      <c r="N24" s="112">
-        <v>450</v>
-      </c>
-      <c r="O24" s="122" t="s">
-        <v>232</v>
-      </c>
-      <c r="P24" s="121"/>
-      <c r="Q24" s="183"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-    </row>
-    <row r="25" spans="1:19" ht="60">
-      <c r="A25" s="56">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B25" s="193" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="189" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" s="192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="175">
-        <v>46309</v>
-      </c>
-      <c r="F25" s="117">
-        <f ca="1">TODAY()-E25</f>
-        <v>12</v>
-      </c>
-      <c r="G25" s="112">
-        <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>4</v>
-      </c>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="35">
-        <v>42</v>
-      </c>
-      <c r="N25" s="112">
-        <v>500</v>
-      </c>
-      <c r="O25" s="122" t="s">
-        <v>233</v>
-      </c>
-      <c r="P25" s="121" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q25" s="179"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="60">
-      <c r="A26" s="56">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B26" s="193" t="s">
-        <v>140</v>
-      </c>
-      <c r="C26" s="189" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="175">
-        <v>46312</v>
-      </c>
-      <c r="F26" s="117">
-        <f ca="1">TODAY()-E26</f>
-        <v>9</v>
-      </c>
-      <c r="G26" s="112">
-        <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>4</v>
-      </c>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="110">
-        <v>23</v>
-      </c>
-      <c r="N26" s="112">
-        <v>350</v>
-      </c>
-      <c r="O26" s="122" t="s">
-        <v>218</v>
-      </c>
-      <c r="P26" s="121"/>
-      <c r="Q26" s="179"/>
-      <c r="R26" s="111"/>
-      <c r="S26" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="28">
-      <c r="A27" s="56">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B27" s="118" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E27" s="119">
-        <v>46312</v>
-      </c>
-      <c r="F27" s="117">
-        <f t="shared" ref="F27" ca="1" si="5">TODAY()-E27</f>
-        <v>9</v>
-      </c>
-      <c r="G27" s="112"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="35">
-        <v>56</v>
-      </c>
-      <c r="N27" s="112">
-        <v>300</v>
-      </c>
-      <c r="O27" s="120"/>
-      <c r="P27" s="120"/>
-      <c r="Q27" s="184"/>
-      <c r="R27" s="111"/>
-      <c r="S27" s="111" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="A28" s="56">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B28" s="130" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="119">
-        <v>46316</v>
-      </c>
-      <c r="F28" s="117">
-        <f ca="1">TODAY()-E28</f>
-        <v>5</v>
-      </c>
-      <c r="G28" s="112"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="128"/>
-      <c r="M28" s="35">
-        <v>109</v>
-      </c>
-      <c r="N28" s="112">
-        <v>350</v>
-      </c>
-      <c r="O28" s="120"/>
-      <c r="P28" s="120"/>
-      <c r="Q28" s="184"/>
-      <c r="R28" s="111"/>
-      <c r="S28" s="111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
-      <c r="A29" s="56">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B29" s="130" t="s">
-        <v>164</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>165</v>
+      <c r="B29" s="122" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>198</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="119">
+      <c r="E29" s="151">
+        <v>46312</v>
+      </c>
+      <c r="F29" s="176">
+        <f ca="1">TODAY()-E29</f>
+        <v>10</v>
+      </c>
+      <c r="G29" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,22)</f>
+        <v>5</v>
+      </c>
+      <c r="H29" s="179"/>
+      <c r="I29" s="180"/>
+      <c r="J29" s="179"/>
+      <c r="K29" s="180"/>
+      <c r="L29" s="180"/>
+      <c r="M29" s="33">
+        <v>33</v>
+      </c>
+      <c r="N29" s="124">
+        <v>450</v>
+      </c>
+      <c r="O29" s="114" t="s">
+        <v>237</v>
+      </c>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="159"/>
+      <c r="R29" s="105"/>
+      <c r="S29" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="186">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="122" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="111">
         <v>46316</v>
       </c>
-      <c r="F29" s="117">
-        <f ca="1">TODAY()-E29</f>
-        <v>5</v>
-      </c>
-      <c r="G29" s="112">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>1</v>
-      </c>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="128"/>
-      <c r="M29" s="35">
-        <v>69</v>
-      </c>
-      <c r="N29" s="112">
-        <v>400</v>
-      </c>
-      <c r="O29" s="120"/>
-      <c r="P29" s="120"/>
-      <c r="Q29" s="184"/>
-      <c r="R29" s="111"/>
-      <c r="S29" s="111" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="28">
-      <c r="A30" s="56">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B30" s="130" t="s">
+      <c r="F30" s="110">
+        <f ca="1">TODAY()-E30</f>
+        <v>6</v>
+      </c>
+      <c r="G30" s="124"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="121"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="33">
+        <v>21</v>
+      </c>
+      <c r="N30" s="124">
+        <v>150</v>
+      </c>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="112"/>
+      <c r="R30" s="105"/>
+      <c r="S30" s="105" t="s">
         <v>170</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="119">
-        <v>46312</v>
-      </c>
-      <c r="F30" s="117">
-        <f ca="1">TODAY()-E30</f>
-        <v>9</v>
-      </c>
-      <c r="G30" s="112">
-        <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>4</v>
-      </c>
-      <c r="H30" s="26"/>
-      <c r="I30" s="129"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="129"/>
-      <c r="L30" s="129"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="132"/>
-      <c r="O30" s="120"/>
-      <c r="P30" s="120"/>
-      <c r="Q30" s="184"/>
-      <c r="R30" s="111"/>
-      <c r="S30" s="111" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="56">
-        <f t="shared" si="0"/>
+      <c r="A31" s="186">
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="B31" s="130" t="s">
-        <v>208</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>209</v>
+      <c r="B31" s="152" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="152" t="s">
+        <v>238</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="119">
-        <v>46316</v>
-      </c>
-      <c r="F31" s="117">
-        <f ca="1">TODAY()-E31</f>
-        <v>5</v>
-      </c>
-      <c r="G31" s="132"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="124"/>
       <c r="H31" s="26"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="129"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="129"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="132"/>
-      <c r="O31" s="120"/>
-      <c r="P31" s="120"/>
-      <c r="Q31" s="184"/>
-      <c r="R31" s="111"/>
-      <c r="S31" s="111"/>
-    </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="56">
-        <f t="shared" si="0"/>
+      <c r="I31" s="121"/>
+      <c r="J31" s="121"/>
+      <c r="K31" s="121"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="33">
+        <v>12</v>
+      </c>
+      <c r="N31" s="124">
+        <v>150</v>
+      </c>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="105"/>
+      <c r="S31" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="29">
+      <c r="A32" s="187">
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="B32" s="176" t="s">
-        <v>234</v>
-      </c>
-      <c r="C32" s="176" t="s">
-        <v>236</v>
+      <c r="B32" s="152" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="152" t="s">
+        <v>239</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="26"/>
       <c r="F32" s="26"/>
-      <c r="G32" s="132"/>
+      <c r="G32" s="124"/>
       <c r="H32" s="26"/>
-      <c r="I32" s="129"/>
-      <c r="J32" s="129"/>
-      <c r="K32" s="129"/>
-      <c r="L32" s="129"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="132"/>
-      <c r="O32" s="120"/>
-      <c r="P32" s="120"/>
-      <c r="Q32" s="184"/>
-      <c r="R32" s="111"/>
-      <c r="S32" s="111"/>
-    </row>
-    <row r="33" spans="1:19" ht="29">
-      <c r="A33" s="35">
-        <f t="shared" si="0"/>
+      <c r="I32" s="121"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="121"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="33">
+        <v>20</v>
+      </c>
+      <c r="N32" s="124">
+        <v>450</v>
+      </c>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="112"/>
+      <c r="R32" s="105"/>
+      <c r="S32" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="28">
+      <c r="A33" s="33">
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="B33" s="176" t="s">
-        <v>235</v>
-      </c>
-      <c r="C33" s="176" t="s">
-        <v>237</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="B33" s="189" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" s="8"/>
       <c r="E33" s="26"/>
       <c r="F33" s="26"/>
-      <c r="G33" s="132"/>
+      <c r="G33" s="124"/>
       <c r="H33" s="26"/>
-      <c r="I33" s="129"/>
-      <c r="J33" s="129"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="129"/>
-      <c r="M33" s="35">
-        <v>20</v>
-      </c>
-      <c r="N33" s="132">
-        <v>450</v>
-      </c>
-      <c r="O33" s="120"/>
-      <c r="P33" s="120"/>
-      <c r="Q33" s="120"/>
-      <c r="R33" s="111"/>
-      <c r="S33" s="111" t="s">
-        <v>174</v>
+      <c r="I33" s="121"/>
+      <c r="J33" s="121"/>
+      <c r="K33" s="121"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="33">
+        <v>16</v>
+      </c>
+      <c r="N33" s="124">
+        <v>200</v>
+      </c>
+      <c r="O33" s="185"/>
+      <c r="P33" s="185"/>
+      <c r="Q33" s="185"/>
+      <c r="R33" s="105"/>
+      <c r="S33" s="105" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="195"/>
-      <c r="B34" s="196">
-        <v>6454</v>
-      </c>
-      <c r="C34" s="197" t="s">
+      <c r="A34" s="33">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="190" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="190" t="s">
         <v>241</v>
       </c>
-      <c r="D34" s="198" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="199"/>
-      <c r="F34" s="199"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="133"/>
-      <c r="I34" s="201"/>
-      <c r="J34" s="201"/>
-      <c r="K34" s="201"/>
-      <c r="L34" s="201"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="200"/>
-      <c r="O34" s="202"/>
-      <c r="P34" s="202"/>
-      <c r="Q34" s="202"/>
-      <c r="R34" s="114"/>
-      <c r="S34" s="114"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="124"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="121"/>
+      <c r="J34" s="121"/>
+      <c r="K34" s="121"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="124"/>
+      <c r="O34" s="185"/>
+      <c r="P34" s="185"/>
+      <c r="Q34" s="185"/>
+      <c r="R34" s="105"/>
+      <c r="S34" s="105"/>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="124"/>
+      <c r="B35" s="183"/>
+      <c r="C35" s="183"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="124"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="124"/>
+      <c r="O35" s="113"/>
+      <c r="P35" s="113"/>
+      <c r="Q35" s="113"/>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="R36" s="188"/>
+      <c r="S36" s="188"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7422,7 +7168,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
@@ -7430,18 +7176,18 @@
     <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.26953125" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" style="63" customWidth="1"/>
-    <col min="7" max="7" width="28.453125" style="63" customWidth="1"/>
-    <col min="8" max="8" width="14.453125" style="63" customWidth="1"/>
-    <col min="9" max="10" width="13.1796875" style="63" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" style="63" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" style="63" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.90625" style="63" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.54296875" style="63" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="63" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" style="59" customWidth="1"/>
+    <col min="7" max="7" width="28.453125" style="59" customWidth="1"/>
+    <col min="8" max="8" width="14.453125" style="59" customWidth="1"/>
+    <col min="9" max="10" width="13.1796875" style="59" customWidth="1"/>
+    <col min="11" max="11" width="14.453125" style="59" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.90625" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.54296875" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="59" customWidth="1"/>
     <col min="16" max="16" width="19.81640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.54296875" style="63" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.54296875" style="59" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7458,64 +7204,64 @@
       <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="163" t="s">
+      <c r="E1" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="164" t="s">
+      <c r="F1" s="140" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="140" t="s">
         <v>125</v>
       </c>
-      <c r="G1" s="164" t="s">
-        <v>126</v>
-      </c>
-      <c r="H1" s="163" t="s">
+      <c r="H1" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="163" t="s">
+      <c r="J1" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="163" t="s">
+      <c r="K1" s="139" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="163" t="s">
+      <c r="L1" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="163" t="s">
+      <c r="M1" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="163" t="s">
+      <c r="N1" s="139" t="s">
+        <v>205</v>
+      </c>
+      <c r="O1" s="139" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="163" t="s">
-        <v>214</v>
-      </c>
-      <c r="O1" s="163" t="s">
+      <c r="P1" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="Q1" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="R1" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>57</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="11" customFormat="1" ht="60">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="43" t="s">
-        <v>79</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="15">
         <v>46202</v>
@@ -7539,7 +7285,7 @@
         <v>6</v>
       </c>
       <c r="L2" s="16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2" s="16">
         <v>6</v>
@@ -7551,29 +7297,29 @@
         <f>372+13</f>
         <v>385</v>
       </c>
-      <c r="P2" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" s="64">
+      <c r="P2" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="R2" s="60">
         <v>46265</v>
       </c>
-      <c r="S2" s="68"/>
-    </row>
-    <row r="3" spans="1:19" ht="60" hidden="1">
+      <c r="S2" s="64"/>
+    </row>
+    <row r="3" spans="1:19" ht="60">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="43" t="s">
-        <v>82</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" s="15">
         <v>46209</v>
@@ -7615,29 +7361,29 @@
         <f>572+15</f>
         <v>587</v>
       </c>
-      <c r="P3" s="38" t="s">
+      <c r="P3" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="Q3" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="R3" s="65">
+      <c r="R3" s="61">
         <v>46272</v>
       </c>
-      <c r="S3" s="68"/>
-    </row>
-    <row r="4" spans="1:19" ht="70" hidden="1">
+      <c r="S3" s="64"/>
+    </row>
+    <row r="4" spans="1:19" ht="70">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>86</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="15">
         <v>46195</v>
@@ -7678,29 +7424,29 @@
       <c r="O4" s="16">
         <v>719</v>
       </c>
-      <c r="P4" s="38" t="s">
+      <c r="P4" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="R4" s="65">
+      <c r="R4" s="61">
         <v>46277</v>
       </c>
-      <c r="S4" s="52"/>
-    </row>
-    <row r="5" spans="1:19" ht="60" hidden="1">
+      <c r="S4" s="49"/>
+    </row>
+    <row r="5" spans="1:19" ht="60">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="43" t="s">
-        <v>90</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="15">
         <v>46196</v>
@@ -7742,29 +7488,29 @@
         <f>826+21</f>
         <v>847</v>
       </c>
-      <c r="P5" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="R5" s="65">
+      <c r="P5" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q5" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" s="61">
         <v>46278</v>
       </c>
-      <c r="S5" s="52"/>
-    </row>
-    <row r="6" spans="1:19" ht="60" hidden="1">
+      <c r="S5" s="49"/>
+    </row>
+    <row r="6" spans="1:19" ht="60">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>93</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="15">
         <v>46195</v>
@@ -7806,61 +7552,61 @@
         <f>766+19</f>
         <v>785</v>
       </c>
-      <c r="P6" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q6" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="R6" s="65">
+      <c r="P6" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="R6" s="61">
         <v>46280</v>
       </c>
-      <c r="S6" s="52"/>
-    </row>
-    <row r="7" spans="1:19" s="27" customFormat="1" ht="60" hidden="1">
+      <c r="S6" s="49"/>
+    </row>
+    <row r="7" spans="1:19" s="27" customFormat="1" ht="60">
       <c r="A7" s="28">
         <v>6</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="15">
         <v>46234</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="32">
         <v>52</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="41">
         <f>DATE(2026,8,24)-DATE(2026,7,31)</f>
         <v>24</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="41">
         <f>DATE(2026,9,5)-DATE(2026,8,24)</f>
         <v>12</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="41">
         <f>DATE(2026,9,9)-DATE(2026,9,5)</f>
         <v>4</v>
       </c>
-      <c r="J7" s="44">
+      <c r="J7" s="41">
         <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
         <v>6</v>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="41">
         <f>DATE(2026,9,17)-DATE(2026,9,14)</f>
         <v>3</v>
       </c>
-      <c r="L7" s="44">
+      <c r="L7" s="41">
         <f>DATE(2026,9,19)-DATE(2026,9,17)</f>
         <v>2</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="32">
         <v>10</v>
       </c>
       <c r="N7" s="16">
@@ -7870,61 +7616,61 @@
         <f>218+7</f>
         <v>225</v>
       </c>
-      <c r="P7" s="38" t="s">
+      <c r="P7" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q7" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="Q7" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="R7" s="65">
+      <c r="R7" s="61">
         <v>46286</v>
       </c>
       <c r="S7" s="26"/>
     </row>
-    <row r="8" spans="1:19" s="27" customFormat="1" ht="69" hidden="1" customHeight="1" thickBot="1">
+    <row r="8" spans="1:19" s="27" customFormat="1" ht="69" customHeight="1" thickBot="1">
       <c r="A8" s="28">
         <v>7</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>124</v>
+      <c r="C8" s="31" t="s">
+        <v>123</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="15">
         <v>46230</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="32">
         <v>58</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="29">
         <f>DATE(2026,8,17)-DATE(2026,7,27)</f>
         <v>21</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="29">
         <f>DATE(2026,8,25)-DATE(2026,8,17)</f>
         <v>8</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="29">
         <f>DATE(2026,9,8)-DATE(2026,8,27)</f>
         <v>12</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="29">
         <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
         <v>6</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="29">
         <f>DATE(2026,9,23)-DATE(2026,9,14)</f>
         <v>9</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="29">
         <f>DATE(2026,9,22)-DATE(2026,9,20)</f>
         <v>2</v>
       </c>
-      <c r="M8" s="34">
+      <c r="M8" s="32">
         <v>21</v>
       </c>
       <c r="N8" s="16">
@@ -7934,64 +7680,64 @@
         <f>372+13</f>
         <v>385</v>
       </c>
-      <c r="P8" s="38" t="s">
+      <c r="P8" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q8" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="Q8" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="R8" s="65">
+      <c r="R8" s="61">
         <v>46288</v>
       </c>
-      <c r="S8" s="69" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="60" hidden="1">
+      <c r="S8" s="65" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="60">
       <c r="A9" s="28">
         <f t="shared" ref="A9:A17" si="0">ROW()-1</f>
         <v>8</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>46</v>
+      <c r="C9" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>45</v>
       </c>
       <c r="E9" s="15">
         <v>46244</v>
       </c>
-      <c r="F9" s="96">
+      <c r="F9" s="91">
         <v>47</v>
       </c>
-      <c r="G9" s="96">
+      <c r="G9" s="91">
         <f>DATE(2026,8,31)-DATE(2026,8,12)</f>
         <v>19</v>
       </c>
-      <c r="H9" s="96">
+      <c r="H9" s="91">
         <f>DATE(2026,9,14)-DATE(2026,8,31)</f>
         <v>14</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="91">
         <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
         <v>1</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="91">
         <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
         <v>6</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="91">
         <f>DATE(2026,9,23)-DATE(2026,9,22)</f>
         <v>1</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="91">
         <f>DATE(2026,9,23)-DATE(2026,9,17)</f>
         <v>6</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="91">
         <v>64</v>
       </c>
       <c r="N9" s="16">
@@ -8001,62 +7747,62 @@
         <f>696+23</f>
         <v>719</v>
       </c>
-      <c r="P9" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="66">
+      <c r="P9" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="62">
         <v>46291</v>
       </c>
       <c r="S9" s="26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="27" customFormat="1" ht="60" hidden="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="27" customFormat="1" ht="60">
       <c r="A10" s="28">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>46</v>
+      <c r="C10" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>45</v>
       </c>
       <c r="E10" s="15">
         <v>46246</v>
       </c>
-      <c r="F10" s="96">
+      <c r="F10" s="91">
         <v>44</v>
       </c>
-      <c r="G10" s="96">
+      <c r="G10" s="91">
         <f>DATE(2026,8,27)-DATE(2026,8,12)</f>
         <v>15</v>
       </c>
-      <c r="H10" s="96">
+      <c r="H10" s="91">
         <f>DATE(2026,9,11)-DATE(2026,8,27)</f>
         <v>15</v>
       </c>
-      <c r="I10" s="96">
+      <c r="I10" s="91">
         <f>DATE(2026,9,16)-DATE(2026,9,14)</f>
         <v>2</v>
       </c>
-      <c r="J10" s="96">
+      <c r="J10" s="91">
         <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
         <v>6</v>
       </c>
-      <c r="K10" s="96">
+      <c r="K10" s="91">
         <f>DATE(2026,9,23)-DATE(2026,9,22)</f>
         <v>1</v>
       </c>
-      <c r="L10" s="96">
+      <c r="L10" s="91">
         <f>DATE(2026,9,25)-DATE(2026,9,23)</f>
         <v>2</v>
       </c>
-      <c r="M10" s="96">
+      <c r="M10" s="91">
         <v>55</v>
       </c>
       <c r="N10" s="16">
@@ -8066,63 +7812,63 @@
         <f>868+21</f>
         <v>889</v>
       </c>
-      <c r="P10" s="38" t="s">
+      <c r="P10" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="62">
+        <v>46290</v>
+      </c>
+      <c r="S10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="66">
-        <v>46290</v>
-      </c>
-      <c r="S10" s="26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" s="27" customFormat="1" ht="130.5" hidden="1">
+    </row>
+    <row r="11" spans="1:19" s="27" customFormat="1" ht="130.5">
       <c r="A11" s="28">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>46</v>
+      <c r="C11" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>45</v>
       </c>
       <c r="E11" s="15">
         <v>46258</v>
       </c>
-      <c r="F11" s="96">
+      <c r="F11" s="91">
         <f>DATE(2026,9,30)-DATE(2026,8,24)</f>
         <v>37</v>
       </c>
-      <c r="G11" s="96">
+      <c r="G11" s="91">
         <f>DATE(2026,9,9)-DATE(2026,8,24)</f>
         <v>16</v>
       </c>
-      <c r="H11" s="96">
+      <c r="H11" s="91">
         <f>DATE(2026,9,14)-DATE(2026,9,9)</f>
         <v>5</v>
       </c>
-      <c r="I11" s="96">
+      <c r="I11" s="91">
         <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="96">
+      <c r="J11" s="91">
         <f ca="1">TODAY()-DATE(2026,9,16)</f>
-        <v>40</v>
-      </c>
-      <c r="K11" s="96">
+        <v>41</v>
+      </c>
+      <c r="K11" s="91">
         <f>DATE(2026,9,23)-DATE(2026,9,23)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="96">
+      <c r="L11" s="91">
         <f>DATE(2026,9,30)-DATE(2026,9,23)</f>
         <v>7</v>
       </c>
-      <c r="M11" s="96">
+      <c r="M11" s="91">
         <v>60</v>
       </c>
       <c r="N11" s="16">
@@ -8132,63 +7878,63 @@
         <f>798+21</f>
         <v>819</v>
       </c>
-      <c r="P11" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="67">
+      <c r="P11" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="63">
         <v>46295</v>
       </c>
       <c r="S11" s="26" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="27" customFormat="1" ht="116" hidden="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="27" customFormat="1" ht="116">
       <c r="A12" s="28">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>46</v>
+      <c r="C12" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>45</v>
       </c>
       <c r="E12" s="15">
         <v>46252</v>
       </c>
-      <c r="F12" s="96">
+      <c r="F12" s="91">
         <f>DATE(2026,10,3)-DATE(2026,8,18)</f>
         <v>46</v>
       </c>
-      <c r="G12" s="96">
+      <c r="G12" s="91">
         <f>DATE(2026,9,14)-DATE(2026,8,18)</f>
         <v>27</v>
       </c>
-      <c r="H12" s="96">
+      <c r="H12" s="91">
         <f>DATE(2026,9,18)-DATE(2026,9,14)</f>
         <v>4</v>
       </c>
-      <c r="I12" s="96">
+      <c r="I12" s="91">
         <f>DATE(2026,9,22)-DATE(2026,9,18)</f>
         <v>4</v>
       </c>
-      <c r="J12" s="96">
+      <c r="J12" s="91">
         <f>DATE(2026,9,26)-DATE(2026,9,22)</f>
         <v>4</v>
       </c>
-      <c r="K12" s="96">
+      <c r="K12" s="91">
         <f>DATE(2026,9,29)-DATE(2026,9,26)</f>
         <v>3</v>
       </c>
-      <c r="L12" s="96">
+      <c r="L12" s="91">
         <f>DATE(2026,10,1)-DATE(2026,9,29)</f>
         <v>2</v>
       </c>
-      <c r="M12" s="96">
+      <c r="M12" s="91">
         <v>25</v>
       </c>
       <c r="N12" s="16">
@@ -8198,62 +7944,62 @@
         <f>446+19</f>
         <v>465</v>
       </c>
-      <c r="P12" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="67">
+      <c r="P12" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="63">
         <v>46298</v>
       </c>
       <c r="S12" s="26" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" s="27" customFormat="1" ht="60" hidden="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" s="27" customFormat="1" ht="60">
       <c r="A13" s="28">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>46</v>
+      <c r="C13" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>45</v>
       </c>
       <c r="E13" s="15">
         <v>46254</v>
       </c>
-      <c r="F13" s="96">
+      <c r="F13" s="91">
         <f>DATE(2026,10,1)-DATE(2026,8,20)</f>
         <v>42</v>
       </c>
-      <c r="G13" s="96">
+      <c r="G13" s="91">
         <f>DATE(2026,9,14)-DATE(2026,8,20)</f>
         <v>25</v>
       </c>
-      <c r="H13" s="96">
+      <c r="H13" s="91">
         <f>DATE(2026,9,17)-DATE(2026,9,12)</f>
         <v>5</v>
       </c>
-      <c r="I13" s="96">
+      <c r="I13" s="91">
         <f>DATE(2026,9,24)-DATE(2026,9,22)</f>
         <v>2</v>
       </c>
-      <c r="J13" s="96">
+      <c r="J13" s="91">
         <f>DATE(2026,9,24)-DATE(2026,9,24)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="96">
+      <c r="K13" s="91">
         <f>DATE(2026,9,25)-DATE(2026,9,24)</f>
         <v>1</v>
       </c>
-      <c r="L13" s="96">
+      <c r="L13" s="91">
         <v>8</v>
       </c>
-      <c r="M13" s="96">
+      <c r="M13" s="91">
         <v>25</v>
       </c>
       <c r="N13" s="16">
@@ -8263,63 +8009,63 @@
         <f>276+19</f>
         <v>295</v>
       </c>
-      <c r="P13" s="38" t="s">
+      <c r="P13" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="63">
+        <v>46296</v>
+      </c>
+      <c r="S13" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="67">
-        <v>46296</v>
-      </c>
-      <c r="S13" s="26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" s="27" customFormat="1" ht="60" hidden="1">
+    </row>
+    <row r="14" spans="1:19" s="27" customFormat="1" ht="60">
       <c r="A14" s="28">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>46</v>
+      <c r="C14" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>45</v>
       </c>
       <c r="E14" s="15">
         <v>46259</v>
       </c>
-      <c r="F14" s="96">
+      <c r="F14" s="91">
         <f>DATE(2026,10,1)-DATE(2026,8,25)</f>
         <v>37</v>
       </c>
-      <c r="G14" s="96">
+      <c r="G14" s="91">
         <f>DATE(2026,9,12)-DATE(2026,8,24)</f>
         <v>19</v>
       </c>
-      <c r="H14" s="96">
+      <c r="H14" s="91">
         <f>DATE(2026,9,17)-DATE(2026,9,12)</f>
         <v>5</v>
       </c>
-      <c r="I14" s="96">
+      <c r="I14" s="91">
         <f>DATE(2026,9,17)-DATE(2026,9,17)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="96">
+      <c r="J14" s="91">
         <f>DATE(2026,9,22)-DATE(2026,9,18)</f>
         <v>4</v>
       </c>
-      <c r="K14" s="96">
+      <c r="K14" s="91">
         <f>DATE(2026,9,24)-DATE(2026,9,22)</f>
         <v>2</v>
       </c>
-      <c r="L14" s="96">
+      <c r="L14" s="91">
         <f>DATE(2026,9,30)-DATE(2026,9,25)</f>
         <v>5</v>
       </c>
-      <c r="M14" s="96">
+      <c r="M14" s="91">
         <v>35</v>
       </c>
       <c r="N14" s="16">
@@ -8329,63 +8075,63 @@
         <f>324+19</f>
         <v>343</v>
       </c>
-      <c r="P14" s="38" t="s">
+      <c r="P14" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="63">
+        <v>46296</v>
+      </c>
+      <c r="S14" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="67">
-        <v>46296</v>
-      </c>
-      <c r="S14" s="26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="27" customFormat="1" ht="60.5" hidden="1" thickBot="1">
+    </row>
+    <row r="15" spans="1:19" s="27" customFormat="1" ht="60">
       <c r="A15" s="28">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="30">
+      <c r="D15" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="173">
         <v>46204</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="41">
         <f>DATE(2026,10,6)-E15</f>
         <v>97</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="41">
         <f>DATE(2026,8,3)-DATE(2026,7,1)</f>
         <v>33</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="41">
         <f>DATE(2026,8,27)-DATE(2026,8,3)</f>
         <v>24</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="41">
         <f>DATE(2026,9,3)-DATE(2026,8,27)</f>
         <v>7</v>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="41">
         <f>DATE(2026,9,10)-DATE(2026,9,3)</f>
         <v>7</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="41">
         <f>DATE(2026,9,30)-DATE(2026,9,12)</f>
         <v>18</v>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="41">
         <f>DATE(2026,10,7)-DATE(2026,9,30)</f>
         <v>7</v>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="41">
         <f>DATE(2026,10,6)-DATE(2026,10,4)</f>
         <v>2</v>
       </c>
@@ -8395,56 +8141,56 @@
       <c r="O15" s="16">
         <v>299</v>
       </c>
-      <c r="P15" s="38" t="s">
+      <c r="P15" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q15" s="169" t="s">
         <v>59</v>
       </c>
-      <c r="Q15" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="R15" s="65">
+      <c r="R15" s="171">
         <v>46301</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="60.5" hidden="1" thickBot="1">
+    <row r="16" spans="1:19" ht="60">
       <c r="A16" s="28">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="150">
+      <c r="C16" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="173">
         <v>46204</v>
       </c>
-      <c r="F16" s="148">
+      <c r="F16" s="41">
         <f>DATE(2026,10,12)-E16</f>
         <v>103</v>
       </c>
-      <c r="G16" s="151">
+      <c r="G16" s="91">
         <v>35</v>
       </c>
-      <c r="H16" s="95">
+      <c r="H16" s="91">
         <v>23</v>
       </c>
-      <c r="I16" s="95">
+      <c r="I16" s="91">
         <v>10</v>
       </c>
-      <c r="J16" s="95">
+      <c r="J16" s="91">
         <v>4</v>
       </c>
-      <c r="K16" s="95">
+      <c r="K16" s="91">
         <v>18</v>
       </c>
-      <c r="L16" s="95">
+      <c r="L16" s="91">
         <v>5</v>
       </c>
-      <c r="M16" s="95">
+      <c r="M16" s="91">
         <v>6</v>
       </c>
       <c r="N16" s="16">
@@ -8453,63 +8199,63 @@
       <c r="O16" s="16">
         <v>333</v>
       </c>
-      <c r="P16" s="38" t="s">
+      <c r="P16" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q16" s="169" t="s">
         <v>61</v>
       </c>
-      <c r="Q16" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="R16" s="65">
+      <c r="R16" s="171">
         <v>46307</v>
       </c>
-      <c r="S16" s="131"/>
-    </row>
-    <row r="17" spans="1:19" ht="60.5" hidden="1" thickBot="1">
+      <c r="S16" s="123"/>
+    </row>
+    <row r="17" spans="1:19" ht="60">
       <c r="A17" s="28">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="153">
+      <c r="D17" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="173">
         <v>46265</v>
       </c>
-      <c r="F17" s="154">
+      <c r="F17" s="41">
         <f>DATE(2026,10,14)-E17</f>
         <v>44</v>
       </c>
-      <c r="G17" s="155">
+      <c r="G17" s="91">
         <f>DATE(2026,9,24)-DATE(2026,8,24)</f>
         <v>31</v>
       </c>
-      <c r="H17" s="95">
+      <c r="H17" s="91">
         <f>DATE(2026,9,30)-DATE(2026,9,24)</f>
         <v>6</v>
       </c>
-      <c r="I17" s="95">
+      <c r="I17" s="91">
         <f>DATE(2026,10,3)-DATE(2026,10,1)</f>
         <v>2</v>
       </c>
-      <c r="J17" s="95">
+      <c r="J17" s="91">
         <f>DATE(2026,10,7)-DATE(2026,10,4)</f>
         <v>3</v>
       </c>
-      <c r="K17" s="95">
+      <c r="K17" s="91">
         <f>DATE(2026,10,10)-DATE(2026,10,7)</f>
         <v>3</v>
       </c>
-      <c r="L17" s="95">
+      <c r="L17" s="91">
         <f>DATE(2026,10,14)-DATE(2026,10,10)</f>
         <v>4</v>
       </c>
-      <c r="M17" s="95">
+      <c r="M17" s="91">
         <v>25</v>
       </c>
       <c r="N17" s="16">
@@ -8518,98 +8264,77 @@
       <c r="O17" s="16">
         <v>385</v>
       </c>
-      <c r="P17" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="65">
+      <c r="P17" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="171">
         <v>46309</v>
       </c>
-      <c r="S17" s="115"/>
-    </row>
-    <row r="18" spans="1:19" hidden="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="142"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="143"/>
-      <c r="I18" s="143"/>
-      <c r="J18" s="143"/>
-      <c r="K18" s="143"/>
-      <c r="L18" s="143"/>
-      <c r="M18" s="143"/>
-      <c r="N18" s="143"/>
-      <c r="O18" s="143"/>
-      <c r="P18" s="144"/>
-      <c r="Q18" s="145"/>
-      <c r="R18" s="146"/>
-      <c r="S18" s="133"/>
-    </row>
-    <row r="19" spans="1:19" hidden="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="142"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="143"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="143"/>
-      <c r="I19" s="143"/>
-      <c r="J19" s="143"/>
-      <c r="K19" s="143"/>
-      <c r="L19" s="143"/>
-      <c r="M19" s="143"/>
-      <c r="N19" s="143"/>
-      <c r="O19" s="143"/>
-      <c r="P19" s="144"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="146"/>
-      <c r="S19" s="133"/>
-    </row>
-    <row r="20" spans="1:19" hidden="1">
-      <c r="A20" s="141"/>
-      <c r="B20" s="142"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="142"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="143"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="143"/>
-      <c r="I20" s="143"/>
-      <c r="J20" s="143"/>
-      <c r="K20" s="143"/>
-      <c r="L20" s="143"/>
-      <c r="M20" s="143"/>
-      <c r="N20" s="143"/>
-      <c r="O20" s="143"/>
-      <c r="P20" s="144"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="146"/>
-      <c r="S20" s="133"/>
-    </row>
-    <row r="21" spans="1:19" hidden="1">
-      <c r="A21" s="141"/>
-      <c r="B21" s="142"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="143"/>
-      <c r="O21" s="143"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="145"/>
-      <c r="R21" s="146"/>
-      <c r="S21" s="133"/>
+      <c r="S17" s="109"/>
+    </row>
+    <row r="18" spans="1:19" s="50" customFormat="1" ht="60">
+      <c r="A18" s="28">
+        <f>ROW()-1</f>
+        <v>17</v>
+      </c>
+      <c r="B18" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="194" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="173">
+        <v>46269</v>
+      </c>
+      <c r="F18" s="174">
+        <f>DATE(2026,10,26)-E18</f>
+        <v>52</v>
+      </c>
+      <c r="G18" s="28">
+        <f>DATE(2026,9,26)-DATE(2026,9,4)</f>
+        <v>22</v>
+      </c>
+      <c r="H18" s="91">
+        <f>DATE(2026,10,11)-DATE(2026,9,26)</f>
+        <v>15</v>
+      </c>
+      <c r="I18" s="28">
+        <f>DATE(2026,10,16)-DATE(2026,10,12)</f>
+        <v>4</v>
+      </c>
+      <c r="J18" s="91">
+        <f>DATE(2026,10,23)-DATE(2026,10,16)</f>
+        <v>7</v>
+      </c>
+      <c r="K18" s="28">
+        <f>DATE(2026,10,26)-DATE(2026,10,23)</f>
+        <v>3</v>
+      </c>
+      <c r="L18" s="91">
+        <f>DATE(2026,10,27)-DATE(2026,10,26)</f>
+        <v>1</v>
+      </c>
+      <c r="M18" s="28">
+        <v>14</v>
+      </c>
+      <c r="N18" s="91">
+        <v>189</v>
+      </c>
+      <c r="O18" s="28"/>
+      <c r="P18" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="172">
+        <v>46321</v>
+      </c>
+      <c r="S18" s="170" t="s">
+        <v>184</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8623,7 +8348,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23.7265625" customWidth="1"/>
@@ -8632,81 +8357,243 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26.5" thickBot="1">
-      <c r="A1" s="102" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="103" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="100" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="97"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="89"/>
+      <c r="A1" s="96" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="97" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="92"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="85"/>
     </row>
     <row r="2" spans="1:11" ht="32.5" customHeight="1" thickBot="1">
-      <c r="A2" s="107" t="s">
-        <v>154</v>
-      </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="109" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="97"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="106"/>
+      <c r="A2" s="101" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="102"/>
+      <c r="C2" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="92"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="100"/>
     </row>
     <row r="3" spans="1:11" ht="15" thickBot="1">
-      <c r="A3" s="99" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="98">
+      <c r="A3" s="93" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="195">
         <f>COUNTA(Table2[MPS ID])</f>
         <v>33</v>
       </c>
-      <c r="C3" s="101">
+      <c r="C3" s="95">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>
-        <v>25.766666666666666</v>
-      </c>
-      <c r="D3" s="97"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
+        <v>25.862068965517242</v>
+      </c>
+      <c r="D3" s="92"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1">
-      <c r="A4" s="104" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="147">
-        <f>COUNTA(Delivered!C2:C21)</f>
-        <v>16</v>
-      </c>
-      <c r="C4" s="105">
+      <c r="A4" s="98" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="131">
+        <f>COUNTA(Delivered!C2:C18)</f>
+        <v>17</v>
+      </c>
+      <c r="C4" s="99">
         <f>AVERAGE(Table3[Total Avg. Aging Days])</f>
         <v>61.3125</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1">
-      <c r="A5" s="88"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-    </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="88"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+    </row>
+    <row r="6" spans="1:11" ht="36">
+      <c r="A6" s="199" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="200" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="200" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="200" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="200" t="s">
+        <v>220</v>
+      </c>
+      <c r="G6" s="200" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="200" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="197">
+        <f>Delivered!G2</f>
+        <v>32</v>
+      </c>
+      <c r="C7" s="197">
+        <f>Delivered!H2</f>
+        <v>11</v>
+      </c>
+      <c r="D7" s="197">
+        <f>Delivered!I2</f>
+        <v>3</v>
+      </c>
+      <c r="E7" s="197">
+        <f>Delivered!J2</f>
+        <v>6</v>
+      </c>
+      <c r="F7" s="197">
+        <f>Delivered!K2</f>
+        <v>6</v>
+      </c>
+      <c r="G7" s="197">
+        <f>Delivered!L2</f>
+        <v>5</v>
+      </c>
+      <c r="H7" s="204">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="198">
+        <f>AVERAGE(Delivered!G3:G11)</f>
+        <v>25</v>
+      </c>
+      <c r="C8" s="198">
+        <f>AVERAGE(Delivered!H3:H11)</f>
+        <v>11.777777777777779</v>
+      </c>
+      <c r="D8" s="198">
+        <f>AVERAGE(Delivered!I3:I11)</f>
+        <v>4.1111111111111107</v>
+      </c>
+      <c r="E8" s="198">
+        <f ca="1">AVERAGE(Delivered!J3:J11)</f>
+        <v>10.666666666666666</v>
+      </c>
+      <c r="F8" s="198">
+        <f>AVERAGE(Delivered!K3:K11)</f>
+        <v>5.8888888888888893</v>
+      </c>
+      <c r="G8" s="198">
+        <f>AVERAGE(Delivered!L3:L11)</f>
+        <v>6</v>
+      </c>
+      <c r="H8" s="204">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="201" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="202">
+        <f>AVERAGE(Delivered!G12:G21)</f>
+        <v>27.428571428571427</v>
+      </c>
+      <c r="C9" s="202">
+        <f>AVERAGE(Delivered!H12:H21)</f>
+        <v>11.714285714285714</v>
+      </c>
+      <c r="D9" s="202">
+        <f>AVERAGE(Delivered!I12:I21)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="E9" s="202">
+        <f>AVERAGE(Delivered!J12:J21)</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="F9" s="202">
+        <f>AVERAGE(Delivered!K12:K21)</f>
+        <v>6.8571428571428568</v>
+      </c>
+      <c r="G9" s="202">
+        <f>AVERAGE(Delivered!L12:L21)</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="H9" s="204">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="29">
+      <c r="A10" s="203" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="197">
+        <f>AVERAGE(B7:B9)</f>
+        <v>28.142857142857142</v>
+      </c>
+      <c r="C10" s="197">
+        <f t="shared" ref="C10:G10" si="0">AVERAGE(C7:C9)</f>
+        <v>11.497354497354499</v>
+      </c>
+      <c r="D10" s="197">
+        <f t="shared" si="0"/>
+        <v>3.7513227513227512</v>
+      </c>
+      <c r="E10" s="197">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.9365079365079358</v>
+      </c>
+      <c r="F10" s="197">
+        <f t="shared" si="0"/>
+        <v>6.2486772486772493</v>
+      </c>
+      <c r="G10" s="197">
+        <f t="shared" si="0"/>
+        <v>5.1904761904761907</v>
+      </c>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="205" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="205">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="205" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="205">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8732,183 +8619,183 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="194" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="194"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="B3" s="182" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="182"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="66">
+        <v>15</v>
+      </c>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="70">
-        <v>15</v>
-      </c>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-    </row>
-    <row r="5" spans="2:10">
-      <c r="B5" s="77" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="78" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
+      <c r="C5" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="79">
+      <c r="B6" s="75">
         <v>46235</v>
       </c>
-      <c r="C6" s="80">
+      <c r="C6" s="76">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</f>
         <v>1</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="79">
+      <c r="B7" s="75">
         <v>46266</v>
       </c>
-      <c r="C7" s="80">
+      <c r="C7" s="76">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B7,Delivered!$R:$R,"&lt;"&amp;EDATE(B7,1))</f>
         <v>9</v>
       </c>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="79">
+      <c r="B8" s="75">
         <v>46296</v>
       </c>
-      <c r="C8" s="80">
+      <c r="C8" s="76">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B8,Delivered!$R:$R,"&lt;"&amp;EDATE(B8,1))</f>
-        <v>6</v>
-      </c>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
+        <v>7</v>
+      </c>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="79"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="79">
+      <c r="B9" s="75">
         <v>46327</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="76">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B9,Delivered!$R:$R,"&lt;"&amp;EDATE(B9,1))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="81">
+      <c r="B10" s="77">
         <v>46357</v>
       </c>
-      <c r="C10" s="82">
+      <c r="C10" s="78">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B10,Delivered!$R:$R,"&lt;"&amp;EDATE(B10,1))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="5:10">
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8925,14 +8812,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
     <col min="2" max="2" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1" outlineLevel="2"/>
     <col min="4" max="4" width="14.54296875" customWidth="1" outlineLevel="2"/>
-    <col min="5" max="5" width="22.7265625" style="63" bestFit="1" customWidth="1" outlineLevel="2"/>
+    <col min="5" max="5" width="22.7265625" style="59" bestFit="1" customWidth="1" outlineLevel="2"/>
     <col min="6" max="6" width="23.08984375" customWidth="1" outlineLevel="2"/>
     <col min="8" max="8" width="21.36328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -8962,8 +8849,8 @@
       <c r="H1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="45" t="s">
-        <v>58</v>
+      <c r="I1" s="42" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -9028,7 +8915,7 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="43" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="16">
@@ -9047,7 +8934,7 @@
         <f>DATE(2026,9,22)-DATE(2026,9,20)</f>
         <v>2</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="51">
         <f>DATE(2026,9,23)-DATE(2026,7,27)</f>
         <v>58</v>
       </c>
@@ -9056,33 +8943,33 @@
         <v>On Track. 47 days buffer</v>
       </c>
       <c r="I4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="44">
         <f>DATE(2026,9,5)-DATE(2026,8,24)</f>
         <v>12</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="44">
         <f>DATE(2026,9,9)-DATE(2026,9,5)</f>
         <v>4</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="44">
         <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
         <v>6</v>
       </c>
-      <c r="F5" s="47">
+      <c r="F5" s="44">
         <f>DATE(2026,9,20)-DATE(2026,9,17)</f>
         <v>3</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="45">
         <f>DATE(2026,9,21)-DATE(2026,7,31)</f>
         <v>52</v>
       </c>
@@ -9091,7 +8978,7 @@
         <v>On Track. 50 days buffer</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9109,15 +8996,15 @@
         <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="44">
         <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
         <v>6</v>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="44">
         <f>DATE(2026,9,26)-DATE(2026,9,22)</f>
         <v>4</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="51">
         <f>DATE(2026,9,25)-DATE(2026,8,12)</f>
         <v>44</v>
       </c>
@@ -9126,7 +9013,7 @@
         <v>On Track. 49 days buffer</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9152,7 +9039,7 @@
         <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
         <v>6</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="51">
         <f>DATE(2026,9,26)-DATE(2026,8,10)</f>
         <v>47</v>
       </c>
@@ -9161,7 +9048,7 @@
         <v>On Track. 48 days buffer</v>
       </c>
       <c r="I7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -9185,7 +9072,7 @@
       </c>
       <c r="F8" s="5">
         <f ca="1">TODAY()-DATE(2026,9,25)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="5" t="e">
         <f ca="1">TODAY()-#REF!</f>
@@ -9193,7 +9080,7 @@
       </c>
       <c r="H8" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 35 days buffer</v>
+        <v>On Track. 34 days buffer</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -9209,7 +9096,7 @@
       </c>
       <c r="D9" s="16">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -9219,7 +9106,7 @@
       </c>
       <c r="H9" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 36 days buffer</v>
+        <v>On Track. 35 days buffer</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -9235,7 +9122,7 @@
       </c>
       <c r="D10" s="16">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -9245,7 +9132,7 @@
       </c>
       <c r="H10" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 36 days buffer</v>
+        <v>On Track. 35 days buffer</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -9265,7 +9152,7 @@
       </c>
       <c r="E11" s="7">
         <f ca="1">TODAY()-DATE(2026,9,16)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="e">
@@ -9274,7 +9161,7 @@
       </c>
       <c r="H11" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 34 days buffer</v>
+        <v>On Track. 33 days buffer</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -9563,8 +9450,8 @@
       <c r="A27" s="8">
         <v>26</v>
       </c>
-      <c r="B27" s="50" t="s">
-        <v>98</v>
+      <c r="B27" s="47" t="s">
+        <v>97</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -9577,8 +9464,8 @@
       <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="51" t="s">
-        <v>99</v>
+      <c r="B28" s="48" t="s">
+        <v>98</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -9589,30 +9476,30 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="10"/>
-      <c r="C46" s="136" t="s">
-        <v>168</v>
-      </c>
-      <c r="D46" s="137">
-        <f>COUNTA(D49:D77)</f>
-        <v>29</v>
+      <c r="C46" s="126" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" s="127">
+        <f>COUNTA(D49:D81)</f>
+        <v>33</v>
       </c>
       <c r="E46" s="18"/>
     </row>
     <row r="47" spans="2:6" ht="15" thickBot="1">
       <c r="B47" s="10"/>
-      <c r="C47" s="138" t="s">
-        <v>187</v>
-      </c>
-      <c r="D47" s="139">
-        <v>16</v>
-      </c>
-      <c r="E47" s="139" t="s">
-        <v>188</v>
+      <c r="C47" s="128" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" s="129">
+        <v>17</v>
+      </c>
+      <c r="E47" s="129" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="15" thickBot="1">
       <c r="B48" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C48" s="22" t="s">
         <v>2</v>
@@ -9620,252 +9507,295 @@
       <c r="D48" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="135" t="s">
-        <v>47</v>
-      </c>
-      <c r="F48" s="158" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
+      <c r="E48" s="125" t="s">
+        <v>46</v>
+      </c>
+      <c r="F48" s="134" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
       <c r="B49" s="18">
         <v>1</v>
       </c>
-      <c r="C49" s="157" t="s">
+      <c r="C49" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="156" t="s">
-        <v>73</v>
-      </c>
-      <c r="E49" s="159">
-        <v>58</v>
+      <c r="D49" s="132" t="s">
+        <v>185</v>
+      </c>
+      <c r="E49" s="135">
+        <v>64</v>
       </c>
       <c r="F49" s="10"/>
     </row>
-    <row r="50" spans="2:6" ht="72.5">
+    <row r="50" spans="2:11">
       <c r="B50" s="18">
         <v>2</v>
       </c>
-      <c r="C50" s="127" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="E50" s="35">
-        <v>47</v>
-      </c>
-      <c r="F50" s="26" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" ht="45.5" customHeight="1">
+      <c r="C50" s="119" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="138">
+        <v>40</v>
+      </c>
+      <c r="F50" s="26"/>
+    </row>
+    <row r="51" spans="2:11" ht="45.5" customHeight="1">
       <c r="B51" s="18">
         <v>3</v>
       </c>
-      <c r="C51" s="127" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E51" s="162">
-        <v>34</v>
+      <c r="C51" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="33">
+        <v>39</v>
       </c>
       <c r="F51" s="10"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:11">
       <c r="B52" s="18">
         <v>4</v>
       </c>
-      <c r="C52" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="D52" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="35">
-        <v>33</v>
+      <c r="C52" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="142" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" s="137">
+        <v>39</v>
       </c>
       <c r="F52" s="10"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:11">
       <c r="B53" s="18">
         <v>5</v>
       </c>
-      <c r="C53" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="D53" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E53" s="35">
-        <v>33</v>
+      <c r="C53" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E53" s="33">
+        <v>39</v>
       </c>
       <c r="F53" s="10"/>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:11" ht="29">
       <c r="B54" s="18">
         <v>6</v>
       </c>
-      <c r="C54" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D54" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="160">
-        <v>33</v>
+      <c r="C54" s="119" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" s="136">
+        <v>36</v>
       </c>
       <c r="F54" s="10"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="G54" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="H54" s="181" t="s">
+        <v>224</v>
+      </c>
+      <c r="I54" s="181">
+        <v>30</v>
+      </c>
+      <c r="J54" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="K54" s="181" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" ht="29">
       <c r="B55" s="18">
         <v>7</v>
       </c>
-      <c r="C55" s="127" t="s">
+      <c r="C55" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E55" s="33">
         <v>34</v>
       </c>
-      <c r="D55" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="161">
-        <v>30</v>
-      </c>
       <c r="F55" s="10"/>
-    </row>
-    <row r="56" spans="2:6">
+      <c r="G55" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="H55" s="181" t="s">
+        <v>224</v>
+      </c>
+      <c r="I55" s="181">
+        <v>46</v>
+      </c>
+      <c r="J55" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="K55" s="181" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" ht="29">
       <c r="B56" s="18">
         <v>8</v>
       </c>
-      <c r="C56" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="35">
-        <v>28</v>
+      <c r="C56" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="33">
+        <v>34</v>
       </c>
       <c r="F56" s="10"/>
-    </row>
-    <row r="57" spans="2:6">
+      <c r="G56" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="H56" s="181" t="s">
+        <v>227</v>
+      </c>
+      <c r="I56" s="181">
+        <v>58</v>
+      </c>
+      <c r="J56" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="K56" s="181" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" s="18">
         <v>9</v>
       </c>
-      <c r="C57" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="D57" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E57" s="35">
-        <v>28</v>
+      <c r="C57" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="D57" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" s="33">
+        <v>33</v>
       </c>
       <c r="F57" s="10"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:11">
       <c r="B58" s="18">
         <v>10</v>
       </c>
-      <c r="C58" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="D58" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="E58" s="35">
-        <v>27</v>
+      <c r="C58" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" s="33">
+        <v>31</v>
       </c>
       <c r="F58" s="10"/>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:11">
       <c r="B59" s="18">
         <v>11</v>
       </c>
-      <c r="C59" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="D59" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="35">
-        <v>25</v>
+      <c r="C59" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D59" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="138">
+        <v>31</v>
       </c>
       <c r="F59" s="10"/>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:11">
       <c r="B60" s="18">
         <v>12</v>
       </c>
-      <c r="C60" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="D60" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="E60" s="35">
-        <v>25</v>
+      <c r="C60" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="138">
+        <v>31</v>
       </c>
       <c r="F60" s="10"/>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:11">
       <c r="B61" s="18">
         <v>13</v>
       </c>
-      <c r="C61" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E61" s="162">
-        <v>25</v>
+      <c r="C61" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="8">
+        <v>30</v>
       </c>
       <c r="F61" s="10"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:11">
       <c r="B62" s="18">
         <v>14</v>
       </c>
-      <c r="C62" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D62" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E62" s="162">
-        <v>24</v>
+      <c r="C62" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="33">
+        <v>29</v>
       </c>
       <c r="F62" s="10"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:11" ht="28.5">
       <c r="B63" s="18">
         <v>15</v>
       </c>
-      <c r="C63" s="36" t="s">
+      <c r="C63" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="35" t="s">
+      <c r="D63" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="8">
-        <v>23</v>
+      <c r="E63" s="138">
+        <v>28</v>
       </c>
       <c r="F63" s="10"/>
     </row>
-    <row r="64" spans="2:6" ht="28">
+    <row r="64" spans="2:11">
       <c r="B64" s="18">
         <v>16</v>
       </c>
-      <c r="C64" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D64" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="E64" s="162">
-        <v>22</v>
+      <c r="C64" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="33">
+        <v>27</v>
       </c>
       <c r="F64" s="10"/>
     </row>
@@ -9873,14 +9803,14 @@
       <c r="B65" s="18">
         <v>17</v>
       </c>
-      <c r="C65" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="D65" s="8" t="s">
+      <c r="C65" s="164" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="8">
-        <v>21</v>
+      <c r="E65" s="138">
+        <v>27</v>
       </c>
       <c r="F65" s="10"/>
     </row>
@@ -9888,14 +9818,14 @@
       <c r="B66" s="18">
         <v>18</v>
       </c>
-      <c r="C66" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D66" s="8" t="s">
+      <c r="C66" s="164" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="162">
-        <v>21</v>
+      <c r="E66" s="138">
+        <v>27</v>
       </c>
       <c r="F66" s="10"/>
     </row>
@@ -9903,14 +9833,14 @@
       <c r="B67" s="18">
         <v>19</v>
       </c>
-      <c r="C67" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D67" s="8" t="s">
+      <c r="C67" s="166" t="s">
+        <v>158</v>
+      </c>
+      <c r="D67" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="162">
-        <v>21</v>
+      <c r="E67" s="8">
+        <v>20</v>
       </c>
       <c r="F67" s="10"/>
     </row>
@@ -9918,14 +9848,14 @@
       <c r="B68" s="18">
         <v>20</v>
       </c>
-      <c r="C68" s="61" t="s">
-        <v>160</v>
+      <c r="C68" s="34" t="s">
+        <v>110</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="162">
-        <v>14</v>
+      <c r="E68" s="18">
+        <v>20</v>
       </c>
       <c r="F68" s="10"/>
     </row>
@@ -9933,14 +9863,14 @@
       <c r="B69" s="18">
         <v>21</v>
       </c>
-      <c r="C69" s="36" t="s">
-        <v>111</v>
+      <c r="C69" s="34" t="s">
+        <v>136</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E69" s="18">
-        <v>14</v>
+        <v>215</v>
+      </c>
+      <c r="E69" s="138">
+        <v>15</v>
       </c>
       <c r="F69" s="10"/>
     </row>
@@ -9948,31 +9878,31 @@
       <c r="B70" s="18">
         <v>22</v>
       </c>
-      <c r="C70" s="36" t="s">
-        <v>137</v>
+      <c r="C70" s="34" t="s">
+        <v>127</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E70" s="18">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="18">
         <v>23</v>
       </c>
-      <c r="C71" s="36" t="s">
-        <v>128</v>
+      <c r="C71" s="34" t="s">
+        <v>130</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E71" s="18">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F71" s="10"/>
     </row>
@@ -9980,44 +9910,44 @@
       <c r="B72" s="18">
         <v>24</v>
       </c>
-      <c r="C72" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>45</v>
+      <c r="C72" s="164" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" s="167" t="s">
+        <v>19</v>
       </c>
       <c r="E72" s="18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F72" s="10"/>
     </row>
-    <row r="73" spans="2:6">
+    <row r="73" spans="2:6" ht="28">
       <c r="B73" s="18">
         <v>25</v>
       </c>
-      <c r="C73" s="36" t="s">
-        <v>131</v>
+      <c r="C73" s="34" t="s">
+        <v>197</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="E73" s="18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F73" s="10"/>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" spans="2:6" ht="28">
       <c r="B74" s="18">
         <v>26</v>
       </c>
-      <c r="C74" s="36" t="s">
-        <v>141</v>
+      <c r="C74" s="34" t="s">
+        <v>198</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E74" s="18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F74" s="10"/>
     </row>
@@ -10025,14 +9955,14 @@
       <c r="B75" s="18">
         <v>27</v>
       </c>
-      <c r="C75" s="36" t="s">
-        <v>163</v>
+      <c r="C75" s="34" t="s">
+        <v>161</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="E75" s="18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F75" s="10"/>
     </row>
@@ -10040,14 +9970,14 @@
       <c r="B76" s="18">
         <v>28</v>
       </c>
-      <c r="C76" s="36" t="s">
-        <v>165</v>
+      <c r="C76" s="34" t="s">
+        <v>163</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E76" s="18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F76" s="10"/>
     </row>
@@ -10055,20 +9985,80 @@
       <c r="B77" s="18">
         <v>29</v>
       </c>
-      <c r="C77" s="36" t="s">
-        <v>196</v>
+      <c r="C77" s="34" t="s">
+        <v>200</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E77" s="18">
         <v>6</v>
       </c>
       <c r="F77" s="10"/>
     </row>
+    <row r="78" spans="2:6">
+      <c r="B78" s="18">
+        <v>30</v>
+      </c>
+      <c r="C78" s="184" t="s">
+        <v>238</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="18">
+        <v>1</v>
+      </c>
+      <c r="F78" s="10"/>
+    </row>
+    <row r="79" spans="2:6" ht="29">
+      <c r="B79" s="18">
+        <v>31</v>
+      </c>
+      <c r="C79" s="184" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="18">
+        <v>0</v>
+      </c>
+      <c r="F79" s="10"/>
+    </row>
+    <row r="80" spans="2:6">
+      <c r="B80" s="18">
+        <v>32</v>
+      </c>
+      <c r="C80" s="184" t="s">
+        <v>243</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="18">
+        <v>0</v>
+      </c>
+      <c r="F80" s="10"/>
+    </row>
+    <row r="81" spans="2:6">
+      <c r="B81" s="18">
+        <v>33</v>
+      </c>
+      <c r="C81" s="184" t="s">
+        <v>241</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81" s="18">
+        <v>0</v>
+      </c>
+      <c r="F81" s="10"/>
+    </row>
   </sheetData>
-  <sortState ref="C49:F77">
-    <sortCondition descending="1" ref="E49:E77"/>
+  <sortState ref="C49:E81">
+    <sortCondition descending="1" ref="E49:E81"/>
   </sortState>
   <conditionalFormatting sqref="C2:C3 C5:C26">
     <cfRule type="colorScale" priority="34">

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="8" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="252">
   <si>
     <t>S. no</t>
   </si>
@@ -671,9 +671,6 @@
   </si>
   <si>
     <t>Overall Avg. Aging 61 days</t>
-  </si>
-  <si>
-    <t>word Tex combo</t>
   </si>
   <si>
     <t>S600</t>
@@ -2054,9 +2051,6 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2120,6 +2114,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4484,7 +4481,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H17" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -5087,7 +5084,7 @@
       <c r="B4" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="191" t="s">
         <v>46</v>
       </c>
       <c r="D4" t="s">
@@ -5195,7 +5192,7 @@
       <c r="B9" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="191">
+      <c r="C9" s="190">
         <v>46291</v>
       </c>
       <c r="D9" s="90">
@@ -5489,7 +5486,7 @@
         <v>53</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O1" s="27" t="s">
         <v>55</v>
@@ -5519,7 +5516,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E2" s="53">
         <v>46258</v>
@@ -5556,10 +5553,10 @@
         <v>69</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q2" s="153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R2" s="105" t="s">
         <v>101</v>
@@ -5614,7 +5611,7 @@
         <v>69</v>
       </c>
       <c r="P3" s="113" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q3" s="154" t="s">
         <v>74</v>
@@ -5669,7 +5666,7 @@
         <v>69</v>
       </c>
       <c r="P4" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q4" s="154" t="s">
         <v>74</v>
@@ -5728,7 +5725,7 @@
         <v>69</v>
       </c>
       <c r="P5" s="113" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q5" s="154" t="s">
         <v>73</v>
@@ -5783,13 +5780,13 @@
         <v>69</v>
       </c>
       <c r="P6" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q6" s="154" t="s">
         <v>155</v>
       </c>
       <c r="R6" s="161" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="S6" s="105" t="s">
         <v>170</v>
@@ -5841,7 +5838,7 @@
         <v>69</v>
       </c>
       <c r="P7" s="113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q7" s="154" t="s">
         <v>128</v>
@@ -5865,7 +5862,7 @@
         <v>179</v>
       </c>
       <c r="D8" s="142" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E8" s="144">
         <v>46283</v>
@@ -5959,7 +5956,7 @@
         <v>69</v>
       </c>
       <c r="P9" s="113" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q9" s="154" t="s">
         <v>73</v>
@@ -6015,7 +6012,7 @@
         <v>69</v>
       </c>
       <c r="P10" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q10" s="154" t="s">
         <v>75</v>
@@ -6064,10 +6061,10 @@
         <v>750</v>
       </c>
       <c r="O11" s="114" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P11" s="113" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q11" s="154" t="s">
         <v>167</v>
@@ -6117,10 +6114,10 @@
         <v>600</v>
       </c>
       <c r="O12" s="114" t="s">
+        <v>227</v>
+      </c>
+      <c r="P12" s="113" t="s">
         <v>228</v>
-      </c>
-      <c r="P12" s="113" t="s">
-        <v>229</v>
       </c>
       <c r="Q12" s="154" t="s">
         <v>76</v>
@@ -6142,7 +6139,7 @@
         <v>34</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E13" s="35">
         <v>46286</v>
@@ -6182,10 +6179,10 @@
         <v>69</v>
       </c>
       <c r="P13" s="113" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q13" s="154" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R13" s="105"/>
       <c r="S13" s="105" t="s">
@@ -6204,7 +6201,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E14" s="35">
         <v>46282</v>
@@ -6289,10 +6286,10 @@
         <v>500</v>
       </c>
       <c r="O15" s="114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P15" s="113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q15" s="154" t="s">
         <v>164</v>
@@ -6342,10 +6339,10 @@
         <v>500</v>
       </c>
       <c r="O16" s="114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P16" s="113" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q16" s="154"/>
       <c r="R16" s="105"/>
@@ -6396,7 +6393,7 @@
         <v>69</v>
       </c>
       <c r="P17" s="116" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="R17" s="105"/>
@@ -6442,13 +6439,13 @@
         <v>1500</v>
       </c>
       <c r="O18" s="117" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P18" s="113" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q18" s="157" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R18" s="105"/>
       <c r="S18" s="105" t="s">
@@ -6492,7 +6489,7 @@
         <v>550</v>
       </c>
       <c r="O19" s="114" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P19" s="113" t="s">
         <v>165</v>
@@ -6500,7 +6497,7 @@
       <c r="Q19" s="154"/>
       <c r="R19" s="105"/>
       <c r="S19" s="105" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="60">
@@ -6540,7 +6537,7 @@
         <v>450</v>
       </c>
       <c r="O20" s="114" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P20" s="113"/>
       <c r="Q20" s="154" t="s">
@@ -6563,7 +6560,7 @@
         <v>136</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E21" s="35">
         <v>46307</v>
@@ -6588,13 +6585,13 @@
         <v>171</v>
       </c>
       <c r="P21" s="113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q21" s="154" t="s">
         <v>149</v>
       </c>
       <c r="R21" s="105" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="S21" s="105" t="s">
         <v>170</v>
@@ -6637,7 +6634,7 @@
         <v>500</v>
       </c>
       <c r="O22" s="114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P22" s="113"/>
       <c r="Q22" s="158"/>
@@ -6683,7 +6680,7 @@
         <v>450</v>
       </c>
       <c r="O23" s="114" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P23" s="113"/>
       <c r="Q23" s="158"/>
@@ -6727,7 +6724,7 @@
         <v>500</v>
       </c>
       <c r="O24" s="114" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P24" s="113"/>
       <c r="Q24" s="154"/>
@@ -6773,7 +6770,7 @@
         <v>350</v>
       </c>
       <c r="O25" s="114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P25" s="113"/>
       <c r="Q25" s="154"/>
@@ -6791,7 +6788,7 @@
         <v>157</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>159</v>
@@ -6816,7 +6813,7 @@
         <v>300</v>
       </c>
       <c r="O26" s="114" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P26" s="112"/>
       <c r="Q26" s="159"/>
@@ -6903,7 +6900,7 @@
         <v>400</v>
       </c>
       <c r="O28" s="114" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P28" s="112"/>
       <c r="Q28" s="159"/>
@@ -6921,7 +6918,7 @@
         <v>168</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>19</v>
@@ -6949,7 +6946,7 @@
         <v>450</v>
       </c>
       <c r="O29" s="114" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P29" s="112"/>
       <c r="Q29" s="159"/>
@@ -6959,15 +6956,15 @@
       </c>
     </row>
     <row r="30" spans="1:19">
-      <c r="A30" s="186">
+      <c r="A30" s="185">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="B30" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="34" t="s">
         <v>199</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>200</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>24</v>
@@ -7000,15 +6997,15 @@
       </c>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="186">
+      <c r="A31" s="185">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="B31" s="152" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C31" s="152" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>24</v>
@@ -7036,15 +7033,15 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="29">
-      <c r="A32" s="187">
+      <c r="A32" s="186">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="B32" s="152" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C32" s="152" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>24</v>
@@ -7076,11 +7073,11 @@
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="B33" s="189" t="s">
+      <c r="B33" s="188" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" s="34" t="s">
         <v>242</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>243</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="26"/>
@@ -7097,9 +7094,9 @@
       <c r="N33" s="124">
         <v>200</v>
       </c>
-      <c r="O33" s="185"/>
-      <c r="P33" s="185"/>
-      <c r="Q33" s="185"/>
+      <c r="O33" s="184"/>
+      <c r="P33" s="184"/>
+      <c r="Q33" s="184"/>
       <c r="R33" s="105"/>
       <c r="S33" s="105" t="s">
         <v>170</v>
@@ -7110,11 +7107,11 @@
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="B34" s="190" t="s">
+      <c r="B34" s="189" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" s="189" t="s">
         <v>240</v>
-      </c>
-      <c r="C34" s="190" t="s">
-        <v>241</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="26"/>
@@ -7127,16 +7124,16 @@
       <c r="L34" s="121"/>
       <c r="M34" s="33"/>
       <c r="N34" s="124"/>
-      <c r="O34" s="185"/>
-      <c r="P34" s="185"/>
-      <c r="Q34" s="185"/>
+      <c r="O34" s="184"/>
+      <c r="P34" s="184"/>
+      <c r="Q34" s="184"/>
       <c r="R34" s="105"/>
       <c r="S34" s="105"/>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="124"/>
-      <c r="B35" s="183"/>
-      <c r="C35" s="183"/>
+      <c r="B35" s="182"/>
+      <c r="C35" s="182"/>
       <c r="D35" s="124"/>
       <c r="E35" s="26"/>
       <c r="F35" s="26"/>
@@ -7153,8 +7150,8 @@
       <c r="Q35" s="113"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="R36" s="188"/>
-      <c r="S36" s="188"/>
+      <c r="R36" s="187"/>
+      <c r="S36" s="187"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7232,7 +7229,7 @@
         <v>53</v>
       </c>
       <c r="N1" s="139" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O1" s="139" t="s">
         <v>54</v>
@@ -7702,7 +7699,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>45</v>
@@ -7767,7 +7764,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D10" s="31" t="s">
         <v>45</v>
@@ -7832,7 +7829,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D11" s="31" t="s">
         <v>45</v>
@@ -8281,10 +8278,10 @@
       <c r="B18" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="193" t="s">
+      <c r="C18" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="194" t="s">
+      <c r="D18" s="193" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="173">
@@ -8324,7 +8321,9 @@
       <c r="N18" s="91">
         <v>189</v>
       </c>
-      <c r="O18" s="28"/>
+      <c r="O18" s="28">
+        <v>201</v>
+      </c>
       <c r="P18" s="36" t="s">
         <v>69</v>
       </c>
@@ -8332,9 +8331,7 @@
       <c r="R18" s="172">
         <v>46321</v>
       </c>
-      <c r="S18" s="170" t="s">
-        <v>184</v>
-      </c>
+      <c r="S18" s="170"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8392,7 +8389,7 @@
       <c r="A3" s="93" t="s">
         <v>150</v>
       </c>
-      <c r="B3" s="195">
+      <c r="B3" s="194">
         <f>COUNTA(Table2[MPS ID])</f>
         <v>33</v>
       </c>
@@ -8422,176 +8419,176 @@
       <c r="E4" s="84"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="196"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
+      <c r="A5" s="195"/>
+      <c r="B5" s="195"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
     </row>
     <row r="6" spans="1:11" ht="36">
-      <c r="A6" s="199" t="s">
-        <v>245</v>
-      </c>
-      <c r="B6" s="200" t="s">
+      <c r="A6" s="198" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="199" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="200" t="s">
+      <c r="C6" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="200" t="s">
+      <c r="D6" s="199" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="200" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="200" t="s">
-        <v>220</v>
-      </c>
-      <c r="G6" s="200" t="s">
+      <c r="E6" s="199" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="199" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="199" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="200" t="s">
-        <v>250</v>
+      <c r="H6" s="199" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="B7" s="197">
+        <v>246</v>
+      </c>
+      <c r="B7" s="196">
         <f>Delivered!G2</f>
         <v>32</v>
       </c>
-      <c r="C7" s="197">
+      <c r="C7" s="196">
         <f>Delivered!H2</f>
         <v>11</v>
       </c>
-      <c r="D7" s="197">
+      <c r="D7" s="196">
         <f>Delivered!I2</f>
         <v>3</v>
       </c>
-      <c r="E7" s="197">
+      <c r="E7" s="196">
         <f>Delivered!J2</f>
         <v>6</v>
       </c>
-      <c r="F7" s="197">
+      <c r="F7" s="196">
         <f>Delivered!K2</f>
         <v>6</v>
       </c>
-      <c r="G7" s="197">
+      <c r="G7" s="196">
         <f>Delivered!L2</f>
         <v>5</v>
       </c>
-      <c r="H7" s="204">
+      <c r="H7" s="203">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B8" s="198">
+        <v>245</v>
+      </c>
+      <c r="B8" s="197">
         <f>AVERAGE(Delivered!G3:G11)</f>
         <v>25</v>
       </c>
-      <c r="C8" s="198">
+      <c r="C8" s="197">
         <f>AVERAGE(Delivered!H3:H11)</f>
         <v>11.777777777777779</v>
       </c>
-      <c r="D8" s="198">
+      <c r="D8" s="197">
         <f>AVERAGE(Delivered!I3:I11)</f>
         <v>4.1111111111111107</v>
       </c>
-      <c r="E8" s="198">
+      <c r="E8" s="197">
         <f ca="1">AVERAGE(Delivered!J3:J11)</f>
         <v>10.666666666666666</v>
       </c>
-      <c r="F8" s="198">
+      <c r="F8" s="197">
         <f>AVERAGE(Delivered!K3:K11)</f>
         <v>5.8888888888888893</v>
       </c>
-      <c r="G8" s="198">
+      <c r="G8" s="197">
         <f>AVERAGE(Delivered!L3:L11)</f>
         <v>6</v>
       </c>
-      <c r="H8" s="204">
+      <c r="H8" s="203">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="201" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" s="202">
+      <c r="A9" s="200" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="201">
         <f>AVERAGE(Delivered!G12:G21)</f>
         <v>27.428571428571427</v>
       </c>
-      <c r="C9" s="202">
+      <c r="C9" s="201">
         <f>AVERAGE(Delivered!H12:H21)</f>
         <v>11.714285714285714</v>
       </c>
-      <c r="D9" s="202">
+      <c r="D9" s="201">
         <f>AVERAGE(Delivered!I12:I21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="E9" s="202">
+      <c r="E9" s="201">
         <f>AVERAGE(Delivered!J12:J21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="F9" s="202">
+      <c r="F9" s="201">
         <f>AVERAGE(Delivered!K12:K21)</f>
         <v>6.8571428571428568</v>
       </c>
-      <c r="G9" s="202">
+      <c r="G9" s="201">
         <f>AVERAGE(Delivered!L12:L21)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="H9" s="204">
+      <c r="H9" s="203">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29">
-      <c r="A10" s="203" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" s="197">
+      <c r="A10" s="202" t="s">
+        <v>248</v>
+      </c>
+      <c r="B10" s="196">
         <f>AVERAGE(B7:B9)</f>
         <v>28.142857142857142</v>
       </c>
-      <c r="C10" s="197">
+      <c r="C10" s="196">
         <f t="shared" ref="C10:G10" si="0">AVERAGE(C7:C9)</f>
         <v>11.497354497354499</v>
       </c>
-      <c r="D10" s="197">
+      <c r="D10" s="196">
         <f t="shared" si="0"/>
         <v>3.7513227513227512</v>
       </c>
-      <c r="E10" s="197">
+      <c r="E10" s="196">
         <f t="shared" ca="1" si="0"/>
         <v>6.9365079365079358</v>
       </c>
-      <c r="F10" s="197">
+      <c r="F10" s="196">
         <f t="shared" si="0"/>
         <v>6.2486772486772493</v>
       </c>
-      <c r="G10" s="197">
+      <c r="G10" s="196">
         <f t="shared" si="0"/>
         <v>5.1904761904761907</v>
       </c>
       <c r="H10" s="10"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="205" t="s">
+      <c r="A12" s="204" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="204">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="204" t="s">
         <v>251</v>
       </c>
-      <c r="B12" s="205">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="205" t="s">
-        <v>252</v>
-      </c>
-      <c r="B13" s="205">
+      <c r="B13" s="204">
         <v>103</v>
       </c>
     </row>
@@ -8627,10 +8624,10 @@
       <c r="J2" s="79"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="182" t="s">
+      <c r="B3" s="205" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="182"/>
+      <c r="C3" s="205"/>
       <c r="E3" s="79"/>
       <c r="F3" s="80"/>
       <c r="G3" s="79"/>
@@ -9499,7 +9496,7 @@
     </row>
     <row r="48" spans="2:6" ht="15" thickBot="1">
       <c r="B48" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C48" s="22" t="s">
         <v>2</v>
@@ -9522,7 +9519,7 @@
         <v>18</v>
       </c>
       <c r="D49" s="132" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E49" s="135">
         <v>64</v>
@@ -9537,7 +9534,7 @@
         <v>36</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E50" s="138">
         <v>40</v>
@@ -9567,7 +9564,7 @@
         <v>179</v>
       </c>
       <c r="D52" s="142" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E52" s="137">
         <v>39</v>
@@ -9597,7 +9594,7 @@
         <v>34</v>
       </c>
       <c r="D54" s="33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E54" s="136">
         <v>36</v>
@@ -9607,16 +9604,16 @@
         <v>112</v>
       </c>
       <c r="H54" s="181" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I54" s="181">
         <v>30</v>
       </c>
       <c r="J54" s="181" t="s">
+        <v>224</v>
+      </c>
+      <c r="K54" s="181" t="s">
         <v>225</v>
-      </c>
-      <c r="K54" s="181" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="55" spans="2:11" ht="29">
@@ -9637,16 +9634,16 @@
         <v>112</v>
       </c>
       <c r="H55" s="181" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I55" s="181">
         <v>46</v>
       </c>
       <c r="J55" s="181" t="s">
+        <v>224</v>
+      </c>
+      <c r="K55" s="181" t="s">
         <v>225</v>
-      </c>
-      <c r="K55" s="181" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="56" spans="2:11" ht="29">
@@ -9667,16 +9664,16 @@
         <v>112</v>
       </c>
       <c r="H56" s="181" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I56" s="181">
         <v>58</v>
       </c>
       <c r="J56" s="181" t="s">
+        <v>224</v>
+      </c>
+      <c r="K56" s="181" t="s">
         <v>225</v>
-      </c>
-      <c r="K56" s="181" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="57" spans="2:11">
@@ -9867,7 +9864,7 @@
         <v>136</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E69" s="138">
         <v>15</v>
@@ -9888,7 +9885,7 @@
         <v>15</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -9926,7 +9923,7 @@
         <v>25</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>159</v>
@@ -9941,7 +9938,7 @@
         <v>26</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>19</v>
@@ -9986,7 +9983,7 @@
         <v>29</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>24</v>
@@ -10000,8 +9997,8 @@
       <c r="B78" s="18">
         <v>30</v>
       </c>
-      <c r="C78" s="184" t="s">
-        <v>238</v>
+      <c r="C78" s="183" t="s">
+        <v>237</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>24</v>
@@ -10015,8 +10012,8 @@
       <c r="B79" s="18">
         <v>31</v>
       </c>
-      <c r="C79" s="184" t="s">
-        <v>239</v>
+      <c r="C79" s="183" t="s">
+        <v>238</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>24</v>
@@ -10030,8 +10027,8 @@
       <c r="B80" s="18">
         <v>32</v>
       </c>
-      <c r="C80" s="184" t="s">
-        <v>243</v>
+      <c r="C80" s="183" t="s">
+        <v>242</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>24</v>
@@ -10045,8 +10042,8 @@
       <c r="B81" s="18">
         <v>33</v>
       </c>
-      <c r="C81" s="184" t="s">
-        <v>241</v>
+      <c r="C81" s="183" t="s">
+        <v>240</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>24</v>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="8" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="6" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="261">
   <si>
     <t>S. no</t>
   </si>
@@ -568,9 +568,6 @@
     <t>Count of S300 TAT</t>
   </si>
   <si>
-    <t>New manuscript recd again and chap-31 added. On 12-Oct26</t>
-  </si>
-  <si>
     <t>Total No of Titles in WIP</t>
   </si>
   <si>
@@ -634,9 +631,6 @@
     <t>Word</t>
   </si>
   <si>
-    <t>HOLD</t>
-  </si>
-  <si>
     <t>Query chap 28. figs missing was reced.</t>
   </si>
   <si>
@@ -679,21 +673,10 @@
     <t>Tex+word</t>
   </si>
   <si>
-    <t>Query for JS regarding mismatch in chaps. BM is also there</t>
-  </si>
-  <si>
     <t>Query will be resolved after 23-oct conferences</t>
   </si>
   <si>
     <t>SL. No</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login :00 Chapters;
-PE : 00 Chapters;
-CE : 25 Chapters;
-Comp : 53 Chapters;
-Online Delivery : 00 Chapters</t>
   </si>
   <si>
     <t>S200 - 
@@ -716,14 +699,6 @@
     <t>2 in Eproof rest revises completed</t>
   </si>
   <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE :  00 Chapters;
-CE : 00 Chapters;
-Comp : 04 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>PERARNAU-DMD-Garcia-Sanchez</t>
   </si>
   <si>
@@ -756,14 +731,6 @@
   </si>
   <si>
     <t>PRR sent on 17th Sep. Query-Reference missing and content mismatch, One new manuscript approval</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 36 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
   </si>
   <si>
     <t>S200 - 
@@ -777,19 +744,7 @@
     <t>28 Chaps-Rev.delivered, 3 Part in Eproof, FM-recept error</t>
   </si>
   <si>
-    <t>11 in revises. 13 in eproof, FM in 200 comp</t>
-  </si>
-  <si>
-    <t>All in in Revises, FM in eproof</t>
-  </si>
-  <si>
     <t>All in revises</t>
-  </si>
-  <si>
-    <t>All in  Revises</t>
-  </si>
-  <si>
-    <t>Part, FM in s200 online delivery so not moved to 300</t>
   </si>
   <si>
     <t>S200Login</t>
@@ -809,21 +764,12 @@
     <t>704476_1_En</t>
   </si>
   <si>
-    <t>Preface &amp; TOC(FM components missing)</t>
-  </si>
-  <si>
     <t>S650A</t>
   </si>
   <si>
-    <t>All are in revises</t>
-  </si>
-  <si>
     <t>S300 completed</t>
   </si>
   <si>
-    <t>Only 8 chaps in Revises. Rest completed</t>
-  </si>
-  <si>
     <t>MetSoc-Vol9-8771159</t>
   </si>
   <si>
@@ -834,20 +780,6 @@
   </si>
   <si>
     <t>etSoc-Vol9-8771159</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 00 Chapters;
-CE : 00 Chapters;
-Comp : 01 Chapters;
-Online Delivery : 03 Chapters</t>
-  </si>
-  <si>
-    <t>20 chap in Revises, rest in eproof</t>
-  </si>
-  <si>
-    <t>15 chap in Eproof,13 Chaps in Revises.</t>
   </si>
   <si>
     <t>S200 - 
@@ -875,14 +807,6 @@
   </si>
   <si>
     <t>S200 - 
-Login : 00 Chapters;
-PE : 00 Chapters;
-CE : 04 Chapters;
-Comp : 24 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
 Login : 47 Chapters;
 PE : 09 Chapters;
 CE : 00 Chapters;
@@ -949,6 +873,109 @@
   </si>
   <si>
     <t>Longest TAT</t>
+  </si>
+  <si>
+    <t>Delivered on 27th</t>
+  </si>
+  <si>
+    <t>6 chaps in revises</t>
+  </si>
+  <si>
+    <t>20 in revises. FM in S200 comp</t>
+  </si>
+  <si>
+    <t>Delivrered</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login :00 Chapters;
+PE : 00 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>11 chaps in Revises</t>
+  </si>
+  <si>
+    <t>25 chap in Revises</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 15 Chapters;
+CE : 21 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE :  00 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>15 Chaps in Revises.</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 30 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 00 Chapters;
+CE : 00 Chapters;
+Comp : 36 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>697730_1_En</t>
+  </si>
+  <si>
+    <t>Hameed, Alaa Ali</t>
+  </si>
+  <si>
+    <t>S50</t>
+  </si>
+  <si>
+    <t>13 Books</t>
+  </si>
+  <si>
+    <t>7 Books</t>
+  </si>
+  <si>
+    <t>S650 A</t>
+  </si>
+  <si>
+    <t>3 Books</t>
+  </si>
+  <si>
+    <t>Delivered on 28-Oct</t>
+  </si>
+  <si>
+    <t>S200 delivered on 27-Oct</t>
+  </si>
+  <si>
+    <t>Query for JS regarding mismatch in chaps. BM is also there+Index</t>
+  </si>
+  <si>
+    <t>Login moved on 29-Oct</t>
+  </si>
+  <si>
+    <t>New manuscript recd again and chap-31 added. On 12-Oct26. Preface &amp; TOC(FM components missing), Index tagging for 2 chaps. missing reced on 28-oct</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Column2</t>
   </si>
 </sst>
 </file>
@@ -959,7 +986,7 @@
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1148,6 +1175,24 @@
       <sz val="7"/>
       <color rgb="FF393939"/>
       <name val="Open Sans"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1528,7 +1573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1876,16 +1921,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1961,9 +2000,6 @@
     <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1994,9 +2030,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2009,9 +2042,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2042,40 +2072,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2114,14 +2125,511 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="172">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3684,15 +4192,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3707,21 +4206,20 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Pawan Mathur" refreshedDate="46310.470623726855" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="29">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Pawan Mathur" refreshedDate="46323.454113541666" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="34">
   <cacheSource type="worksheet">
     <worksheetSource name="Table2"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="S. no" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="29"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="33"/>
     </cacheField>
     <cacheField name="Book ID" numFmtId="0">
       <sharedItems/>
     </cacheField>
     <cacheField name="MPS ID" numFmtId="0">
-      <sharedItems count="42">
+      <sharedItems count="50">
         <s v="Sánchez, Angeles"/>
-        <s v="Zawawi, Iskandar Shah Mohd"/>
         <s v="Metsoc Vol-I-8771046"/>
         <s v="Metsoc Vol-II-8771047"/>
         <s v="Metsoc Vol-III-8771048"/>
@@ -3745,101 +4243,121 @@
         <s v="Martín-Rojas, Rodrigo"/>
         <s v="Teba, Tarek"/>
         <s v="Gunka, Volodymyr"/>
-        <s v="PERARNAU-DMD"/>
+        <s v="PERARNAU-DMD-Garcia-Sanchez"/>
         <s v="Lo Presti, Davide"/>
         <s v="De Marchi, Luca"/>
-        <s v="Ihalanayake, Ranjith"/>
+        <s v="AL-Emran-Ihalanayake Ranjith"/>
+        <s v="Barla, Marco"/>
+        <s v="Zi,-PIC Yunlong 8770448"/>
+        <s v="Zhan-Ventura, Michele Della-8770452"/>
+        <s v="González, Carina S. González"/>
+        <s v="Ullah, Abrar"/>
+        <s v="Hameed, Alaa Ali"/>
         <s v="Metallurgy and Materials Society of CIM, Vol-III-8771048" u="1"/>
         <s v="Metallurgy and Materials Society of CIM Vol-VI-8771051" u="1"/>
         <s v="García-Sánchez, Pedro A." u="1"/>
         <s v="Metallurgy and Materials Society of CIM, Vol-IV-8771049" u="1"/>
         <s v="Xu-Jiuping, MSEM-8771092-Tex" u="1"/>
+        <s v="Ihalanayake, Ranjith" u="1"/>
         <s v="Tortorella-PGMP2-8770424 Error Enrichmenet controller" u="1"/>
         <s v="Metallurgy and Materials Society of CIM, Vol-V-8771050" u="1"/>
         <s v="Bhat, Vijay Kumar" u="1"/>
         <s v="Metallurgy and Materials Society of CIM Vol-VIII-8771060" u="1"/>
         <s v="Metallurgy and Materials Society of CIM, Vol-VII-8771052" u="1"/>
+        <s v="Zawawi, Iskandar Shah Mohd" u="1"/>
         <s v="Metallurgy and Materials Society of CIM, Vol-II-8771047" u="1"/>
         <s v="Metallurgy-MetSoc-Vol-IX-8771159" u="1"/>
+        <s v="PERARNAU-DMD" u="1"/>
         <s v="Metallurgy and Materials Society of CIM, Vol-I-8771046" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Stage" numFmtId="0">
-      <sharedItems containsBlank="1" count="8">
+      <sharedItems containsBlank="1" count="10">
+        <s v="S600"/>
+        <s v="S300"/>
         <s v="S300A"/>
-        <s v="S300"/>
+        <s v="S650A"/>
+        <s v="S650"/>
         <s v="S200"/>
         <s v="S200 Login"/>
+        <s v="S5"/>
         <s v="S50"/>
-        <s v="S5"/>
-        <m/>
-        <s v="S650" u="1"/>
+        <m u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Received Date (S50)" numFmtId="0">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-08-24T00:00:00" maxDate="2026-10-15T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-08-24T00:00:00" maxDate="2026-10-28T00:00:00"/>
     </cacheField>
     <cacheField name="Current TAT (S50 onward)" numFmtId="0">
-      <sharedItems containsDate="1" containsString="0" containsBlank="1" containsMixedTypes="1" minDate="1899-12-31T04:01:03" maxDate="1899-12-31T01:31:04" count="35">
-        <n v="52"/>
+      <sharedItems containsDate="1" containsString="0" containsBlank="1" containsMixedTypes="1" minDate="1899-12-31T04:01:03" maxDate="1900-01-05T09:14:04" count="44">
+        <n v="65"/>
+        <n v="32"/>
+        <n v="35"/>
+        <n v="40"/>
+        <n v="34"/>
+        <n v="28"/>
+        <n v="30"/>
+        <n v="37"/>
         <n v="41"/>
-        <d v="2026-09-26T00:00:00"/>
-        <n v="19"/>
-        <n v="22"/>
-        <n v="27"/>
+        <n v="29"/>
+        <n v="31"/>
         <n v="21"/>
-        <n v="15"/>
-        <n v="17"/>
-        <n v="24"/>
-        <n v="28"/>
         <n v="16"/>
-        <n v="18"/>
-        <n v="8"/>
-        <n v="3"/>
+        <n v="14"/>
+        <n v="11"/>
+        <n v="7"/>
+        <n v="2"/>
         <n v="1"/>
-        <n v="2"/>
         <m/>
         <n v="13" u="1"/>
         <n v="104" u="1"/>
         <n v="38" u="1"/>
         <n v="5" u="1"/>
-        <n v="14" u="1"/>
-        <n v="40" u="1"/>
         <n v="42" u="1"/>
+        <n v="15" u="1"/>
         <n v="44" u="1"/>
         <n v="6" u="1"/>
-        <n v="7" u="1"/>
+        <n v="17" u="1"/>
+        <n v="18" u="1"/>
+        <n v="52" u="1"/>
+        <n v="19" u="1"/>
         <n v="20" u="1"/>
+        <n v="22" u="1"/>
         <n v="23" u="1"/>
+        <n v="3" u="1"/>
+        <n v="8" u="1"/>
+        <d v="2026-09-26T00:00:00" u="1"/>
+        <n v="24" u="1"/>
         <n v="25" u="1"/>
         <n v="26" u="1"/>
+        <n v="27" u="1"/>
         <n v="49" u="1"/>
         <n v="51" u="1"/>
         <n v="12" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="S200 TAT" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="28"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="33"/>
     </cacheField>
     <cacheField name="S300A TAT" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="26"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="33"/>
     </cacheField>
     <cacheField name="S300 TAT" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="2"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
     </cacheField>
     <cacheField name="S600 TAT" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
     </cacheField>
     <cacheField name="S650A TAT" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
     </cacheField>
     <cacheField name="S650 TAT" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Total Chapters" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="6" maxValue="130"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="7" maxValue="135"/>
     </cacheField>
-    <cacheField name="TS Pages" numFmtId="0">
+    <cacheField name="MS Pages" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="100" maxValue="1500"/>
     </cacheField>
     <cacheField name="Status - S200" numFmtId="0">
@@ -3849,13 +4367,13 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Remarks" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems containsBlank="1" longText="1"/>
     </cacheField>
     <cacheField name="Column1" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Plateform" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="25"/>
+      <sharedItems containsBlank="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -3867,7 +4385,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="29">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="34">
   <r>
     <n v="1"/>
     <s v="705744_1_En"/>
@@ -3875,456 +4393,456 @@
     <x v="0"/>
     <d v="2026-08-24T00:00:00"/>
     <x v="0"/>
-    <n v="28"/>
     <n v="26"/>
-    <m/>
-    <m/>
+    <n v="33"/>
+    <n v="2"/>
+    <n v="3"/>
     <m/>
     <m/>
     <n v="32"/>
     <n v="500"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="12 Chaps-Rev.delivered, 19 chaps in Eproof, FM-recept error"/>
-    <s v="GraySci-Template issue resolved on 6-Oct"/>
+    <s v="28 Chaps-Rev.delivered, 3 Part in Eproof, FM-recept error"/>
+    <s v="GraySci-Template issue resolved on 6-Oct.Pls follow Instruction of  Janet provided on 22-Oct. Chap-09- &quot;There are some things that need to be revised: _x000a_1. The keywords for the Pasuruan regency should be Pasuruan Regency. Big R for Regency. _x000a_2. Images on Figures 6 and 7 were reversed; the image on Figure 7 should come first. _x000a_3. The captions on Figure 3.1 should be placed before Figure 1. _x000a_4. The captions on Figure 4.1 should be placed before Figure 13. "/>
     <s v="FM1 receipt error"/>
-    <n v="25"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="2"/>
-    <s v="691371_1_En"/>
+    <s v="696264_1_En"/>
     <x v="1"/>
     <x v="1"/>
-    <d v="2026-09-04T00:00:00"/>
+    <d v="2026-09-26T00:00:00"/>
     <x v="1"/>
-    <n v="22"/>
-    <n v="19"/>
+    <n v="14"/>
+    <n v="14"/>
     <n v="2"/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="14"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <n v="15"/>
     <n v="200"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="10 Chaps S300 revises completed, 3 Chaps in Eproof"/>
-    <m/>
-    <s v="FM1 receipt. Chap-01 query response not recd from Author"/>
-    <n v="12"/>
+    <s v="Delivered on 27th"/>
+    <s v="email sent to PE (MS ISSUE)"/>
+    <s v="Delayed from VE"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="3"/>
-    <s v="696264_1_En"/>
+    <s v="696260_1_En"/>
     <x v="2"/>
-    <x v="0"/>
+    <x v="1"/>
     <d v="2026-09-26T00:00:00"/>
-    <x v="2"/>
-    <n v="13"/>
-    <n v="3"/>
-    <m/>
+    <x v="1"/>
+    <n v="16"/>
+    <n v="10"/>
+    <n v="5"/>
     <m/>
     <m/>
     <m/>
     <n v="15"/>
     <n v="200"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All chaps in Eproof"/>
+    <s v="6 chaps in revises"/>
     <s v="email sent to PE (MS ISSUE)"/>
-    <s v="Delayed from VE"/>
-    <n v="8"/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="4"/>
-    <s v="696260_1_En"/>
+    <s v="695444_1_En"/>
     <x v="3"/>
-    <x v="0"/>
-    <d v="2026-09-26T00:00:00"/>
-    <x v="3"/>
-    <n v="14"/>
-    <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <x v="2"/>
+    <d v="2026-09-23T00:00:00"/>
+    <x v="2"/>
     <n v="15"/>
-    <n v="200"/>
+    <n v="16"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <n v="31"/>
+    <n v="280"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All chaps in Eproof"/>
-    <s v="email sent to PE (MS ISSUE)"/>
-    <m/>
-    <n v="8"/>
+    <s v="S300 completed"/>
+    <s v="PRR Sent on 15th Sep"/>
+    <s v="FM1 receipt error"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="5"/>
-    <s v="695444_1_En"/>
+    <s v="695897_1_En"/>
     <x v="4"/>
-    <x v="0"/>
+    <x v="1"/>
     <d v="2026-09-23T00:00:00"/>
-    <x v="4"/>
-    <n v="16"/>
-    <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="31"/>
-    <n v="280"/>
+    <x v="2"/>
+    <n v="12"/>
+    <n v="13"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="25"/>
+    <n v="240"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All chaps in Eproof"/>
-    <s v="PRR Sent on 15th Sep"/>
-    <m/>
-    <n v="1"/>
+    <s v="20 in revises. FM in S200 comp"/>
+    <s v="PRR Sent on 15th Sep, Job Sheet updated for missing chapters and TOC on 10-Oct"/>
+    <s v="Final Manuscript recd on 20th Oct"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="6"/>
-    <s v="695897_1_En"/>
+    <s v="696258_1_En"/>
     <x v="5"/>
-    <x v="0"/>
-    <d v="2026-09-23T00:00:00"/>
-    <x v="4"/>
-    <n v="2"/>
-    <n v="1"/>
-    <m/>
+    <x v="1"/>
+    <d v="2026-09-18T00:00:00"/>
+    <x v="3"/>
+    <n v="16"/>
+    <n v="16"/>
+    <n v="3"/>
     <m/>
     <m/>
     <m/>
     <n v="25"/>
-    <n v="240"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 01 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="3 chaps Revises completed, 21 Chaps in Eproof"/>
-    <s v="PRR Sent on 15th Sep, Job Sheet updated for missing chapters and TOC on 10-Oct"/>
-    <m/>
-    <n v="8"/>
+    <n v="244"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="13 chaps in Revises, FM in eproof"/>
+    <s v="PRR Sent on 15th Sep, "/>
+    <s v="Chap-04 removed as per author instructions"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="7"/>
-    <s v="696258_1_En"/>
+    <s v="696262_1_En"/>
     <x v="6"/>
-    <x v="0"/>
+    <x v="3"/>
     <d v="2026-09-18T00:00:00"/>
-    <x v="5"/>
+    <x v="3"/>
     <n v="16"/>
-    <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="25"/>
-    <n v="244"/>
+    <n v="7"/>
+    <n v="8"/>
+    <n v="4"/>
+    <n v="1"/>
+    <m/>
+    <n v="9"/>
+    <n v="100"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All in eproof"/>
-    <s v="PRR Sent on 15th Sep, "/>
-    <s v="Chap-04 removed as per author instructions"/>
-    <n v="0"/>
+    <m/>
+    <s v="PRR Sent on 15th Sep"/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="8"/>
-    <s v="696262_1_En"/>
+    <s v="695893_1_En"/>
     <x v="7"/>
-    <x v="0"/>
+    <x v="1"/>
     <d v="2026-09-18T00:00:00"/>
-    <x v="5"/>
-    <n v="16"/>
+    <x v="3"/>
+    <n v="18"/>
+    <n v="12"/>
     <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="9"/>
-    <n v="100"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <n v="13"/>
+    <n v="120"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All in eproof"/>
+    <s v="Delivrered"/>
     <s v="PRR Sent on 15th Sep"/>
     <m/>
-    <n v="0"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="9"/>
-    <s v="695893_1_En"/>
+    <s v="696253_1_En"/>
     <x v="8"/>
-    <x v="0"/>
-    <d v="2026-09-18T00:00:00"/>
-    <x v="5"/>
-    <n v="18"/>
+    <x v="1"/>
+    <d v="2026-09-24T00:00:00"/>
+    <x v="4"/>
+    <n v="33"/>
+    <n v="12"/>
     <n v="3"/>
     <m/>
     <m/>
     <m/>
-    <m/>
-    <n v="13"/>
-    <n v="120"/>
+    <n v="37"/>
+    <n v="200"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All in eproof"/>
-    <s v="PRR Sent on 15th Sep"/>
-    <m/>
-    <n v="0"/>
+    <s v="All in revises"/>
+    <s v="Received in Production on 18th Sep (2.50pm)"/>
+    <s v="Delayed from VE"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="10"/>
-    <s v="696253_1_En"/>
+    <s v="696263_1_En"/>
     <x v="9"/>
-    <x v="0"/>
-    <d v="2026-09-24T00:00:00"/>
-    <x v="6"/>
-    <n v="20"/>
-    <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="37"/>
-    <n v="200"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All in Eproofs"/>
-    <s v="Received in Production on 18th Sep (2.50pm)"/>
-    <s v="Delayed from VE"/>
-    <n v="8"/>
+    <x v="2"/>
+    <d v="2026-09-30T00:00:00"/>
+    <x v="5"/>
+    <n v="15"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="78"/>
+    <n v="750"/>
+    <s v="S200 - _x000a_Login :00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="11 chaps in Revises"/>
+    <s v="Query solved on 12-Oct(FM component recd. Autho &amp; Aff missing in chap-60)"/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="11"/>
-    <s v="696263_1_En"/>
+    <s v="708036_1_En"/>
     <x v="10"/>
     <x v="2"/>
-    <d v="2026-09-30T00:00:00"/>
-    <x v="7"/>
-    <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="78"/>
-    <n v="750"/>
-    <s v="S200 - _x000a_Login : 43 Chapters;_x000a_PE : 29 Chapters;_x000a_CE : 49 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <m/>
-    <s v="Query solved on 12-Oct(FM component recd. Autho &amp; Aff missing in chap-60)"/>
-    <m/>
-    <m/>
+    <d v="2026-09-28T00:00:00"/>
+    <x v="6"/>
+    <n v="26"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="81"/>
+    <n v="600"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="25 chap in Revises"/>
+    <s v="PRR sent on 17th Sep"/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="12"/>
-    <s v="708036_1_En"/>
+    <s v="702839_1_En"/>
     <x v="11"/>
-    <x v="2"/>
-    <d v="2026-09-28T00:00:00"/>
-    <x v="8"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="81"/>
-    <n v="600"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 01 Chapters;_x000a_CE : 50 Chapters;_x000a_Comp : 30 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <m/>
-    <s v="PRR sent on 17th Sep"/>
-    <m/>
+    <x v="4"/>
+    <d v="2026-09-21T00:00:00"/>
+    <x v="7"/>
+    <n v="16"/>
+    <n v="21"/>
     <n v="5"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="7"/>
+    <n v="100"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="2 in Eproof rest revises completed"/>
+    <s v="PRR sent on 17th Sep. Query-Reference missing and content mismatch, One new manuscript approval"/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="13"/>
-    <s v="702839_1_En"/>
+    <s v="704353_1_En"/>
     <x v="12"/>
-    <x v="0"/>
-    <d v="2026-09-21T00:00:00"/>
-    <x v="9"/>
-    <n v="16"/>
-    <n v="8"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="7"/>
-    <n v="100"/>
+    <x v="3"/>
+    <d v="2026-09-17T00:00:00"/>
+    <x v="8"/>
+    <n v="19"/>
+    <n v="13"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <m/>
+    <n v="41"/>
+    <n v="500"/>
     <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="All in Eproof, FM receipt error"/>
-    <s v="PRR sent on 17th Sep. Query-Reference missing and content mismatch"/>
-    <m/>
-    <n v="0"/>
+    <m/>
+    <s v="PRR sent on 17th Sep"/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="14"/>
-    <s v="704353_1_En"/>
+    <s v="708652_1_En"/>
     <x v="13"/>
-    <x v="0"/>
-    <d v="2026-09-17T00:00:00"/>
-    <x v="10"/>
-    <n v="19"/>
-    <n v="7"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="41"/>
+    <x v="5"/>
+    <d v="2026-09-29T00:00:00"/>
+    <x v="9"/>
+    <n v="25"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="36"/>
     <n v="500"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="21 Chaps in Eproof, 11 Chaps in revises, 6 chaps in Mastercopy, 3 chaps revs complted."/>
-    <s v="PRR sent on 17th Sep"/>
-    <m/>
-    <m/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 15 Chapters;_x000a_CE : 21 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="Query will be resolved after 23-oct conferences"/>
+    <s v="Hold for new manuscript solved. Will receive today"/>
+    <m/>
+    <s v="Tex"/>
   </r>
   <r>
     <n v="15"/>
-    <s v="708652_1_En"/>
+    <s v="709492_1_En"/>
     <x v="14"/>
-    <x v="3"/>
-    <d v="2026-09-29T00:00:00"/>
-    <x v="11"/>
-    <n v="12"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="36"/>
+    <x v="2"/>
+    <d v="2026-09-27T00:00:00"/>
+    <x v="10"/>
+    <n v="30"/>
+    <n v="8"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="31"/>
     <n v="500"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <m/>
-    <s v="Hold for new manuscript solved. Will receive today"/>
-    <m/>
-    <m/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE :  00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="16"/>
-    <s v="709492_1_En"/>
+    <s v="704172_1_En"/>
     <x v="15"/>
-    <x v="2"/>
-    <d v="2026-09-27T00:00:00"/>
-    <x v="12"/>
-    <n v="17"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="31"/>
-    <n v="500"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE :  00 Chapters;_x000a_CE : 15 Chapters;_x000a_Comp : 16 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <x v="1"/>
+    <d v="2026-09-26T00:00:00"/>
+    <x v="1"/>
+    <n v="24"/>
+    <n v="5"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="28"/>
+    <n v="350"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="15 Chaps in Revises."/>
+    <m/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="17"/>
-    <s v="704172_1_En"/>
+    <s v="710752_1_En"/>
     <x v="16"/>
-    <x v="2"/>
-    <d v="2026-09-26T00:00:00"/>
-    <x v="3"/>
-    <n v="17"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="28"/>
-    <n v="500"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 1 Chapters;_x000a_Comp : 15 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="12 chap in Eproof"/>
-    <m/>
-    <m/>
-    <m/>
+    <x v="5"/>
+    <d v="2026-10-07T00:00:00"/>
+    <x v="11"/>
+    <n v="7"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="135"/>
+    <n v="1500"/>
+    <s v="S200 - _x000a_Login : 129 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="Query for JS regarding mismatch in chaps. BM is also there"/>
+    <s v="Books should be spilit in Two vol-I and II in S600 stage"/>
+    <m/>
+    <s v="Tex"/>
   </r>
   <r>
     <n v="18"/>
-    <s v="710752_1_En"/>
+    <s v="695571_1_En"/>
     <x v="17"/>
-    <x v="4"/>
-    <d v="2026-10-07T00:00:00"/>
-    <x v="13"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="130"/>
-    <n v="1500"/>
-    <s v="12 chapters missing"/>
-    <s v="Query for JS regarding mismatch in chaps."/>
-    <s v="All tex input; PRR will be sent 05th OCT"/>
-    <m/>
-    <m/>
+    <x v="5"/>
+    <d v="2026-09-30T00:00:00"/>
+    <x v="5"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="48"/>
+    <n v="550"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 13 Chapters;_x000a_Comp : 35 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="Login reinstated, workflow issue solved"/>
+    <m/>
+    <m/>
+    <s v="Tex+word"/>
   </r>
   <r>
     <n v="19"/>
-    <s v="695571_1_En"/>
+    <s v="706742_1_En"/>
     <x v="18"/>
-    <x v="2"/>
+    <x v="5"/>
     <d v="2026-09-30T00:00:00"/>
-    <x v="7"/>
-    <n v="2"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="48"/>
-    <n v="550"/>
-    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 48 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
-    <s v="Login reinstated, workflow issue solved"/>
-    <m/>
-    <m/>
-    <m/>
+    <x v="5"/>
+    <n v="16"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="40"/>
+    <n v="450"/>
+    <s v="S200 - _x000a_Login : 01 Chapters;_x000a_PE : 21 Chapters;_x000a_CE : 18 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <m/>
+    <s v="Query chap 28. figs missing was reced."/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="20"/>
-    <s v="706742_1_En"/>
+    <s v="704411_1_En"/>
     <x v="19"/>
-    <x v="3"/>
-    <d v="2026-09-30T00:00:00"/>
-    <x v="7"/>
-    <n v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="33"/>
-    <n v="450"/>
-    <s v="package awaited for S200 from PE"/>
-    <m/>
-    <s v="Query chap 28. figs missing was reced."/>
-    <m/>
-    <m/>
+    <x v="5"/>
+    <d v="2026-10-12T00:00:00"/>
+    <x v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="30"/>
+    <n v="350"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 30 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <s v="Preface &amp; TOC(FM components missing)"/>
+    <s v="New manuscript recd again and chap-31 added. On 12-Oct26"/>
+    <s v="FM &amp; TOC will be recd in S200 stage"/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="21"/>
-    <s v="704411_1_En"/>
+    <s v="710147_1_En"/>
     <x v="20"/>
-    <x v="4"/>
+    <x v="5"/>
     <d v="2026-10-12T00:00:00"/>
-    <x v="14"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="30"/>
-    <n v="350"/>
-    <s v="HOLD"/>
-    <m/>
-    <s v="New manuscript recd again and chap-31 added. On 12-Oct26"/>
-    <m/>
-    <m/>
+    <x v="12"/>
+    <n v="9"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="28"/>
+    <n v="500"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 28 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="22"/>
-    <s v="710147_1_En"/>
+    <s v="708159_1_En"/>
     <x v="21"/>
-    <x v="3"/>
-    <d v="2026-10-12T00:00:00"/>
-    <x v="14"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="28"/>
-    <n v="500"/>
-    <s v="package awaited for S200 from PE"/>
+    <x v="5"/>
+    <d v="2026-10-07T00:00:00"/>
+    <x v="11"/>
+    <s v="9"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="36"/>
+    <n v="450"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 00 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 36 Chapters;_x000a_Online Delivery : 00 Chapters"/>
     <m/>
     <m/>
     <m/>
@@ -4332,52 +4850,73 @@
   </r>
   <r>
     <n v="23"/>
-    <s v="708159_1_En"/>
+    <s v="707038_1_En"/>
     <x v="22"/>
-    <x v="3"/>
-    <d v="2026-10-07T00:00:00"/>
+    <x v="5"/>
+    <d v="2026-10-14T00:00:00"/>
     <x v="13"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="30"/>
-    <n v="450"/>
-    <s v="package awaited for S200 from PE"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <n v="6"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="42"/>
+    <n v="500"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 42 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="24"/>
-    <s v="707038_1_En"/>
+    <s v="708552_1_En"/>
     <x v="23"/>
-    <x v="4"/>
-    <d v="2026-10-14T00:00:00"/>
-    <x v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <x v="5"/>
+    <d v="2026-10-17T00:00:00"/>
+    <x v="14"/>
     <n v="6"/>
-    <n v="100"/>
-    <m/>
-    <s v="Package received on 12 oct "/>
-    <m/>
-    <m/>
-    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="23"/>
+    <n v="350"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 23 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
     <n v="25"/>
-    <s v="708552_1_En"/>
+    <s v="700862_1_En"/>
     <x v="24"/>
-    <x v="5"/>
-    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <d v="2026-10-17T00:00:00"/>
+    <x v="14"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="56"/>
+    <n v="300"/>
+    <s v="S200 - _x000a_Login : 47 Chapters;_x000a_PE : 09 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Tex"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <s v="713085_1_En"/>
+    <x v="25"/>
+    <x v="6"/>
+    <d v="2026-10-21T00:00:00"/>
     <x v="15"/>
     <m/>
     <m/>
@@ -4385,7 +4924,7 @@
     <m/>
     <m/>
     <m/>
-    <n v="23"/>
+    <n v="109"/>
     <n v="350"/>
     <m/>
     <m/>
@@ -4394,53 +4933,53 @@
     <s v="Word"/>
   </r>
   <r>
-    <n v="26"/>
-    <s v="700862_1_En"/>
-    <x v="25"/>
-    <x v="5"/>
-    <d v="2026-10-13T00:00:00"/>
-    <x v="16"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="56"/>
-    <n v="300"/>
-    <m/>
+    <n v="27"/>
+    <s v="710384_1_En"/>
+    <x v="26"/>
+    <x v="6"/>
+    <d v="2026-10-21T00:00:00"/>
+    <x v="15"/>
+    <n v="3"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="69"/>
+    <n v="400"/>
+    <s v="S200 - _x000a_Login : 36 Chapters;_x000a_PE : 33 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
     <m/>
     <m/>
     <m/>
     <s v="Tex"/>
   </r>
   <r>
-    <n v="27"/>
-    <s v="713085_1_En"/>
-    <x v="26"/>
+    <n v="28"/>
+    <s v="713564_1_En"/>
+    <x v="27"/>
     <x v="5"/>
-    <d v="2026-10-14T00:00:00"/>
-    <x v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="109"/>
-    <n v="350"/>
-    <m/>
+    <d v="2026-10-17T00:00:00"/>
+    <x v="14"/>
+    <n v="6"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="33"/>
+    <n v="450"/>
+    <s v="S200 - _x000a_Login : 00 Chapters;_x000a_PE : 33 Chapters;_x000a_CE : 00 Chapters;_x000a_Comp : 00 Chapters;_x000a_Online Delivery : 00 Chapters"/>
     <m/>
     <m/>
     <m/>
     <s v="Word"/>
   </r>
   <r>
-    <n v="28"/>
-    <s v="710384_1_En"/>
-    <x v="27"/>
-    <x v="5"/>
-    <d v="2026-10-14T00:00:00"/>
+    <n v="29"/>
+    <s v="717901_1_En"/>
+    <x v="28"/>
+    <x v="7"/>
+    <d v="2026-10-21T00:00:00"/>
     <x v="15"/>
     <m/>
     <m/>
@@ -4448,21 +4987,105 @@
     <m/>
     <m/>
     <m/>
-    <n v="69"/>
-    <n v="400"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <s v="Tex"/>
+    <n v="21"/>
+    <n v="150"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
   </r>
   <r>
-    <n v="29"/>
-    <s v="713564_1_En"/>
-    <x v="28"/>
-    <x v="6"/>
-    <m/>
+    <n v="30"/>
+    <s v="701850_1_En"/>
+    <x v="29"/>
+    <x v="7"/>
+    <d v="2026-10-26T00:00:00"/>
+    <x v="16"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="12"/>
+    <n v="150"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <s v="704476_1_En"/>
+    <x v="30"/>
+    <x v="7"/>
+    <d v="2026-10-27T00:00:00"/>
     <x v="17"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="20"/>
+    <n v="450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <s v="704485_1_En"/>
+    <x v="31"/>
+    <x v="8"/>
+    <d v="2026-10-27T00:00:00"/>
+    <x v="17"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="16"/>
+    <n v="200"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Word"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <s v="707996_1_En"/>
+    <x v="32"/>
+    <x v="7"/>
+    <m/>
+    <x v="18"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <s v="697730_1_En"/>
+    <x v="33"/>
+    <x v="7"/>
+    <m/>
+    <x v="18"/>
     <m/>
     <m/>
     <m/>
@@ -4481,46 +5104,47 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
-  <location ref="A3:H17" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="A3:H12" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="42">
+      <items count="50">
+        <item x="11"/>
+        <item m="1" x="42"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="13"/>
         <item x="12"/>
-        <item m="1" x="36"/>
-        <item x="16"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="19"/>
         <item x="21"/>
-        <item x="14"/>
-        <item x="13"/>
-        <item x="24"/>
-        <item x="18"/>
-        <item x="20"/>
-        <item x="22"/>
-        <item m="1" x="30"/>
+        <item m="1" x="35"/>
+        <item m="1" x="43"/>
+        <item m="1" x="49"/>
+        <item m="1" x="46"/>
+        <item m="1" x="34"/>
         <item m="1" x="37"/>
         <item m="1" x="41"/>
+        <item m="1" x="44"/>
+        <item m="1" x="47"/>
+        <item x="18"/>
+        <item x="0"/>
+        <item x="22"/>
+        <item m="1" x="40"/>
+        <item x="14"/>
+        <item m="1" x="38"/>
+        <item m="1" x="45"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item m="1" x="36"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item m="1" x="48"/>
         <item m="1" x="39"/>
-        <item m="1" x="29"/>
-        <item m="1" x="32"/>
-        <item m="1" x="35"/>
-        <item m="1" x="38"/>
-        <item m="1" x="40"/>
-        <item x="19"/>
-        <item x="0"/>
-        <item x="23"/>
-        <item m="1" x="34"/>
-        <item x="15"/>
-        <item m="1" x="33"/>
         <item x="1"/>
-        <item x="11"/>
-        <item x="17"/>
-        <item m="1" x="31"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="25"/>
-        <item x="28"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
@@ -4529,59 +5153,77 @@
         <item x="7"/>
         <item x="8"/>
         <item x="9"/>
-        <item x="10"/>
+        <item x="24"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="8">
+      <items count="10">
+        <item h="1" x="5"/>
+        <item x="1"/>
         <item h="1" x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item h="1" x="5"/>
+        <item h="1" x="7"/>
+        <item h="1" x="8"/>
         <item h="1" x="4"/>
-        <item h="1" m="1" x="7"/>
+        <item h="1" m="1" x="9"/>
         <item h="1" x="6"/>
+        <item h="1" x="0"/>
         <item h="1" x="3"/>
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="35">
-        <item x="14"/>
+      <items count="44">
+        <item m="1" x="34"/>
+        <item m="1" x="22"/>
+        <item m="1" x="26"/>
+        <item m="1" x="43"/>
+        <item m="1" x="19"/>
+        <item x="13"/>
+        <item m="1" x="24"/>
+        <item x="12"/>
+        <item m="1" x="28"/>
+        <item m="1" x="30"/>
+        <item x="11"/>
+        <item m="1" x="37"/>
+        <item m="1" x="38"/>
         <item m="1" x="21"/>
-        <item m="1" x="26"/>
-        <item m="1" x="34"/>
-        <item m="1" x="18"/>
-        <item m="1" x="22"/>
-        <item x="7"/>
-        <item x="11"/>
-        <item x="12"/>
+        <item m="1" x="23"/>
+        <item m="1" x="41"/>
+        <item m="1" x="20"/>
+        <item x="18"/>
+        <item m="1" x="42"/>
+        <item m="1" x="25"/>
         <item x="3"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item m="1" x="30"/>
-        <item m="1" x="20"/>
-        <item m="1" x="24"/>
+        <item m="1" x="39"/>
+        <item m="1" x="31"/>
+        <item m="1" x="33"/>
+        <item m="1" x="40"/>
+        <item m="1" x="27"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item m="1" x="29"/>
+        <item x="8"/>
         <item m="1" x="32"/>
-        <item m="1" x="19"/>
-        <item x="17"/>
-        <item m="1" x="33"/>
-        <item m="1" x="25"/>
-        <item m="1" x="23"/>
-        <item m="1" x="31"/>
-        <item m="1" x="28"/>
-        <item m="1" x="29"/>
         <item x="5"/>
-        <item x="8"/>
-        <item m="1" x="27"/>
-        <item x="16"/>
-        <item x="15"/>
+        <item m="1" x="35"/>
+        <item m="1" x="36"/>
         <item x="0"/>
         <item x="1"/>
+        <item x="2"/>
         <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="9"/>
         <item x="10"/>
-        <item x="13"/>
-        <item x="2"/>
+        <item x="14"/>
       </items>
     </pivotField>
     <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4603,66 +5245,41 @@
     <field x="3"/>
     <field x="5"/>
   </rowFields>
-  <rowItems count="13">
+  <rowItems count="8">
     <i>
-      <x/>
       <x v="2"/>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x v="2"/>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="20"/>
-      <x v="2"/>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="25"/>
       <x v="1"/>
-      <x v="30"/>
+      <x v="36"/>
     </i>
     <i>
       <x v="33"/>
-      <x v="2"/>
-      <x v="34"/>
+      <x v="1"/>
+      <x v="36"/>
     </i>
     <i>
       <x v="34"/>
-      <x v="2"/>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="35"/>
-      <x v="2"/>
-      <x v="31"/>
+      <x v="1"/>
+      <x v="36"/>
     </i>
     <i>
       <x v="36"/>
-      <x v="2"/>
-      <x v="31"/>
+      <x v="1"/>
+      <x v="37"/>
     </i>
     <i>
       <x v="37"/>
-      <x v="2"/>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="38"/>
-      <x v="2"/>
-      <x v="24"/>
+      <x v="1"/>
+      <x v="20"/>
     </i>
     <i>
       <x v="39"/>
-      <x v="2"/>
-      <x v="24"/>
+      <x v="1"/>
+      <x v="20"/>
     </i>
     <i>
       <x v="40"/>
-      <x v="2"/>
-      <x v="10"/>
+      <x v="1"/>
+      <x v="38"/>
     </i>
     <i t="grand">
       <x/>
@@ -4695,15 +5312,78 @@
     <dataField name="Count of S600 TAT" fld="9" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Count of S650 TAT" fld="11" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="3">
-    <format dxfId="71">
+  <formats count="9">
+    <format dxfId="64">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="70">
+    <format dxfId="65">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
+    <format dxfId="66">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="67">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="68">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
     <format dxfId="69">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="70">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="27"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="71">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="72">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="2" count="1" selected="0">
+            <x v="27"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -4716,28 +5396,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:S34" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
-  <autoFilter ref="A1:S34"/>
-  <tableColumns count="19">
-    <tableColumn id="1" name="S. no" dataDxfId="66"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="65"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="64"/>
-    <tableColumn id="4" name="Stage" dataDxfId="63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T35" totalsRowShown="0" headerRowDxfId="171" dataDxfId="170">
+  <autoFilter ref="A1:T35"/>
+  <tableColumns count="20">
+    <tableColumn id="1" name="S. no" dataDxfId="169"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="168"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="167"/>
+    <tableColumn id="4" name="Stage" dataDxfId="166"/>
     <tableColumn id="5" name="Received Date (S50)"/>
     <tableColumn id="6" name="Current TAT (S50 onward)"/>
-    <tableColumn id="7" name="S200 TAT" dataDxfId="62"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="61"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="60"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="59"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="58"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="57"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="56"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="55"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="54"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="53"/>
-    <tableColumn id="17" name="Remarks" dataDxfId="52"/>
-    <tableColumn id="18" name="Column1" dataDxfId="51"/>
-    <tableColumn id="19" name="Plateform" dataDxfId="50"/>
+    <tableColumn id="7" name="S200 TAT" dataDxfId="165"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="164"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="163"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="162"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="161"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="160"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="159"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="158"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="157"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="156"/>
+    <tableColumn id="17" name="Remarks" dataDxfId="155"/>
+    <tableColumn id="18" name="Column1" dataDxfId="154"/>
+    <tableColumn id="19" name="Plateform" dataDxfId="153"/>
+    <tableColumn id="20" name="Column2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4746,32 +5427,32 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
   <tableColumns count="19">
-    <tableColumn id="1" name="S. no" dataDxfId="49"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="48"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="47"/>
-    <tableColumn id="4" name="Stage" dataDxfId="46"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="45"/>
-    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="44"/>
-    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="43"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="42"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="41"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="40"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="39"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="38"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="37"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="36"/>
-    <tableColumn id="19" name="TS Pages" dataDxfId="35"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="34"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="33"/>
-    <tableColumn id="17" name="Delivered Date " dataDxfId="32"/>
-    <tableColumn id="18" name="Remarks" dataDxfId="31"/>
+    <tableColumn id="1" name="S. no" dataDxfId="152"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="151"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="150"/>
+    <tableColumn id="4" name="Stage" dataDxfId="149"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="148"/>
+    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="147"/>
+    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="146"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="145"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="144"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="143"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="142"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="141"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="140"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="139"/>
+    <tableColumn id="19" name="TS Pages" dataDxfId="138"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="137"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="136"/>
+    <tableColumn id="17" name="Delivered Date " dataDxfId="135"/>
+    <tableColumn id="18" name="Remarks" dataDxfId="134"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="133" tableBorderDxfId="132" totalsRowBorderDxfId="131">
   <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="1" name="DESCriptions"/>
@@ -4783,11 +5464,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="130" dataDxfId="128" headerRowBorderDxfId="129" tableBorderDxfId="127" totalsRowBorderDxfId="126">
   <autoFilter ref="B5:C10"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Month" dataDxfId="22"/>
-    <tableColumn id="2" name="No of titles delivered" dataDxfId="21">
+    <tableColumn id="1" name="Month" dataDxfId="125"/>
+    <tableColumn id="2" name="No of titles delivered" dataDxfId="124">
       <calculatedColumnFormula>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5059,7 +5740,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A3:H34"/>
+  <dimension ref="A3:H39"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="29.1796875" customWidth="1"/>
@@ -5084,7 +5765,7 @@
       <c r="B4" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="191" t="s">
+      <c r="C4" s="179" t="s">
         <v>46</v>
       </c>
       <c r="D4" t="s">
@@ -5105,13 +5786,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="C5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D5" s="90">
         <v>1</v>
@@ -5119,19 +5800,21 @@
       <c r="E5" s="90">
         <v>1</v>
       </c>
-      <c r="F5" s="90"/>
+      <c r="F5" s="90">
+        <v>1</v>
+      </c>
       <c r="G5" s="90"/>
       <c r="H5" s="90"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="90">
         <v>1</v>
@@ -5139,19 +5822,23 @@
       <c r="E6" s="90">
         <v>1</v>
       </c>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
+      <c r="F6" s="90">
+        <v>1</v>
+      </c>
+      <c r="G6" s="90">
+        <v>1</v>
+      </c>
       <c r="H6" s="90"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="C7">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D7" s="90">
         <v>1</v>
@@ -5159,19 +5846,21 @@
       <c r="E7" s="90">
         <v>1</v>
       </c>
-      <c r="F7" s="90"/>
+      <c r="F7" s="90">
+        <v>1</v>
+      </c>
       <c r="G7" s="90"/>
       <c r="H7" s="90"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
         <v>137</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D8" s="90">
         <v>1</v>
@@ -5187,13 +5876,13 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="190">
-        <v>46291</v>
+        <v>137</v>
+      </c>
+      <c r="C9">
+        <v>40</v>
       </c>
       <c r="D9" s="90">
         <v>1</v>
@@ -5201,19 +5890,21 @@
       <c r="E9" s="90">
         <v>1</v>
       </c>
-      <c r="F9" s="90"/>
+      <c r="F9" s="90">
+        <v>1</v>
+      </c>
       <c r="G9" s="90"/>
       <c r="H9" s="90"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="C10">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D10" s="90">
         <v>1</v>
@@ -5221,19 +5912,23 @@
       <c r="E10" s="90">
         <v>1</v>
       </c>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
+      <c r="F10" s="90">
+        <v>1</v>
+      </c>
+      <c r="G10" s="90">
+        <v>1</v>
+      </c>
       <c r="H10" s="90"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D11" s="90">
         <v>1</v>
@@ -5241,170 +5936,89 @@
       <c r="E11" s="90">
         <v>1</v>
       </c>
-      <c r="F11" s="90"/>
+      <c r="F11" s="90">
+        <v>1</v>
+      </c>
       <c r="G11" s="90"/>
       <c r="H11" s="90"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12">
-        <v>22</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C12"/>
       <c r="D12" s="90">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E12" s="90">
-        <v>1</v>
-      </c>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
+        <v>7</v>
+      </c>
+      <c r="F12" s="90">
+        <v>7</v>
+      </c>
+      <c r="G12" s="90">
+        <v>2</v>
+      </c>
       <c r="H12" s="90"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13">
-        <v>27</v>
-      </c>
-      <c r="D13" s="90">
-        <v>1</v>
-      </c>
-      <c r="E13" s="90">
-        <v>1</v>
-      </c>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90"/>
+      <c r="C13"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14">
-        <v>27</v>
-      </c>
-      <c r="D14" s="90">
-        <v>1</v>
-      </c>
-      <c r="E14" s="90">
-        <v>1</v>
-      </c>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
+      <c r="C14"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15">
-        <v>27</v>
-      </c>
-      <c r="D15" s="90">
-        <v>1</v>
-      </c>
-      <c r="E15" s="90">
-        <v>1</v>
-      </c>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
+      <c r="C15"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16">
-        <v>21</v>
-      </c>
-      <c r="D16" s="90">
-        <v>1</v>
-      </c>
-      <c r="E16" s="90">
-        <v>1</v>
-      </c>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>142</v>
-      </c>
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="3:3">
       <c r="C17"/>
-      <c r="D17" s="90">
-        <v>12</v>
-      </c>
-      <c r="E17" s="90">
-        <v>12</v>
-      </c>
-      <c r="F17" s="90">
-        <v>1</v>
-      </c>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-    </row>
-    <row r="18" spans="1:8">
+    </row>
+    <row r="18" spans="3:3">
       <c r="C18"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="3:3">
       <c r="C19"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="3:3">
       <c r="C20"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="3:3">
       <c r="C21"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="3:3">
       <c r="C22"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="3:3">
       <c r="C23"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="3:3">
       <c r="C24"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="3:3">
       <c r="C25"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="3:3">
       <c r="C26"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="3:3">
       <c r="C27"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="3:3">
       <c r="C28"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="3:3">
       <c r="C29"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="3:3">
       <c r="C30"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="3:3">
       <c r="C31"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="3:3">
       <c r="C32"/>
     </row>
     <row r="33" spans="3:3">
@@ -5412,6 +6026,21 @@
     </row>
     <row r="34" spans="3:3">
       <c r="C34"/>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35"/>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36"/>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37"/>
+    </row>
+    <row r="38" spans="3:3">
+      <c r="C38"/>
+    </row>
+    <row r="39" spans="3:3">
+      <c r="C39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5421,7 +6050,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" style="50" customWidth="1"/>
@@ -5445,7 +6074,7 @@
     <col min="20" max="16384" width="15.81640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" thickBot="1">
+    <row r="1" spans="1:20" ht="15" thickBot="1">
       <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
@@ -5486,7 +6115,7 @@
         <v>53</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="O1" s="27" t="s">
         <v>55</v>
@@ -5503,8 +6132,11 @@
       <c r="S1" s="26" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="240">
+      <c r="T1" s="204" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="240">
       <c r="A2" s="52">
         <f t="shared" ref="A2:A10" si="0">ROW()-1</f>
         <v>1</v>
@@ -5516,14 +6148,14 @@
         <v>18</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E2" s="53">
         <v>46258</v>
       </c>
       <c r="F2" s="88">
         <f ca="1">TODAY()-E2</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" s="52">
         <f>DATE(2026,9,19)-DATE(2026,8,24)</f>
@@ -5539,7 +6171,7 @@
       </c>
       <c r="J2" s="33">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="33"/>
       <c r="L2" s="33"/>
@@ -5553,19 +6185,20 @@
         <v>69</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q2" s="153" t="s">
-        <v>200</v>
+        <v>202</v>
+      </c>
+      <c r="Q2" s="150" t="s">
+        <v>195</v>
       </c>
       <c r="R2" s="105" t="s">
         <v>101</v>
       </c>
       <c r="S2" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T2" s="203"/>
+    </row>
+    <row r="3" spans="1:20" ht="60">
       <c r="A3" s="52">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -5573,8 +6206,8 @@
       <c r="B3" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="57" t="s">
-        <v>173</v>
+      <c r="C3" s="200" t="s">
+        <v>171</v>
       </c>
       <c r="D3" s="58" t="s">
         <v>137</v>
@@ -5584,7 +6217,7 @@
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F8" ca="1" si="1">TODAY()-E3</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="33">
         <f>DATE(2026,10,10)-DATE(2026,9,26)</f>
@@ -5595,10 +6228,13 @@
         <v>14</v>
       </c>
       <c r="I3" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
+        <f>DATE(2026,10,27)-DATE(2026,10,25)</f>
         <v>2</v>
       </c>
-      <c r="J3" s="54"/>
+      <c r="J3" s="54">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="K3" s="26"/>
       <c r="L3" s="26"/>
       <c r="M3" s="33">
@@ -5611,19 +6247,20 @@
         <v>69</v>
       </c>
       <c r="P3" s="113" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q3" s="154" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q3" s="151" t="s">
         <v>74</v>
       </c>
-      <c r="R3" s="160" t="s">
+      <c r="R3" s="157" t="s">
         <v>100</v>
       </c>
       <c r="S3" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T3" s="176"/>
+    </row>
+    <row r="4" spans="1:20" ht="60">
       <c r="A4" s="52">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -5631,28 +6268,31 @@
       <c r="B4" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>174</v>
+      <c r="C4" s="199" t="s">
+        <v>172</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="E4" s="35">
         <v>46291</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="33">
         <f>DATE(2026,10,12)-DATE(2026,9,26)</f>
         <v>16</v>
       </c>
       <c r="H4" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>15</v>
-      </c>
-      <c r="I4" s="104"/>
+        <f>DATE(2026,10,22)-DATE(2026,10,12)</f>
+        <v>10</v>
+      </c>
+      <c r="I4" s="104">
+        <f>DATE(2026,10,28)-DATE(2026,10,23)</f>
+        <v>5</v>
+      </c>
       <c r="J4" s="104"/>
       <c r="K4" s="104"/>
       <c r="L4" s="104"/>
@@ -5666,17 +6306,18 @@
         <v>69</v>
       </c>
       <c r="P4" s="113" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q4" s="154" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q4" s="151" t="s">
         <v>74</v>
       </c>
       <c r="R4" s="105"/>
       <c r="S4" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T4" s="176"/>
+    </row>
+    <row r="5" spans="1:20" ht="60">
       <c r="A5" s="52">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5685,17 +6326,17 @@
         <v>25</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="E5" s="35">
         <v>46288</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="68">
         <f>DATE(2026,10,8)-DATE(2026,9,23)</f>
@@ -5711,7 +6352,7 @@
       </c>
       <c r="J5" s="54">
         <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="54"/>
       <c r="L5" s="54"/>
@@ -5725,19 +6366,20 @@
         <v>69</v>
       </c>
       <c r="P5" s="113" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q5" s="154" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q5" s="151" t="s">
         <v>73</v>
       </c>
       <c r="R5" s="105" t="s">
         <v>101</v>
       </c>
       <c r="S5" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T5" s="176"/>
+    </row>
+    <row r="6" spans="1:20" ht="60">
       <c r="A6" s="52">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -5745,28 +6387,31 @@
       <c r="B6" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>176</v>
+      <c r="C6" s="199" t="s">
+        <v>174</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="E6" s="35">
         <v>46288</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="G6" s="104">
-        <f>DATE(2026,10,14)-DATE(2026,10,12)</f>
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="G6" s="193">
+        <f>DATE(2026,10,14)-DATE(2026,10,2)</f>
+        <v>12</v>
       </c>
       <c r="H6" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,14)</f>
+        <f>DATE(2026,10,27)-DATE(2026,10,14)</f>
         <v>13</v>
       </c>
-      <c r="I6" s="104"/>
+      <c r="I6" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="J6" s="104"/>
       <c r="K6" s="104"/>
       <c r="L6" s="104"/>
@@ -5780,19 +6425,20 @@
         <v>69</v>
       </c>
       <c r="P6" s="113" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q6" s="154" t="s">
-        <v>155</v>
-      </c>
-      <c r="R6" s="161" t="s">
-        <v>191</v>
+        <v>237</v>
+      </c>
+      <c r="Q6" s="151" t="s">
+        <v>154</v>
+      </c>
+      <c r="R6" s="158" t="s">
+        <v>187</v>
       </c>
       <c r="S6" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T6" s="176"/>
+    </row>
+    <row r="7" spans="1:20" ht="60">
       <c r="A7" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5801,7 +6447,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>137</v>
@@ -5811,19 +6457,19 @@
       </c>
       <c r="F7" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="33">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
       <c r="H7" s="54">
-        <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
-        <v>12</v>
-      </c>
-      <c r="I7" s="150">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>2</v>
+        <f>DATE(2026,10,24)-DATE(2026,10,8)</f>
+        <v>16</v>
+      </c>
+      <c r="I7" s="148">
+        <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
+        <v>3</v>
       </c>
       <c r="J7" s="26"/>
       <c r="K7" s="26"/>
@@ -5838,79 +6484,81 @@
         <v>69</v>
       </c>
       <c r="P7" s="113" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q7" s="154" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q7" s="151" t="s">
         <v>128</v>
       </c>
       <c r="R7" s="105" t="s">
         <v>138</v>
       </c>
       <c r="S7" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="149" customFormat="1" ht="60">
-      <c r="A8" s="142">
+        <v>169</v>
+      </c>
+      <c r="T7" s="176"/>
+    </row>
+    <row r="8" spans="1:20" s="147" customFormat="1" ht="60">
+      <c r="A8" s="140">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="143" t="s">
+      <c r="B8" s="141" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="119" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="142" t="s">
-        <v>219</v>
-      </c>
-      <c r="E8" s="144">
+        <v>177</v>
+      </c>
+      <c r="D8" s="140" t="s">
+        <v>208</v>
+      </c>
+      <c r="E8" s="142">
         <v>46283</v>
       </c>
-      <c r="F8" s="142">
+      <c r="F8" s="140">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="G8" s="142">
+        <v>40</v>
+      </c>
+      <c r="G8" s="140">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H8" s="145">
+      <c r="H8" s="143">
         <f>DATE(2026,10,19)-DATE(2026,10,12)</f>
         <v>7</v>
       </c>
-      <c r="I8" s="145">
+      <c r="I8" s="143">
         <f ca="1">TODAY()-DATE(2026,10,20)</f>
-        <v>7</v>
-      </c>
-      <c r="J8" s="145">
+        <v>8</v>
+      </c>
+      <c r="J8" s="143">
         <f>DATE(2026,10,26)-DATE(2026,10,22)</f>
         <v>4</v>
       </c>
-      <c r="K8" s="146">
+      <c r="K8" s="143">
         <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="146"/>
-      <c r="M8" s="142">
+        <v>1</v>
+      </c>
+      <c r="L8" s="144"/>
+      <c r="M8" s="140">
         <v>9</v>
       </c>
-      <c r="N8" s="142">
+      <c r="N8" s="140">
         <v>100</v>
       </c>
-      <c r="O8" s="147" t="s">
+      <c r="O8" s="145" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="148"/>
-      <c r="Q8" s="155" t="s">
+      <c r="P8" s="146"/>
+      <c r="Q8" s="152" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="146"/>
-      <c r="S8" s="146" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="60">
+      <c r="R8" s="144"/>
+      <c r="S8" s="144" t="s">
+        <v>169</v>
+      </c>
+      <c r="T8" s="176"/>
+    </row>
+    <row r="9" spans="1:20" ht="60">
       <c r="A9" s="33">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5919,17 +6567,17 @@
         <v>23</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="E9" s="35">
         <v>46283</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" ref="F9:F19" ca="1" si="2">TODAY()-E9</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="33">
         <f>DATE(2026,10,9)-DATE(2026,9,21)</f>
@@ -5939,11 +6587,14 @@
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I9" s="150">
-        <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>2</v>
-      </c>
-      <c r="J9" s="105"/>
+      <c r="I9" s="148">
+        <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
+        <v>3</v>
+      </c>
+      <c r="J9" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="K9" s="105"/>
       <c r="L9" s="105"/>
       <c r="M9" s="33">
@@ -5956,17 +6607,18 @@
         <v>69</v>
       </c>
       <c r="P9" s="113" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q9" s="154" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q9" s="151" t="s">
         <v>73</v>
       </c>
       <c r="R9" s="105"/>
       <c r="S9" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T9" s="176"/>
+    </row>
+    <row r="10" spans="1:20" ht="60">
       <c r="A10" s="52">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5974,8 +6626,8 @@
       <c r="B10" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="57" t="s">
-        <v>180</v>
+      <c r="C10" s="200" t="s">
+        <v>178</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>137</v>
@@ -5985,19 +6637,19 @@
       </c>
       <c r="F10" s="58">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" s="33">
         <f ca="1">TODAY()-DATE(2026,9,25)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10" s="54">
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I10" s="150">
+      <c r="I10" s="148">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="105"/>
       <c r="K10" s="105"/>
@@ -6012,19 +6664,20 @@
         <v>69</v>
       </c>
       <c r="P10" s="113" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q10" s="154" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q10" s="151" t="s">
         <v>75</v>
       </c>
-      <c r="R10" s="160" t="s">
+      <c r="R10" s="157" t="s">
         <v>100</v>
       </c>
       <c r="S10" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T10" s="176"/>
+    </row>
+    <row r="11" spans="1:20" ht="60">
       <c r="A11" s="52">
         <f t="shared" ref="A11" si="3">ROW()-1</f>
         <v>10</v>
@@ -6032,24 +6685,27 @@
       <c r="B11" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="34" t="s">
-        <v>181</v>
+      <c r="C11" s="199" t="s">
+        <v>179</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="E11" s="35">
         <v>46295</v>
       </c>
       <c r="F11" s="8">
         <f ca="1">TODAY()-E11</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G11" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,12)</f>
+        <f>DATE(2026,10,27)-DATE(2026,10,12)</f>
         <v>15</v>
       </c>
-      <c r="H11" s="105"/>
+      <c r="H11" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="I11" s="105"/>
       <c r="J11" s="105"/>
       <c r="K11" s="105"/>
@@ -6061,28 +6717,29 @@
         <v>750</v>
       </c>
       <c r="O11" s="114" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="P11" s="113" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q11" s="154" t="s">
-        <v>167</v>
+        <v>240</v>
+      </c>
+      <c r="Q11" s="151" t="s">
+        <v>166</v>
       </c>
       <c r="R11" s="105"/>
       <c r="S11" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T11" s="176"/>
+    </row>
+    <row r="12" spans="1:20" ht="60">
       <c r="A12" s="52">
-        <f t="shared" ref="A12:A34" si="4">ROW()-1</f>
+        <f t="shared" ref="A12:A35" si="4">ROW()-1</f>
         <v>11</v>
       </c>
       <c r="B12" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="199" t="s">
         <v>113</v>
       </c>
       <c r="D12" s="33" t="s">
@@ -6093,17 +6750,17 @@
       </c>
       <c r="F12" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="104">
-        <f>DATE(2026,10,26)-DATE(2026,9,30)</f>
-        <v>26</v>
+        <f>DATE(2026,10,21)-DATE(2026,9,30)</f>
+        <v>21</v>
       </c>
       <c r="H12" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="105"/>
+        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <v>2</v>
+      </c>
+      <c r="I12" s="104"/>
       <c r="J12" s="105"/>
       <c r="K12" s="105"/>
       <c r="L12" s="105"/>
@@ -6114,20 +6771,21 @@
         <v>600</v>
       </c>
       <c r="O12" s="114" t="s">
-        <v>227</v>
+        <v>69</v>
       </c>
       <c r="P12" s="113" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q12" s="154" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q12" s="151" t="s">
         <v>76</v>
       </c>
       <c r="R12" s="105"/>
       <c r="S12" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T12" s="176"/>
+    </row>
+    <row r="13" spans="1:20" ht="60">
       <c r="A13" s="52">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -6139,14 +6797,14 @@
         <v>34</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>219</v>
+        <v>45</v>
       </c>
       <c r="E13" s="35">
         <v>46286</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="33">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
@@ -6154,21 +6812,24 @@
       </c>
       <c r="H13" s="107">
         <f ca="1">TODAY()-DATE(2026,10,7)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" s="107">
         <f ca="1">TODAY()-DATE(2026,10,23)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" s="107">
         <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
         <v>1</v>
       </c>
       <c r="K13" s="107">
-        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <f>DATE(2026,10,27)-DATE(2026,10,26)</f>
         <v>1</v>
       </c>
-      <c r="L13" s="105"/>
+      <c r="L13" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="M13" s="33">
         <v>7</v>
       </c>
@@ -6179,17 +6840,18 @@
         <v>69</v>
       </c>
       <c r="P13" s="113" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q13" s="154" t="s">
-        <v>205</v>
+        <v>190</v>
+      </c>
+      <c r="Q13" s="151" t="s">
+        <v>200</v>
       </c>
       <c r="R13" s="105"/>
       <c r="S13" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T13" s="176"/>
+    </row>
+    <row r="14" spans="1:20" ht="60">
       <c r="A14" s="52">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -6201,14 +6863,14 @@
         <v>36</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E14" s="35">
         <v>46282</v>
       </c>
       <c r="F14" s="33">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" s="33">
         <f>DATE(2026,10,6)-DATE(2026,9,17)</f>
@@ -6222,13 +6884,13 @@
         <f>DATE(2026,10,22)-DATE(2026,10,21)</f>
         <v>1</v>
       </c>
-      <c r="J14" s="141">
+      <c r="J14" s="139">
         <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
         <v>1</v>
       </c>
       <c r="K14" s="107">
         <f ca="1">TODAY()-DATE(2026,10,26)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="108"/>
       <c r="M14" s="33">
@@ -6241,26 +6903,27 @@
         <v>69</v>
       </c>
       <c r="P14" s="113"/>
-      <c r="Q14" s="156" t="s">
+      <c r="Q14" s="153" t="s">
         <v>76</v>
       </c>
       <c r="R14" s="105"/>
       <c r="S14" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T14" s="176"/>
+    </row>
+    <row r="15" spans="1:20" ht="60">
       <c r="A15" s="52">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="B15" s="163" t="s">
+      <c r="B15" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="164" t="s">
+      <c r="C15" s="199" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="165" t="s">
+      <c r="D15" s="33" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="35">
@@ -6268,11 +6931,11 @@
       </c>
       <c r="F15" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" s="104">
         <f ca="1">TODAY()-DATE(2026,10,3)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H15" s="105"/>
       <c r="I15" s="105"/>
@@ -6286,20 +6949,21 @@
         <v>500</v>
       </c>
       <c r="O15" s="114" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="P15" s="113" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q15" s="154" t="s">
-        <v>164</v>
+        <v>184</v>
+      </c>
+      <c r="Q15" s="151" t="s">
+        <v>163</v>
       </c>
       <c r="R15" s="105"/>
       <c r="S15" s="105" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="60">
+        <v>168</v>
+      </c>
+      <c r="T15" s="176"/>
+    </row>
+    <row r="16" spans="1:20" ht="60">
       <c r="A16" s="52">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -6307,7 +6971,7 @@
       <c r="B16" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="199" t="s">
         <v>96</v>
       </c>
       <c r="D16" s="33" t="s">
@@ -6318,17 +6982,20 @@
       </c>
       <c r="F16" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="G16" s="52">
-        <f ca="1">TODAY()-DATE(2026,9,28)</f>
+        <v>31</v>
+      </c>
+      <c r="G16" s="104">
+        <f>DATE(2026,10,27)-DATE(2026,9,28)</f>
         <v>29</v>
       </c>
       <c r="H16" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,19)</f>
-        <v>8</v>
-      </c>
-      <c r="I16" s="105"/>
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="J16" s="105"/>
       <c r="K16" s="105"/>
       <c r="L16" s="105"/>
@@ -6339,18 +7006,19 @@
         <v>500</v>
       </c>
       <c r="O16" s="114" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="P16" s="113" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q16" s="154"/>
+        <v>255</v>
+      </c>
+      <c r="Q16" s="151"/>
       <c r="R16" s="105"/>
       <c r="S16" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T16" s="176"/>
+    </row>
+    <row r="17" spans="1:20" ht="60">
       <c r="A17" s="52">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -6362,24 +7030,27 @@
         <v>102</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="E17" s="35">
         <v>46291</v>
       </c>
       <c r="F17" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" s="52">
         <f>DATE(2026,10,22)-DATE(2026,9,28)</f>
         <v>24</v>
       </c>
       <c r="H17" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,22)</f>
+        <f>DATE(2026,10,27)-DATE(2026,10,22)</f>
         <v>5</v>
       </c>
-      <c r="I17" s="105"/>
+      <c r="I17" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="J17" s="105"/>
       <c r="K17" s="105"/>
       <c r="L17" s="105"/>
@@ -6387,21 +7058,22 @@
         <v>28</v>
       </c>
       <c r="N17" s="104">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="O17" s="117" t="s">
         <v>69</v>
       </c>
       <c r="P17" s="116" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q17" s="156"/>
+        <v>244</v>
+      </c>
+      <c r="Q17" s="153"/>
       <c r="R17" s="105"/>
       <c r="S17" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T17" s="176"/>
+    </row>
+    <row r="18" spans="1:20" ht="60">
       <c r="A18" s="52">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -6409,10 +7081,10 @@
       <c r="B18" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="166" t="s">
-        <v>158</v>
-      </c>
-      <c r="D18" s="167" t="s">
+      <c r="C18" s="202" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E18" s="35">
@@ -6420,11 +7092,11 @@
       </c>
       <c r="F18" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="87">
         <f ca="1">TODAY()-DATE(2026,10,21)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="105"/>
       <c r="I18" s="105"/>
@@ -6439,31 +7111,32 @@
         <v>1500</v>
       </c>
       <c r="O18" s="117" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="P18" s="113" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q18" s="157" t="s">
-        <v>192</v>
+        <v>256</v>
+      </c>
+      <c r="Q18" s="154" t="s">
+        <v>188</v>
       </c>
       <c r="R18" s="105"/>
       <c r="S18" s="105" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="33.5" customHeight="1">
+        <v>168</v>
+      </c>
+      <c r="T18" s="176"/>
+    </row>
+    <row r="19" spans="1:20" ht="33.5" customHeight="1">
       <c r="A19" s="52">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="B19" s="162" t="s">
+      <c r="B19" s="159" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="164" t="s">
+      <c r="C19" s="201" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="167" t="s">
+      <c r="D19" s="163" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="35">
@@ -6471,11 +7144,11 @@
       </c>
       <c r="F19" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="106">
         <f ca="1">TODAY()-DATE(2026,10,13)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="105"/>
       <c r="I19" s="105"/>
@@ -6489,29 +7162,30 @@
         <v>550</v>
       </c>
       <c r="O19" s="114" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="P19" s="113" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q19" s="154"/>
+        <v>164</v>
+      </c>
+      <c r="Q19" s="151"/>
       <c r="R19" s="105"/>
       <c r="S19" s="105" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="60">
+        <v>183</v>
+      </c>
+      <c r="T19" s="176"/>
+    </row>
+    <row r="20" spans="1:20" ht="60">
       <c r="A20" s="52">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="B20" s="162" t="s">
+      <c r="B20" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="164" t="s">
+      <c r="C20" s="199" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="167" t="s">
+      <c r="D20" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E20" s="35">
@@ -6519,11 +7193,11 @@
       </c>
       <c r="F20" s="8">
         <f t="shared" ref="F20" ca="1" si="5">TODAY()-E20</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G20" s="106">
         <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="105"/>
       <c r="I20" s="105"/>
@@ -6537,18 +7211,19 @@
         <v>450</v>
       </c>
       <c r="O20" s="114" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="P20" s="113"/>
-      <c r="Q20" s="154" t="s">
-        <v>172</v>
+      <c r="Q20" s="151" t="s">
+        <v>170</v>
       </c>
       <c r="R20" s="105"/>
       <c r="S20" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="32.5">
+        <v>169</v>
+      </c>
+      <c r="T20" s="176"/>
+    </row>
+    <row r="21" spans="1:20" ht="85">
       <c r="A21" s="52">
         <f t="shared" si="4"/>
         <v>20</v>
@@ -6560,14 +7235,14 @@
         <v>136</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>214</v>
+        <v>19</v>
       </c>
       <c r="E21" s="35">
         <v>46307</v>
       </c>
       <c r="F21" s="8">
         <f ca="1">TODAY()-E21</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" s="106"/>
       <c r="H21" s="105"/>
@@ -6576,28 +7251,29 @@
       <c r="K21" s="105"/>
       <c r="L21" s="105"/>
       <c r="M21" s="33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N21" s="104">
         <v>350</v>
       </c>
-      <c r="O21" s="113" t="s">
-        <v>171</v>
+      <c r="O21" s="114" t="s">
+        <v>245</v>
       </c>
       <c r="P21" s="113" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q21" s="154" t="s">
-        <v>149</v>
+        <v>257</v>
+      </c>
+      <c r="Q21" s="151" t="s">
+        <v>258</v>
       </c>
       <c r="R21" s="105" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="S21" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T21" s="176"/>
+    </row>
+    <row r="22" spans="1:20" ht="60">
       <c r="A22" s="52">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -6616,15 +7292,15 @@
       </c>
       <c r="F22" s="107">
         <f ca="1">TODAY()-E22</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="104">
         <f ca="1">TODAY()-DATE(2026,10,19)</f>
-        <v>8</v>
-      </c>
-      <c r="H22" s="175"/>
-      <c r="I22" s="175"/>
-      <c r="J22" s="175"/>
+        <v>9</v>
+      </c>
+      <c r="H22" s="170"/>
+      <c r="I22" s="170"/>
+      <c r="J22" s="170"/>
       <c r="K22" s="105"/>
       <c r="L22" s="105"/>
       <c r="M22" s="33">
@@ -6634,16 +7310,17 @@
         <v>500</v>
       </c>
       <c r="O22" s="114" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="P22" s="113"/>
-      <c r="Q22" s="158"/>
+      <c r="Q22" s="155"/>
       <c r="R22" s="105"/>
       <c r="S22" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T22" s="176"/>
+    </row>
+    <row r="23" spans="1:20" ht="60">
       <c r="A23" s="52">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -6651,7 +7328,7 @@
       <c r="B23" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="199" t="s">
         <v>110</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -6660,16 +7337,16 @@
       <c r="E23" s="9">
         <v>46302</v>
       </c>
-      <c r="F23" s="176">
+      <c r="F23" s="171">
         <f ca="1">TODAY()-E23</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" s="104" t="str">
         <f ca="1">TRIM(TODAY()-DATE(2026,10,19))</f>
-        <v>8</v>
-      </c>
-      <c r="H23" s="175"/>
-      <c r="I23" s="175"/>
+        <v>9</v>
+      </c>
+      <c r="H23" s="170"/>
+      <c r="I23" s="170"/>
       <c r="J23" s="105"/>
       <c r="K23" s="105"/>
       <c r="L23" s="105"/>
@@ -6680,19 +7357,20 @@
         <v>450</v>
       </c>
       <c r="O23" s="114" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="P23" s="113"/>
-      <c r="Q23" s="158"/>
+      <c r="Q23" s="155"/>
       <c r="R23" s="105"/>
       <c r="S23" s="105"/>
-    </row>
-    <row r="24" spans="1:19" ht="60">
+      <c r="T23" s="176"/>
+    </row>
+    <row r="24" spans="1:20" ht="60">
       <c r="A24" s="52">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="B24" s="177" t="s">
+      <c r="B24" s="172" t="s">
         <v>129</v>
       </c>
       <c r="C24" s="34" t="s">
@@ -6701,16 +7379,16 @@
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="151">
+      <c r="E24" s="149">
         <v>46309</v>
       </c>
-      <c r="F24" s="176">
+      <c r="F24" s="171">
         <f ca="1">TODAY()-E24</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="104">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="105"/>
       <c r="I24" s="105"/>
@@ -6724,39 +7402,40 @@
         <v>500</v>
       </c>
       <c r="O24" s="114" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="P24" s="113"/>
-      <c r="Q24" s="154"/>
+      <c r="Q24" s="151"/>
       <c r="R24" s="105"/>
       <c r="S24" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T24" s="176"/>
+    </row>
+    <row r="25" spans="1:20" ht="60">
       <c r="A25" s="52">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="B25" s="168" t="s">
+      <c r="B25" s="172" t="s">
         <v>139</v>
       </c>
-      <c r="C25" s="164" t="s">
+      <c r="C25" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="D25" s="167" t="s">
+      <c r="D25" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="151">
+      <c r="E25" s="149">
         <v>46312</v>
       </c>
       <c r="F25" s="110">
         <f ca="1">TODAY()-E25</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="106">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="105"/>
       <c r="I25" s="105"/>
@@ -6770,35 +7449,36 @@
         <v>350</v>
       </c>
       <c r="O25" s="114" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="P25" s="113"/>
-      <c r="Q25" s="154"/>
+      <c r="Q25" s="151"/>
       <c r="R25" s="105"/>
       <c r="S25" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T25" s="176"/>
+    </row>
+    <row r="26" spans="1:20" ht="60">
       <c r="A26" s="52">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="B26" s="178" t="s">
-        <v>157</v>
+      <c r="B26" s="173" t="s">
+        <v>156</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E26" s="111">
         <v>46312</v>
       </c>
       <c r="F26" s="110">
         <f t="shared" ref="F26" ca="1" si="6">TODAY()-E26</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="106"/>
       <c r="H26" s="105"/>
@@ -6809,39 +7489,40 @@
       <c r="M26" s="33">
         <v>56</v>
       </c>
-      <c r="N26" s="106">
+      <c r="N26" s="104">
         <v>300</v>
       </c>
       <c r="O26" s="114" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="P26" s="112"/>
-      <c r="Q26" s="159"/>
+      <c r="Q26" s="156"/>
       <c r="R26" s="105"/>
       <c r="S26" s="105" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
+        <v>168</v>
+      </c>
+      <c r="T26" s="176"/>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27" s="52">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="B27" s="122" t="s">
+      <c r="B27" s="121" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="C27" s="34" t="s">
-        <v>161</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E27" s="111">
         <v>46316</v>
       </c>
       <c r="F27" s="110">
         <f ca="1">TODAY()-E27</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G27" s="106"/>
       <c r="H27" s="105"/>
@@ -6857,39 +7538,40 @@
       </c>
       <c r="O27" s="112"/>
       <c r="P27" s="112"/>
-      <c r="Q27" s="159"/>
+      <c r="Q27" s="156"/>
       <c r="R27" s="105"/>
       <c r="S27" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="60">
+        <v>169</v>
+      </c>
+      <c r="T27" s="176"/>
+    </row>
+    <row r="28" spans="1:20" ht="60">
       <c r="A28" s="52">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="B28" s="122" t="s">
+      <c r="B28" s="121" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="C28" s="34" t="s">
-        <v>163</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="151">
+        <v>158</v>
+      </c>
+      <c r="E28" s="149">
         <v>46316</v>
       </c>
-      <c r="F28" s="176">
+      <c r="F28" s="171">
         <f ca="1">TODAY()-E28</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="104">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>2</v>
-      </c>
-      <c r="H28" s="175"/>
-      <c r="I28" s="175"/>
+        <v>3</v>
+      </c>
+      <c r="H28" s="170"/>
+      <c r="I28" s="170"/>
       <c r="J28" s="105"/>
       <c r="K28" s="105"/>
       <c r="L28" s="120"/>
@@ -6900,71 +7582,73 @@
         <v>400</v>
       </c>
       <c r="O28" s="114" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="P28" s="112"/>
-      <c r="Q28" s="159"/>
+      <c r="Q28" s="156"/>
       <c r="R28" s="105"/>
       <c r="S28" s="105" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="60">
+        <v>168</v>
+      </c>
+      <c r="T28" s="176"/>
+    </row>
+    <row r="29" spans="1:20" ht="60">
       <c r="A29" s="52">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="B29" s="122" t="s">
-        <v>168</v>
+      <c r="B29" s="121" t="s">
+        <v>167</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="151">
+      <c r="E29" s="149">
         <v>46312</v>
       </c>
-      <c r="F29" s="176">
+      <c r="F29" s="171">
         <f ca="1">TODAY()-E29</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" s="104">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>5</v>
-      </c>
-      <c r="H29" s="179"/>
-      <c r="I29" s="180"/>
-      <c r="J29" s="179"/>
-      <c r="K29" s="180"/>
-      <c r="L29" s="180"/>
+        <v>6</v>
+      </c>
+      <c r="H29" s="170"/>
+      <c r="I29" s="196"/>
+      <c r="J29" s="170"/>
+      <c r="K29" s="196"/>
+      <c r="L29" s="196"/>
       <c r="M29" s="33">
         <v>33</v>
       </c>
-      <c r="N29" s="124">
+      <c r="N29" s="104">
         <v>450</v>
       </c>
       <c r="O29" s="114" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="P29" s="112"/>
-      <c r="Q29" s="159"/>
+      <c r="Q29" s="156"/>
       <c r="R29" s="105"/>
       <c r="S29" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="185">
+        <v>169</v>
+      </c>
+      <c r="T29" s="176"/>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="33">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="B30" s="122" t="s">
-        <v>198</v>
+      <c r="B30" s="121" t="s">
+        <v>193</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>24</v>
@@ -6974,18 +7658,18 @@
       </c>
       <c r="F30" s="110">
         <f ca="1">TODAY()-E30</f>
-        <v>6</v>
-      </c>
-      <c r="G30" s="124"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="121"/>
-      <c r="J30" s="121"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
+        <v>7</v>
+      </c>
+      <c r="G30" s="106"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="120"/>
+      <c r="L30" s="120"/>
       <c r="M30" s="33">
         <v>21</v>
       </c>
-      <c r="N30" s="124">
+      <c r="N30" s="106">
         <v>150</v>
       </c>
       <c r="O30" s="112"/>
@@ -6993,35 +7677,41 @@
       <c r="Q30" s="112"/>
       <c r="R30" s="105"/>
       <c r="S30" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19">
-      <c r="A31" s="185">
+        <v>169</v>
+      </c>
+      <c r="T30" s="176"/>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" s="33">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="B31" s="152" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="152" t="s">
-        <v>237</v>
+      <c r="B31" s="197" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="197" t="s">
+        <v>220</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="121"/>
-      <c r="J31" s="121"/>
-      <c r="K31" s="121"/>
-      <c r="L31" s="121"/>
+      <c r="E31" s="111">
+        <v>46321</v>
+      </c>
+      <c r="F31" s="110">
+        <f ca="1">TODAY()-E31</f>
+        <v>2</v>
+      </c>
+      <c r="G31" s="106"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
       <c r="M31" s="33">
         <v>12</v>
       </c>
-      <c r="N31" s="124">
+      <c r="N31" s="106">
         <v>150</v>
       </c>
       <c r="O31" s="112"/>
@@ -7029,35 +7719,41 @@
       <c r="Q31" s="112"/>
       <c r="R31" s="105"/>
       <c r="S31" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="29">
-      <c r="A32" s="186">
+        <v>169</v>
+      </c>
+      <c r="T31" s="176"/>
+    </row>
+    <row r="32" spans="1:20" ht="29">
+      <c r="A32" s="33">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="B32" s="152" t="s">
-        <v>217</v>
-      </c>
-      <c r="C32" s="152" t="s">
-        <v>238</v>
+      <c r="B32" s="197" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="197" t="s">
+        <v>221</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="124"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="121"/>
-      <c r="J32" s="121"/>
-      <c r="K32" s="121"/>
-      <c r="L32" s="121"/>
+      <c r="E32" s="111">
+        <v>46322</v>
+      </c>
+      <c r="F32" s="110">
+        <f ca="1">TODAY()-E32</f>
+        <v>1</v>
+      </c>
+      <c r="G32" s="106"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="120"/>
+      <c r="K32" s="120"/>
+      <c r="L32" s="120"/>
       <c r="M32" s="33">
         <v>20</v>
       </c>
-      <c r="N32" s="124">
+      <c r="N32" s="106">
         <v>450</v>
       </c>
       <c r="O32" s="112"/>
@@ -7065,93 +7761,119 @@
       <c r="Q32" s="112"/>
       <c r="R32" s="105"/>
       <c r="S32" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="28">
+        <v>169</v>
+      </c>
+      <c r="T32" s="176"/>
+    </row>
+    <row r="33" spans="1:20" ht="28">
       <c r="A33" s="33">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="B33" s="188" t="s">
-        <v>241</v>
+      <c r="B33" s="178" t="s">
+        <v>224</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="121"/>
-      <c r="J33" s="121"/>
-      <c r="K33" s="121"/>
-      <c r="L33" s="121"/>
+        <v>225</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E33" s="111">
+        <v>46322</v>
+      </c>
+      <c r="F33" s="110">
+        <f ca="1">TODAY()-E33</f>
+        <v>1</v>
+      </c>
+      <c r="G33" s="106"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="120"/>
+      <c r="K33" s="120"/>
+      <c r="L33" s="120"/>
       <c r="M33" s="33">
         <v>16</v>
       </c>
-      <c r="N33" s="124">
+      <c r="N33" s="106">
         <v>200</v>
       </c>
-      <c r="O33" s="184"/>
-      <c r="P33" s="184"/>
-      <c r="Q33" s="184"/>
+      <c r="O33" s="176"/>
+      <c r="P33" s="176"/>
+      <c r="Q33" s="176"/>
       <c r="R33" s="105"/>
       <c r="S33" s="105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+        <v>169</v>
+      </c>
+      <c r="T33" s="176"/>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34" s="33">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="B34" s="189" t="s">
-        <v>239</v>
-      </c>
-      <c r="C34" s="189" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="121"/>
-      <c r="J34" s="121"/>
-      <c r="K34" s="121"/>
-      <c r="L34" s="121"/>
+      <c r="B34" s="198" t="s">
+        <v>222</v>
+      </c>
+      <c r="C34" s="198" t="s">
+        <v>223</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="120"/>
       <c r="M34" s="33"/>
-      <c r="N34" s="124"/>
-      <c r="O34" s="184"/>
-      <c r="P34" s="184"/>
-      <c r="Q34" s="184"/>
+      <c r="N34" s="106"/>
+      <c r="O34" s="176"/>
+      <c r="P34" s="176"/>
+      <c r="Q34" s="176"/>
       <c r="R34" s="105"/>
       <c r="S34" s="105"/>
-    </row>
-    <row r="35" spans="1:19">
-      <c r="A35" s="124"/>
-      <c r="B35" s="182"/>
-      <c r="C35" s="182"/>
-      <c r="D35" s="124"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="124"/>
-      <c r="O35" s="113"/>
-      <c r="P35" s="113"/>
-      <c r="Q35" s="113"/>
-    </row>
-    <row r="36" spans="1:19">
-      <c r="R36" s="187"/>
-      <c r="S36" s="187"/>
+      <c r="T34" s="176"/>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35" s="33">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="178" t="s">
+        <v>247</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="120"/>
+      <c r="J35" s="120"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="106"/>
+      <c r="O35" s="176"/>
+      <c r="P35" s="176"/>
+      <c r="Q35" s="176"/>
+      <c r="R35" s="105"/>
+      <c r="S35" s="105"/>
+      <c r="T35" s="195" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="R36" s="177"/>
+      <c r="S36" s="177"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7174,18 +7896,19 @@
     <col min="4" max="4" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.26953125" customWidth="1"/>
     <col min="6" max="6" width="9.81640625" style="59" customWidth="1"/>
-    <col min="7" max="7" width="28.453125" style="59" customWidth="1"/>
-    <col min="8" max="8" width="14.453125" style="59" customWidth="1"/>
-    <col min="9" max="10" width="13.1796875" style="59" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" style="59" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.90625" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.54296875" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="59" customWidth="1"/>
-    <col min="16" max="16" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.26953125" style="59" customWidth="1"/>
+    <col min="8" max="8" width="7.54296875" style="59" customWidth="1"/>
+    <col min="9" max="9" width="8.1796875" style="59" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="59" customWidth="1"/>
+    <col min="11" max="11" width="8.1796875" style="59" customWidth="1"/>
+    <col min="12" max="12" width="8.36328125" style="59" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" style="59" customWidth="1"/>
+    <col min="14" max="14" width="7.6328125" style="59" customWidth="1"/>
+    <col min="15" max="15" width="7.54296875" style="59" customWidth="1"/>
+    <col min="16" max="16" width="19.81640625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="14.08984375" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="17.54296875" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="19" max="19" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="11" customFormat="1" ht="26">
@@ -7201,37 +7924,37 @@
       <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="139" t="s">
+      <c r="E1" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="140" t="s">
+      <c r="F1" s="138" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="140" t="s">
+      <c r="G1" s="138" t="s">
         <v>125</v>
       </c>
-      <c r="H1" s="139" t="s">
+      <c r="H1" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="139" t="s">
+      <c r="I1" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="139" t="s">
+      <c r="J1" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="139" t="s">
+      <c r="K1" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="139" t="s">
+      <c r="L1" s="137" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="139" t="s">
+      <c r="M1" s="138" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="O1" s="139" t="s">
+      <c r="N1" s="138" t="s">
+        <v>199</v>
+      </c>
+      <c r="O1" s="138" t="s">
         <v>54</v>
       </c>
       <c r="P1" s="23" t="s">
@@ -7699,7 +8422,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>45</v>
@@ -7764,7 +8487,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D10" s="31" t="s">
         <v>45</v>
@@ -7829,7 +8552,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D11" s="31" t="s">
         <v>45</v>
@@ -7854,8 +8577,8 @@
         <v>1</v>
       </c>
       <c r="J11" s="91">
-        <f ca="1">TODAY()-DATE(2026,9,16)</f>
-        <v>41</v>
+        <f>DATE(2026,9,23)-DATE(2026,9,16)</f>
+        <v>7</v>
       </c>
       <c r="K11" s="91">
         <f>DATE(2026,9,23)-DATE(2026,9,23)</f>
@@ -8097,7 +8820,7 @@
       <c r="D15" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="173">
+      <c r="E15" s="168">
         <v>46204</v>
       </c>
       <c r="F15" s="41">
@@ -8141,10 +8864,10 @@
       <c r="P15" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="Q15" s="169" t="s">
+      <c r="Q15" s="164" t="s">
         <v>59</v>
       </c>
-      <c r="R15" s="171">
+      <c r="R15" s="166">
         <v>46301</v>
       </c>
     </row>
@@ -8157,12 +8880,12 @@
         <v>7</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="173">
+      <c r="E16" s="168">
         <v>46204</v>
       </c>
       <c r="F16" s="41">
@@ -8196,16 +8919,16 @@
       <c r="O16" s="16">
         <v>333</v>
       </c>
-      <c r="P16" s="130" t="s">
+      <c r="P16" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="Q16" s="169" t="s">
+      <c r="Q16" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="171">
+      <c r="R16" s="166">
         <v>46307</v>
       </c>
-      <c r="S16" s="123"/>
+      <c r="S16" s="122"/>
     </row>
     <row r="17" spans="1:19" ht="60">
       <c r="A17" s="28">
@@ -8221,7 +8944,7 @@
       <c r="D17" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="173">
+      <c r="E17" s="168">
         <v>46265</v>
       </c>
       <c r="F17" s="41">
@@ -8265,7 +8988,7 @@
         <v>69</v>
       </c>
       <c r="Q17" s="31"/>
-      <c r="R17" s="171">
+      <c r="R17" s="166">
         <v>46309</v>
       </c>
       <c r="S17" s="109"/>
@@ -8278,16 +9001,16 @@
       <c r="B18" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="192" t="s">
+      <c r="C18" s="180" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="193" t="s">
+      <c r="D18" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="173">
+      <c r="E18" s="168">
         <v>46269</v>
       </c>
-      <c r="F18" s="174">
+      <c r="F18" s="169">
         <f>DATE(2026,10,26)-E18</f>
         <v>52</v>
       </c>
@@ -8328,10 +9051,10 @@
         <v>69</v>
       </c>
       <c r="Q18" s="28"/>
-      <c r="R18" s="172">
+      <c r="R18" s="167">
         <v>46321</v>
       </c>
-      <c r="S18" s="170"/>
+      <c r="S18" s="165"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8345,7 +9068,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23.7265625" customWidth="1"/>
@@ -8355,13 +9078,13 @@
   <sheetData>
     <row r="1" spans="1:11" ht="26.5" thickBot="1">
       <c r="A1" s="96" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B1" s="97" t="s">
         <v>141</v>
       </c>
       <c r="C1" s="94" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D1" s="92"/>
       <c r="G1" s="84"/>
@@ -8372,11 +9095,11 @@
     </row>
     <row r="2" spans="1:11" ht="32.5" customHeight="1" thickBot="1">
       <c r="A2" s="101" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2" s="102"/>
       <c r="C2" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D2" s="92"/>
       <c r="G2" s="84"/>
@@ -8387,15 +9110,15 @@
     </row>
     <row r="3" spans="1:11" ht="15" thickBot="1">
       <c r="A3" s="93" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="194">
+        <v>149</v>
+      </c>
+      <c r="B3" s="182">
         <f>COUNTA(Table2[MPS ID])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="95">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>
-        <v>25.862068965517242</v>
+        <v>24.46875</v>
       </c>
       <c r="D3" s="92"/>
       <c r="G3" s="84"/>
@@ -8405,9 +9128,9 @@
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1">
       <c r="A4" s="98" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="131">
+        <v>150</v>
+      </c>
+      <c r="B4" s="129">
         <f>COUNTA(Delivered!C2:C18)</f>
         <v>17</v>
       </c>
@@ -8419,177 +9142,225 @@
       <c r="E4" s="84"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="195"/>
-      <c r="B5" s="195"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
+      <c r="A5" s="183"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="183"/>
+      <c r="D5" s="183"/>
     </row>
     <row r="6" spans="1:11" ht="36">
-      <c r="A6" s="198" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" s="199" t="s">
+      <c r="A6" s="186" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="199" t="s">
+      <c r="C6" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="199" t="s">
+      <c r="D6" s="187" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="199" t="s">
-        <v>184</v>
-      </c>
-      <c r="F6" s="199" t="s">
-        <v>219</v>
-      </c>
-      <c r="G6" s="199" t="s">
+      <c r="E6" s="187" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="187" t="s">
+        <v>208</v>
+      </c>
+      <c r="G6" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="199" t="s">
-        <v>249</v>
+      <c r="H6" s="187" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" s="196">
+        <v>229</v>
+      </c>
+      <c r="B7" s="184">
         <f>Delivered!G2</f>
         <v>32</v>
       </c>
-      <c r="C7" s="196">
+      <c r="C7" s="184">
         <f>Delivered!H2</f>
         <v>11</v>
       </c>
-      <c r="D7" s="196">
+      <c r="D7" s="184">
         <f>Delivered!I2</f>
         <v>3</v>
       </c>
-      <c r="E7" s="196">
+      <c r="E7" s="184">
         <f>Delivered!J2</f>
         <v>6</v>
       </c>
-      <c r="F7" s="196">
+      <c r="F7" s="184">
         <f>Delivered!K2</f>
         <v>6</v>
       </c>
-      <c r="G7" s="196">
+      <c r="G7" s="184">
         <f>Delivered!L2</f>
         <v>5</v>
       </c>
-      <c r="H7" s="203">
+      <c r="H7" s="191">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" s="197">
+        <v>228</v>
+      </c>
+      <c r="B8" s="185">
         <f>AVERAGE(Delivered!G3:G11)</f>
         <v>25</v>
       </c>
-      <c r="C8" s="197">
+      <c r="C8" s="185">
         <f>AVERAGE(Delivered!H3:H11)</f>
         <v>11.777777777777779</v>
       </c>
-      <c r="D8" s="197">
+      <c r="D8" s="185">
         <f>AVERAGE(Delivered!I3:I11)</f>
         <v>4.1111111111111107</v>
       </c>
-      <c r="E8" s="197">
-        <f ca="1">AVERAGE(Delivered!J3:J11)</f>
-        <v>10.666666666666666</v>
-      </c>
-      <c r="F8" s="197">
+      <c r="E8" s="185">
+        <f>AVERAGE(Delivered!J3:J11)</f>
+        <v>6.8888888888888893</v>
+      </c>
+      <c r="F8" s="185">
         <f>AVERAGE(Delivered!K3:K11)</f>
         <v>5.8888888888888893</v>
       </c>
-      <c r="G8" s="197">
+      <c r="G8" s="185">
         <f>AVERAGE(Delivered!L3:L11)</f>
         <v>6</v>
       </c>
-      <c r="H8" s="203">
+      <c r="H8" s="191">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="200" t="s">
-        <v>247</v>
-      </c>
-      <c r="B9" s="201">
+      <c r="A9" s="188" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="189">
         <f>AVERAGE(Delivered!G12:G21)</f>
         <v>27.428571428571427</v>
       </c>
-      <c r="C9" s="201">
+      <c r="C9" s="189">
         <f>AVERAGE(Delivered!H12:H21)</f>
         <v>11.714285714285714</v>
       </c>
-      <c r="D9" s="201">
+      <c r="D9" s="189">
         <f>AVERAGE(Delivered!I12:I21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="E9" s="201">
+      <c r="E9" s="189">
         <f>AVERAGE(Delivered!J12:J21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="F9" s="201">
+      <c r="F9" s="189">
         <f>AVERAGE(Delivered!K12:K21)</f>
         <v>6.8571428571428568</v>
       </c>
-      <c r="G9" s="201">
+      <c r="G9" s="189">
         <f>AVERAGE(Delivered!L12:L21)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="H9" s="203">
+      <c r="H9" s="191">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29">
-      <c r="A10" s="202" t="s">
-        <v>248</v>
-      </c>
-      <c r="B10" s="196">
+      <c r="A10" s="190" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="191">
         <f>AVERAGE(B7:B9)</f>
         <v>28.142857142857142</v>
       </c>
-      <c r="C10" s="196">
+      <c r="C10" s="191">
         <f t="shared" ref="C10:G10" si="0">AVERAGE(C7:C9)</f>
         <v>11.497354497354499</v>
       </c>
-      <c r="D10" s="196">
+      <c r="D10" s="191">
         <f t="shared" si="0"/>
         <v>3.7513227513227512</v>
       </c>
-      <c r="E10" s="196">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.9365079365079358</v>
-      </c>
-      <c r="F10" s="196">
+      <c r="E10" s="191">
+        <f t="shared" si="0"/>
+        <v>5.6772486772486772</v>
+      </c>
+      <c r="F10" s="191">
         <f t="shared" si="0"/>
         <v>6.2486772486772493</v>
       </c>
-      <c r="G10" s="196">
+      <c r="G10" s="191">
         <f t="shared" si="0"/>
         <v>5.1904761904761907</v>
       </c>
       <c r="H10" s="10"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="204" t="s">
+      <c r="A12" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="B12" s="192">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" s="192">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B12" s="204">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="204" t="s">
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B13" s="204">
-        <v>103</v>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8624,10 +9395,10 @@
       <c r="J2" s="79"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="194" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="205"/>
+      <c r="C3" s="194"/>
       <c r="E3" s="79"/>
       <c r="F3" s="80"/>
       <c r="G3" s="79"/>
@@ -9069,7 +9840,7 @@
       </c>
       <c r="F8" s="5">
         <f ca="1">TODAY()-DATE(2026,9,25)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="5" t="e">
         <f ca="1">TODAY()-#REF!</f>
@@ -9077,7 +9848,7 @@
       </c>
       <c r="H8" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 34 days buffer</v>
+        <v>On Track. 33 days buffer</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -9093,7 +9864,7 @@
       </c>
       <c r="D9" s="16">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -9103,7 +9874,7 @@
       </c>
       <c r="H9" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 35 days buffer</v>
+        <v>On Track. 34 days buffer</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -9119,7 +9890,7 @@
       </c>
       <c r="D10" s="16">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -9129,7 +9900,7 @@
       </c>
       <c r="H10" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 35 days buffer</v>
+        <v>On Track. 34 days buffer</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -9149,7 +9920,7 @@
       </c>
       <c r="E11" s="7">
         <f ca="1">TODAY()-DATE(2026,9,16)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="e">
@@ -9158,7 +9929,7 @@
       </c>
       <c r="H11" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 33 days buffer</v>
+        <v>On Track. 32 days buffer</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -9473,10 +10244,10 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="10"/>
-      <c r="C46" s="126" t="s">
-        <v>166</v>
-      </c>
-      <c r="D46" s="127">
+      <c r="C46" s="124" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" s="125">
         <f>COUNTA(D49:D81)</f>
         <v>33</v>
       </c>
@@ -9484,19 +10255,19 @@
     </row>
     <row r="47" spans="2:6" ht="15" thickBot="1">
       <c r="B47" s="10"/>
-      <c r="C47" s="128" t="s">
-        <v>182</v>
-      </c>
-      <c r="D47" s="129">
+      <c r="C47" s="126" t="s">
+        <v>180</v>
+      </c>
+      <c r="D47" s="127">
         <v>17</v>
       </c>
-      <c r="E47" s="129" t="s">
-        <v>183</v>
+      <c r="E47" s="127" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="15" thickBot="1">
       <c r="B48" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C48" s="22" t="s">
         <v>2</v>
@@ -9504,10 +10275,10 @@
       <c r="D48" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="125" t="s">
+      <c r="E48" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="134" t="s">
+      <c r="F48" s="132" t="s">
         <v>57</v>
       </c>
     </row>
@@ -9515,13 +10286,13 @@
       <c r="B49" s="18">
         <v>1</v>
       </c>
-      <c r="C49" s="133" t="s">
+      <c r="C49" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="132" t="s">
-        <v>184</v>
-      </c>
-      <c r="E49" s="135">
+      <c r="D49" s="130" t="s">
+        <v>182</v>
+      </c>
+      <c r="E49" s="133">
         <v>64</v>
       </c>
       <c r="F49" s="10"/>
@@ -9534,9 +10305,9 @@
         <v>36</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="E50" s="138">
+        <v>208</v>
+      </c>
+      <c r="E50" s="136">
         <v>40</v>
       </c>
       <c r="F50" s="26"/>
@@ -9546,7 +10317,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D51" s="33" t="s">
         <v>137</v>
@@ -9561,12 +10332,12 @@
         <v>4</v>
       </c>
       <c r="C52" s="119" t="s">
-        <v>179</v>
-      </c>
-      <c r="D52" s="142" t="s">
-        <v>184</v>
-      </c>
-      <c r="E52" s="137">
+        <v>177</v>
+      </c>
+      <c r="D52" s="140" t="s">
+        <v>182</v>
+      </c>
+      <c r="E52" s="135">
         <v>39</v>
       </c>
       <c r="F52" s="10"/>
@@ -9576,7 +10347,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D53" s="33" t="s">
         <v>137</v>
@@ -9594,26 +10365,26 @@
         <v>34</v>
       </c>
       <c r="D54" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="E54" s="136">
+        <v>208</v>
+      </c>
+      <c r="E54" s="134">
         <v>36</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="H54" s="181" t="s">
-        <v>223</v>
-      </c>
-      <c r="I54" s="181">
+      <c r="H54" s="174" t="s">
+        <v>210</v>
+      </c>
+      <c r="I54" s="174">
         <v>30</v>
       </c>
-      <c r="J54" s="181" t="s">
-        <v>224</v>
-      </c>
-      <c r="K54" s="181" t="s">
-        <v>225</v>
+      <c r="J54" s="174" t="s">
+        <v>211</v>
+      </c>
+      <c r="K54" s="174" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="2:11" ht="29">
@@ -9621,7 +10392,7 @@
         <v>7</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D55" s="33" t="s">
         <v>137</v>
@@ -9633,17 +10404,17 @@
       <c r="G55" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="H55" s="181" t="s">
-        <v>223</v>
-      </c>
-      <c r="I55" s="181">
+      <c r="H55" s="174" t="s">
+        <v>210</v>
+      </c>
+      <c r="I55" s="174">
         <v>46</v>
       </c>
-      <c r="J55" s="181" t="s">
-        <v>224</v>
-      </c>
-      <c r="K55" s="181" t="s">
-        <v>225</v>
+      <c r="J55" s="174" t="s">
+        <v>211</v>
+      </c>
+      <c r="K55" s="174" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="2:11" ht="29">
@@ -9651,7 +10422,7 @@
         <v>8</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D56" s="33" t="s">
         <v>72</v>
@@ -9663,17 +10434,17 @@
       <c r="G56" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="H56" s="181" t="s">
-        <v>226</v>
-      </c>
-      <c r="I56" s="181">
+      <c r="H56" s="174" t="s">
+        <v>213</v>
+      </c>
+      <c r="I56" s="174">
         <v>58</v>
       </c>
-      <c r="J56" s="181" t="s">
-        <v>224</v>
-      </c>
-      <c r="K56" s="181" t="s">
-        <v>225</v>
+      <c r="J56" s="174" t="s">
+        <v>211</v>
+      </c>
+      <c r="K56" s="174" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="2:11">
@@ -9681,7 +10452,7 @@
         <v>9</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D57" s="58" t="s">
         <v>137</v>
@@ -9696,7 +10467,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="57" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D58" s="58" t="s">
         <v>137</v>
@@ -9711,12 +10482,12 @@
         <v>11</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D59" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E59" s="138">
+      <c r="E59" s="136">
         <v>31</v>
       </c>
       <c r="F59" s="10"/>
@@ -9731,7 +10502,7 @@
       <c r="D60" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="E60" s="138">
+      <c r="E60" s="136">
         <v>31</v>
       </c>
       <c r="F60" s="10"/>
@@ -9770,13 +10541,13 @@
       <c r="B63" s="18">
         <v>15</v>
       </c>
-      <c r="C63" s="164" t="s">
+      <c r="C63" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="165" t="s">
+      <c r="D63" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="138">
+      <c r="E63" s="136">
         <v>28</v>
       </c>
       <c r="F63" s="10"/>
@@ -9786,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>19</v>
@@ -9800,13 +10571,13 @@
       <c r="B65" s="18">
         <v>17</v>
       </c>
-      <c r="C65" s="164" t="s">
+      <c r="C65" s="160" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="167" t="s">
+      <c r="D65" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="138">
+      <c r="E65" s="136">
         <v>27</v>
       </c>
       <c r="F65" s="10"/>
@@ -9815,13 +10586,13 @@
       <c r="B66" s="18">
         <v>18</v>
       </c>
-      <c r="C66" s="164" t="s">
+      <c r="C66" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="D66" s="167" t="s">
+      <c r="D66" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="138">
+      <c r="E66" s="136">
         <v>27</v>
       </c>
       <c r="F66" s="10"/>
@@ -9830,10 +10601,10 @@
       <c r="B67" s="18">
         <v>19</v>
       </c>
-      <c r="C67" s="166" t="s">
-        <v>158</v>
-      </c>
-      <c r="D67" s="167" t="s">
+      <c r="C67" s="162" t="s">
+        <v>157</v>
+      </c>
+      <c r="D67" s="163" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="8">
@@ -9864,9 +10635,9 @@
         <v>136</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E69" s="138">
+        <v>204</v>
+      </c>
+      <c r="E69" s="136">
         <v>15</v>
       </c>
       <c r="F69" s="10"/>
@@ -9885,7 +10656,7 @@
         <v>15</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -9907,10 +10678,10 @@
       <c r="B72" s="18">
         <v>24</v>
       </c>
-      <c r="C72" s="164" t="s">
+      <c r="C72" s="160" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="167" t="s">
+      <c r="D72" s="163" t="s">
         <v>19</v>
       </c>
       <c r="E72" s="18">
@@ -9923,10 +10694,10 @@
         <v>25</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E73" s="18">
         <v>10</v>
@@ -9938,7 +10709,7 @@
         <v>26</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>19</v>
@@ -9953,10 +10724,10 @@
         <v>27</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E75" s="18">
         <v>6</v>
@@ -9968,7 +10739,7 @@
         <v>28</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>19</v>
@@ -9983,7 +10754,7 @@
         <v>29</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>24</v>
@@ -9997,8 +10768,8 @@
       <c r="B78" s="18">
         <v>30</v>
       </c>
-      <c r="C78" s="183" t="s">
-        <v>237</v>
+      <c r="C78" s="175" t="s">
+        <v>220</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>24</v>
@@ -10012,8 +10783,8 @@
       <c r="B79" s="18">
         <v>31</v>
       </c>
-      <c r="C79" s="183" t="s">
-        <v>238</v>
+      <c r="C79" s="175" t="s">
+        <v>221</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>24</v>
@@ -10027,8 +10798,8 @@
       <c r="B80" s="18">
         <v>32</v>
       </c>
-      <c r="C80" s="183" t="s">
-        <v>242</v>
+      <c r="C80" s="175" t="s">
+        <v>225</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>24</v>
@@ -10042,8 +10813,8 @@
       <c r="B81" s="18">
         <v>33</v>
       </c>
-      <c r="C81" s="183" t="s">
-        <v>240</v>
+      <c r="C81" s="175" t="s">
+        <v>223</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>24</v>
@@ -10068,89 +10839,89 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3 C5:C26">
-    <cfRule type="cellIs" dxfId="20" priority="33" operator="between">
+    <cfRule type="cellIs" dxfId="123" priority="33" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8 D11:D26">
-    <cfRule type="cellIs" dxfId="19" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="122" priority="29" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="121" priority="30" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E26">
-    <cfRule type="cellIs" dxfId="17" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="120" priority="27" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="28" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4 F8:F26">
-    <cfRule type="cellIs" dxfId="15" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="25" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="26" operator="equal">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G26">
-    <cfRule type="cellIs" dxfId="13" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="116" priority="23" operator="greaterThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="115" priority="24" operator="lessThan">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="11" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="21" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="22" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="9" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="19" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="20" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="7" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="17" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="18" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="108" priority="5" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="107" priority="6" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="106" priority="3" operator="between">
       <formula>0</formula>
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="105" priority="4" operator="greaterThan">
       <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="104" priority="1" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="103" priority="2" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId7"/>
+    <pivotCache cacheId="7" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="260">
   <si>
     <t>S. no</t>
   </si>
@@ -878,12 +878,6 @@
     <t>Delivered on 27th</t>
   </si>
   <si>
-    <t>6 chaps in revises</t>
-  </si>
-  <si>
-    <t>20 in revises. FM in S200 comp</t>
-  </si>
-  <si>
     <t>Delivrered</t>
   </si>
   <si>
@@ -957,9 +951,6 @@
     <t>3 Books</t>
   </si>
   <si>
-    <t>Delivered on 28-Oct</t>
-  </si>
-  <si>
     <t>S200 delivered on 27-Oct</t>
   </si>
   <si>
@@ -976,6 +967,12 @@
   </si>
   <si>
     <t>Column2</t>
+  </si>
+  <si>
+    <t>Delivered S300 on 28-Oct</t>
+  </si>
+  <si>
+    <t>5 chap in Revises</t>
   </si>
 </sst>
 </file>
@@ -2128,508 +2125,44 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="172">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <fill>
         <patternFill>
@@ -3648,6 +3181,44 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
@@ -4191,6 +3762,45 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5104,7 +4714,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H12" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -5313,16 +4923,16 @@
     <dataField name="Count of S650 TAT" fld="11" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="64">
+    <format dxfId="78">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="77">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="66">
+    <format dxfId="76">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="67">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5331,7 +4941,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5340,7 +4950,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5349,7 +4959,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5370,7 +4980,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="3">
           <reference field="2" count="1" selected="0">
@@ -5396,29 +5006,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T35" totalsRowShown="0" headerRowDxfId="171" dataDxfId="170">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T35" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:T35"/>
   <tableColumns count="20">
-    <tableColumn id="1" name="S. no" dataDxfId="169"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="168"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="167"/>
-    <tableColumn id="4" name="Stage" dataDxfId="166"/>
+    <tableColumn id="1" name="S. no" dataDxfId="67"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="66"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="65"/>
+    <tableColumn id="4" name="Stage" dataDxfId="64"/>
     <tableColumn id="5" name="Received Date (S50)"/>
     <tableColumn id="6" name="Current TAT (S50 onward)"/>
-    <tableColumn id="7" name="S200 TAT" dataDxfId="165"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="164"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="163"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="162"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="161"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="160"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="159"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="158"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="157"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="156"/>
-    <tableColumn id="17" name="Remarks" dataDxfId="155"/>
-    <tableColumn id="18" name="Column1" dataDxfId="154"/>
-    <tableColumn id="19" name="Plateform" dataDxfId="153"/>
-    <tableColumn id="20" name="Column2" dataDxfId="0"/>
+    <tableColumn id="7" name="S200 TAT" dataDxfId="63"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="62"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="61"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="60"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="59"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="58"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="57"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="56"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="55"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="54"/>
+    <tableColumn id="17" name="Remarks" dataDxfId="53"/>
+    <tableColumn id="18" name="Column1" dataDxfId="52"/>
+    <tableColumn id="19" name="Plateform" dataDxfId="51"/>
+    <tableColumn id="20" name="Column2" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5427,32 +5037,32 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
   <tableColumns count="19">
-    <tableColumn id="1" name="S. no" dataDxfId="152"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="151"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="150"/>
-    <tableColumn id="4" name="Stage" dataDxfId="149"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="148"/>
-    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="147"/>
-    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="146"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="145"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="144"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="143"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="142"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="141"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="140"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="139"/>
-    <tableColumn id="19" name="TS Pages" dataDxfId="138"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="137"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="136"/>
-    <tableColumn id="17" name="Delivered Date " dataDxfId="135"/>
-    <tableColumn id="18" name="Remarks" dataDxfId="134"/>
+    <tableColumn id="1" name="S. no" dataDxfId="49"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="48"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="47"/>
+    <tableColumn id="4" name="Stage" dataDxfId="46"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="45"/>
+    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="44"/>
+    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="43"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="42"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="41"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="40"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="39"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="38"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="37"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="36"/>
+    <tableColumn id="19" name="TS Pages" dataDxfId="35"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="34"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="33"/>
+    <tableColumn id="17" name="Delivered Date " dataDxfId="32"/>
+    <tableColumn id="18" name="Remarks" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="133" tableBorderDxfId="132" totalsRowBorderDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="1" name="DESCriptions"/>
@@ -5464,11 +5074,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="130" dataDxfId="128" headerRowBorderDxfId="129" tableBorderDxfId="127" totalsRowBorderDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="B5:C10"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Month" dataDxfId="125"/>
-    <tableColumn id="2" name="No of titles delivered" dataDxfId="124">
+    <tableColumn id="1" name="Month" dataDxfId="22"/>
+    <tableColumn id="2" name="No of titles delivered" dataDxfId="21">
       <calculatedColumnFormula>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6132,8 +5742,8 @@
       <c r="S1" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="T1" s="204" t="s">
-        <v>260</v>
+      <c r="T1" s="203" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="240">
@@ -6196,7 +5806,7 @@
       <c r="S2" s="105" t="s">
         <v>169</v>
       </c>
-      <c r="T2" s="203"/>
+      <c r="T2" s="202"/>
     </row>
     <row r="3" spans="1:20" ht="60">
       <c r="A3" s="52">
@@ -6206,7 +5816,7 @@
       <c r="B3" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="200" t="s">
+      <c r="C3" s="199" t="s">
         <v>171</v>
       </c>
       <c r="D3" s="58" t="s">
@@ -6268,11 +5878,11 @@
       <c r="B4" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="198" t="s">
         <v>172</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="E4" s="35">
         <v>46291</v>
@@ -6293,7 +5903,10 @@
         <f>DATE(2026,10,28)-DATE(2026,10,23)</f>
         <v>5</v>
       </c>
-      <c r="J4" s="104"/>
+      <c r="J4" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <v>0</v>
+      </c>
       <c r="K4" s="104"/>
       <c r="L4" s="104"/>
       <c r="M4" s="33">
@@ -6305,9 +5918,7 @@
       <c r="O4" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="P4" s="113" t="s">
-        <v>236</v>
-      </c>
+      <c r="P4" s="113"/>
       <c r="Q4" s="151" t="s">
         <v>74</v>
       </c>
@@ -6387,7 +5998,7 @@
       <c r="B6" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="199" t="s">
+      <c r="C6" s="198" t="s">
         <v>174</v>
       </c>
       <c r="D6" s="33" t="s">
@@ -6425,7 +6036,7 @@
         <v>69</v>
       </c>
       <c r="P6" s="113" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="Q6" s="151" t="s">
         <v>154</v>
@@ -6484,7 +6095,7 @@
         <v>69</v>
       </c>
       <c r="P7" s="113" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q7" s="151" t="s">
         <v>128</v>
@@ -6607,7 +6218,7 @@
         <v>69</v>
       </c>
       <c r="P9" s="113" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Q9" s="151" t="s">
         <v>73</v>
@@ -6626,7 +6237,7 @@
       <c r="B10" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="200" t="s">
+      <c r="C10" s="199" t="s">
         <v>178</v>
       </c>
       <c r="D10" s="58" t="s">
@@ -6685,7 +6296,7 @@
       <c r="B11" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="199" t="s">
+      <c r="C11" s="198" t="s">
         <v>179</v>
       </c>
       <c r="D11" s="8" t="s">
@@ -6717,10 +6328,10 @@
         <v>750</v>
       </c>
       <c r="O11" s="114" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P11" s="113" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q11" s="151" t="s">
         <v>166</v>
@@ -6739,7 +6350,7 @@
       <c r="B12" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="199" t="s">
+      <c r="C12" s="198" t="s">
         <v>113</v>
       </c>
       <c r="D12" s="33" t="s">
@@ -6774,7 +6385,7 @@
         <v>69</v>
       </c>
       <c r="P12" s="113" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Q12" s="151" t="s">
         <v>76</v>
@@ -6920,7 +6531,7 @@
       <c r="B15" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="199" t="s">
+      <c r="C15" s="198" t="s">
         <v>114</v>
       </c>
       <c r="D15" s="33" t="s">
@@ -6949,7 +6560,7 @@
         <v>500</v>
       </c>
       <c r="O15" s="114" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P15" s="113" t="s">
         <v>184</v>
@@ -6971,7 +6582,7 @@
       <c r="B16" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="199" t="s">
+      <c r="C16" s="198" t="s">
         <v>96</v>
       </c>
       <c r="D16" s="33" t="s">
@@ -7006,10 +6617,10 @@
         <v>500</v>
       </c>
       <c r="O16" s="114" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P16" s="113" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="Q16" s="151"/>
       <c r="R16" s="105"/>
@@ -7064,7 +6675,7 @@
         <v>69</v>
       </c>
       <c r="P17" s="116" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Q17" s="153"/>
       <c r="R17" s="105"/>
@@ -7081,7 +6692,7 @@
       <c r="B18" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="202" t="s">
+      <c r="C18" s="201" t="s">
         <v>157</v>
       </c>
       <c r="D18" s="8" t="s">
@@ -7114,7 +6725,7 @@
         <v>214</v>
       </c>
       <c r="P18" s="113" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Q18" s="154" t="s">
         <v>188</v>
@@ -7133,7 +6744,7 @@
       <c r="B19" s="159" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="201" t="s">
+      <c r="C19" s="200" t="s">
         <v>106</v>
       </c>
       <c r="D19" s="163" t="s">
@@ -7182,7 +6793,7 @@
       <c r="B20" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="199" t="s">
+      <c r="C20" s="198" t="s">
         <v>115</v>
       </c>
       <c r="D20" s="8" t="s">
@@ -7257,13 +6868,13 @@
         <v>350</v>
       </c>
       <c r="O21" s="114" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P21" s="113" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q21" s="151" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="R21" s="105" t="s">
         <v>226</v>
@@ -7328,7 +6939,7 @@
       <c r="B23" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="199" t="s">
+      <c r="C23" s="198" t="s">
         <v>110</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -7357,7 +6968,7 @@
         <v>450</v>
       </c>
       <c r="O23" s="114" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P23" s="113"/>
       <c r="Q23" s="155"/>
@@ -7521,7 +7132,7 @@
         <v>46316</v>
       </c>
       <c r="F27" s="110">
-        <f ca="1">TODAY()-E27</f>
+        <f t="shared" ref="F27:F33" ca="1" si="7">TODAY()-E27</f>
         <v>7</v>
       </c>
       <c r="G27" s="106"/>
@@ -7563,7 +7174,7 @@
         <v>46316</v>
       </c>
       <c r="F28" s="171">
-        <f ca="1">TODAY()-E28</f>
+        <f t="shared" ca="1" si="7"/>
         <v>7</v>
       </c>
       <c r="G28" s="104">
@@ -7610,7 +7221,7 @@
         <v>46312</v>
       </c>
       <c r="F29" s="171">
-        <f ca="1">TODAY()-E29</f>
+        <f t="shared" ca="1" si="7"/>
         <v>11</v>
       </c>
       <c r="G29" s="104">
@@ -7618,10 +7229,10 @@
         <v>6</v>
       </c>
       <c r="H29" s="170"/>
-      <c r="I29" s="196"/>
+      <c r="I29" s="195"/>
       <c r="J29" s="170"/>
-      <c r="K29" s="196"/>
-      <c r="L29" s="196"/>
+      <c r="K29" s="195"/>
+      <c r="L29" s="195"/>
       <c r="M29" s="33">
         <v>33</v>
       </c>
@@ -7657,7 +7268,7 @@
         <v>46316</v>
       </c>
       <c r="F30" s="110">
-        <f ca="1">TODAY()-E30</f>
+        <f t="shared" ca="1" si="7"/>
         <v>7</v>
       </c>
       <c r="G30" s="106"/>
@@ -7686,10 +7297,10 @@
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="B31" s="197" t="s">
+      <c r="B31" s="196" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="197" t="s">
+      <c r="C31" s="196" t="s">
         <v>220</v>
       </c>
       <c r="D31" s="8" t="s">
@@ -7699,7 +7310,7 @@
         <v>46321</v>
       </c>
       <c r="F31" s="110">
-        <f ca="1">TODAY()-E31</f>
+        <f t="shared" ca="1" si="7"/>
         <v>2</v>
       </c>
       <c r="G31" s="106"/>
@@ -7728,10 +7339,10 @@
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="B32" s="197" t="s">
+      <c r="B32" s="196" t="s">
         <v>207</v>
       </c>
-      <c r="C32" s="197" t="s">
+      <c r="C32" s="196" t="s">
         <v>221</v>
       </c>
       <c r="D32" s="8" t="s">
@@ -7741,7 +7352,7 @@
         <v>46322</v>
       </c>
       <c r="F32" s="110">
-        <f ca="1">TODAY()-E32</f>
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="G32" s="106"/>
@@ -7777,13 +7388,13 @@
         <v>225</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E33" s="111">
         <v>46322</v>
       </c>
       <c r="F33" s="110">
-        <f ca="1">TODAY()-E33</f>
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="G33" s="106"/>
@@ -7812,10 +7423,10 @@
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="B34" s="198" t="s">
+      <c r="B34" s="197" t="s">
         <v>222</v>
       </c>
-      <c r="C34" s="198" t="s">
+      <c r="C34" s="197" t="s">
         <v>223</v>
       </c>
       <c r="D34" s="8" t="s">
@@ -7844,10 +7455,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="178" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>24</v>
@@ -7867,8 +7478,8 @@
       <c r="Q35" s="176"/>
       <c r="R35" s="105"/>
       <c r="S35" s="105"/>
-      <c r="T35" s="195" t="s">
-        <v>259</v>
+      <c r="T35" s="194" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -9320,7 +8931,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -9328,7 +8939,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9336,7 +8947,7 @@
         <v>137</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9349,7 +8960,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B19" s="10">
         <v>2</v>
@@ -9395,10 +9006,10 @@
       <c r="J2" s="79"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="194" t="s">
+      <c r="B3" s="204" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="194"/>
+      <c r="C3" s="204"/>
       <c r="E3" s="79"/>
       <c r="F3" s="80"/>
       <c r="G3" s="79"/>
@@ -10839,89 +10450,89 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3 C5:C26">
-    <cfRule type="cellIs" dxfId="123" priority="33" operator="between">
+    <cfRule type="cellIs" dxfId="20" priority="33" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8 D11:D26">
-    <cfRule type="cellIs" dxfId="122" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="29" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="30" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E26">
-    <cfRule type="cellIs" dxfId="120" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="27" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="28" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4 F8:F26">
-    <cfRule type="cellIs" dxfId="118" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="25" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G26">
-    <cfRule type="cellIs" dxfId="116" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="23" operator="greaterThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="24" operator="lessThan">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="114" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="21" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="22" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="112" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="19" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="110" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="108" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" dxfId="106" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
       <formula>0</formula>
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
       <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="104" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="261">
   <si>
     <t>S. no</t>
   </si>
@@ -610,9 +610,6 @@
     <t>De Marchi, Luca</t>
   </si>
   <si>
-    <t>Hold for new manuscript solved. Will receive today</t>
-  </si>
-  <si>
     <t>Login reinstated, workflow issue solved</t>
   </si>
   <si>
@@ -767,9 +764,6 @@
     <t>S650A</t>
   </si>
   <si>
-    <t>S300 completed</t>
-  </si>
-  <si>
     <t>MetSoc-Vol9-8771159</t>
   </si>
   <si>
@@ -780,38 +774,6 @@
   </si>
   <si>
     <t>etSoc-Vol9-8771159</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 129 Chapters;
-PE : 00 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 00 Chapters;
-CE : 13 Chapters;
-Comp : 35 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 01 Chapters;
-PE : 21 Chapters;
-CE : 18 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 47 Chapters;
-PE : 09 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
   </si>
   <si>
     <t>S200 - 
@@ -822,14 +784,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 33 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>Zi,-PIC Yunlong 8770448</t>
   </si>
   <si>
@@ -873,12 +827,6 @@
   </si>
   <si>
     <t>Longest TAT</t>
-  </si>
-  <si>
-    <t>Delivered on 27th</t>
-  </si>
-  <si>
-    <t>Delivrered</t>
   </si>
   <si>
     <t>S200 - 
@@ -889,20 +837,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>11 chaps in Revises</t>
-  </si>
-  <si>
-    <t>25 chap in Revises</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 15 Chapters;
-CE : 21 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>S200 - 
 Login : 00 Chapters;
 PE :  00 Chapters;
@@ -911,17 +845,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>15 Chaps in Revises.</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 30 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>S200 - 
 Login : 00 Chapters;
 PE : 00 Chapters;
@@ -957,9 +880,6 @@
     <t>Query for JS regarding mismatch in chaps. BM is also there+Index</t>
   </si>
   <si>
-    <t>Login moved on 29-Oct</t>
-  </si>
-  <si>
     <t>New manuscript recd again and chap-31 added. On 12-Oct26. Preface &amp; TOC(FM components missing), Index tagging for 2 chaps. missing reced on 28-oct</t>
   </si>
   <si>
@@ -969,10 +889,98 @@
     <t>Column2</t>
   </si>
   <si>
-    <t>Delivered S300 on 28-Oct</t>
-  </si>
-  <si>
-    <t>5 chap in Revises</t>
+    <t>Delivered on 28th. Will move to S600 today</t>
+  </si>
+  <si>
+    <t>Delivered on 28th- Will move to S600 today</t>
+  </si>
+  <si>
+    <t>29 chap in Revises</t>
+  </si>
+  <si>
+    <t>16 chaps in Revises</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 05 Chapters;
+CE : 25 Chapters;
+Comp : 06 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>Hold for new manuscript solved.</t>
+  </si>
+  <si>
+    <t>16 Chaps in Revises.</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 01 Chapters;
+PE : 126 Chapters;
+CE : 02 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 00 Chapters;
+CE : 01 Chapters;
+Comp : 47 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 17 Chapters;
+CE : 23 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 13 Chapters;
+PE : 18 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>Login pending</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 03 Chapters;
+PE : 53 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 39 Chapters;
+PE : 17 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 29 Chapters;
+PE : 04 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>González, Carina-8770441</t>
+  </si>
+  <si>
+    <t>703158_1_En</t>
+  </si>
+  <si>
+    <t>Camara, Moctar</t>
   </si>
 </sst>
 </file>
@@ -1570,7 +1578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1885,12 +1893,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2125,9 +2127,6 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2155,14 +2154,67 @@
     <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="81">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3549,7 +3601,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3566,44 +3618,10 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4714,7 +4732,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H12" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4923,16 +4941,16 @@
     <dataField name="Count of S650 TAT" fld="11" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
+    <format dxfId="80">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="79">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
     <format dxfId="78">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
     <format dxfId="77">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
-    </format>
-    <format dxfId="76">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
-    </format>
-    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4941,7 +4959,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4950,7 +4968,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4959,7 +4977,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4968,7 +4986,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4980,7 +4998,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="3">
           <reference field="2" count="1" selected="0">
@@ -5006,29 +5024,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T35" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:T35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T36" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
+  <autoFilter ref="A1:T36"/>
   <tableColumns count="20">
-    <tableColumn id="1" name="S. no" dataDxfId="67"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="66"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="65"/>
-    <tableColumn id="4" name="Stage" dataDxfId="64"/>
-    <tableColumn id="5" name="Received Date (S50)"/>
-    <tableColumn id="6" name="Current TAT (S50 onward)"/>
-    <tableColumn id="7" name="S200 TAT" dataDxfId="63"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="62"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="61"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="60"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="59"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="58"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="57"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="56"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="55"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="54"/>
-    <tableColumn id="17" name="Remarks" dataDxfId="53"/>
-    <tableColumn id="18" name="Column1" dataDxfId="52"/>
-    <tableColumn id="19" name="Plateform" dataDxfId="51"/>
-    <tableColumn id="20" name="Column2" dataDxfId="50"/>
+    <tableColumn id="1" name="S. no" dataDxfId="69"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="68"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="67"/>
+    <tableColumn id="4" name="Stage" dataDxfId="0"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="66"/>
+    <tableColumn id="6" name="Current TAT (S50 onward)" dataDxfId="65"/>
+    <tableColumn id="7" name="S200 TAT" dataDxfId="64"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="63"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="62"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="61"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="60"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="59"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="58"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="57"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="56"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="55"/>
+    <tableColumn id="17" name="Remarks" dataDxfId="54"/>
+    <tableColumn id="18" name="Column1" dataDxfId="53"/>
+    <tableColumn id="19" name="Plateform" dataDxfId="52"/>
+    <tableColumn id="20" name="Column2" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5037,32 +5055,32 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
   <tableColumns count="19">
-    <tableColumn id="1" name="S. no" dataDxfId="49"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="48"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="47"/>
-    <tableColumn id="4" name="Stage" dataDxfId="46"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="45"/>
-    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="44"/>
-    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="43"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="42"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="41"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="40"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="39"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="38"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="37"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="36"/>
-    <tableColumn id="19" name="TS Pages" dataDxfId="35"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="34"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="33"/>
-    <tableColumn id="17" name="Delivered Date " dataDxfId="32"/>
-    <tableColumn id="18" name="Remarks" dataDxfId="31"/>
+    <tableColumn id="1" name="S. no" dataDxfId="50"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="49"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="48"/>
+    <tableColumn id="4" name="Stage" dataDxfId="47"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="46"/>
+    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="45"/>
+    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="44"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="43"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="42"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="41"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="40"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="39"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="38"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="37"/>
+    <tableColumn id="19" name="TS Pages" dataDxfId="36"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="35"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="34"/>
+    <tableColumn id="17" name="Delivered Date " dataDxfId="33"/>
+    <tableColumn id="18" name="Remarks" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="1" name="DESCriptions"/>
@@ -5074,11 +5092,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <autoFilter ref="B5:C10"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Month" dataDxfId="22"/>
-    <tableColumn id="2" name="No of titles delivered" dataDxfId="21">
+    <tableColumn id="1" name="Month" dataDxfId="23"/>
+    <tableColumn id="2" name="No of titles delivered" dataDxfId="22">
       <calculatedColumnFormula>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5375,7 +5393,7 @@
       <c r="B4" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="179" t="s">
+      <c r="C4" s="177" t="s">
         <v>46</v>
       </c>
       <c r="D4" t="s">
@@ -5418,7 +5436,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
         <v>137</v>
@@ -5442,7 +5460,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B7" t="s">
         <v>137</v>
@@ -5464,7 +5482,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
         <v>137</v>
@@ -5486,7 +5504,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
         <v>137</v>
@@ -5508,7 +5526,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
         <v>137</v>
@@ -5532,7 +5550,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
         <v>137</v>
@@ -5660,31 +5678,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" style="50" customWidth="1"/>
     <col min="2" max="2" width="13.08984375" style="69" customWidth="1"/>
     <col min="3" max="3" width="21.453125" style="69" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" style="50" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="27" customWidth="1"/>
-    <col min="6" max="6" width="23.90625" style="27" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" style="50" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" style="55" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" style="201" customWidth="1"/>
+    <col min="6" max="6" width="23.90625" style="201" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="55" customWidth="1"/>
     <col min="8" max="8" width="10" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="8.7265625" style="27" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="27" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7265625" style="27" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.08984375" style="55" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.6328125" style="50" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.54296875" style="115" customWidth="1"/>
-    <col min="16" max="16" width="16" style="115" customWidth="1"/>
-    <col min="17" max="17" width="15.81640625" style="115" customWidth="1"/>
+    <col min="15" max="15" width="19.54296875" style="113" customWidth="1"/>
+    <col min="16" max="16" width="16" style="113" customWidth="1"/>
+    <col min="17" max="17" width="15.81640625" style="113" customWidth="1"/>
     <col min="18" max="18" width="19.26953125" style="26" customWidth="1"/>
     <col min="19" max="19" width="15.81640625" style="26"/>
     <col min="20" max="16384" width="15.81640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" thickBot="1">
+    <row r="1" spans="1:20" ht="15" hidden="1" customHeight="1" thickBot="1">
       <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
@@ -5725,7 +5743,7 @@
         <v>53</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O1" s="27" t="s">
         <v>55</v>
@@ -5742,8 +5760,8 @@
       <c r="S1" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="T1" s="203" t="s">
-        <v>257</v>
+      <c r="T1" s="200" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="240">
@@ -5754,18 +5772,18 @@
       <c r="B2" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="116" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E2" s="53">
         <v>46258</v>
       </c>
       <c r="F2" s="88">
         <f ca="1">TODAY()-E2</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="52">
         <f>DATE(2026,9,19)-DATE(2026,8,24)</f>
@@ -5781,7 +5799,7 @@
       </c>
       <c r="J2" s="33">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="33"/>
       <c r="L2" s="33"/>
@@ -5791,22 +5809,22 @@
       <c r="N2" s="33">
         <v>500</v>
       </c>
-      <c r="O2" s="114" t="s">
+      <c r="O2" s="112" t="s">
         <v>69</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q2" s="150" t="s">
-        <v>195</v>
+        <v>201</v>
+      </c>
+      <c r="Q2" s="148" t="s">
+        <v>194</v>
       </c>
       <c r="R2" s="105" t="s">
         <v>101</v>
       </c>
       <c r="S2" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T2" s="202"/>
+        <v>168</v>
+      </c>
+      <c r="T2" s="199"/>
     </row>
     <row r="3" spans="1:20" ht="60">
       <c r="A3" s="52">
@@ -5816,8 +5834,8 @@
       <c r="B3" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="199" t="s">
-        <v>171</v>
+      <c r="C3" s="196" t="s">
+        <v>170</v>
       </c>
       <c r="D3" s="58" t="s">
         <v>137</v>
@@ -5827,7 +5845,7 @@
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F8" ca="1" si="1">TODAY()-E3</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="33">
         <f>DATE(2026,10,10)-DATE(2026,9,26)</f>
@@ -5838,11 +5856,11 @@
         <v>14</v>
       </c>
       <c r="I3" s="104">
-        <f>DATE(2026,10,27)-DATE(2026,10,25)</f>
-        <v>2</v>
+        <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
+        <v>3</v>
       </c>
       <c r="J3" s="54">
-        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <f ca="1">TODAY()-DATE(2026,10,29)</f>
         <v>0</v>
       </c>
       <c r="K3" s="26"/>
@@ -5853,22 +5871,22 @@
       <c r="N3" s="33">
         <v>200</v>
       </c>
-      <c r="O3" s="114" t="s">
+      <c r="O3" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P3" s="113" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q3" s="151" t="s">
+      <c r="P3" s="111" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q3" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="R3" s="157" t="s">
+      <c r="R3" s="155" t="s">
         <v>100</v>
       </c>
       <c r="S3" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T3" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T3" s="174"/>
     </row>
     <row r="4" spans="1:20" ht="60">
       <c r="A4" s="52">
@@ -5878,18 +5896,18 @@
       <c r="B4" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="198" t="s">
-        <v>172</v>
+      <c r="C4" s="195" t="s">
+        <v>171</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E4" s="35">
         <v>46291</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="33">
         <f>DATE(2026,10,12)-DATE(2026,9,26)</f>
@@ -5905,7 +5923,7 @@
       </c>
       <c r="J4" s="104">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="104"/>
       <c r="L4" s="104"/>
@@ -5915,18 +5933,18 @@
       <c r="N4" s="33">
         <v>200</v>
       </c>
-      <c r="O4" s="114" t="s">
+      <c r="O4" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="151" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="149" t="s">
         <v>74</v>
       </c>
       <c r="R4" s="105"/>
       <c r="S4" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T4" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T4" s="174"/>
     </row>
     <row r="5" spans="1:20" ht="60">
       <c r="A5" s="52">
@@ -5937,17 +5955,17 @@
         <v>25</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E5" s="35">
         <v>46288</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="68">
         <f>DATE(2026,10,8)-DATE(2026,9,23)</f>
@@ -5963,7 +5981,7 @@
       </c>
       <c r="J5" s="54">
         <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="54"/>
       <c r="L5" s="54"/>
@@ -5973,22 +5991,20 @@
       <c r="N5" s="33">
         <v>280</v>
       </c>
-      <c r="O5" s="114" t="s">
+      <c r="O5" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P5" s="113" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q5" s="151" t="s">
+      <c r="P5" s="111"/>
+      <c r="Q5" s="149" t="s">
         <v>73</v>
       </c>
       <c r="R5" s="105" t="s">
         <v>101</v>
       </c>
       <c r="S5" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T5" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T5" s="174"/>
     </row>
     <row r="6" spans="1:20" ht="60">
       <c r="A6" s="52">
@@ -5998,8 +6014,8 @@
       <c r="B6" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="198" t="s">
-        <v>174</v>
+      <c r="C6" s="195" t="s">
+        <v>173</v>
       </c>
       <c r="D6" s="33" t="s">
         <v>137</v>
@@ -6009,9 +6025,9 @@
       </c>
       <c r="F6" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="G6" s="193">
+        <v>36</v>
+      </c>
+      <c r="G6" s="191">
         <f>DATE(2026,10,14)-DATE(2026,10,2)</f>
         <v>12</v>
       </c>
@@ -6020,7 +6036,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <f>DATE(2026,10,28)-DATE(2026,10,28)</f>
         <v>0</v>
       </c>
       <c r="J6" s="104"/>
@@ -6032,22 +6048,22 @@
       <c r="N6" s="33">
         <v>240</v>
       </c>
-      <c r="O6" s="114" t="s">
+      <c r="O6" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P6" s="113" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q6" s="151" t="s">
+      <c r="P6" s="111" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q6" s="149" t="s">
         <v>154</v>
       </c>
-      <c r="R6" s="158" t="s">
-        <v>187</v>
+      <c r="R6" s="156" t="s">
+        <v>186</v>
       </c>
       <c r="S6" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T6" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T6" s="174"/>
     </row>
     <row r="7" spans="1:20" ht="60">
       <c r="A7" s="52">
@@ -6058,7 +6074,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>137</v>
@@ -6068,7 +6084,7 @@
       </c>
       <c r="F7" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" s="33">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
@@ -6078,7 +6094,7 @@
         <f>DATE(2026,10,24)-DATE(2026,10,8)</f>
         <v>16</v>
       </c>
-      <c r="I7" s="148">
+      <c r="I7" s="146">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
@@ -6091,83 +6107,80 @@
       <c r="N7" s="33">
         <v>244</v>
       </c>
-      <c r="O7" s="114" t="s">
+      <c r="O7" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P7" s="113" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q7" s="151" t="s">
+      <c r="P7" s="111" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q7" s="149" t="s">
         <v>128</v>
       </c>
       <c r="R7" s="105" t="s">
         <v>138</v>
       </c>
       <c r="S7" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T7" s="176"/>
-    </row>
-    <row r="8" spans="1:20" s="147" customFormat="1" ht="60">
-      <c r="A8" s="140">
+        <v>168</v>
+      </c>
+      <c r="T7" s="174"/>
+    </row>
+    <row r="8" spans="1:20" s="145" customFormat="1" ht="60">
+      <c r="A8" s="138">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="141" t="s">
+      <c r="B8" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="119" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="140" t="s">
-        <v>208</v>
-      </c>
-      <c r="E8" s="142">
+      <c r="C8" s="117" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="138" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="140">
         <v>46283</v>
       </c>
-      <c r="F8" s="140">
+      <c r="F8" s="138">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="G8" s="140">
+        <v>41</v>
+      </c>
+      <c r="G8" s="138">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H8" s="143">
+      <c r="H8" s="141">
         <f>DATE(2026,10,19)-DATE(2026,10,12)</f>
         <v>7</v>
       </c>
-      <c r="I8" s="143">
+      <c r="I8" s="141">
         <f ca="1">TODAY()-DATE(2026,10,20)</f>
-        <v>8</v>
-      </c>
-      <c r="J8" s="143">
+        <v>9</v>
+      </c>
+      <c r="J8" s="141">
         <f>DATE(2026,10,26)-DATE(2026,10,22)</f>
         <v>4</v>
       </c>
-      <c r="K8" s="143">
-        <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>1</v>
-      </c>
-      <c r="L8" s="144"/>
-      <c r="M8" s="140">
+      <c r="K8" s="141"/>
+      <c r="L8" s="142"/>
+      <c r="M8" s="138">
         <v>9</v>
       </c>
-      <c r="N8" s="140">
+      <c r="N8" s="138">
         <v>100</v>
       </c>
-      <c r="O8" s="145" t="s">
+      <c r="O8" s="143" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="146"/>
-      <c r="Q8" s="152" t="s">
+      <c r="P8" s="144"/>
+      <c r="Q8" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="144"/>
-      <c r="S8" s="144" t="s">
-        <v>169</v>
-      </c>
-      <c r="T8" s="176"/>
+      <c r="R8" s="142"/>
+      <c r="S8" s="142" t="s">
+        <v>168</v>
+      </c>
+      <c r="T8" s="174"/>
     </row>
     <row r="9" spans="1:20" ht="60">
       <c r="A9" s="33">
@@ -6178,17 +6191,17 @@
         <v>23</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E9" s="35">
         <v>46283</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" ref="F9:F19" ca="1" si="2">TODAY()-E9</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" s="33">
         <f>DATE(2026,10,9)-DATE(2026,9,21)</f>
@@ -6198,13 +6211,13 @@
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I9" s="148">
+      <c r="I9" s="146">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
       <c r="J9" s="104">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="105"/>
       <c r="L9" s="105"/>
@@ -6214,20 +6227,18 @@
       <c r="N9" s="33">
         <v>120</v>
       </c>
-      <c r="O9" s="114" t="s">
+      <c r="O9" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P9" s="113" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q9" s="151" t="s">
+      <c r="P9" s="111"/>
+      <c r="Q9" s="149" t="s">
         <v>73</v>
       </c>
       <c r="R9" s="105"/>
       <c r="S9" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T9" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T9" s="174"/>
     </row>
     <row r="10" spans="1:20" ht="60">
       <c r="A10" s="52">
@@ -6237,8 +6248,8 @@
       <c r="B10" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="199" t="s">
-        <v>178</v>
+      <c r="C10" s="196" t="s">
+        <v>177</v>
       </c>
       <c r="D10" s="58" t="s">
         <v>137</v>
@@ -6248,19 +6259,19 @@
       </c>
       <c r="F10" s="58">
         <f t="shared" ca="1" si="2"/>
-        <v>34</v>
-      </c>
-      <c r="G10" s="33">
-        <f ca="1">TODAY()-DATE(2026,9,25)</f>
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="G10" s="54">
+        <f>DATE(2026,10,11)-DATE(2026,9,25)</f>
+        <v>16</v>
       </c>
       <c r="H10" s="54">
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I10" s="148">
+      <c r="I10" s="146">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="105"/>
       <c r="K10" s="105"/>
@@ -6271,22 +6282,22 @@
       <c r="N10" s="33">
         <v>200</v>
       </c>
-      <c r="O10" s="114" t="s">
+      <c r="O10" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P10" s="113" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q10" s="151" t="s">
+      <c r="P10" s="111" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q10" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="R10" s="157" t="s">
+      <c r="R10" s="155" t="s">
         <v>100</v>
       </c>
       <c r="S10" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T10" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T10" s="174"/>
     </row>
     <row r="11" spans="1:20" ht="60">
       <c r="A11" s="52">
@@ -6296,8 +6307,8 @@
       <c r="B11" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="198" t="s">
-        <v>179</v>
+      <c r="C11" s="195" t="s">
+        <v>178</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>72</v>
@@ -6307,17 +6318,20 @@
       </c>
       <c r="F11" s="8">
         <f ca="1">TODAY()-E11</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" s="104">
         <f>DATE(2026,10,27)-DATE(2026,10,12)</f>
         <v>15</v>
       </c>
       <c r="H11" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,28)</f>
+        <f>DATE(2026,10,28)-DATE(2026,10,28)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="105"/>
+      <c r="I11" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,29)</f>
+        <v>0</v>
+      </c>
       <c r="J11" s="105"/>
       <c r="K11" s="105"/>
       <c r="L11" s="105"/>
@@ -6327,20 +6341,20 @@
       <c r="N11" s="33">
         <v>750</v>
       </c>
-      <c r="O11" s="114" t="s">
-        <v>237</v>
-      </c>
-      <c r="P11" s="113" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q11" s="151" t="s">
-        <v>166</v>
+      <c r="O11" s="112" t="s">
+        <v>228</v>
+      </c>
+      <c r="P11" s="111" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q11" s="149" t="s">
+        <v>165</v>
       </c>
       <c r="R11" s="105"/>
       <c r="S11" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T11" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T11" s="174"/>
     </row>
     <row r="12" spans="1:20" ht="60">
       <c r="A12" s="52">
@@ -6350,7 +6364,7 @@
       <c r="B12" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="198" t="s">
+      <c r="C12" s="195" t="s">
         <v>113</v>
       </c>
       <c r="D12" s="33" t="s">
@@ -6361,17 +6375,20 @@
       </c>
       <c r="F12" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G12" s="104">
         <f>DATE(2026,10,21)-DATE(2026,9,30)</f>
         <v>21</v>
       </c>
       <c r="H12" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <f>DATE(2026,10,28)-DATE(2026,10,26)</f>
         <v>2</v>
       </c>
-      <c r="I12" s="104"/>
+      <c r="I12" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,29)</f>
+        <v>0</v>
+      </c>
       <c r="J12" s="105"/>
       <c r="K12" s="105"/>
       <c r="L12" s="105"/>
@@ -6381,20 +6398,20 @@
       <c r="N12" s="33">
         <v>600</v>
       </c>
-      <c r="O12" s="114" t="s">
+      <c r="O12" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="113" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q12" s="151" t="s">
+      <c r="P12" s="111" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q12" s="149" t="s">
         <v>76</v>
       </c>
       <c r="R12" s="105"/>
       <c r="S12" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T12" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T12" s="174"/>
     </row>
     <row r="13" spans="1:20" ht="60">
       <c r="A13" s="52">
@@ -6404,7 +6421,7 @@
       <c r="B13" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="117" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6415,7 +6432,7 @@
       </c>
       <c r="F13" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="33">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
@@ -6423,11 +6440,11 @@
       </c>
       <c r="H13" s="107">
         <f ca="1">TODAY()-DATE(2026,10,7)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="107">
         <f ca="1">TODAY()-DATE(2026,10,23)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="107">
         <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
@@ -6439,7 +6456,7 @@
       </c>
       <c r="L13" s="104">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="33">
         <v>7</v>
@@ -6447,20 +6464,20 @@
       <c r="N13" s="33">
         <v>100</v>
       </c>
-      <c r="O13" s="114" t="s">
+      <c r="O13" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P13" s="113" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q13" s="151" t="s">
-        <v>200</v>
+      <c r="P13" s="111" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q13" s="149" t="s">
+        <v>199</v>
       </c>
       <c r="R13" s="105"/>
       <c r="S13" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T13" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T13" s="174"/>
     </row>
     <row r="14" spans="1:20" ht="60">
       <c r="A14" s="52">
@@ -6470,18 +6487,18 @@
       <c r="B14" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="119" t="s">
+      <c r="C14" s="117" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E14" s="35">
         <v>46282</v>
       </c>
       <c r="F14" s="33">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" s="33">
         <f>DATE(2026,10,6)-DATE(2026,9,17)</f>
@@ -6495,13 +6512,13 @@
         <f>DATE(2026,10,22)-DATE(2026,10,21)</f>
         <v>1</v>
       </c>
-      <c r="J14" s="139">
+      <c r="J14" s="137">
         <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
         <v>1</v>
       </c>
       <c r="K14" s="107">
         <f ca="1">TODAY()-DATE(2026,10,26)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="108"/>
       <c r="M14" s="33">
@@ -6510,18 +6527,18 @@
       <c r="N14" s="33">
         <v>500</v>
       </c>
-      <c r="O14" s="114" t="s">
+      <c r="O14" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="113"/>
-      <c r="Q14" s="153" t="s">
+      <c r="P14" s="111"/>
+      <c r="Q14" s="151" t="s">
         <v>76</v>
       </c>
       <c r="R14" s="105"/>
       <c r="S14" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T14" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T14" s="174"/>
     </row>
     <row r="15" spans="1:20" ht="60">
       <c r="A15" s="52">
@@ -6531,7 +6548,7 @@
       <c r="B15" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="198" t="s">
+      <c r="C15" s="195" t="s">
         <v>114</v>
       </c>
       <c r="D15" s="33" t="s">
@@ -6542,11 +6559,11 @@
       </c>
       <c r="F15" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G15" s="104">
         <f ca="1">TODAY()-DATE(2026,10,3)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" s="105"/>
       <c r="I15" s="105"/>
@@ -6559,20 +6576,20 @@
       <c r="N15" s="33">
         <v>500</v>
       </c>
-      <c r="O15" s="114" t="s">
-        <v>240</v>
-      </c>
-      <c r="P15" s="113" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q15" s="151" t="s">
-        <v>163</v>
+      <c r="O15" s="112" t="s">
+        <v>247</v>
+      </c>
+      <c r="P15" s="111" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q15" s="149" t="s">
+        <v>248</v>
       </c>
       <c r="R15" s="105"/>
       <c r="S15" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T15" s="176"/>
+        <v>167</v>
+      </c>
+      <c r="T15" s="174"/>
     </row>
     <row r="16" spans="1:20" ht="60">
       <c r="A16" s="52">
@@ -6582,7 +6599,7 @@
       <c r="B16" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="198" t="s">
+      <c r="C16" s="195" t="s">
         <v>96</v>
       </c>
       <c r="D16" s="33" t="s">
@@ -6593,7 +6610,7 @@
       </c>
       <c r="F16" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" s="104">
         <f>DATE(2026,10,27)-DATE(2026,9,28)</f>
@@ -6601,12 +6618,9 @@
       </c>
       <c r="H16" s="104">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I16" s="104"/>
       <c r="J16" s="105"/>
       <c r="K16" s="105"/>
       <c r="L16" s="105"/>
@@ -6616,18 +6630,18 @@
       <c r="N16" s="104">
         <v>500</v>
       </c>
-      <c r="O16" s="114" t="s">
-        <v>241</v>
-      </c>
-      <c r="P16" s="113" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q16" s="151"/>
+      <c r="O16" s="112" t="s">
+        <v>229</v>
+      </c>
+      <c r="P16" s="111" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q16" s="149"/>
       <c r="R16" s="105"/>
       <c r="S16" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T16" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T16" s="174"/>
     </row>
     <row r="17" spans="1:20" ht="60">
       <c r="A17" s="52">
@@ -6641,14 +6655,14 @@
         <v>102</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="E17" s="35">
         <v>46291</v>
       </c>
       <c r="F17" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="52">
         <f>DATE(2026,10,22)-DATE(2026,9,28)</f>
@@ -6660,7 +6674,7 @@
       </c>
       <c r="I17" s="104">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="105"/>
       <c r="K17" s="105"/>
@@ -6671,18 +6685,18 @@
       <c r="N17" s="104">
         <v>350</v>
       </c>
-      <c r="O17" s="117" t="s">
+      <c r="O17" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="P17" s="116" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q17" s="153"/>
+      <c r="P17" s="114" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q17" s="151"/>
       <c r="R17" s="105"/>
       <c r="S17" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T17" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T17" s="174"/>
     </row>
     <row r="18" spans="1:20" ht="60">
       <c r="A18" s="52">
@@ -6692,7 +6706,7 @@
       <c r="B18" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="201" t="s">
+      <c r="C18" s="198" t="s">
         <v>157</v>
       </c>
       <c r="D18" s="8" t="s">
@@ -6703,11 +6717,11 @@
       </c>
       <c r="F18" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="87">
         <f ca="1">TODAY()-DATE(2026,10,21)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="105"/>
       <c r="I18" s="105"/>
@@ -6721,33 +6735,33 @@
       <c r="N18" s="104">
         <v>1500</v>
       </c>
-      <c r="O18" s="117" t="s">
-        <v>214</v>
-      </c>
-      <c r="P18" s="113" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q18" s="154" t="s">
-        <v>188</v>
+      <c r="O18" s="115" t="s">
+        <v>250</v>
+      </c>
+      <c r="P18" s="111" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q18" s="152" t="s">
+        <v>187</v>
       </c>
       <c r="R18" s="105"/>
       <c r="S18" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T18" s="176"/>
+        <v>167</v>
+      </c>
+      <c r="T18" s="174"/>
     </row>
     <row r="19" spans="1:20" ht="33.5" customHeight="1">
       <c r="A19" s="52">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="B19" s="159" t="s">
+      <c r="B19" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="200" t="s">
+      <c r="C19" s="197" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="163" t="s">
+      <c r="D19" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="35">
@@ -6755,11 +6769,11 @@
       </c>
       <c r="F19" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="G19" s="106">
+        <v>29</v>
+      </c>
+      <c r="G19" s="104">
         <f ca="1">TODAY()-DATE(2026,10,13)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" s="105"/>
       <c r="I19" s="105"/>
@@ -6772,18 +6786,18 @@
       <c r="N19" s="104">
         <v>550</v>
       </c>
-      <c r="O19" s="114" t="s">
-        <v>215</v>
-      </c>
-      <c r="P19" s="113" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q19" s="151"/>
+      <c r="O19" s="112" t="s">
+        <v>251</v>
+      </c>
+      <c r="P19" s="111" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q19" s="149"/>
       <c r="R19" s="105"/>
       <c r="S19" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="T19" s="176"/>
+        <v>182</v>
+      </c>
+      <c r="T19" s="174"/>
     </row>
     <row r="20" spans="1:20" ht="60">
       <c r="A20" s="52">
@@ -6793,7 +6807,7 @@
       <c r="B20" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="198" t="s">
+      <c r="C20" s="195" t="s">
         <v>115</v>
       </c>
       <c r="D20" s="8" t="s">
@@ -6804,11 +6818,11 @@
       </c>
       <c r="F20" s="8">
         <f t="shared" ref="F20" ca="1" si="5">TODAY()-E20</f>
-        <v>28</v>
-      </c>
-      <c r="G20" s="106">
+        <v>29</v>
+      </c>
+      <c r="G20" s="104">
         <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="105"/>
       <c r="I20" s="105"/>
@@ -6821,18 +6835,18 @@
       <c r="N20" s="104">
         <v>450</v>
       </c>
-      <c r="O20" s="114" t="s">
-        <v>216</v>
-      </c>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="151" t="s">
-        <v>170</v>
+      <c r="O20" s="112" t="s">
+        <v>252</v>
+      </c>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="149" t="s">
+        <v>169</v>
       </c>
       <c r="R20" s="105"/>
       <c r="S20" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T20" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T20" s="174"/>
     </row>
     <row r="21" spans="1:20" ht="85">
       <c r="A21" s="52">
@@ -6853,9 +6867,12 @@
       </c>
       <c r="F21" s="8">
         <f ca="1">TODAY()-E21</f>
-        <v>16</v>
-      </c>
-      <c r="G21" s="106"/>
+        <v>17</v>
+      </c>
+      <c r="G21" s="104">
+        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <v>3</v>
+      </c>
       <c r="H21" s="105"/>
       <c r="I21" s="105"/>
       <c r="J21" s="105"/>
@@ -6867,22 +6884,22 @@
       <c r="N21" s="104">
         <v>350</v>
       </c>
-      <c r="O21" s="114" t="s">
-        <v>243</v>
-      </c>
-      <c r="P21" s="113" t="s">
+      <c r="O21" s="112" t="s">
+        <v>253</v>
+      </c>
+      <c r="P21" s="111" t="s">
         <v>254</v>
       </c>
-      <c r="Q21" s="151" t="s">
-        <v>255</v>
+      <c r="Q21" s="149" t="s">
+        <v>240</v>
       </c>
       <c r="R21" s="105" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="S21" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T21" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T21" s="174"/>
     </row>
     <row r="22" spans="1:20" ht="60">
       <c r="A22" s="52">
@@ -6903,15 +6920,15 @@
       </c>
       <c r="F22" s="107">
         <f ca="1">TODAY()-E22</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" s="104">
         <f ca="1">TODAY()-DATE(2026,10,19)</f>
-        <v>9</v>
-      </c>
-      <c r="H22" s="170"/>
-      <c r="I22" s="170"/>
-      <c r="J22" s="170"/>
+        <v>10</v>
+      </c>
+      <c r="H22" s="168"/>
+      <c r="I22" s="168"/>
+      <c r="J22" s="168"/>
       <c r="K22" s="105"/>
       <c r="L22" s="105"/>
       <c r="M22" s="33">
@@ -6920,16 +6937,16 @@
       <c r="N22" s="104">
         <v>500</v>
       </c>
-      <c r="O22" s="114" t="s">
-        <v>186</v>
-      </c>
-      <c r="P22" s="113"/>
-      <c r="Q22" s="155"/>
+      <c r="O22" s="112" t="s">
+        <v>185</v>
+      </c>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="153"/>
       <c r="R22" s="105"/>
       <c r="S22" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T22" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T22" s="174"/>
     </row>
     <row r="23" spans="1:20" ht="60">
       <c r="A23" s="52">
@@ -6939,7 +6956,7 @@
       <c r="B23" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="198" t="s">
+      <c r="C23" s="195" t="s">
         <v>110</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -6948,16 +6965,16 @@
       <c r="E23" s="9">
         <v>46302</v>
       </c>
-      <c r="F23" s="171">
+      <c r="F23" s="169">
         <f ca="1">TODAY()-E23</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G23" s="104" t="str">
         <f ca="1">TRIM(TODAY()-DATE(2026,10,19))</f>
-        <v>9</v>
-      </c>
-      <c r="H23" s="170"/>
-      <c r="I23" s="170"/>
+        <v>10</v>
+      </c>
+      <c r="H23" s="168"/>
+      <c r="I23" s="168"/>
       <c r="J23" s="105"/>
       <c r="K23" s="105"/>
       <c r="L23" s="105"/>
@@ -6967,21 +6984,21 @@
       <c r="N23" s="104">
         <v>450</v>
       </c>
-      <c r="O23" s="114" t="s">
-        <v>244</v>
-      </c>
-      <c r="P23" s="113"/>
-      <c r="Q23" s="155"/>
+      <c r="O23" s="112" t="s">
+        <v>230</v>
+      </c>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="153"/>
       <c r="R23" s="105"/>
       <c r="S23" s="105"/>
-      <c r="T23" s="176"/>
+      <c r="T23" s="174"/>
     </row>
     <row r="24" spans="1:20" ht="60">
       <c r="A24" s="52">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="B24" s="172" t="s">
+      <c r="B24" s="170" t="s">
         <v>129</v>
       </c>
       <c r="C24" s="34" t="s">
@@ -6990,16 +7007,16 @@
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="149">
+      <c r="E24" s="147">
         <v>46309</v>
       </c>
-      <c r="F24" s="171">
+      <c r="F24" s="169">
         <f ca="1">TODAY()-E24</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" s="104">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H24" s="105"/>
       <c r="I24" s="105"/>
@@ -7012,41 +7029,41 @@
       <c r="N24" s="104">
         <v>500</v>
       </c>
-      <c r="O24" s="114" t="s">
-        <v>205</v>
-      </c>
-      <c r="P24" s="113"/>
-      <c r="Q24" s="151"/>
+      <c r="O24" s="112" t="s">
+        <v>204</v>
+      </c>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="149"/>
       <c r="R24" s="105"/>
       <c r="S24" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T24" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T24" s="174"/>
     </row>
     <row r="25" spans="1:20" ht="60">
       <c r="A25" s="52">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="B25" s="172" t="s">
+      <c r="B25" s="170" t="s">
         <v>139</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="D25" s="163" t="s">
+      <c r="D25" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="149">
+      <c r="E25" s="147">
         <v>46312</v>
       </c>
-      <c r="F25" s="110">
+      <c r="F25" s="169">
         <f ca="1">TODAY()-E25</f>
-        <v>11</v>
-      </c>
-      <c r="G25" s="106">
+        <v>12</v>
+      </c>
+      <c r="G25" s="104">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H25" s="105"/>
       <c r="I25" s="105"/>
@@ -7056,42 +7073,42 @@
       <c r="M25" s="104">
         <v>23</v>
       </c>
-      <c r="N25" s="106">
+      <c r="N25" s="104">
         <v>350</v>
       </c>
-      <c r="O25" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="151"/>
+      <c r="O25" s="112" t="s">
+        <v>200</v>
+      </c>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="149"/>
       <c r="R25" s="105"/>
       <c r="S25" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T25" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T25" s="174"/>
     </row>
     <row r="26" spans="1:20" ht="60">
       <c r="A26" s="52">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="B26" s="173" t="s">
+      <c r="B26" s="171" t="s">
         <v>156</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26" s="111">
+        <v>19</v>
+      </c>
+      <c r="E26" s="147">
         <v>46312</v>
       </c>
-      <c r="F26" s="110">
+      <c r="F26" s="169">
         <f t="shared" ref="F26" ca="1" si="6">TODAY()-E26</f>
-        <v>11</v>
-      </c>
-      <c r="G26" s="106"/>
+        <v>12</v>
+      </c>
+      <c r="G26" s="104"/>
       <c r="H26" s="105"/>
       <c r="I26" s="105"/>
       <c r="J26" s="105"/>
@@ -7103,23 +7120,23 @@
       <c r="N26" s="104">
         <v>300</v>
       </c>
-      <c r="O26" s="114" t="s">
-        <v>217</v>
-      </c>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="156"/>
+      <c r="O26" s="112" t="s">
+        <v>255</v>
+      </c>
+      <c r="P26" s="110"/>
+      <c r="Q26" s="154"/>
       <c r="R26" s="105"/>
       <c r="S26" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T26" s="176"/>
-    </row>
-    <row r="27" spans="1:20">
+        <v>167</v>
+      </c>
+      <c r="T26" s="174"/>
+    </row>
+    <row r="27" spans="1:20" ht="60">
       <c r="A27" s="52">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="B27" s="121" t="s">
+      <c r="B27" s="119" t="s">
         <v>159</v>
       </c>
       <c r="C27" s="34" t="s">
@@ -7128,40 +7145,45 @@
       <c r="D27" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E27" s="111">
+      <c r="E27" s="147">
         <v>46316</v>
       </c>
-      <c r="F27" s="110">
-        <f t="shared" ref="F27:F33" ca="1" si="7">TODAY()-E27</f>
-        <v>7</v>
-      </c>
-      <c r="G27" s="106"/>
+      <c r="F27" s="169">
+        <f t="shared" ref="F27:F35" ca="1" si="7">TODAY()-E27</f>
+        <v>8</v>
+      </c>
+      <c r="G27" s="104" t="str">
+        <f ca="1">TRIM(TODAY()-DATE(2026,10,26))</f>
+        <v>3</v>
+      </c>
       <c r="H27" s="105"/>
       <c r="I27" s="105"/>
       <c r="J27" s="105"/>
       <c r="K27" s="105"/>
-      <c r="L27" s="120"/>
+      <c r="L27" s="118"/>
       <c r="M27" s="33">
         <v>109</v>
       </c>
       <c r="N27" s="106">
         <v>350</v>
       </c>
-      <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
-      <c r="Q27" s="156"/>
+      <c r="O27" s="112" t="s">
+        <v>256</v>
+      </c>
+      <c r="P27" s="110"/>
+      <c r="Q27" s="154"/>
       <c r="R27" s="105"/>
       <c r="S27" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T27" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T27" s="174"/>
     </row>
     <row r="28" spans="1:20" ht="60">
       <c r="A28" s="52">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="B28" s="121" t="s">
+      <c r="B28" s="119" t="s">
         <v>161</v>
       </c>
       <c r="C28" s="34" t="s">
@@ -7170,321 +7192,360 @@
       <c r="D28" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E28" s="149">
+      <c r="E28" s="147">
         <v>46316</v>
       </c>
-      <c r="F28" s="171">
+      <c r="F28" s="169">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="104">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>3</v>
-      </c>
-      <c r="H28" s="170"/>
-      <c r="I28" s="170"/>
+        <v>4</v>
+      </c>
+      <c r="H28" s="168"/>
+      <c r="I28" s="168"/>
       <c r="J28" s="105"/>
       <c r="K28" s="105"/>
-      <c r="L28" s="120"/>
+      <c r="L28" s="118"/>
       <c r="M28" s="33">
         <v>69</v>
       </c>
       <c r="N28" s="104">
         <v>400</v>
       </c>
-      <c r="O28" s="114" t="s">
-        <v>218</v>
-      </c>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="156"/>
+      <c r="O28" s="112" t="s">
+        <v>212</v>
+      </c>
+      <c r="P28" s="110"/>
+      <c r="Q28" s="154"/>
       <c r="R28" s="105"/>
       <c r="S28" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T28" s="176"/>
+        <v>167</v>
+      </c>
+      <c r="T28" s="174"/>
     </row>
     <row r="29" spans="1:20" ht="60">
       <c r="A29" s="52">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="B29" s="121" t="s">
-        <v>167</v>
+      <c r="B29" s="119" t="s">
+        <v>166</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="149">
+      <c r="E29" s="147">
         <v>46312</v>
       </c>
-      <c r="F29" s="171">
+      <c r="F29" s="169">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="104">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>6</v>
-      </c>
-      <c r="H29" s="170"/>
-      <c r="I29" s="195"/>
-      <c r="J29" s="170"/>
-      <c r="K29" s="195"/>
-      <c r="L29" s="195"/>
+        <v>7</v>
+      </c>
+      <c r="H29" s="168"/>
+      <c r="I29" s="192"/>
+      <c r="J29" s="168"/>
+      <c r="K29" s="192"/>
+      <c r="L29" s="192"/>
       <c r="M29" s="33">
         <v>33</v>
       </c>
       <c r="N29" s="104">
         <v>450</v>
       </c>
-      <c r="O29" s="114" t="s">
-        <v>219</v>
-      </c>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="156"/>
+      <c r="O29" s="112" t="s">
+        <v>257</v>
+      </c>
+      <c r="P29" s="110"/>
+      <c r="Q29" s="154"/>
       <c r="R29" s="105"/>
       <c r="S29" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T29" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T29" s="174"/>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="33">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="B30" s="121" t="s">
+      <c r="B30" s="119" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="C30" s="34" t="s">
-        <v>194</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="111">
-        <v>46316</v>
-      </c>
-      <c r="F30" s="110">
+        <v>233</v>
+      </c>
+      <c r="E30" s="147">
+        <v>46323</v>
+      </c>
+      <c r="F30" s="169">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="G30" s="106"/>
+        <v>1</v>
+      </c>
+      <c r="G30" s="104"/>
       <c r="H30" s="105"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="120"/>
-      <c r="L30" s="120"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="118"/>
       <c r="M30" s="33">
         <v>21</v>
       </c>
       <c r="N30" s="106">
         <v>150</v>
       </c>
-      <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="112"/>
+      <c r="O30" s="110"/>
+      <c r="P30" s="110"/>
+      <c r="Q30" s="110"/>
       <c r="R30" s="105"/>
       <c r="S30" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T30" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T30" s="174"/>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="33">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="B31" s="196" t="s">
-        <v>206</v>
-      </c>
-      <c r="C31" s="196" t="s">
-        <v>220</v>
+      <c r="B31" s="193" t="s">
+        <v>205</v>
+      </c>
+      <c r="C31" s="193" t="s">
+        <v>213</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="111">
+        <v>233</v>
+      </c>
+      <c r="E31" s="147">
         <v>46321</v>
       </c>
-      <c r="F31" s="110">
+      <c r="F31" s="169">
         <f t="shared" ca="1" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="G31" s="106"/>
+        <v>3</v>
+      </c>
+      <c r="G31" s="104"/>
       <c r="H31" s="105"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="120"/>
-      <c r="L31" s="120"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="118"/>
       <c r="M31" s="33">
         <v>12</v>
       </c>
       <c r="N31" s="106">
         <v>150</v>
       </c>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
+      <c r="O31" s="110"/>
+      <c r="P31" s="110"/>
+      <c r="Q31" s="110"/>
       <c r="R31" s="105"/>
       <c r="S31" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T31" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T31" s="174"/>
     </row>
     <row r="32" spans="1:20" ht="29">
       <c r="A32" s="33">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="B32" s="196" t="s">
-        <v>207</v>
-      </c>
-      <c r="C32" s="196" t="s">
-        <v>221</v>
+      <c r="B32" s="193" t="s">
+        <v>206</v>
+      </c>
+      <c r="C32" s="193" t="s">
+        <v>214</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="111">
+        <v>19</v>
+      </c>
+      <c r="E32" s="147">
         <v>46322</v>
       </c>
-      <c r="F32" s="110">
+      <c r="F32" s="169">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="G32" s="106"/>
+        <v>2</v>
+      </c>
+      <c r="G32" s="104"/>
       <c r="H32" s="105"/>
-      <c r="I32" s="120"/>
-      <c r="J32" s="120"/>
-      <c r="K32" s="120"/>
-      <c r="L32" s="120"/>
+      <c r="I32" s="118"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="118"/>
+      <c r="L32" s="118"/>
       <c r="M32" s="33">
         <v>20</v>
       </c>
       <c r="N32" s="106">
         <v>450</v>
       </c>
-      <c r="O32" s="112"/>
-      <c r="P32" s="112"/>
-      <c r="Q32" s="112"/>
+      <c r="O32" s="110"/>
+      <c r="P32" s="110"/>
+      <c r="Q32" s="110"/>
       <c r="R32" s="105"/>
       <c r="S32" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T32" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T32" s="174"/>
     </row>
     <row r="33" spans="1:20" ht="28">
       <c r="A33" s="33">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="B33" s="178" t="s">
-        <v>224</v>
+      <c r="B33" s="176" t="s">
+        <v>217</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E33" s="111">
+        <v>233</v>
+      </c>
+      <c r="E33" s="147">
         <v>46322</v>
       </c>
-      <c r="F33" s="110">
+      <c r="F33" s="169">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="G33" s="106"/>
+        <v>2</v>
+      </c>
+      <c r="G33" s="104"/>
       <c r="H33" s="105"/>
-      <c r="I33" s="120"/>
-      <c r="J33" s="120"/>
-      <c r="K33" s="120"/>
-      <c r="L33" s="120"/>
+      <c r="I33" s="118"/>
+      <c r="J33" s="118"/>
+      <c r="K33" s="118"/>
+      <c r="L33" s="118"/>
       <c r="M33" s="33">
         <v>16</v>
       </c>
       <c r="N33" s="106">
         <v>200</v>
       </c>
-      <c r="O33" s="176"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="176"/>
+      <c r="O33" s="174"/>
+      <c r="P33" s="174"/>
+      <c r="Q33" s="174"/>
       <c r="R33" s="105"/>
       <c r="S33" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="T33" s="176"/>
+        <v>168</v>
+      </c>
+      <c r="T33" s="174"/>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" s="33">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="B34" s="197" t="s">
-        <v>222</v>
-      </c>
-      <c r="C34" s="197" t="s">
-        <v>223</v>
+      <c r="B34" s="194" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="194" t="s">
+        <v>216</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="106"/>
+      <c r="E34" s="168"/>
+      <c r="F34" s="168"/>
+      <c r="G34" s="104"/>
       <c r="H34" s="105"/>
-      <c r="I34" s="120"/>
-      <c r="J34" s="120"/>
-      <c r="K34" s="120"/>
-      <c r="L34" s="120"/>
+      <c r="I34" s="118"/>
+      <c r="J34" s="118"/>
+      <c r="K34" s="118"/>
+      <c r="L34" s="118"/>
       <c r="M34" s="33"/>
       <c r="N34" s="106"/>
-      <c r="O34" s="176"/>
-      <c r="P34" s="176"/>
-      <c r="Q34" s="176"/>
+      <c r="O34" s="174"/>
+      <c r="P34" s="174"/>
+      <c r="Q34" s="174"/>
       <c r="R34" s="105"/>
       <c r="S34" s="105"/>
-      <c r="T34" s="176"/>
+      <c r="T34" s="174"/>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="33">
         <f t="shared" si="4"/>
         <v>34</v>
       </c>
-      <c r="B35" s="178" t="s">
-        <v>245</v>
+      <c r="B35" s="176" t="s">
+        <v>231</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="106"/>
+      <c r="E35" s="203">
+        <v>46323</v>
+      </c>
+      <c r="F35" s="169">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G35" s="104"/>
       <c r="H35" s="105"/>
-      <c r="I35" s="120"/>
-      <c r="J35" s="120"/>
-      <c r="K35" s="120"/>
-      <c r="L35" s="120"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="106"/>
-      <c r="O35" s="176"/>
-      <c r="P35" s="176"/>
-      <c r="Q35" s="176"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="118"/>
+      <c r="M35" s="33">
+        <v>74</v>
+      </c>
+      <c r="N35" s="106">
+        <v>700</v>
+      </c>
+      <c r="O35" s="174"/>
+      <c r="P35" s="174"/>
+      <c r="Q35" s="174"/>
       <c r="R35" s="105"/>
       <c r="S35" s="105"/>
-      <c r="T35" s="194" t="s">
-        <v>256</v>
+      <c r="T35" s="174" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="36" spans="1:20">
-      <c r="R36" s="177"/>
-      <c r="S36" s="177"/>
+      <c r="A36" s="33">
+        <v>35</v>
+      </c>
+      <c r="B36" s="176" t="s">
+        <v>259</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="206"/>
+      <c r="F36" s="206"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="204"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="204"/>
+      <c r="L36" s="204"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="205"/>
+      <c r="O36" s="174"/>
+      <c r="P36" s="174"/>
+      <c r="Q36" s="174"/>
+      <c r="R36" s="105"/>
+      <c r="S36" s="105"/>
+      <c r="T36" s="174"/>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="R37" s="175"/>
+      <c r="S37" s="175"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7535,37 +7596,37 @@
       <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="137" t="s">
+      <c r="E1" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="138" t="s">
+      <c r="F1" s="136" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="138" t="s">
+      <c r="G1" s="136" t="s">
         <v>125</v>
       </c>
-      <c r="H1" s="138" t="s">
+      <c r="H1" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="138" t="s">
+      <c r="I1" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="138" t="s">
+      <c r="J1" s="136" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="138" t="s">
+      <c r="K1" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="137" t="s">
+      <c r="L1" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="138" t="s">
+      <c r="M1" s="136" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="138" t="s">
-        <v>199</v>
-      </c>
-      <c r="O1" s="138" t="s">
+      <c r="N1" s="136" t="s">
+        <v>198</v>
+      </c>
+      <c r="O1" s="136" t="s">
         <v>54</v>
       </c>
       <c r="P1" s="23" t="s">
@@ -8033,7 +8094,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>45</v>
@@ -8098,7 +8159,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D10" s="31" t="s">
         <v>45</v>
@@ -8163,7 +8224,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D11" s="31" t="s">
         <v>45</v>
@@ -8431,7 +8492,7 @@
       <c r="D15" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="168">
+      <c r="E15" s="166">
         <v>46204</v>
       </c>
       <c r="F15" s="41">
@@ -8475,10 +8536,10 @@
       <c r="P15" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="Q15" s="164" t="s">
+      <c r="Q15" s="162" t="s">
         <v>59</v>
       </c>
-      <c r="R15" s="166">
+      <c r="R15" s="164">
         <v>46301</v>
       </c>
     </row>
@@ -8496,7 +8557,7 @@
       <c r="D16" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="168">
+      <c r="E16" s="166">
         <v>46204</v>
       </c>
       <c r="F16" s="41">
@@ -8530,16 +8591,16 @@
       <c r="O16" s="16">
         <v>333</v>
       </c>
-      <c r="P16" s="128" t="s">
+      <c r="P16" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="Q16" s="164" t="s">
+      <c r="Q16" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="166">
+      <c r="R16" s="164">
         <v>46307</v>
       </c>
-      <c r="S16" s="122"/>
+      <c r="S16" s="120"/>
     </row>
     <row r="17" spans="1:19" ht="60">
       <c r="A17" s="28">
@@ -8555,7 +8616,7 @@
       <c r="D17" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="168">
+      <c r="E17" s="166">
         <v>46265</v>
       </c>
       <c r="F17" s="41">
@@ -8599,7 +8660,7 @@
         <v>69</v>
       </c>
       <c r="Q17" s="31"/>
-      <c r="R17" s="166">
+      <c r="R17" s="164">
         <v>46309</v>
       </c>
       <c r="S17" s="109"/>
@@ -8612,16 +8673,16 @@
       <c r="B18" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="180" t="s">
+      <c r="C18" s="178" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="181" t="s">
+      <c r="D18" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="168">
+      <c r="E18" s="166">
         <v>46269</v>
       </c>
-      <c r="F18" s="169">
+      <c r="F18" s="167">
         <f>DATE(2026,10,26)-E18</f>
         <v>52</v>
       </c>
@@ -8662,10 +8723,10 @@
         <v>69</v>
       </c>
       <c r="Q18" s="28"/>
-      <c r="R18" s="167">
+      <c r="R18" s="165">
         <v>46321</v>
       </c>
-      <c r="S18" s="165"/>
+      <c r="S18" s="163"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8723,13 +8784,13 @@
       <c r="A3" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="182">
+      <c r="B3" s="180">
         <f>COUNTA(Table2[MPS ID])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="95">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>
-        <v>24.46875</v>
+        <v>24.515151515151516</v>
       </c>
       <c r="D3" s="92"/>
       <c r="G3" s="84"/>
@@ -8741,7 +8802,7 @@
       <c r="A4" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="129">
+      <c r="B4" s="127">
         <f>COUNTA(Delivered!C2:C18)</f>
         <v>17</v>
       </c>
@@ -8753,176 +8814,176 @@
       <c r="E4" s="84"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="183"/>
-      <c r="B5" s="183"/>
-      <c r="C5" s="183"/>
-      <c r="D5" s="183"/>
+      <c r="A5" s="181"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
     </row>
     <row r="6" spans="1:11" ht="36">
-      <c r="A6" s="186" t="s">
-        <v>227</v>
-      </c>
-      <c r="B6" s="187" t="s">
+      <c r="A6" s="184" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="187" t="s">
+      <c r="C6" s="185" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="187" t="s">
+      <c r="D6" s="185" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="187" t="s">
-        <v>182</v>
-      </c>
-      <c r="F6" s="187" t="s">
-        <v>208</v>
-      </c>
-      <c r="G6" s="187" t="s">
+      <c r="E6" s="185" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="185" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="187" t="s">
-        <v>232</v>
+      <c r="H6" s="185" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="184">
+        <v>222</v>
+      </c>
+      <c r="B7" s="182">
         <f>Delivered!G2</f>
         <v>32</v>
       </c>
-      <c r="C7" s="184">
+      <c r="C7" s="182">
         <f>Delivered!H2</f>
         <v>11</v>
       </c>
-      <c r="D7" s="184">
+      <c r="D7" s="182">
         <f>Delivered!I2</f>
         <v>3</v>
       </c>
-      <c r="E7" s="184">
+      <c r="E7" s="182">
         <f>Delivered!J2</f>
         <v>6</v>
       </c>
-      <c r="F7" s="184">
+      <c r="F7" s="182">
         <f>Delivered!K2</f>
         <v>6</v>
       </c>
-      <c r="G7" s="184">
+      <c r="G7" s="182">
         <f>Delivered!L2</f>
         <v>5</v>
       </c>
-      <c r="H7" s="191">
+      <c r="H7" s="189">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="185">
+        <v>221</v>
+      </c>
+      <c r="B8" s="183">
         <f>AVERAGE(Delivered!G3:G11)</f>
         <v>25</v>
       </c>
-      <c r="C8" s="185">
+      <c r="C8" s="183">
         <f>AVERAGE(Delivered!H3:H11)</f>
         <v>11.777777777777779</v>
       </c>
-      <c r="D8" s="185">
+      <c r="D8" s="183">
         <f>AVERAGE(Delivered!I3:I11)</f>
         <v>4.1111111111111107</v>
       </c>
-      <c r="E8" s="185">
+      <c r="E8" s="183">
         <f>AVERAGE(Delivered!J3:J11)</f>
         <v>6.8888888888888893</v>
       </c>
-      <c r="F8" s="185">
+      <c r="F8" s="183">
         <f>AVERAGE(Delivered!K3:K11)</f>
         <v>5.8888888888888893</v>
       </c>
-      <c r="G8" s="185">
+      <c r="G8" s="183">
         <f>AVERAGE(Delivered!L3:L11)</f>
         <v>6</v>
       </c>
-      <c r="H8" s="191">
+      <c r="H8" s="189">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="188" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="189">
+      <c r="A9" s="186" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="187">
         <f>AVERAGE(Delivered!G12:G21)</f>
         <v>27.428571428571427</v>
       </c>
-      <c r="C9" s="189">
+      <c r="C9" s="187">
         <f>AVERAGE(Delivered!H12:H21)</f>
         <v>11.714285714285714</v>
       </c>
-      <c r="D9" s="189">
+      <c r="D9" s="187">
         <f>AVERAGE(Delivered!I12:I21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="E9" s="189">
+      <c r="E9" s="187">
         <f>AVERAGE(Delivered!J12:J21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="F9" s="189">
+      <c r="F9" s="187">
         <f>AVERAGE(Delivered!K12:K21)</f>
         <v>6.8571428571428568</v>
       </c>
-      <c r="G9" s="189">
+      <c r="G9" s="187">
         <f>AVERAGE(Delivered!L12:L21)</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="H9" s="191">
+      <c r="H9" s="189">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29">
-      <c r="A10" s="190" t="s">
-        <v>231</v>
-      </c>
-      <c r="B10" s="191">
+      <c r="A10" s="188" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" s="189">
         <f>AVERAGE(B7:B9)</f>
         <v>28.142857142857142</v>
       </c>
-      <c r="C10" s="191">
+      <c r="C10" s="189">
         <f t="shared" ref="C10:G10" si="0">AVERAGE(C7:C9)</f>
         <v>11.497354497354499</v>
       </c>
-      <c r="D10" s="191">
+      <c r="D10" s="189">
         <f t="shared" si="0"/>
         <v>3.7513227513227512</v>
       </c>
-      <c r="E10" s="191">
+      <c r="E10" s="189">
         <f t="shared" si="0"/>
         <v>5.6772486772486772</v>
       </c>
-      <c r="F10" s="191">
+      <c r="F10" s="189">
         <f t="shared" si="0"/>
         <v>6.2486772486772493</v>
       </c>
-      <c r="G10" s="191">
+      <c r="G10" s="189">
         <f t="shared" si="0"/>
         <v>5.1904761904761907</v>
       </c>
       <c r="H10" s="10"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="192" t="s">
-        <v>233</v>
-      </c>
-      <c r="B12" s="192">
+      <c r="A12" s="190" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="190">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="192" t="s">
-        <v>234</v>
-      </c>
-      <c r="B13" s="192">
+      <c r="A13" s="190" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="190">
         <v>103</v>
       </c>
     </row>
@@ -8931,7 +8992,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8939,7 +9000,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8947,12 +9008,12 @@
         <v>137</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" s="10">
         <v>2</v>
@@ -8960,7 +9021,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B19" s="10">
         <v>2</v>
@@ -9006,10 +9067,10 @@
       <c r="J2" s="79"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="202" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="204"/>
+      <c r="C3" s="202"/>
       <c r="E3" s="79"/>
       <c r="F3" s="80"/>
       <c r="G3" s="79"/>
@@ -9451,7 +9512,7 @@
       </c>
       <c r="F8" s="5">
         <f ca="1">TODAY()-DATE(2026,9,25)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="5" t="e">
         <f ca="1">TODAY()-#REF!</f>
@@ -9459,7 +9520,7 @@
       </c>
       <c r="H8" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 33 days buffer</v>
+        <v>On Track. 32 days buffer</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -9475,7 +9536,7 @@
       </c>
       <c r="D9" s="16">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -9485,7 +9546,7 @@
       </c>
       <c r="H9" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 34 days buffer</v>
+        <v>On Track. 33 days buffer</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -9501,7 +9562,7 @@
       </c>
       <c r="D10" s="16">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -9511,7 +9572,7 @@
       </c>
       <c r="H10" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 34 days buffer</v>
+        <v>On Track. 33 days buffer</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -9531,7 +9592,7 @@
       </c>
       <c r="E11" s="7">
         <f ca="1">TODAY()-DATE(2026,9,16)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="e">
@@ -9540,7 +9601,7 @@
       </c>
       <c r="H11" s="18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>On Track. 32 days buffer</v>
+        <v>On Track. 31 days buffer</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -9855,10 +9916,10 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="10"/>
-      <c r="C46" s="124" t="s">
-        <v>165</v>
-      </c>
-      <c r="D46" s="125">
+      <c r="C46" s="122" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="123">
         <f>COUNTA(D49:D81)</f>
         <v>33</v>
       </c>
@@ -9866,19 +9927,19 @@
     </row>
     <row r="47" spans="2:6" ht="15" thickBot="1">
       <c r="B47" s="10"/>
-      <c r="C47" s="126" t="s">
+      <c r="C47" s="124" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="125">
+        <v>17</v>
+      </c>
+      <c r="E47" s="125" t="s">
         <v>180</v>
-      </c>
-      <c r="D47" s="127">
-        <v>17</v>
-      </c>
-      <c r="E47" s="127" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="15" thickBot="1">
       <c r="B48" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C48" s="22" t="s">
         <v>2</v>
@@ -9886,10 +9947,10 @@
       <c r="D48" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="123" t="s">
+      <c r="E48" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="132" t="s">
+      <c r="F48" s="130" t="s">
         <v>57</v>
       </c>
     </row>
@@ -9897,13 +9958,13 @@
       <c r="B49" s="18">
         <v>1</v>
       </c>
-      <c r="C49" s="131" t="s">
+      <c r="C49" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="130" t="s">
-        <v>182</v>
-      </c>
-      <c r="E49" s="133">
+      <c r="D49" s="128" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49" s="131">
         <v>64</v>
       </c>
       <c r="F49" s="10"/>
@@ -9912,13 +9973,13 @@
       <c r="B50" s="18">
         <v>2</v>
       </c>
-      <c r="C50" s="119" t="s">
+      <c r="C50" s="117" t="s">
         <v>36</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E50" s="136">
+        <v>207</v>
+      </c>
+      <c r="E50" s="134">
         <v>40</v>
       </c>
       <c r="F50" s="26"/>
@@ -9928,7 +9989,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D51" s="33" t="s">
         <v>137</v>
@@ -9942,13 +10003,13 @@
       <c r="B52" s="18">
         <v>4</v>
       </c>
-      <c r="C52" s="119" t="s">
-        <v>177</v>
-      </c>
-      <c r="D52" s="140" t="s">
-        <v>182</v>
-      </c>
-      <c r="E52" s="135">
+      <c r="C52" s="117" t="s">
+        <v>176</v>
+      </c>
+      <c r="D52" s="138" t="s">
+        <v>181</v>
+      </c>
+      <c r="E52" s="133">
         <v>39</v>
       </c>
       <c r="F52" s="10"/>
@@ -9958,7 +10019,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D53" s="33" t="s">
         <v>137</v>
@@ -9972,30 +10033,30 @@
       <c r="B54" s="18">
         <v>6</v>
       </c>
-      <c r="C54" s="119" t="s">
+      <c r="C54" s="117" t="s">
         <v>34</v>
       </c>
       <c r="D54" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E54" s="134">
+        <v>207</v>
+      </c>
+      <c r="E54" s="132">
         <v>36</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="H54" s="174" t="s">
+      <c r="H54" s="172" t="s">
+        <v>208</v>
+      </c>
+      <c r="I54" s="172">
+        <v>30</v>
+      </c>
+      <c r="J54" s="172" t="s">
+        <v>209</v>
+      </c>
+      <c r="K54" s="172" t="s">
         <v>210</v>
-      </c>
-      <c r="I54" s="174">
-        <v>30</v>
-      </c>
-      <c r="J54" s="174" t="s">
-        <v>211</v>
-      </c>
-      <c r="K54" s="174" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="55" spans="2:11" ht="29">
@@ -10003,7 +10064,7 @@
         <v>7</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D55" s="33" t="s">
         <v>137</v>
@@ -10015,17 +10076,17 @@
       <c r="G55" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="H55" s="174" t="s">
+      <c r="H55" s="172" t="s">
+        <v>208</v>
+      </c>
+      <c r="I55" s="172">
+        <v>46</v>
+      </c>
+      <c r="J55" s="172" t="s">
+        <v>209</v>
+      </c>
+      <c r="K55" s="172" t="s">
         <v>210</v>
-      </c>
-      <c r="I55" s="174">
-        <v>46</v>
-      </c>
-      <c r="J55" s="174" t="s">
-        <v>211</v>
-      </c>
-      <c r="K55" s="174" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="56" spans="2:11" ht="29">
@@ -10033,7 +10094,7 @@
         <v>8</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D56" s="33" t="s">
         <v>72</v>
@@ -10045,17 +10106,17 @@
       <c r="G56" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="H56" s="174" t="s">
-        <v>213</v>
-      </c>
-      <c r="I56" s="174">
+      <c r="H56" s="172" t="s">
+        <v>211</v>
+      </c>
+      <c r="I56" s="172">
         <v>58</v>
       </c>
-      <c r="J56" s="174" t="s">
-        <v>211</v>
-      </c>
-      <c r="K56" s="174" t="s">
-        <v>212</v>
+      <c r="J56" s="172" t="s">
+        <v>209</v>
+      </c>
+      <c r="K56" s="172" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="2:11">
@@ -10063,7 +10124,7 @@
         <v>9</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D57" s="58" t="s">
         <v>137</v>
@@ -10078,7 +10139,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D58" s="58" t="s">
         <v>137</v>
@@ -10093,12 +10154,12 @@
         <v>11</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D59" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E59" s="136">
+      <c r="E59" s="134">
         <v>31</v>
       </c>
       <c r="F59" s="10"/>
@@ -10113,7 +10174,7 @@
       <c r="D60" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="E60" s="136">
+      <c r="E60" s="134">
         <v>31</v>
       </c>
       <c r="F60" s="10"/>
@@ -10152,13 +10213,13 @@
       <c r="B63" s="18">
         <v>15</v>
       </c>
-      <c r="C63" s="160" t="s">
+      <c r="C63" s="158" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="161" t="s">
+      <c r="D63" s="159" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="136">
+      <c r="E63" s="134">
         <v>28</v>
       </c>
       <c r="F63" s="10"/>
@@ -10168,7 +10229,7 @@
         <v>16</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>19</v>
@@ -10182,13 +10243,13 @@
       <c r="B65" s="18">
         <v>17</v>
       </c>
-      <c r="C65" s="160" t="s">
+      <c r="C65" s="158" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="163" t="s">
+      <c r="D65" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="136">
+      <c r="E65" s="134">
         <v>27</v>
       </c>
       <c r="F65" s="10"/>
@@ -10197,13 +10258,13 @@
       <c r="B66" s="18">
         <v>18</v>
       </c>
-      <c r="C66" s="160" t="s">
+      <c r="C66" s="158" t="s">
         <v>115</v>
       </c>
-      <c r="D66" s="163" t="s">
+      <c r="D66" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="136">
+      <c r="E66" s="134">
         <v>27</v>
       </c>
       <c r="F66" s="10"/>
@@ -10212,10 +10273,10 @@
       <c r="B67" s="18">
         <v>19</v>
       </c>
-      <c r="C67" s="162" t="s">
+      <c r="C67" s="160" t="s">
         <v>157</v>
       </c>
-      <c r="D67" s="163" t="s">
+      <c r="D67" s="161" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="8">
@@ -10246,9 +10307,9 @@
         <v>136</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="E69" s="136">
+        <v>203</v>
+      </c>
+      <c r="E69" s="134">
         <v>15</v>
       </c>
       <c r="F69" s="10"/>
@@ -10267,7 +10328,7 @@
         <v>15</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -10289,10 +10350,10 @@
       <c r="B72" s="18">
         <v>24</v>
       </c>
-      <c r="C72" s="160" t="s">
+      <c r="C72" s="158" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="163" t="s">
+      <c r="D72" s="161" t="s">
         <v>19</v>
       </c>
       <c r="E72" s="18">
@@ -10305,7 +10366,7 @@
         <v>25</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>158</v>
@@ -10320,7 +10381,7 @@
         <v>26</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>19</v>
@@ -10365,7 +10426,7 @@
         <v>29</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>24</v>
@@ -10379,8 +10440,8 @@
       <c r="B78" s="18">
         <v>30</v>
       </c>
-      <c r="C78" s="175" t="s">
-        <v>220</v>
+      <c r="C78" s="173" t="s">
+        <v>213</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>24</v>
@@ -10394,8 +10455,8 @@
       <c r="B79" s="18">
         <v>31</v>
       </c>
-      <c r="C79" s="175" t="s">
-        <v>221</v>
+      <c r="C79" s="173" t="s">
+        <v>214</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>24</v>
@@ -10409,8 +10470,8 @@
       <c r="B80" s="18">
         <v>32</v>
       </c>
-      <c r="C80" s="175" t="s">
-        <v>225</v>
+      <c r="C80" s="173" t="s">
+        <v>218</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>24</v>
@@ -10424,8 +10485,8 @@
       <c r="B81" s="18">
         <v>33</v>
       </c>
-      <c r="C81" s="175" t="s">
-        <v>223</v>
+      <c r="C81" s="173" t="s">
+        <v>216</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>24</v>
@@ -10450,89 +10511,89 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3 C5:C26">
-    <cfRule type="cellIs" dxfId="20" priority="33" operator="between">
+    <cfRule type="cellIs" dxfId="21" priority="33" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8 D11:D26">
-    <cfRule type="cellIs" dxfId="19" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="29" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="30" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E26">
-    <cfRule type="cellIs" dxfId="17" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="27" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="28" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4 F8:F26">
-    <cfRule type="cellIs" dxfId="15" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="25" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="26" operator="equal">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G26">
-    <cfRule type="cellIs" dxfId="13" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="23" operator="greaterThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="24" operator="lessThan">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="11" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="21" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="22" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="9" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="19" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="7" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="17" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
       <formula>0</formula>
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2157,64 +2157,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="81">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3622,6 +3584,44 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4732,7 +4732,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H12" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -5030,23 +5030,23 @@
     <tableColumn id="1" name="S. no" dataDxfId="69"/>
     <tableColumn id="2" name="Book ID" dataDxfId="68"/>
     <tableColumn id="3" name="MPS ID" dataDxfId="67"/>
-    <tableColumn id="4" name="Stage" dataDxfId="0"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="66"/>
-    <tableColumn id="6" name="Current TAT (S50 onward)" dataDxfId="65"/>
-    <tableColumn id="7" name="S200 TAT" dataDxfId="64"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="63"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="62"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="61"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="60"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="59"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="58"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="57"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="56"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="55"/>
-    <tableColumn id="17" name="Remarks" dataDxfId="54"/>
-    <tableColumn id="18" name="Column1" dataDxfId="53"/>
-    <tableColumn id="19" name="Plateform" dataDxfId="52"/>
-    <tableColumn id="20" name="Column2" dataDxfId="51"/>
+    <tableColumn id="4" name="Stage" dataDxfId="66"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="65"/>
+    <tableColumn id="6" name="Current TAT (S50 onward)" dataDxfId="64"/>
+    <tableColumn id="7" name="S200 TAT" dataDxfId="63"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="62"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="61"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="60"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="59"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="58"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="57"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="56"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="55"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="54"/>
+    <tableColumn id="17" name="Remarks" dataDxfId="53"/>
+    <tableColumn id="18" name="Column1" dataDxfId="52"/>
+    <tableColumn id="19" name="Plateform" dataDxfId="51"/>
+    <tableColumn id="20" name="Column2" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5055,32 +5055,32 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
   <tableColumns count="19">
-    <tableColumn id="1" name="S. no" dataDxfId="50"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="49"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="48"/>
-    <tableColumn id="4" name="Stage" dataDxfId="47"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="46"/>
-    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="45"/>
-    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="44"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="43"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="42"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="41"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="40"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="39"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="38"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="37"/>
-    <tableColumn id="19" name="TS Pages" dataDxfId="36"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="35"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="34"/>
-    <tableColumn id="17" name="Delivered Date " dataDxfId="33"/>
-    <tableColumn id="18" name="Remarks" dataDxfId="32"/>
+    <tableColumn id="1" name="S. no" dataDxfId="49"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="48"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="47"/>
+    <tableColumn id="4" name="Stage" dataDxfId="46"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="45"/>
+    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="44"/>
+    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="43"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="42"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="41"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="40"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="39"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="38"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="37"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="36"/>
+    <tableColumn id="19" name="TS Pages" dataDxfId="35"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="34"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="33"/>
+    <tableColumn id="17" name="Delivered Date " dataDxfId="32"/>
+    <tableColumn id="18" name="Remarks" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="1" name="DESCriptions"/>
@@ -5092,11 +5092,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="B5:C10"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Month" dataDxfId="23"/>
-    <tableColumn id="2" name="No of titles delivered" dataDxfId="22">
+    <tableColumn id="1" name="Month" dataDxfId="22"/>
+    <tableColumn id="2" name="No of titles delivered" dataDxfId="21">
       <calculatedColumnFormula>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7143,7 +7143,7 @@
         <v>160</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="E27" s="147">
         <v>46316</v>
@@ -7190,7 +7190,7 @@
         <v>162</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="E28" s="147">
         <v>46316</v>
@@ -7485,7 +7485,7 @@
       <c r="D35" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="203">
+      <c r="E35" s="202">
         <v>46323</v>
       </c>
       <c r="F35" s="169">
@@ -7526,16 +7526,16 @@
       <c r="D36" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="206"/>
-      <c r="F36" s="206"/>
+      <c r="E36" s="205"/>
+      <c r="F36" s="205"/>
       <c r="G36" s="54"/>
       <c r="H36" s="26"/>
-      <c r="I36" s="204"/>
-      <c r="J36" s="204"/>
-      <c r="K36" s="204"/>
-      <c r="L36" s="204"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="203"/>
+      <c r="K36" s="203"/>
+      <c r="L36" s="203"/>
       <c r="M36" s="33"/>
-      <c r="N36" s="205"/>
+      <c r="N36" s="204"/>
       <c r="O36" s="174"/>
       <c r="P36" s="174"/>
       <c r="Q36" s="174"/>
@@ -9067,10 +9067,10 @@
       <c r="J2" s="79"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="202" t="s">
+      <c r="B3" s="206" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="202"/>
+      <c r="C3" s="206"/>
       <c r="E3" s="79"/>
       <c r="F3" s="80"/>
       <c r="G3" s="79"/>
@@ -10511,89 +10511,89 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3 C5:C26">
-    <cfRule type="cellIs" dxfId="21" priority="33" operator="between">
+    <cfRule type="cellIs" dxfId="20" priority="33" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D8 D11:D26">
-    <cfRule type="cellIs" dxfId="20" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="29" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="30" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E26">
-    <cfRule type="cellIs" dxfId="18" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="27" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="28" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4 F8:F26">
-    <cfRule type="cellIs" dxfId="16" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="25" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G26">
-    <cfRule type="cellIs" dxfId="14" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="23" operator="greaterThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="24" operator="lessThan">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="12" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="21" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="22" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="10" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="19" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="8" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
       <formula>0</formula>
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
       <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="8" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="MISC" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current Status'!$A$1:$S$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MISC!$D$48:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current Status'!$A$1:$S$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MISC!$D$19:$E$45</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="251">
   <si>
     <t>S. no</t>
   </si>
@@ -150,24 +150,6 @@
   </si>
   <si>
     <t>708652_1_En</t>
-  </si>
-  <si>
-    <t>Action Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total  TAT </t>
-  </si>
-  <si>
-    <t>S300 TAT(Target:7)</t>
-  </si>
-  <si>
-    <t>S300A TAT(Target:10)</t>
-  </si>
-  <si>
-    <t>S600 TAT(Target:7)</t>
-  </si>
-  <si>
-    <t>S650 TAT(Target:7)</t>
   </si>
   <si>
     <t>703192_1_En</t>
@@ -220,12 +202,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>S300 - 
-Comp : 00 Chapters; 
-Online Delivery : 00 Chapters
-Delivered: 00 Chapters</t>
-  </si>
-  <si>
     <t>S200 - Delivered on 05th Aug
 Login : 00 Chapters;
 PE : 00 Chapters;
@@ -234,12 +210,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>S300 - 
-Comp : 00 Chapters; 
-Online Delivery : 01 Chapters
-Delivered: 05 Chapters</t>
-  </si>
-  <si>
     <t>S200 - Delivered on 17th Aug
 Login : 00 Chapters;
 PE : 00 Chapters;
@@ -248,12 +218,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>S300 - 
-Comp : 00 Chapters; 
-Online Delivery : FM
-Delivered: 20 Chapters</t>
-  </si>
-  <si>
     <t>S200 - Delivered on 24th Aug
 Login : 00 Chapters;
 PE : 00 Chapters;
@@ -262,12 +226,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>S300 - 
-Comp : 02 Chapters; 
-Online Delivery : 00 Chapters
-Delivered: 08 Chapters</t>
-  </si>
-  <si>
     <t>S200 - Delivered on 27th Aug
 Login : 00 Chapters;
 PE : 00 Chapters;
@@ -349,12 +307,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t xml:space="preserve">S300 - 
-Comp : 00 Chapters; 
-Online Delivery : 00 Chapters
-Delivered: </t>
-  </si>
-  <si>
     <t>701319_1_En</t>
   </si>
   <si>
@@ -369,12 +321,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>S300 - Delivered on 12th Aug
-Comp : 00 Chapters; 
-Online Delivery : 00 Chapters
-Delivered: 00 Chapters</t>
-  </si>
-  <si>
     <t>701541_1_En</t>
   </si>
   <si>
@@ -403,9 +349,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>Released on 21-Sep</t>
-  </si>
-  <si>
     <t>Moved to accessibility on 21st</t>
   </si>
   <si>
@@ -415,12 +358,6 @@
     <t>709492_1_En</t>
   </si>
   <si>
-    <t>702446_1_En</t>
-  </si>
-  <si>
-    <t>Released on 22-Sep</t>
-  </si>
-  <si>
     <t>Delayed from VE</t>
   </si>
   <si>
@@ -440,12 +377,6 @@
   </si>
   <si>
     <t>Kalmani, Vijay</t>
-  </si>
-  <si>
-    <t>Released on 26-Sep</t>
-  </si>
-  <si>
-    <t>Released on 25-Sep</t>
   </si>
   <si>
     <t>708159_1_En</t>
@@ -693,9 +624,6 @@
     <t>Hold  for Manuscript</t>
   </si>
   <si>
-    <t>2 in Eproof rest revises completed</t>
-  </si>
-  <si>
     <t>PERARNAU-DMD-Garcia-Sanchez</t>
   </si>
   <si>
@@ -802,9 +730,6 @@
     <t>González, Carina S. González</t>
   </si>
   <si>
-    <t>FM &amp; TOC will be recd in S200 stage</t>
-  </si>
-  <si>
     <t>Month/No Of Titles</t>
   </si>
   <si>
@@ -862,12 +787,6 @@
     <t>S50</t>
   </si>
   <si>
-    <t>13 Books</t>
-  </si>
-  <si>
-    <t>7 Books</t>
-  </si>
-  <si>
     <t>S650 A</t>
   </si>
   <si>
@@ -877,12 +796,6 @@
     <t>S200 delivered on 27-Oct</t>
   </si>
   <si>
-    <t>Query for JS regarding mismatch in chaps. BM is also there+Index</t>
-  </si>
-  <si>
-    <t>New manuscript recd again and chap-31 added. On 12-Oct26. Preface &amp; TOC(FM components missing), Index tagging for 2 chaps. missing reced on 28-oct</t>
-  </si>
-  <si>
     <t>Rahul</t>
   </si>
   <si>
@@ -893,9 +806,6 @@
   </si>
   <si>
     <t>Delivered on 28th- Will move to S600 today</t>
-  </si>
-  <si>
-    <t>29 chap in Revises</t>
   </si>
   <si>
     <t>16 chaps in Revises</t>
@@ -909,9 +819,6 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>Hold for new manuscript solved.</t>
-  </si>
-  <si>
     <t>16 Chaps in Revises.</t>
   </si>
   <si>
@@ -940,17 +847,6 @@
   </si>
   <si>
     <t>S200 - 
-Login : 13 Chapters;
-PE : 18 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>Login pending</t>
-  </si>
-  <si>
-    <t>S200 - 
 Login : 03 Chapters;
 PE : 53 Chapters;
 CE : 00 Chapters;
@@ -958,29 +854,85 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
+    <t>González, Carina-8770441</t>
+  </si>
+  <si>
+    <t>703158_1_En</t>
+  </si>
+  <si>
+    <t>Camara, Moctar</t>
+  </si>
+  <si>
+    <t>14 Books</t>
+  </si>
+  <si>
+    <t>4 Books</t>
+  </si>
+  <si>
+    <t>5 books</t>
+  </si>
+  <si>
+    <t>1 Books</t>
+  </si>
+  <si>
+    <t>1 books</t>
+  </si>
+  <si>
+    <t>Mix Tex+word</t>
+  </si>
+  <si>
+    <t>Supplementary Chapter 23 was there but in js it was showing "No" for all books. But was unable to move from Pred-edit stage so it was stuck for many days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold for new manuscript solved. Index tagging query was raised on 6-Oct and query solved on 19th Oct.(Chap-05 &amp; 30) </t>
+  </si>
+  <si>
+    <t>New manuscript recd again in S50 stage and chap-31 added. On 12-Oct26.-It was on hold and resumed back on 26th. Preface &amp; TOC(updated according to new manuscript recd on 27th-Oct), Index tagging for entire books was.updated raised on 27th &amp; reced on 28-oct)</t>
+  </si>
+  <si>
     <t>S200 - 
-Login : 39 Chapters;
-PE : 17 Chapters;
+Login : 00 Chapters;
+PE : 31 Chapters;
 CE : 00 Chapters;
 Comp : 00 Chapters;
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
+    <t>Moved from Login on 29-oct</t>
+  </si>
+  <si>
+    <t>FM &amp; TOC recd on27th and moved to S200 stage on 28th &amp; 29-oct.</t>
+  </si>
+  <si>
+    <t>1 chap in Query in S50 stage(References file missing)</t>
+  </si>
+  <si>
+    <t>Query for JS regarding mismatch in chaps. (1 week in query) in s50 stage. BM is also there+Index</t>
+  </si>
+  <si>
     <t>S200 - 
-Login : 29 Chapters;
-PE : 04 Chapters;
+Login : 101 Chapters;
+PE : 16 Chapters;
 CE : 00 Chapters;
 Comp : 00 Chapters;
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>González, Carina-8770441</t>
-  </si>
-  <si>
-    <t>703158_1_En</t>
-  </si>
-  <si>
-    <t>Camara, Moctar</t>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 69 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>30 chap in Revises</t>
+  </si>
+  <si>
+    <t>Delivered titles</t>
+  </si>
+  <si>
+    <t>Remarks2</t>
   </si>
 </sst>
 </file>
@@ -991,7 +943,7 @@
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1023,11 +975,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -1042,13 +989,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1200,7 +1140,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1234,12 +1174,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1280,7 +1214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1300,15 +1234,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1403,17 +1328,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1578,28 +1492,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1610,13 +1509,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1624,28 +1517,22 @@
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1660,10 +1547,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1681,56 +1568,35 @@
     <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1739,22 +1605,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1767,10 +1633,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1779,31 +1645,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1816,22 +1682,22 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1839,40 +1705,40 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1887,164 +1753,164 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2071,266 +1937,106 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="60">
     <dxf>
       <font>
         <b val="0"/>
@@ -2936,7 +2642,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2949,8 +2655,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3583,7 +3287,7 @@
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4941,16 +4645,16 @@
     <dataField name="Count of S650 TAT" fld="11" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="80">
+    <format dxfId="59">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="58">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="57">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="77">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4959,7 +4663,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4968,7 +4672,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="75">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4977,7 +4681,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4986,7 +4690,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4998,7 +4702,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="3">
           <reference field="2" count="1" selected="0">
@@ -5024,29 +4728,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T36" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
-  <autoFilter ref="A1:T36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T35" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+  <autoFilter ref="A1:T35"/>
   <tableColumns count="20">
-    <tableColumn id="1" name="S. no" dataDxfId="69"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="68"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="67"/>
-    <tableColumn id="4" name="Stage" dataDxfId="66"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="65"/>
-    <tableColumn id="6" name="Current TAT (S50 onward)" dataDxfId="64"/>
-    <tableColumn id="7" name="S200 TAT" dataDxfId="63"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="62"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="61"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="60"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="59"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="58"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="57"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="56"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="55"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="54"/>
-    <tableColumn id="17" name="Remarks" dataDxfId="53"/>
-    <tableColumn id="18" name="Column1" dataDxfId="52"/>
-    <tableColumn id="19" name="Plateform" dataDxfId="51"/>
-    <tableColumn id="20" name="Column2" dataDxfId="50"/>
+    <tableColumn id="1" name="S. no" dataDxfId="48"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="47"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="46"/>
+    <tableColumn id="4" name="Stage" dataDxfId="45"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="44"/>
+    <tableColumn id="6" name="Current TAT (S50 onward)" dataDxfId="43"/>
+    <tableColumn id="7" name="S200 TAT" dataDxfId="42"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="41"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="40"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="39"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="38"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="37"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="36"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="35"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="34"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="33"/>
+    <tableColumn id="17" name="Remarks" dataDxfId="32"/>
+    <tableColumn id="18" name="Column1" dataDxfId="31"/>
+    <tableColumn id="19" name="Plateform" dataDxfId="30"/>
+    <tableColumn id="20" name="Column2" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5055,32 +4759,32 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
   <tableColumns count="19">
-    <tableColumn id="1" name="S. no" dataDxfId="49"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="48"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="47"/>
-    <tableColumn id="4" name="Stage" dataDxfId="46"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="45"/>
-    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="44"/>
-    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="43"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="42"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="41"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="40"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="39"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="38"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="37"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="36"/>
-    <tableColumn id="19" name="TS Pages" dataDxfId="35"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="34"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="33"/>
-    <tableColumn id="17" name="Delivered Date " dataDxfId="32"/>
-    <tableColumn id="18" name="Remarks" dataDxfId="31"/>
+    <tableColumn id="1" name="S. no" dataDxfId="28"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="27"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="26"/>
+    <tableColumn id="4" name="Stage" dataDxfId="25"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="24"/>
+    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="23"/>
+    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="22"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="21"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="20"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="19"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="18"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="17"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="16"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="15"/>
+    <tableColumn id="19" name="TS Pages" dataDxfId="14"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="13"/>
+    <tableColumn id="16" name="Remarks" dataDxfId="12"/>
+    <tableColumn id="17" name="Delivered Date " dataDxfId="11"/>
+    <tableColumn id="18" name="Remarks2" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="1" name="DESCriptions"/>
@@ -5092,11 +4796,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="B5:C10"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Month" dataDxfId="22"/>
-    <tableColumn id="2" name="No of titles delivered" dataDxfId="21">
+    <tableColumn id="1" name="Month" dataDxfId="1"/>
+    <tableColumn id="2" name="No of titles delivered" dataDxfId="0">
       <calculatedColumnFormula>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5373,7 +5077,7 @@
   <cols>
     <col min="1" max="1" width="29.1796875" customWidth="1"/>
     <col min="2" max="2" width="13.26953125" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" style="59" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" style="43" customWidth="1"/>
     <col min="4" max="4" width="16.1796875" customWidth="1"/>
     <col min="5" max="5" width="17.453125" customWidth="1"/>
     <col min="6" max="7" width="16.1796875" customWidth="1"/>
@@ -5382,212 +5086,212 @@
   <sheetData>
     <row r="3" spans="1:8">
       <c r="C3"/>
-      <c r="D3" s="89" t="s">
-        <v>144</v>
+      <c r="D3" s="73" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="177" t="s">
-        <v>46</v>
+      <c r="C4" s="161" t="s">
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
-      <c r="D5" s="90">
+      <c r="D5" s="74">
         <v>1</v>
       </c>
-      <c r="E5" s="90">
+      <c r="E5" s="74">
         <v>1</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="74">
         <v>1</v>
       </c>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
-      <c r="D6" s="90">
+      <c r="D6" s="74">
         <v>1</v>
       </c>
-      <c r="E6" s="90">
+      <c r="E6" s="74">
         <v>1</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="74">
         <v>1</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="74">
         <v>1</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="74"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
-      <c r="D7" s="90">
+      <c r="D7" s="74">
         <v>1</v>
       </c>
-      <c r="E7" s="90">
+      <c r="E7" s="74">
         <v>1</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="74">
         <v>1</v>
       </c>
-      <c r="G7" s="90"/>
-      <c r="H7" s="90"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C8">
         <v>35</v>
       </c>
-      <c r="D8" s="90">
+      <c r="D8" s="74">
         <v>1</v>
       </c>
-      <c r="E8" s="90">
+      <c r="E8" s="74">
         <v>1</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="74">
         <v>1</v>
       </c>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C9">
         <v>40</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="74">
         <v>1</v>
       </c>
-      <c r="E9" s="90">
+      <c r="E9" s="74">
         <v>1</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="74">
         <v>1</v>
       </c>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C10">
         <v>40</v>
       </c>
-      <c r="D10" s="90">
+      <c r="D10" s="74">
         <v>1</v>
       </c>
-      <c r="E10" s="90">
+      <c r="E10" s="74">
         <v>1</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="74">
         <v>1</v>
       </c>
-      <c r="G10" s="90">
+      <c r="G10" s="74">
         <v>1</v>
       </c>
-      <c r="H10" s="90"/>
+      <c r="H10" s="74"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C11">
         <v>34</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="74">
         <v>1</v>
       </c>
-      <c r="E11" s="90">
+      <c r="E11" s="74">
         <v>1</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="74">
         <v>1</v>
       </c>
-      <c r="G11" s="90"/>
-      <c r="H11" s="90"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C12"/>
-      <c r="D12" s="90">
+      <c r="D12" s="74">
         <v>7</v>
       </c>
-      <c r="E12" s="90">
+      <c r="E12" s="74">
         <v>7</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="74">
         <v>7</v>
       </c>
-      <c r="G12" s="90">
+      <c r="G12" s="74">
         <v>2</v>
       </c>
-      <c r="H12" s="90"/>
+      <c r="H12" s="74"/>
     </row>
     <row r="13" spans="1:8">
       <c r="C13"/>
@@ -5678,1874 +5382,1840 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7" style="50" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" style="69" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" style="69" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" style="55" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="201" customWidth="1"/>
-    <col min="6" max="6" width="23.90625" style="201" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="55" customWidth="1"/>
-    <col min="8" max="8" width="10" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.7265625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08984375" style="55" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6328125" style="50" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.54296875" style="113" customWidth="1"/>
-    <col min="16" max="16" width="16" style="113" customWidth="1"/>
-    <col min="17" max="17" width="15.81640625" style="113" customWidth="1"/>
-    <col min="18" max="18" width="19.26953125" style="26" customWidth="1"/>
-    <col min="19" max="19" width="15.81640625" style="26"/>
-    <col min="20" max="16384" width="15.81640625" style="27"/>
+    <col min="1" max="1" width="7" style="35" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" style="53" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" style="53" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" style="39" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" style="39" customWidth="1"/>
+    <col min="6" max="6" width="23.90625" style="185" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="39" customWidth="1"/>
+    <col min="8" max="8" width="10" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.7265625" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" style="35" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.54296875" style="97" customWidth="1"/>
+    <col min="16" max="16" width="16" style="97" customWidth="1"/>
+    <col min="17" max="17" width="15.81640625" style="97" customWidth="1"/>
+    <col min="18" max="18" width="19.26953125" style="17" customWidth="1"/>
+    <col min="19" max="19" width="15.81640625" style="17"/>
+    <col min="20" max="16384" width="15.81640625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="M1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="22" t="s">
+      <c r="N1" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="O1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="P1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="Q1" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="O1" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="P1" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q1" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="R1" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="S1" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="T1" s="200" t="s">
-        <v>242</v>
+      <c r="R1" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="T1" s="184" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="240">
-      <c r="A2" s="52">
+      <c r="A2" s="36">
         <f t="shared" ref="A2:A10" si="0">ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="53">
+      <c r="D2" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="37">
         <v>46258</v>
       </c>
-      <c r="F2" s="88">
-        <f ca="1">TODAY()-E2</f>
+      <c r="F2" s="72">
+        <f t="shared" ref="F2:F12" ca="1" si="1">TODAY()-E2</f>
         <v>66</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="36">
         <f>DATE(2026,9,19)-DATE(2026,8,24)</f>
         <v>26</v>
       </c>
-      <c r="H2" s="52">
+      <c r="H2" s="36">
         <f>DATE(2026,10,22)-DATE(2026,9,19)</f>
         <v>33</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="36">
         <f>DATE(2026,10,24)-DATE(2026,10,22)</f>
         <v>2</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J2" s="24">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
         <v>4</v>
       </c>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33">
+      <c r="K2" s="24">
+        <f ca="1">TODAY()-DATE(2026,10,27)</f>
+        <v>2</v>
+      </c>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24">
         <v>32</v>
       </c>
-      <c r="N2" s="33">
+      <c r="N2" s="24">
         <v>500</v>
       </c>
-      <c r="O2" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P2" s="39" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q2" s="148" t="s">
-        <v>194</v>
-      </c>
-      <c r="R2" s="105" t="s">
-        <v>101</v>
-      </c>
-      <c r="S2" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T2" s="199"/>
+      <c r="O2" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q2" s="132" t="s">
+        <v>176</v>
+      </c>
+      <c r="R2" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T2" s="183"/>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="52">
+      <c r="A3" s="36">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="196" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="35">
+      <c r="C3" s="180" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="26">
         <v>46291</v>
       </c>
-      <c r="F3" s="33">
-        <f t="shared" ref="F3:F8" ca="1" si="1">TODAY()-E3</f>
+      <c r="F3" s="24">
+        <f t="shared" ca="1" si="1"/>
         <v>33</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="24">
         <f>DATE(2026,10,10)-DATE(2026,9,26)</f>
         <v>14</v>
       </c>
-      <c r="H3" s="104">
+      <c r="H3" s="88">
         <f>DATE(2026,10,24)-DATE(2026,10,10)</f>
         <v>14</v>
       </c>
-      <c r="I3" s="104">
+      <c r="I3" s="88">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
-      <c r="J3" s="54">
+      <c r="J3" s="38">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="33">
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="24">
         <v>15</v>
       </c>
-      <c r="N3" s="33">
+      <c r="N3" s="24">
         <v>200</v>
       </c>
-      <c r="O3" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P3" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q3" s="149" t="s">
-        <v>74</v>
-      </c>
-      <c r="R3" s="155" t="s">
-        <v>100</v>
-      </c>
-      <c r="S3" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T3" s="174"/>
+      <c r="O3" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="95" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q3" s="133" t="s">
+        <v>64</v>
+      </c>
+      <c r="R3" s="139" t="s">
+        <v>85</v>
+      </c>
+      <c r="S3" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T3" s="158"/>
     </row>
     <row r="4" spans="1:20" ht="60">
-      <c r="A4" s="52">
+      <c r="A4" s="36">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="195" t="s">
-        <v>171</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="35">
+      <c r="C4" s="179" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="26">
         <v>46291</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>33</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="24">
         <f>DATE(2026,10,12)-DATE(2026,9,26)</f>
         <v>16</v>
       </c>
-      <c r="H4" s="104">
+      <c r="H4" s="88">
         <f>DATE(2026,10,22)-DATE(2026,10,12)</f>
         <v>10</v>
       </c>
-      <c r="I4" s="104">
+      <c r="I4" s="88">
         <f>DATE(2026,10,28)-DATE(2026,10,23)</f>
         <v>5</v>
       </c>
-      <c r="J4" s="104">
+      <c r="J4" s="88">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
         <v>1</v>
       </c>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="33">
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="24">
         <v>15</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="24">
         <v>200</v>
       </c>
-      <c r="O4" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="149" t="s">
-        <v>74</v>
-      </c>
-      <c r="R4" s="105"/>
-      <c r="S4" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T4" s="174"/>
+      <c r="O4" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P4" s="95"/>
+      <c r="Q4" s="133" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T4" s="158"/>
     </row>
     <row r="5" spans="1:20" ht="60">
-      <c r="A5" s="52">
+      <c r="A5" s="36">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="35">
+      <c r="C5" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="26">
         <v>46288</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
-      <c r="G5" s="68">
+      <c r="G5" s="52">
         <f>DATE(2026,10,8)-DATE(2026,9,23)</f>
         <v>15</v>
       </c>
-      <c r="H5" s="54">
+      <c r="H5" s="38">
         <f>DATE(2026,10,24)-DATE(2026,10,8)</f>
         <v>16</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="38">
         <f>DATE(2026,10,26)-DATE(2026,10,25)</f>
         <v>1</v>
       </c>
-      <c r="J5" s="54">
+      <c r="J5" s="38">
         <f ca="1">TODAY()-DATE(2026,10,27)</f>
         <v>2</v>
       </c>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="33">
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="24">
         <v>31</v>
       </c>
-      <c r="N5" s="33">
+      <c r="N5" s="24">
         <v>280</v>
       </c>
-      <c r="O5" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="149" t="s">
-        <v>73</v>
-      </c>
-      <c r="R5" s="105" t="s">
-        <v>101</v>
-      </c>
-      <c r="S5" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T5" s="174"/>
+      <c r="O5" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="133" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T5" s="158"/>
     </row>
     <row r="6" spans="1:20" ht="60">
-      <c r="A6" s="52">
+      <c r="A6" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="195" t="s">
-        <v>173</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="35">
+      <c r="C6" s="179" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="26">
         <v>46288</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
-      <c r="G6" s="191">
+      <c r="G6" s="175">
         <f>DATE(2026,10,14)-DATE(2026,10,2)</f>
         <v>12</v>
       </c>
-      <c r="H6" s="104">
+      <c r="H6" s="88">
         <f>DATE(2026,10,27)-DATE(2026,10,14)</f>
         <v>13</v>
       </c>
-      <c r="I6" s="104">
+      <c r="I6" s="88">
         <f>DATE(2026,10,28)-DATE(2026,10,28)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="33">
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="24">
         <v>25</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="24">
         <v>240</v>
       </c>
-      <c r="O6" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P6" s="111" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q6" s="149" t="s">
-        <v>154</v>
-      </c>
-      <c r="R6" s="156" t="s">
-        <v>186</v>
-      </c>
-      <c r="S6" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T6" s="174"/>
+      <c r="O6" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="95" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q6" s="133" t="s">
+        <v>137</v>
+      </c>
+      <c r="R6" s="140" t="s">
+        <v>169</v>
+      </c>
+      <c r="S6" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T6" s="158"/>
     </row>
     <row r="7" spans="1:20" ht="60">
-      <c r="A7" s="52">
+      <c r="A7" s="36">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="35">
+      <c r="C7" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="26">
         <v>46283</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="24">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H7" s="54">
+      <c r="H7" s="38">
         <f>DATE(2026,10,24)-DATE(2026,10,8)</f>
         <v>16</v>
       </c>
-      <c r="I7" s="146">
+      <c r="I7" s="130">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="33">
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="24">
         <v>25</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="24">
         <v>244</v>
       </c>
-      <c r="O7" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P7" s="111" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q7" s="149" t="s">
-        <v>128</v>
-      </c>
-      <c r="R7" s="105" t="s">
-        <v>138</v>
-      </c>
-      <c r="S7" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T7" s="174"/>
-    </row>
-    <row r="8" spans="1:20" s="145" customFormat="1" ht="60">
-      <c r="A8" s="138">
+      <c r="O7" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="95" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q7" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7" s="89" t="s">
+        <v>121</v>
+      </c>
+      <c r="S7" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T7" s="158"/>
+    </row>
+    <row r="8" spans="1:20" s="129" customFormat="1" ht="60">
+      <c r="A8" s="122">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="139" t="s">
+      <c r="B8" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="117" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="138" t="s">
-        <v>181</v>
-      </c>
-      <c r="E8" s="140">
+      <c r="C8" s="101" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="122" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="124">
         <v>46283</v>
       </c>
-      <c r="F8" s="138">
+      <c r="F8" s="122">
         <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
-      <c r="G8" s="138">
+      <c r="G8" s="122">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H8" s="141">
+      <c r="H8" s="125">
         <f>DATE(2026,10,19)-DATE(2026,10,12)</f>
         <v>7</v>
       </c>
-      <c r="I8" s="141">
+      <c r="I8" s="125">
         <f ca="1">TODAY()-DATE(2026,10,20)</f>
         <v>9</v>
       </c>
-      <c r="J8" s="141">
+      <c r="J8" s="125">
         <f>DATE(2026,10,26)-DATE(2026,10,22)</f>
         <v>4</v>
       </c>
-      <c r="K8" s="141"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="138">
+      <c r="K8" s="125">
+        <f ca="1">TODAY()-DATE(2026,10,29)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="126"/>
+      <c r="M8" s="122">
         <v>9</v>
       </c>
-      <c r="N8" s="138">
+      <c r="N8" s="122">
         <v>100</v>
       </c>
-      <c r="O8" s="143" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" s="144"/>
-      <c r="Q8" s="150" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="142"/>
-      <c r="S8" s="142" t="s">
-        <v>168</v>
-      </c>
-      <c r="T8" s="174"/>
+      <c r="O8" s="127" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" s="128"/>
+      <c r="Q8" s="134" t="s">
+        <v>63</v>
+      </c>
+      <c r="R8" s="126"/>
+      <c r="S8" s="126" t="s">
+        <v>151</v>
+      </c>
+      <c r="T8" s="158"/>
     </row>
     <row r="9" spans="1:20" ht="60">
-      <c r="A9" s="33">
+      <c r="A9" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="35">
+      <c r="C9" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="26">
         <v>46283</v>
       </c>
-      <c r="F9" s="33">
-        <f t="shared" ref="F9:F19" ca="1" si="2">TODAY()-E9</f>
+      <c r="F9" s="24">
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="24">
         <f>DATE(2026,10,9)-DATE(2026,9,21)</f>
         <v>18</v>
       </c>
-      <c r="H9" s="54">
+      <c r="H9" s="38">
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I9" s="146">
+      <c r="I9" s="130">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="88">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="33">
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="24">
         <v>13</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="24">
         <v>120</v>
       </c>
-      <c r="O9" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="149" t="s">
-        <v>73</v>
-      </c>
-      <c r="R9" s="105"/>
-      <c r="S9" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T9" s="174"/>
+      <c r="O9" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P9" s="95"/>
+      <c r="Q9" s="133" t="s">
+        <v>63</v>
+      </c>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T9" s="158"/>
     </row>
     <row r="10" spans="1:20" ht="60">
-      <c r="A10" s="52">
+      <c r="A10" s="36">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="196" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" s="35">
+      <c r="C10" s="180" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="26">
         <v>46289</v>
       </c>
-      <c r="F10" s="58">
-        <f t="shared" ca="1" si="2"/>
+      <c r="F10" s="42">
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="38">
         <f>DATE(2026,10,11)-DATE(2026,9,25)</f>
         <v>16</v>
       </c>
-      <c r="H10" s="54">
+      <c r="H10" s="38">
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I10" s="146">
+      <c r="I10" s="130">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
         <v>4</v>
       </c>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="105"/>
-      <c r="M10" s="33">
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="24">
         <v>37</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="24">
         <v>200</v>
       </c>
-      <c r="O10" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P10" s="111" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q10" s="149" t="s">
-        <v>75</v>
-      </c>
-      <c r="R10" s="155" t="s">
-        <v>100</v>
-      </c>
-      <c r="S10" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" s="174"/>
+      <c r="O10" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P10" s="95" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q10" s="133" t="s">
+        <v>65</v>
+      </c>
+      <c r="R10" s="139" t="s">
+        <v>85</v>
+      </c>
+      <c r="S10" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T10" s="158"/>
     </row>
     <row r="11" spans="1:20" ht="60">
-      <c r="A11" s="52">
-        <f t="shared" ref="A11" si="3">ROW()-1</f>
+      <c r="A11" s="36">
+        <f t="shared" ref="A11" si="2">ROW()-1</f>
         <v>10</v>
       </c>
-      <c r="B11" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="195" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" s="35">
+      <c r="B11" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="179" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="26">
         <v>46295</v>
       </c>
-      <c r="F11" s="8">
-        <f ca="1">TODAY()-E11</f>
+      <c r="F11" s="3">
+        <f t="shared" ca="1" si="1"/>
         <v>29</v>
       </c>
-      <c r="G11" s="104">
+      <c r="G11" s="88">
         <f>DATE(2026,10,27)-DATE(2026,10,12)</f>
         <v>15</v>
       </c>
-      <c r="H11" s="104">
+      <c r="H11" s="88">
         <f>DATE(2026,10,28)-DATE(2026,10,28)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="104">
+      <c r="I11" s="88">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="105"/>
-      <c r="M11" s="33">
+      <c r="J11" s="89"/>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="24">
         <v>78</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="24">
         <v>750</v>
       </c>
-      <c r="O11" s="112" t="s">
-        <v>228</v>
-      </c>
-      <c r="P11" s="111" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q11" s="149" t="s">
-        <v>165</v>
-      </c>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T11" s="174"/>
-    </row>
-    <row r="12" spans="1:20" ht="60">
-      <c r="A12" s="52">
-        <f t="shared" ref="A12:A35" si="4">ROW()-1</f>
+      <c r="O11" s="96" t="s">
+        <v>209</v>
+      </c>
+      <c r="P11" s="95" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q11" s="133" t="s">
+        <v>148</v>
+      </c>
+      <c r="R11" s="89"/>
+      <c r="S11" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T11" s="158"/>
+    </row>
+    <row r="12" spans="1:20" ht="130.5">
+      <c r="A12" s="36">
+        <f t="shared" ref="A12:A34" si="3">ROW()-1</f>
         <v>11</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="195" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="35">
+      <c r="C12" s="179" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="26">
         <v>46293</v>
       </c>
-      <c r="F12" s="33">
-        <f t="shared" ca="1" si="2"/>
+      <c r="F12" s="24">
+        <f t="shared" ca="1" si="1"/>
         <v>31</v>
       </c>
-      <c r="G12" s="104">
+      <c r="G12" s="88">
         <f>DATE(2026,10,21)-DATE(2026,9,30)</f>
         <v>21</v>
       </c>
-      <c r="H12" s="104">
+      <c r="H12" s="88">
         <f>DATE(2026,10,28)-DATE(2026,10,26)</f>
         <v>2</v>
       </c>
-      <c r="I12" s="104">
+      <c r="I12" s="88">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="105"/>
-      <c r="M12" s="33">
+      <c r="J12" s="89"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
+      <c r="M12" s="24">
         <v>81</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="24">
         <v>600</v>
       </c>
-      <c r="O12" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P12" s="111" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q12" s="149" t="s">
-        <v>76</v>
-      </c>
-      <c r="R12" s="105"/>
-      <c r="S12" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T12" s="174"/>
+      <c r="O12" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P12" s="95" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q12" s="133" t="s">
+        <v>66</v>
+      </c>
+      <c r="R12" s="89" t="s">
+        <v>238</v>
+      </c>
+      <c r="S12" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T12" s="158"/>
     </row>
     <row r="13" spans="1:20" ht="60">
-      <c r="A13" s="52">
-        <f t="shared" si="4"/>
+      <c r="A13" s="36">
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="B13" s="87" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="117" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="35">
-        <v>46286</v>
-      </c>
-      <c r="F13" s="33">
-        <f t="shared" ca="1" si="2"/>
-        <v>38</v>
-      </c>
-      <c r="G13" s="33">
-        <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
-        <v>16</v>
-      </c>
-      <c r="H13" s="107">
-        <f ca="1">TODAY()-DATE(2026,10,7)</f>
-        <v>22</v>
-      </c>
-      <c r="I13" s="107">
-        <f ca="1">TODAY()-DATE(2026,10,23)</f>
-        <v>6</v>
-      </c>
-      <c r="J13" s="107">
+      <c r="B13" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="26">
+        <v>46282</v>
+      </c>
+      <c r="F13" s="24">
+        <f ca="1">TODAY()-DATE(2026,9,17)</f>
+        <v>42</v>
+      </c>
+      <c r="G13" s="24">
+        <f>DATE(2026,10,6)-DATE(2026,9,17)</f>
+        <v>19</v>
+      </c>
+      <c r="H13" s="88">
+        <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
+        <v>13</v>
+      </c>
+      <c r="I13" s="88">
+        <f>DATE(2026,10,22)-DATE(2026,10,21)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="121">
         <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
         <v>1</v>
       </c>
-      <c r="K13" s="107">
-        <f>DATE(2026,10,27)-DATE(2026,10,26)</f>
-        <v>1</v>
-      </c>
-      <c r="L13" s="104">
+      <c r="K13" s="91">
+        <f ca="1">TODAY()-DATE(2026,10,26)</f>
+        <v>3</v>
+      </c>
+      <c r="L13" s="92"/>
+      <c r="M13" s="24">
+        <v>41</v>
+      </c>
+      <c r="N13" s="24">
+        <v>500</v>
+      </c>
+      <c r="O13" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P13" s="95"/>
+      <c r="Q13" s="135" t="s">
+        <v>66</v>
+      </c>
+      <c r="R13" s="89"/>
+      <c r="S13" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T13" s="158"/>
+    </row>
+    <row r="14" spans="1:20" ht="60">
+      <c r="A14" s="36">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="179" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="26">
+        <v>46294</v>
+      </c>
+      <c r="F14" s="33">
+        <f ca="1">TODAY()-E14</f>
+        <v>30</v>
+      </c>
+      <c r="G14" s="88">
+        <f ca="1">TODAY()-DATE(2026,10,3)</f>
+        <v>26</v>
+      </c>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="24">
+        <v>36</v>
+      </c>
+      <c r="N14" s="24">
+        <v>500</v>
+      </c>
+      <c r="O14" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="P14" s="95" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q14" s="133" t="s">
+        <v>239</v>
+      </c>
+      <c r="R14" s="89"/>
+      <c r="S14" s="89" t="s">
+        <v>150</v>
+      </c>
+      <c r="T14" s="158"/>
+    </row>
+    <row r="15" spans="1:20" ht="60">
+      <c r="A15" s="36">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="179" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="26">
+        <v>46292</v>
+      </c>
+      <c r="F15" s="24">
+        <f ca="1">TODAY()-E15</f>
+        <v>32</v>
+      </c>
+      <c r="G15" s="88">
+        <f>DATE(2026,10,27)-DATE(2026,9,28)</f>
+        <v>29</v>
+      </c>
+      <c r="H15" s="88">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
         <v>1</v>
       </c>
-      <c r="M13" s="33">
-        <v>7</v>
-      </c>
-      <c r="N13" s="33">
-        <v>100</v>
-      </c>
-      <c r="O13" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P13" s="111" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q13" s="149" t="s">
-        <v>199</v>
-      </c>
-      <c r="R13" s="105"/>
-      <c r="S13" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T13" s="174"/>
-    </row>
-    <row r="14" spans="1:20" ht="60">
-      <c r="A14" s="52">
-        <f t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="87" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="117" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" s="35">
-        <v>46282</v>
-      </c>
-      <c r="F14" s="33">
-        <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>42</v>
-      </c>
-      <c r="G14" s="33">
-        <f>DATE(2026,10,6)-DATE(2026,9,17)</f>
-        <v>19</v>
-      </c>
-      <c r="H14" s="104">
-        <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
-        <v>13</v>
-      </c>
-      <c r="I14" s="104">
-        <f>DATE(2026,10,22)-DATE(2026,10,21)</f>
-        <v>1</v>
-      </c>
-      <c r="J14" s="137">
-        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="107">
-        <f ca="1">TODAY()-DATE(2026,10,26)</f>
-        <v>3</v>
-      </c>
-      <c r="L14" s="108"/>
-      <c r="M14" s="33">
-        <v>41</v>
-      </c>
-      <c r="N14" s="33">
+      <c r="I15" s="88"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="24">
+        <v>31</v>
+      </c>
+      <c r="N15" s="88">
         <v>500</v>
       </c>
-      <c r="O14" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="151" t="s">
-        <v>76</v>
-      </c>
-      <c r="R14" s="105"/>
-      <c r="S14" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T14" s="174"/>
-    </row>
-    <row r="15" spans="1:20" ht="60">
-      <c r="A15" s="52">
-        <f t="shared" si="4"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="67" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="195" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="35">
-        <v>46294</v>
-      </c>
-      <c r="F15" s="46">
-        <f t="shared" ca="1" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="G15" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,3)</f>
-        <v>26</v>
-      </c>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="33">
-        <v>36</v>
-      </c>
-      <c r="N15" s="33">
-        <v>500</v>
-      </c>
-      <c r="O15" s="112" t="s">
-        <v>247</v>
-      </c>
-      <c r="P15" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q15" s="149" t="s">
-        <v>248</v>
-      </c>
-      <c r="R15" s="105"/>
-      <c r="S15" s="105" t="s">
-        <v>167</v>
-      </c>
-      <c r="T15" s="174"/>
+      <c r="O15" s="96" t="s">
+        <v>210</v>
+      </c>
+      <c r="P15" s="95" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T15" s="158"/>
     </row>
     <row r="16" spans="1:20" ht="60">
-      <c r="A16" s="52">
-        <f t="shared" si="4"/>
+      <c r="A16" s="36">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="B16" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="195" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="35">
-        <v>46292</v>
-      </c>
-      <c r="F16" s="33">
-        <f t="shared" ca="1" si="2"/>
-        <v>32</v>
-      </c>
-      <c r="G16" s="104">
-        <f>DATE(2026,10,27)-DATE(2026,9,28)</f>
-        <v>29</v>
-      </c>
-      <c r="H16" s="104">
+      <c r="B16" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="26">
+        <v>46291</v>
+      </c>
+      <c r="F16" s="24">
+        <f ca="1">TODAY()-E16</f>
+        <v>33</v>
+      </c>
+      <c r="G16" s="36">
+        <f>DATE(2026,10,22)-DATE(2026,9,28)</f>
+        <v>24</v>
+      </c>
+      <c r="H16" s="88">
+        <f>DATE(2026,10,27)-DATE(2026,10,22)</f>
+        <v>5</v>
+      </c>
+      <c r="I16" s="88">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
         <v>1</v>
       </c>
-      <c r="I16" s="104"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
-      <c r="L16" s="105"/>
-      <c r="M16" s="33">
-        <v>31</v>
-      </c>
-      <c r="N16" s="104">
-        <v>500</v>
-      </c>
-      <c r="O16" s="112" t="s">
-        <v>229</v>
-      </c>
-      <c r="P16" s="111" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q16" s="149"/>
-      <c r="R16" s="105"/>
-      <c r="S16" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T16" s="174"/>
+      <c r="J16" s="89"/>
+      <c r="K16" s="89"/>
+      <c r="L16" s="89"/>
+      <c r="M16" s="24">
+        <v>28</v>
+      </c>
+      <c r="N16" s="88">
+        <v>350</v>
+      </c>
+      <c r="O16" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="P16" s="98" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="89"/>
+      <c r="S16" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T16" s="158"/>
     </row>
     <row r="17" spans="1:20" ht="60">
-      <c r="A17" s="52">
-        <f t="shared" si="4"/>
+      <c r="A17" s="36">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="B17" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="35">
-        <v>46291</v>
-      </c>
-      <c r="F17" s="33">
-        <f t="shared" ca="1" si="2"/>
-        <v>33</v>
-      </c>
-      <c r="G17" s="52">
-        <f>DATE(2026,10,22)-DATE(2026,9,28)</f>
-        <v>24</v>
-      </c>
-      <c r="H17" s="104">
-        <f>DATE(2026,10,27)-DATE(2026,10,22)</f>
-        <v>5</v>
-      </c>
-      <c r="I17" s="104">
+      <c r="B17" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="182" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="26">
+        <v>46302</v>
+      </c>
+      <c r="F17" s="24">
+        <f ca="1">TODAY()-E17</f>
+        <v>22</v>
+      </c>
+      <c r="G17" s="71">
+        <f ca="1">TODAY()-DATE(2026,10,21)</f>
+        <v>8</v>
+      </c>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="24">
+        <f>129+6</f>
+        <v>135</v>
+      </c>
+      <c r="N17" s="88">
+        <v>1500</v>
+      </c>
+      <c r="O17" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="P17" s="95" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q17" s="136" t="s">
+        <v>170</v>
+      </c>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89" t="s">
+        <v>150</v>
+      </c>
+      <c r="T17" s="158"/>
+    </row>
+    <row r="18" spans="1:20" ht="33.5" customHeight="1">
+      <c r="A18" s="36">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="141" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="181" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="26">
+        <v>46295</v>
+      </c>
+      <c r="F18" s="24">
+        <f ca="1">TODAY()-E18</f>
+        <v>29</v>
+      </c>
+      <c r="G18" s="88">
+        <f ca="1">TODAY()-DATE(2026,10,13)</f>
+        <v>16</v>
+      </c>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="24">
+        <v>48</v>
+      </c>
+      <c r="N18" s="88">
+        <v>550</v>
+      </c>
+      <c r="O18" s="96" t="s">
+        <v>226</v>
+      </c>
+      <c r="P18" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q18" s="133"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="89" t="s">
+        <v>165</v>
+      </c>
+      <c r="T18" s="158"/>
+    </row>
+    <row r="19" spans="1:20" ht="60">
+      <c r="A19" s="36">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="179" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="26">
+        <v>46295</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" ref="F19" ca="1" si="4">TODAY()-E19</f>
+        <v>29</v>
+      </c>
+      <c r="G19" s="88">
+        <f ca="1">TODAY()-DATE(2026,10,12)</f>
+        <v>17</v>
+      </c>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="89"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="24">
+        <v>40</v>
+      </c>
+      <c r="N19" s="88">
+        <v>450</v>
+      </c>
+      <c r="O19" s="96" t="s">
+        <v>227</v>
+      </c>
+      <c r="P19" s="95"/>
+      <c r="Q19" s="133" t="s">
+        <v>152</v>
+      </c>
+      <c r="R19" s="89"/>
+      <c r="S19" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T19" s="158"/>
+    </row>
+    <row r="20" spans="1:20" ht="127">
+      <c r="A20" s="36">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="26">
+        <v>46307</v>
+      </c>
+      <c r="F20" s="3">
+        <f ca="1">TODAY()-E20</f>
+        <v>17</v>
+      </c>
+      <c r="G20" s="88">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
         <v>1</v>
       </c>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
-      <c r="L17" s="105"/>
-      <c r="M17" s="33">
-        <v>28</v>
-      </c>
-      <c r="N17" s="104">
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="24">
+        <v>31</v>
+      </c>
+      <c r="N20" s="88">
         <v>350</v>
       </c>
-      <c r="O17" s="115" t="s">
-        <v>69</v>
-      </c>
-      <c r="P17" s="114" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q17" s="151"/>
-      <c r="R17" s="105"/>
-      <c r="S17" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T17" s="174"/>
-    </row>
-    <row r="18" spans="1:20" ht="60">
-      <c r="A18" s="52">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="198" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="O20" s="96" t="s">
+        <v>241</v>
+      </c>
+      <c r="P20" s="95" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q20" s="133" t="s">
+        <v>240</v>
+      </c>
+      <c r="R20" s="89" t="s">
+        <v>243</v>
+      </c>
+      <c r="S20" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T20" s="158"/>
+    </row>
+    <row r="21" spans="1:20" ht="60">
+      <c r="A21" s="36">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="35">
-        <v>46302</v>
-      </c>
-      <c r="F18" s="33">
-        <f t="shared" ca="1" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="G18" s="87">
-        <f ca="1">TODAY()-DATE(2026,10,21)</f>
-        <v>8</v>
-      </c>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="105"/>
-      <c r="M18" s="33">
-        <f>129+6</f>
-        <v>135</v>
-      </c>
-      <c r="N18" s="104">
-        <v>1500</v>
-      </c>
-      <c r="O18" s="115" t="s">
-        <v>250</v>
-      </c>
-      <c r="P18" s="111" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q18" s="152" t="s">
-        <v>187</v>
-      </c>
-      <c r="R18" s="105"/>
-      <c r="S18" s="105" t="s">
-        <v>167</v>
-      </c>
-      <c r="T18" s="174"/>
-    </row>
-    <row r="19" spans="1:20" ht="33.5" customHeight="1">
-      <c r="A19" s="52">
-        <f t="shared" si="4"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="157" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="197" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="35">
-        <v>46295</v>
-      </c>
-      <c r="F19" s="33">
-        <f t="shared" ca="1" si="2"/>
-        <v>29</v>
-      </c>
-      <c r="G19" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,13)</f>
-        <v>16</v>
-      </c>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="33">
-        <v>48</v>
-      </c>
-      <c r="N19" s="104">
-        <v>550</v>
-      </c>
-      <c r="O19" s="112" t="s">
-        <v>251</v>
-      </c>
-      <c r="P19" s="111" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q19" s="149"/>
-      <c r="R19" s="105"/>
-      <c r="S19" s="105" t="s">
-        <v>182</v>
-      </c>
-      <c r="T19" s="174"/>
-    </row>
-    <row r="20" spans="1:20" ht="60">
-      <c r="A20" s="52">
-        <f t="shared" si="4"/>
-        <v>19</v>
-      </c>
-      <c r="B20" s="87" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="195" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="35">
-        <v>46295</v>
-      </c>
-      <c r="F20" s="8">
-        <f t="shared" ref="F20" ca="1" si="5">TODAY()-E20</f>
-        <v>29</v>
-      </c>
-      <c r="G20" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>17</v>
-      </c>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="33">
-        <v>40</v>
-      </c>
-      <c r="N20" s="104">
-        <v>450</v>
-      </c>
-      <c r="O20" s="112" t="s">
-        <v>252</v>
-      </c>
-      <c r="P20" s="111"/>
-      <c r="Q20" s="149" t="s">
-        <v>169</v>
-      </c>
-      <c r="R20" s="105"/>
-      <c r="S20" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T20" s="174"/>
-    </row>
-    <row r="21" spans="1:20" ht="85">
-      <c r="A21" s="52">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="B21" s="87" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="35">
+      <c r="E21" s="26">
         <v>46307</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="91">
         <f ca="1">TODAY()-E21</f>
         <v>17</v>
       </c>
-      <c r="G21" s="104">
-        <f ca="1">TODAY()-DATE(2026,10,26)</f>
-        <v>3</v>
-      </c>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="105"/>
-      <c r="M21" s="33">
-        <v>31</v>
-      </c>
-      <c r="N21" s="104">
-        <v>350</v>
-      </c>
-      <c r="O21" s="112" t="s">
-        <v>253</v>
-      </c>
-      <c r="P21" s="111" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q21" s="149" t="s">
-        <v>240</v>
-      </c>
-      <c r="R21" s="105" t="s">
-        <v>219</v>
-      </c>
-      <c r="S21" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T21" s="174"/>
-    </row>
-    <row r="22" spans="1:20" ht="60">
-      <c r="A22" s="52">
-        <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="B22" s="87" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="35">
-        <v>46307</v>
-      </c>
-      <c r="F22" s="107">
-        <f ca="1">TODAY()-E22</f>
-        <v>17</v>
-      </c>
-      <c r="G22" s="104">
+      <c r="G21" s="88">
         <f ca="1">TODAY()-DATE(2026,10,19)</f>
         <v>10</v>
       </c>
-      <c r="H22" s="168"/>
-      <c r="I22" s="168"/>
-      <c r="J22" s="168"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="33">
+      <c r="H21" s="152"/>
+      <c r="I21" s="152"/>
+      <c r="J21" s="152"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="24">
         <v>28</v>
       </c>
-      <c r="N22" s="104">
+      <c r="N21" s="88">
         <v>500</v>
       </c>
-      <c r="O22" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="153"/>
-      <c r="R22" s="105"/>
-      <c r="S22" s="105" t="s">
+      <c r="O21" s="96" t="s">
         <v>168</v>
       </c>
-      <c r="T22" s="174"/>
-    </row>
-    <row r="23" spans="1:20" ht="60">
-      <c r="A23" s="52">
-        <f t="shared" si="4"/>
+      <c r="P21" s="95"/>
+      <c r="Q21" s="137"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T21" s="158"/>
+    </row>
+    <row r="22" spans="1:20" ht="60">
+      <c r="A22" s="36">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="179" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="4">
+        <v>46302</v>
+      </c>
+      <c r="F22" s="153">
+        <f ca="1">TODAY()-E22</f>
         <v>22</v>
       </c>
-      <c r="B23" s="87" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="195" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="9">
-        <v>46302</v>
-      </c>
-      <c r="F23" s="169">
-        <f ca="1">TODAY()-E23</f>
-        <v>22</v>
-      </c>
-      <c r="G23" s="104" t="str">
+      <c r="G22" s="88" t="str">
         <f ca="1">TRIM(TODAY()-DATE(2026,10,19))</f>
         <v>10</v>
       </c>
-      <c r="H23" s="168"/>
-      <c r="I23" s="168"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="105"/>
-      <c r="M23" s="33">
+      <c r="H22" s="152"/>
+      <c r="I22" s="152"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="24">
         <v>36</v>
       </c>
-      <c r="N23" s="104">
+      <c r="N22" s="88">
         <v>450</v>
       </c>
-      <c r="O23" s="112" t="s">
-        <v>230</v>
-      </c>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="153"/>
-      <c r="R23" s="105"/>
-      <c r="S23" s="105"/>
-      <c r="T23" s="174"/>
-    </row>
-    <row r="24" spans="1:20" ht="60">
-      <c r="A24" s="52">
-        <f t="shared" si="4"/>
-        <v>23</v>
-      </c>
-      <c r="B24" s="170" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="O22" s="96" t="s">
+        <v>211</v>
+      </c>
+      <c r="P22" s="95"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="89"/>
+      <c r="T22" s="158"/>
+    </row>
+    <row r="23" spans="1:20" ht="60">
+      <c r="A23" s="36">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="154" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="147">
+      <c r="E23" s="131">
         <v>46309</v>
       </c>
-      <c r="F24" s="169">
-        <f ca="1">TODAY()-E24</f>
+      <c r="F23" s="153">
+        <f ca="1">TODAY()-E23</f>
         <v>15</v>
       </c>
-      <c r="G24" s="104">
+      <c r="G23" s="88">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
         <v>7</v>
       </c>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="33">
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="24">
         <v>42</v>
       </c>
-      <c r="N24" s="104">
+      <c r="N23" s="88">
         <v>500</v>
       </c>
-      <c r="O24" s="112" t="s">
-        <v>204</v>
-      </c>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="149"/>
-      <c r="R24" s="105"/>
-      <c r="S24" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T24" s="174"/>
-    </row>
-    <row r="25" spans="1:20" ht="60">
-      <c r="A25" s="52">
-        <f t="shared" si="4"/>
-        <v>24</v>
-      </c>
-      <c r="B25" s="170" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="O23" s="96" t="s">
+        <v>186</v>
+      </c>
+      <c r="P23" s="95"/>
+      <c r="Q23" s="133"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T23" s="158"/>
+    </row>
+    <row r="24" spans="1:20" ht="60">
+      <c r="A24" s="36">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="154" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="147">
+      <c r="E24" s="131">
         <v>46312</v>
       </c>
-      <c r="F25" s="169">
-        <f ca="1">TODAY()-E25</f>
+      <c r="F24" s="153">
+        <f ca="1">TODAY()-E24</f>
         <v>12</v>
       </c>
-      <c r="G25" s="104">
+      <c r="G24" s="88">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
         <v>7</v>
       </c>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="104">
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="88">
         <v>23</v>
       </c>
-      <c r="N25" s="104">
+      <c r="N24" s="88">
         <v>350</v>
       </c>
-      <c r="O25" s="112" t="s">
-        <v>200</v>
-      </c>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="149"/>
-      <c r="R25" s="105"/>
-      <c r="S25" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T25" s="174"/>
+      <c r="O24" s="96" t="s">
+        <v>182</v>
+      </c>
+      <c r="P24" s="95"/>
+      <c r="Q24" s="133"/>
+      <c r="R24" s="89"/>
+      <c r="S24" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T24" s="158"/>
+    </row>
+    <row r="25" spans="1:20" ht="60">
+      <c r="A25" s="36">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="131">
+        <v>46312</v>
+      </c>
+      <c r="F25" s="153">
+        <f t="shared" ref="F25" ca="1" si="5">TODAY()-E25</f>
+        <v>12</v>
+      </c>
+      <c r="G25" s="88">
+        <f ca="1">TODAY()-DATE(2026,10,27)</f>
+        <v>2</v>
+      </c>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="24">
+        <v>56</v>
+      </c>
+      <c r="N25" s="88">
+        <v>300</v>
+      </c>
+      <c r="O25" s="96" t="s">
+        <v>228</v>
+      </c>
+      <c r="P25" s="95" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q25" s="138"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89" t="s">
+        <v>150</v>
+      </c>
+      <c r="T25" s="158"/>
     </row>
     <row r="26" spans="1:20" ht="60">
-      <c r="A26" s="52">
-        <f t="shared" si="4"/>
+      <c r="A26" s="36">
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="B26" s="171" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="B26" s="103" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="147">
-        <v>46312</v>
-      </c>
-      <c r="F26" s="169">
-        <f t="shared" ref="F26" ca="1" si="6">TODAY()-E26</f>
-        <v>12</v>
-      </c>
-      <c r="G26" s="104"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="105"/>
-      <c r="M26" s="33">
-        <v>56</v>
-      </c>
-      <c r="N26" s="104">
-        <v>300</v>
-      </c>
-      <c r="O26" s="112" t="s">
-        <v>255</v>
-      </c>
-      <c r="P26" s="110"/>
-      <c r="Q26" s="154"/>
-      <c r="R26" s="105"/>
-      <c r="S26" s="105" t="s">
-        <v>167</v>
-      </c>
-      <c r="T26" s="174"/>
-    </row>
-    <row r="27" spans="1:20" ht="60">
-      <c r="A27" s="52">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="B27" s="119" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="147">
+      <c r="E26" s="131">
         <v>46316</v>
       </c>
-      <c r="F27" s="169">
-        <f t="shared" ref="F27:F35" ca="1" si="7">TODAY()-E27</f>
+      <c r="F26" s="153">
+        <f t="shared" ref="F26:F34" ca="1" si="6">TODAY()-E26</f>
         <v>8</v>
       </c>
-      <c r="G27" s="104" t="str">
+      <c r="G26" s="88" t="str">
         <f ca="1">TRIM(TODAY()-DATE(2026,10,26))</f>
         <v>3</v>
       </c>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="105"/>
-      <c r="K27" s="105"/>
-      <c r="L27" s="118"/>
-      <c r="M27" s="33">
-        <v>109</v>
-      </c>
-      <c r="N27" s="106">
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="89"/>
+      <c r="K26" s="89"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="24">
+        <f>8+109</f>
+        <v>117</v>
+      </c>
+      <c r="N26" s="88">
         <v>350</v>
       </c>
-      <c r="O27" s="112" t="s">
-        <v>256</v>
-      </c>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="154"/>
-      <c r="R27" s="105"/>
-      <c r="S27" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T27" s="174"/>
-    </row>
-    <row r="28" spans="1:20" ht="60">
-      <c r="A28" s="52">
-        <f t="shared" si="4"/>
-        <v>27</v>
-      </c>
-      <c r="B28" s="119" t="s">
-        <v>161</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="O26" s="96" t="s">
+        <v>246</v>
+      </c>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="138"/>
+      <c r="R26" s="89"/>
+      <c r="S26" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T26" s="158"/>
+    </row>
+    <row r="27" spans="1:20" ht="60">
+      <c r="A27" s="36">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="147">
+      <c r="E27" s="131">
         <v>46316</v>
       </c>
-      <c r="F28" s="169">
-        <f t="shared" ca="1" si="7"/>
+      <c r="F27" s="153">
+        <f t="shared" ca="1" si="6"/>
         <v>8</v>
       </c>
-      <c r="G28" s="104">
+      <c r="G27" s="88">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
         <v>4</v>
       </c>
-      <c r="H28" s="168"/>
-      <c r="I28" s="168"/>
-      <c r="J28" s="105"/>
-      <c r="K28" s="105"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="33">
+      <c r="H27" s="152"/>
+      <c r="I27" s="152"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="24">
         <v>69</v>
       </c>
-      <c r="N28" s="104">
+      <c r="N27" s="88">
         <v>400</v>
       </c>
-      <c r="O28" s="112" t="s">
-        <v>212</v>
-      </c>
-      <c r="P28" s="110"/>
-      <c r="Q28" s="154"/>
-      <c r="R28" s="105"/>
-      <c r="S28" s="105" t="s">
-        <v>167</v>
-      </c>
-      <c r="T28" s="174"/>
-    </row>
-    <row r="29" spans="1:20" ht="60">
-      <c r="A29" s="52">
-        <f t="shared" si="4"/>
-        <v>28</v>
-      </c>
-      <c r="B29" s="119" t="s">
-        <v>166</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="O27" s="96" t="s">
+        <v>194</v>
+      </c>
+      <c r="P27" s="95"/>
+      <c r="Q27" s="138"/>
+      <c r="R27" s="89"/>
+      <c r="S27" s="89" t="s">
+        <v>150</v>
+      </c>
+      <c r="T27" s="158"/>
+    </row>
+    <row r="28" spans="1:20" ht="60">
+      <c r="A28" s="36">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="103" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="147">
+      <c r="E28" s="131">
         <v>46312</v>
       </c>
-      <c r="F29" s="169">
-        <f t="shared" ca="1" si="7"/>
+      <c r="F28" s="153">
+        <f t="shared" ca="1" si="6"/>
         <v>12</v>
       </c>
-      <c r="G29" s="104">
+      <c r="G28" s="88">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
         <v>7</v>
       </c>
-      <c r="H29" s="168"/>
-      <c r="I29" s="192"/>
-      <c r="J29" s="168"/>
-      <c r="K29" s="192"/>
-      <c r="L29" s="192"/>
-      <c r="M29" s="33">
+      <c r="H28" s="152"/>
+      <c r="I28" s="176"/>
+      <c r="J28" s="152"/>
+      <c r="K28" s="176"/>
+      <c r="L28" s="176"/>
+      <c r="M28" s="24">
         <v>33</v>
       </c>
-      <c r="N29" s="104">
+      <c r="N28" s="88">
         <v>450</v>
       </c>
-      <c r="O29" s="112" t="s">
-        <v>257</v>
-      </c>
-      <c r="P29" s="110"/>
-      <c r="Q29" s="154"/>
-      <c r="R29" s="105"/>
-      <c r="S29" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T29" s="174"/>
+      <c r="O28" s="96" t="s">
+        <v>247</v>
+      </c>
+      <c r="P28" s="94"/>
+      <c r="Q28" s="138"/>
+      <c r="R28" s="89"/>
+      <c r="S28" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T28" s="158"/>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="103" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" s="131">
+        <v>46323</v>
+      </c>
+      <c r="F29" s="153">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G29" s="88"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="102"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="24">
+        <v>21</v>
+      </c>
+      <c r="N29" s="90">
+        <v>150</v>
+      </c>
+      <c r="O29" s="94"/>
+      <c r="P29" s="94"/>
+      <c r="Q29" s="94"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T29" s="158"/>
     </row>
     <row r="30" spans="1:20">
-      <c r="A30" s="33">
-        <f t="shared" si="4"/>
+      <c r="A30" s="24">
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
-      <c r="B30" s="119" t="s">
-        <v>192</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E30" s="147">
+      <c r="B30" s="177" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="177" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="131">
+        <v>46321</v>
+      </c>
+      <c r="F30" s="153">
+        <f t="shared" ca="1" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="G30" s="88"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="102"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="102"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="24">
+        <v>12</v>
+      </c>
+      <c r="N30" s="90">
+        <v>150</v>
+      </c>
+      <c r="O30" s="94"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="94"/>
+      <c r="R30" s="89"/>
+      <c r="S30" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T30" s="158"/>
+    </row>
+    <row r="31" spans="1:20" ht="29">
+      <c r="A31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="177" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="177" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="131">
+        <v>46322</v>
+      </c>
+      <c r="F31" s="153">
+        <f t="shared" ca="1" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="G31" s="88">
+        <f ca="1">TODAY()-DATE(2026,10,29)</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="89"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="102"/>
+      <c r="K31" s="102"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="24">
+        <v>26</v>
+      </c>
+      <c r="N31" s="90">
+        <v>450</v>
+      </c>
+      <c r="O31" s="94"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="94"/>
+      <c r="R31" s="89"/>
+      <c r="S31" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T31" s="158"/>
+    </row>
+    <row r="32" spans="1:20" ht="28">
+      <c r="A32" s="24">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="160" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E32" s="131">
+        <v>46322</v>
+      </c>
+      <c r="F32" s="153">
+        <f t="shared" ca="1" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="G32" s="88"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="102"/>
+      <c r="K32" s="102"/>
+      <c r="L32" s="102"/>
+      <c r="M32" s="24">
+        <v>16</v>
+      </c>
+      <c r="N32" s="90">
+        <v>200</v>
+      </c>
+      <c r="O32" s="158"/>
+      <c r="P32" s="158"/>
+      <c r="Q32" s="158"/>
+      <c r="R32" s="89"/>
+      <c r="S32" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T32" s="158"/>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="178" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="178" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="131">
         <v>46323</v>
       </c>
-      <c r="F30" s="169">
-        <f t="shared" ca="1" si="7"/>
+      <c r="F33" s="153">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="G30" s="104"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="33">
-        <v>21</v>
-      </c>
-      <c r="N30" s="106">
-        <v>150</v>
-      </c>
-      <c r="O30" s="110"/>
-      <c r="P30" s="110"/>
-      <c r="Q30" s="110"/>
-      <c r="R30" s="105"/>
-      <c r="S30" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T30" s="174"/>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="33">
-        <f t="shared" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="B31" s="193" t="s">
-        <v>205</v>
-      </c>
-      <c r="C31" s="193" t="s">
+      <c r="G33" s="88"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="102"/>
+      <c r="K33" s="102"/>
+      <c r="L33" s="102"/>
+      <c r="M33" s="24">
+        <v>17</v>
+      </c>
+      <c r="N33" s="90">
+        <v>600</v>
+      </c>
+      <c r="O33" s="158"/>
+      <c r="P33" s="158"/>
+      <c r="Q33" s="158"/>
+      <c r="R33" s="89"/>
+      <c r="S33" s="89" t="s">
+        <v>237</v>
+      </c>
+      <c r="T33" s="158" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" s="24">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="160" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E31" s="147">
-        <v>46321</v>
-      </c>
-      <c r="F31" s="169">
-        <f t="shared" ca="1" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="G31" s="104"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="33">
-        <v>12</v>
-      </c>
-      <c r="N31" s="106">
-        <v>150</v>
-      </c>
-      <c r="O31" s="110"/>
-      <c r="P31" s="110"/>
-      <c r="Q31" s="110"/>
-      <c r="R31" s="105"/>
-      <c r="S31" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T31" s="174"/>
-    </row>
-    <row r="32" spans="1:20" ht="29">
-      <c r="A32" s="33">
-        <f t="shared" si="4"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="193" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="193" t="s">
-        <v>214</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="147">
-        <v>46322</v>
-      </c>
-      <c r="F32" s="169">
-        <f t="shared" ca="1" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="G32" s="104"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="118"/>
-      <c r="L32" s="118"/>
-      <c r="M32" s="33">
-        <v>20</v>
-      </c>
-      <c r="N32" s="106">
-        <v>450</v>
-      </c>
-      <c r="O32" s="110"/>
-      <c r="P32" s="110"/>
-      <c r="Q32" s="110"/>
-      <c r="R32" s="105"/>
-      <c r="S32" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T32" s="174"/>
-    </row>
-    <row r="33" spans="1:20" ht="28">
-      <c r="A33" s="33">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-      <c r="B33" s="176" t="s">
-        <v>217</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E33" s="147">
-        <v>46322</v>
-      </c>
-      <c r="F33" s="169">
-        <f t="shared" ca="1" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="G33" s="104"/>
-      <c r="H33" s="105"/>
-      <c r="I33" s="118"/>
-      <c r="J33" s="118"/>
-      <c r="K33" s="118"/>
-      <c r="L33" s="118"/>
-      <c r="M33" s="33">
-        <v>16</v>
-      </c>
-      <c r="N33" s="106">
-        <v>200</v>
-      </c>
-      <c r="O33" s="174"/>
-      <c r="P33" s="174"/>
-      <c r="Q33" s="174"/>
-      <c r="R33" s="105"/>
-      <c r="S33" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="T33" s="174"/>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="33">
-        <f t="shared" si="4"/>
-        <v>33</v>
-      </c>
-      <c r="B34" s="194" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="194" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="168"/>
-      <c r="F34" s="168"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="118"/>
-      <c r="J34" s="118"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="106"/>
-      <c r="O34" s="174"/>
-      <c r="P34" s="174"/>
-      <c r="Q34" s="174"/>
-      <c r="R34" s="105"/>
-      <c r="S34" s="105"/>
-      <c r="T34" s="174"/>
+      <c r="E34" s="131">
+        <v>46323</v>
+      </c>
+      <c r="F34" s="153">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="88"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="24">
+        <v>74</v>
+      </c>
+      <c r="N34" s="90">
+        <v>700</v>
+      </c>
+      <c r="O34" s="158"/>
+      <c r="P34" s="158"/>
+      <c r="Q34" s="158"/>
+      <c r="R34" s="89"/>
+      <c r="S34" s="89" t="s">
+        <v>237</v>
+      </c>
+      <c r="T34" s="158" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="35" spans="1:20">
-      <c r="A35" s="33">
-        <f t="shared" si="4"/>
-        <v>34</v>
-      </c>
-      <c r="B35" s="176" t="s">
+      <c r="A35" s="24">
+        <v>35</v>
+      </c>
+      <c r="B35" s="160" t="s">
+        <v>230</v>
+      </c>
+      <c r="C35" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="C35" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="202">
-        <v>46323</v>
-      </c>
-      <c r="F35" s="169">
-        <f t="shared" ca="1" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="G35" s="104"/>
-      <c r="H35" s="105"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="118"/>
-      <c r="L35" s="118"/>
-      <c r="M35" s="33">
-        <v>74</v>
-      </c>
-      <c r="N35" s="106">
-        <v>700</v>
-      </c>
-      <c r="O35" s="174"/>
-      <c r="P35" s="174"/>
-      <c r="Q35" s="174"/>
-      <c r="R35" s="105"/>
-      <c r="S35" s="105"/>
-      <c r="T35" s="174" t="s">
-        <v>241</v>
-      </c>
+      <c r="E35" s="88"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="89"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="102"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="158"/>
+      <c r="P35" s="158"/>
+      <c r="Q35" s="158"/>
+      <c r="R35" s="89"/>
+      <c r="S35" s="89"/>
+      <c r="T35" s="158"/>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" s="33">
-        <v>35</v>
-      </c>
-      <c r="B36" s="176" t="s">
-        <v>259</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="205"/>
-      <c r="F36" s="205"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="203"/>
-      <c r="J36" s="203"/>
-      <c r="K36" s="203"/>
-      <c r="L36" s="203"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="204"/>
-      <c r="O36" s="174"/>
-      <c r="P36" s="174"/>
-      <c r="Q36" s="174"/>
-      <c r="R36" s="105"/>
-      <c r="S36" s="105"/>
-      <c r="T36" s="174"/>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="R37" s="175"/>
-      <c r="S37" s="175"/>
+      <c r="R36" s="159"/>
+      <c r="S36" s="159"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7559,7 +7229,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
@@ -7567,1166 +7237,1215 @@
     <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.26953125" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" style="59" customWidth="1"/>
-    <col min="7" max="7" width="16.26953125" style="59" customWidth="1"/>
-    <col min="8" max="8" width="7.54296875" style="59" customWidth="1"/>
-    <col min="9" max="9" width="8.1796875" style="59" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" style="59" customWidth="1"/>
-    <col min="11" max="11" width="8.1796875" style="59" customWidth="1"/>
-    <col min="12" max="12" width="8.36328125" style="59" customWidth="1"/>
-    <col min="13" max="13" width="8.7265625" style="59" customWidth="1"/>
-    <col min="14" max="14" width="7.6328125" style="59" customWidth="1"/>
-    <col min="15" max="15" width="7.54296875" style="59" customWidth="1"/>
-    <col min="16" max="16" width="19.81640625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="14.08984375" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="17.54296875" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" style="43" customWidth="1"/>
+    <col min="7" max="7" width="16.26953125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="7.54296875" style="43" customWidth="1"/>
+    <col min="9" max="9" width="8.1796875" style="43" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="8.1796875" style="43" customWidth="1"/>
+    <col min="12" max="12" width="8.36328125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" style="43" customWidth="1"/>
+    <col min="14" max="14" width="7.6328125" style="43" customWidth="1"/>
+    <col min="15" max="15" width="7.54296875" style="43" customWidth="1"/>
+    <col min="16" max="16" width="19.81640625" customWidth="1"/>
+    <col min="17" max="17" width="7.90625" customWidth="1"/>
+    <col min="18" max="18" width="17.54296875" style="43" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="11" customFormat="1" ht="26">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:19" s="6" customFormat="1" ht="26">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="135" t="s">
+      <c r="E1" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="136" t="s">
-        <v>124</v>
-      </c>
-      <c r="G1" s="136" t="s">
-        <v>125</v>
-      </c>
-      <c r="H1" s="136" t="s">
+      <c r="F1" s="120" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="120" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="120" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="120" t="s">
+        <v>180</v>
+      </c>
+      <c r="O1" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="136" t="s">
+      <c r="P1" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="136" t="s">
-        <v>50</v>
-      </c>
-      <c r="K1" s="136" t="s">
+      <c r="Q1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="135" t="s">
-        <v>52</v>
-      </c>
-      <c r="M1" s="136" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="136" t="s">
-        <v>198</v>
-      </c>
-      <c r="O1" s="136" t="s">
-        <v>54</v>
-      </c>
-      <c r="P1" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q1" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="11" customFormat="1" ht="60">
+      <c r="R1" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="60">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="15">
+      <c r="B2" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="8">
         <v>46202</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="9">
         <v>63</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="9">
         <v>32</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="9">
         <v>11</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="9">
         <v>3</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="9">
         <v>6</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="9">
         <v>6</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="9">
         <v>5</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="9">
         <v>6</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N2" s="9">
         <v>184</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O2" s="9">
         <f>372+13</f>
         <v>385</v>
       </c>
-      <c r="P2" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="R2" s="60">
+      <c r="P2" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="44">
         <v>46265</v>
       </c>
-      <c r="S2" s="64"/>
+      <c r="S2" s="48"/>
     </row>
     <row r="3" spans="1:19" ht="60">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="15">
+      <c r="B3" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="8">
         <v>46209</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="9">
         <v>62</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="9">
         <f>DATE(2026,8,1)-DATE(2026,7,8)</f>
         <v>24</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="9">
         <f>DATE(2026,8,15)-DATE(2026,8,1)</f>
         <v>14</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="9">
         <f>DATE(2026,8,21)-DATE(2026,8,20)</f>
         <v>1</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="9">
         <f>DATE(2026,8,24)-DATE(2026,8,21)</f>
         <v>3</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="9">
         <f>DATE(2026,8,31)-DATE(2026,8,24)</f>
         <v>7</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="9">
         <f>DATE(2026,9,7)-DATE(2026,8,31)</f>
         <v>7</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="9">
         <v>44</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="9">
         <v>569</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="9">
         <f>572+15</f>
         <v>587</v>
       </c>
-      <c r="P3" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q3" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="R3" s="61">
+      <c r="P3" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="45">
         <v>46272</v>
       </c>
-      <c r="S3" s="64"/>
-    </row>
-    <row r="4" spans="1:19" ht="70">
+      <c r="S3" s="48"/>
+    </row>
+    <row r="4" spans="1:19" ht="60">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="15">
+      <c r="B4" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="8">
         <v>46195</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="9">
         <v>83</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="9">
         <f>DATE(2026,7,25)-DATE(2026,6,22)</f>
         <v>33</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="9">
         <f>DATE(2026,8,7)-DATE(2026,7,25)</f>
         <v>13</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="9">
         <f>DATE(2026,8,12)-DATE(2026,8,7)</f>
         <v>5</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="9">
         <f>DATE(2026,8,25)-DATE(2026,8,12)</f>
         <v>13</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="9">
         <f>DATE(2026,9,4)-DATE(2026,8,25)</f>
         <v>10</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="9">
         <f>DATE(2026,9,12)-DATE(2026,9,4)</f>
         <v>8</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="9">
         <v>66</v>
       </c>
-      <c r="N4" s="16">
+      <c r="N4" s="9">
         <v>717</v>
       </c>
-      <c r="O4" s="16">
+      <c r="O4" s="9">
         <v>719</v>
       </c>
-      <c r="P4" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q4" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="R4" s="61">
+      <c r="P4" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="45">
         <v>46277</v>
       </c>
-      <c r="S4" s="49"/>
+      <c r="S4" s="34"/>
     </row>
     <row r="5" spans="1:19" ht="60">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="B5" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="8">
         <v>46196</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="9">
         <v>81</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="9">
         <f>DATE(2026,7,30)-DATE(2026,6,24)</f>
         <v>36</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="9">
         <f>DATE(2026,8,11)-DATE(2026,7,30)</f>
         <v>12</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="9">
         <f>DATE(2026,8,19)-DATE(2026,8,11)</f>
         <v>8</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="9">
         <f>DATE(2026,8,24)-DATE(2026,8,19)</f>
         <v>5</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="9">
         <f>DATE(2026,9,4)-DATE(2026,8,24)</f>
         <v>11</v>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="9">
         <f>DATE(2026,9,13)-DATE(2026,9,4)</f>
         <v>9</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="9">
         <v>74</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="9">
         <v>826</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="9">
         <f>826+21</f>
         <v>847</v>
       </c>
-      <c r="P5" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q5" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="R5" s="61">
+      <c r="P5" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="45">
         <v>46278</v>
       </c>
-      <c r="S5" s="49"/>
+      <c r="S5" s="34"/>
     </row>
     <row r="6" spans="1:19" ht="60">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="15">
+      <c r="B6" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="8">
         <v>46195</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="9">
         <v>85</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="9">
         <f>DATE(2026,7,29)-DATE(2026,6,22)</f>
         <v>37</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="9">
         <f>DATE(2026,8,11)-DATE(2026,7,29)</f>
         <v>13</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="9">
         <f>DATE(2026,8,14)-DATE(2026,8,11)</f>
         <v>3</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="9">
         <f>DATE(2026,8,24)-DATE(2026,8,14)</f>
         <v>10</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="9">
         <f>DATE(2026,9,4)-DATE(2026,8,24)</f>
         <v>11</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="9">
         <f>DATE(2026,9,15)-DATE(2026,9,4)</f>
         <v>11</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="9">
         <v>65</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="9">
         <v>802</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="9">
         <f>766+19</f>
         <v>785</v>
       </c>
-      <c r="P6" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q6" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="R6" s="61">
+      <c r="P6" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="45">
         <v>46280</v>
       </c>
-      <c r="S6" s="49"/>
-    </row>
-    <row r="7" spans="1:19" s="27" customFormat="1" ht="60">
-      <c r="A7" s="28">
+      <c r="S6" s="34"/>
+    </row>
+    <row r="7" spans="1:19" s="18" customFormat="1" ht="60">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="D7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="8">
         <v>46234</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="23">
         <v>52</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="32">
         <f>DATE(2026,8,24)-DATE(2026,7,31)</f>
         <v>24</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="32">
         <f>DATE(2026,9,5)-DATE(2026,8,24)</f>
         <v>12</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="32">
         <f>DATE(2026,9,9)-DATE(2026,9,5)</f>
         <v>4</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="32">
         <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
         <v>6</v>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="32">
         <f>DATE(2026,9,17)-DATE(2026,9,14)</f>
         <v>3</v>
       </c>
-      <c r="L7" s="41">
+      <c r="L7" s="32">
         <f>DATE(2026,9,19)-DATE(2026,9,17)</f>
         <v>2</v>
       </c>
-      <c r="M7" s="32">
+      <c r="M7" s="23">
         <v>10</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="9">
         <v>250</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="9">
         <f>218+7</f>
         <v>225</v>
       </c>
-      <c r="P7" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q7" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="61">
+      <c r="P7" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="45">
         <v>46286</v>
       </c>
-      <c r="S7" s="26"/>
-    </row>
-    <row r="8" spans="1:19" s="27" customFormat="1" ht="69" customHeight="1" thickBot="1">
-      <c r="A8" s="28">
+      <c r="S7" s="17"/>
+    </row>
+    <row r="8" spans="1:19" s="18" customFormat="1" ht="69" customHeight="1" thickBot="1">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="15">
+      <c r="C8" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="8">
         <v>46230</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="23">
         <v>58</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="20">
         <f>DATE(2026,8,17)-DATE(2026,7,27)</f>
         <v>21</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="20">
         <f>DATE(2026,8,25)-DATE(2026,8,17)</f>
         <v>8</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="20">
         <f>DATE(2026,9,8)-DATE(2026,8,27)</f>
         <v>12</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="20">
         <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
         <v>6</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="20">
         <f>DATE(2026,9,23)-DATE(2026,9,14)</f>
         <v>9</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="20">
         <f>DATE(2026,9,22)-DATE(2026,9,20)</f>
         <v>2</v>
       </c>
-      <c r="M8" s="32">
+      <c r="M8" s="23">
         <v>21</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="9">
         <v>780</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="9">
         <f>372+13</f>
         <v>385</v>
       </c>
-      <c r="P8" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q8" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="R8" s="61">
+      <c r="P8" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="45">
         <v>46288</v>
       </c>
-      <c r="S8" s="65" t="s">
-        <v>95</v>
+      <c r="S8" s="49" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="60">
-      <c r="A9" s="28">
-        <f t="shared" ref="A9:A17" si="0">ROW()-1</f>
+      <c r="A9" s="19">
+        <f t="shared" ref="A9:A19" si="0">ROW()-1</f>
         <v>8</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="15">
+      <c r="C9" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="8">
         <v>46244</v>
       </c>
-      <c r="F9" s="91">
+      <c r="F9" s="75">
         <v>47</v>
       </c>
-      <c r="G9" s="91">
+      <c r="G9" s="75">
         <f>DATE(2026,8,31)-DATE(2026,8,12)</f>
         <v>19</v>
       </c>
-      <c r="H9" s="91">
+      <c r="H9" s="75">
         <f>DATE(2026,9,14)-DATE(2026,8,31)</f>
         <v>14</v>
       </c>
-      <c r="I9" s="91">
+      <c r="I9" s="75">
         <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
         <v>1</v>
       </c>
-      <c r="J9" s="91">
+      <c r="J9" s="75">
         <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
         <v>6</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9" s="75">
         <f>DATE(2026,9,23)-DATE(2026,9,22)</f>
         <v>1</v>
       </c>
-      <c r="L9" s="91">
+      <c r="L9" s="75">
         <f>DATE(2026,9,23)-DATE(2026,9,17)</f>
         <v>6</v>
       </c>
-      <c r="M9" s="91">
+      <c r="M9" s="75">
         <v>64</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="9">
         <v>700</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="9">
         <f>696+23</f>
         <v>719</v>
       </c>
-      <c r="P9" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="62">
+      <c r="P9" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="46">
         <v>46291</v>
       </c>
-      <c r="S9" s="26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="27" customFormat="1" ht="60">
-      <c r="A10" s="28">
+      <c r="S9" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="18" customFormat="1" ht="60">
+      <c r="A10" s="19">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="15">
+      <c r="C10" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="8">
         <v>46246</v>
       </c>
-      <c r="F10" s="91">
+      <c r="F10" s="75">
         <v>44</v>
       </c>
-      <c r="G10" s="91">
+      <c r="G10" s="75">
         <f>DATE(2026,8,27)-DATE(2026,8,12)</f>
         <v>15</v>
       </c>
-      <c r="H10" s="91">
+      <c r="H10" s="75">
         <f>DATE(2026,9,11)-DATE(2026,8,27)</f>
         <v>15</v>
       </c>
-      <c r="I10" s="91">
+      <c r="I10" s="75">
         <f>DATE(2026,9,16)-DATE(2026,9,14)</f>
         <v>2</v>
       </c>
-      <c r="J10" s="91">
+      <c r="J10" s="75">
         <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
         <v>6</v>
       </c>
-      <c r="K10" s="91">
+      <c r="K10" s="75">
         <f>DATE(2026,9,23)-DATE(2026,9,22)</f>
         <v>1</v>
       </c>
-      <c r="L10" s="91">
+      <c r="L10" s="75">
         <f>DATE(2026,9,25)-DATE(2026,9,23)</f>
         <v>2</v>
       </c>
-      <c r="M10" s="91">
+      <c r="M10" s="75">
         <v>55</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="9">
         <v>700</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="9">
         <f>868+21</f>
         <v>889</v>
       </c>
-      <c r="P10" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="62">
+      <c r="P10" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="46">
         <v>46290</v>
       </c>
-      <c r="S10" s="26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" s="27" customFormat="1" ht="130.5">
-      <c r="A11" s="28">
+      <c r="S10" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" s="18" customFormat="1" ht="130.5">
+      <c r="A11" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="C11" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="8">
         <v>46258</v>
       </c>
-      <c r="F11" s="91">
+      <c r="F11" s="75">
         <f>DATE(2026,9,30)-DATE(2026,8,24)</f>
         <v>37</v>
       </c>
-      <c r="G11" s="91">
+      <c r="G11" s="75">
         <f>DATE(2026,9,9)-DATE(2026,8,24)</f>
         <v>16</v>
       </c>
-      <c r="H11" s="91">
+      <c r="H11" s="75">
         <f>DATE(2026,9,14)-DATE(2026,9,9)</f>
         <v>5</v>
       </c>
-      <c r="I11" s="91">
+      <c r="I11" s="75">
         <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="91">
+      <c r="J11" s="75">
         <f>DATE(2026,9,23)-DATE(2026,9,16)</f>
         <v>7</v>
       </c>
-      <c r="K11" s="91">
+      <c r="K11" s="75">
         <f>DATE(2026,9,23)-DATE(2026,9,23)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="91">
+      <c r="L11" s="75">
         <f>DATE(2026,9,30)-DATE(2026,9,23)</f>
         <v>7</v>
       </c>
-      <c r="M11" s="91">
+      <c r="M11" s="75">
         <v>60</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="9">
         <v>500</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="9">
         <f>798+21</f>
         <v>819</v>
       </c>
-      <c r="P11" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="63">
+      <c r="P11" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="47">
         <v>46295</v>
       </c>
-      <c r="S11" s="26" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="27" customFormat="1" ht="116">
-      <c r="A12" s="28">
+      <c r="S11" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="18" customFormat="1" ht="116">
+      <c r="A12" s="19">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="15">
+      <c r="C12" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="8">
         <v>46252</v>
       </c>
-      <c r="F12" s="91">
+      <c r="F12" s="75">
         <f>DATE(2026,10,3)-DATE(2026,8,18)</f>
         <v>46</v>
       </c>
-      <c r="G12" s="91">
+      <c r="G12" s="75">
         <f>DATE(2026,9,14)-DATE(2026,8,18)</f>
         <v>27</v>
       </c>
-      <c r="H12" s="91">
+      <c r="H12" s="75">
         <f>DATE(2026,9,18)-DATE(2026,9,14)</f>
         <v>4</v>
       </c>
-      <c r="I12" s="91">
+      <c r="I12" s="75">
         <f>DATE(2026,9,22)-DATE(2026,9,18)</f>
         <v>4</v>
       </c>
-      <c r="J12" s="91">
+      <c r="J12" s="75">
         <f>DATE(2026,9,26)-DATE(2026,9,22)</f>
         <v>4</v>
       </c>
-      <c r="K12" s="91">
+      <c r="K12" s="75">
         <f>DATE(2026,9,29)-DATE(2026,9,26)</f>
         <v>3</v>
       </c>
-      <c r="L12" s="91">
+      <c r="L12" s="75">
         <f>DATE(2026,10,1)-DATE(2026,9,29)</f>
         <v>2</v>
       </c>
-      <c r="M12" s="91">
+      <c r="M12" s="75">
         <v>25</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="9">
         <v>500</v>
       </c>
-      <c r="O12" s="16">
+      <c r="O12" s="9">
         <f>446+19</f>
         <v>465</v>
       </c>
-      <c r="P12" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="63">
+      <c r="P12" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="47">
         <v>46298</v>
       </c>
-      <c r="S12" s="26" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" s="27" customFormat="1" ht="60">
-      <c r="A13" s="28">
+      <c r="S12" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" s="18" customFormat="1" ht="60">
+      <c r="A13" s="19">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="15">
+      <c r="C13" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="8">
         <v>46254</v>
       </c>
-      <c r="F13" s="91">
+      <c r="F13" s="75">
         <f>DATE(2026,10,1)-DATE(2026,8,20)</f>
         <v>42</v>
       </c>
-      <c r="G13" s="91">
+      <c r="G13" s="75">
         <f>DATE(2026,9,14)-DATE(2026,8,20)</f>
         <v>25</v>
       </c>
-      <c r="H13" s="91">
+      <c r="H13" s="75">
         <f>DATE(2026,9,17)-DATE(2026,9,12)</f>
         <v>5</v>
       </c>
-      <c r="I13" s="91">
+      <c r="I13" s="75">
         <f>DATE(2026,9,24)-DATE(2026,9,22)</f>
         <v>2</v>
       </c>
-      <c r="J13" s="91">
+      <c r="J13" s="75">
         <f>DATE(2026,9,24)-DATE(2026,9,24)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="91">
+      <c r="K13" s="75">
         <f>DATE(2026,9,25)-DATE(2026,9,24)</f>
         <v>1</v>
       </c>
-      <c r="L13" s="91">
+      <c r="L13" s="75">
         <v>8</v>
       </c>
-      <c r="M13" s="91">
+      <c r="M13" s="75">
         <v>25</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="9">
         <v>500</v>
       </c>
-      <c r="O13" s="16">
+      <c r="O13" s="9">
         <f>276+19</f>
         <v>295</v>
       </c>
-      <c r="P13" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="63">
+      <c r="P13" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="47">
         <v>46296</v>
       </c>
-      <c r="S13" s="26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" s="27" customFormat="1" ht="60">
-      <c r="A14" s="28">
+      <c r="S13" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" s="18" customFormat="1" ht="60">
+      <c r="A14" s="19">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="C14" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="8">
         <v>46259</v>
       </c>
-      <c r="F14" s="91">
+      <c r="F14" s="75">
         <f>DATE(2026,10,1)-DATE(2026,8,25)</f>
         <v>37</v>
       </c>
-      <c r="G14" s="91">
+      <c r="G14" s="75">
         <f>DATE(2026,9,12)-DATE(2026,8,24)</f>
         <v>19</v>
       </c>
-      <c r="H14" s="91">
+      <c r="H14" s="75">
         <f>DATE(2026,9,17)-DATE(2026,9,12)</f>
         <v>5</v>
       </c>
-      <c r="I14" s="91">
+      <c r="I14" s="75">
         <f>DATE(2026,9,17)-DATE(2026,9,17)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="91">
+      <c r="J14" s="75">
         <f>DATE(2026,9,22)-DATE(2026,9,18)</f>
         <v>4</v>
       </c>
-      <c r="K14" s="91">
+      <c r="K14" s="75">
         <f>DATE(2026,9,24)-DATE(2026,9,22)</f>
         <v>2</v>
       </c>
-      <c r="L14" s="91">
+      <c r="L14" s="75">
         <f>DATE(2026,9,30)-DATE(2026,9,25)</f>
         <v>5</v>
       </c>
-      <c r="M14" s="91">
+      <c r="M14" s="75">
         <v>35</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="9">
         <v>500</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O14" s="9">
         <f>324+19</f>
         <v>343</v>
       </c>
-      <c r="P14" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="63">
+      <c r="P14" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="47">
         <v>46296</v>
       </c>
-      <c r="S14" s="26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="27" customFormat="1" ht="60">
-      <c r="A15" s="28">
+      <c r="S14" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="18" customFormat="1" ht="60">
+      <c r="A15" s="19">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="166">
+      <c r="D15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="150">
         <v>46204</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="32">
         <f>DATE(2026,10,6)-E15</f>
         <v>97</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="32">
         <f>DATE(2026,8,3)-DATE(2026,7,1)</f>
         <v>33</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="32">
         <f>DATE(2026,8,27)-DATE(2026,8,3)</f>
         <v>24</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="32">
         <f>DATE(2026,9,3)-DATE(2026,8,27)</f>
         <v>7</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="32">
         <f>DATE(2026,9,10)-DATE(2026,9,3)</f>
         <v>7</v>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="32">
         <f>DATE(2026,9,30)-DATE(2026,9,12)</f>
         <v>18</v>
       </c>
-      <c r="L15" s="41">
+      <c r="L15" s="32">
         <f>DATE(2026,10,7)-DATE(2026,9,30)</f>
         <v>7</v>
       </c>
-      <c r="M15" s="41">
+      <c r="M15" s="32">
         <f>DATE(2026,10,6)-DATE(2026,10,4)</f>
         <v>2</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="9">
         <v>317</v>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="9">
         <v>299</v>
       </c>
-      <c r="P15" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q15" s="162" t="s">
-        <v>59</v>
-      </c>
-      <c r="R15" s="164">
+      <c r="P15" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q15" s="146"/>
+      <c r="R15" s="148">
         <v>46301</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="60">
-      <c r="A16" s="28">
+      <c r="A16" s="19">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="166">
+      <c r="C16" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="150">
         <v>46204</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="32">
         <f>DATE(2026,10,12)-E16</f>
         <v>103</v>
       </c>
-      <c r="G16" s="91">
+      <c r="G16" s="75">
         <v>35</v>
       </c>
-      <c r="H16" s="91">
+      <c r="H16" s="75">
         <v>23</v>
       </c>
-      <c r="I16" s="91">
+      <c r="I16" s="75">
         <v>10</v>
       </c>
-      <c r="J16" s="91">
+      <c r="J16" s="75">
         <v>4</v>
       </c>
-      <c r="K16" s="91">
+      <c r="K16" s="75">
         <v>18</v>
       </c>
-      <c r="L16" s="91">
+      <c r="L16" s="75">
         <v>5</v>
       </c>
-      <c r="M16" s="91">
+      <c r="M16" s="75">
         <v>6</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="9">
         <v>302</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="9">
         <v>333</v>
       </c>
-      <c r="P16" s="126" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q16" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="R16" s="164">
+      <c r="P16" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q16" s="146"/>
+      <c r="R16" s="148">
         <v>46307</v>
       </c>
-      <c r="S16" s="120"/>
-    </row>
-    <row r="17" spans="1:19" ht="60">
-      <c r="A17" s="28">
+      <c r="S16" s="104"/>
+    </row>
+    <row r="17" spans="1:20" ht="60">
+      <c r="A17" s="19">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="31" t="s">
+      <c r="B17" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="166">
+      <c r="D17" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="150">
         <v>46265</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="32">
         <f>DATE(2026,10,14)-E17</f>
         <v>44</v>
       </c>
-      <c r="G17" s="91">
+      <c r="G17" s="75">
         <f>DATE(2026,9,24)-DATE(2026,8,24)</f>
         <v>31</v>
       </c>
-      <c r="H17" s="91">
+      <c r="H17" s="75">
         <f>DATE(2026,9,30)-DATE(2026,9,24)</f>
         <v>6</v>
       </c>
-      <c r="I17" s="91">
+      <c r="I17" s="75">
         <f>DATE(2026,10,3)-DATE(2026,10,1)</f>
         <v>2</v>
       </c>
-      <c r="J17" s="91">
+      <c r="J17" s="75">
         <f>DATE(2026,10,7)-DATE(2026,10,4)</f>
         <v>3</v>
       </c>
-      <c r="K17" s="91">
+      <c r="K17" s="75">
         <f>DATE(2026,10,10)-DATE(2026,10,7)</f>
         <v>3</v>
       </c>
-      <c r="L17" s="91">
+      <c r="L17" s="75">
         <f>DATE(2026,10,14)-DATE(2026,10,10)</f>
         <v>4</v>
       </c>
-      <c r="M17" s="91">
+      <c r="M17" s="75">
         <v>25</v>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="9">
         <v>500</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O17" s="9">
         <v>385</v>
       </c>
-      <c r="P17" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="164">
+      <c r="P17" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="148">
         <v>46309</v>
       </c>
-      <c r="S17" s="109"/>
-    </row>
-    <row r="18" spans="1:19" s="50" customFormat="1" ht="60">
-      <c r="A18" s="28">
+      <c r="S17" s="93"/>
+    </row>
+    <row r="18" spans="1:20" s="35" customFormat="1" ht="60">
+      <c r="A18" s="19">
         <f>ROW()-1</f>
         <v>17</v>
       </c>
-      <c r="B18" s="91" t="s">
+      <c r="B18" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="178" t="s">
+      <c r="C18" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="179" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="166">
+      <c r="D18" s="163" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="150">
         <v>46269</v>
       </c>
-      <c r="F18" s="167">
+      <c r="F18" s="151">
         <f>DATE(2026,10,26)-E18</f>
         <v>52</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="19">
         <f>DATE(2026,9,26)-DATE(2026,9,4)</f>
         <v>22</v>
       </c>
-      <c r="H18" s="91">
+      <c r="H18" s="75">
         <f>DATE(2026,10,11)-DATE(2026,9,26)</f>
         <v>15</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="19">
         <f>DATE(2026,10,16)-DATE(2026,10,12)</f>
         <v>4</v>
       </c>
-      <c r="J18" s="91">
+      <c r="J18" s="75">
         <f>DATE(2026,10,23)-DATE(2026,10,16)</f>
         <v>7</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="19">
         <f>DATE(2026,10,26)-DATE(2026,10,23)</f>
         <v>3</v>
       </c>
-      <c r="L18" s="91">
+      <c r="L18" s="75">
         <f>DATE(2026,10,27)-DATE(2026,10,26)</f>
         <v>1</v>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="19">
         <v>14</v>
       </c>
-      <c r="N18" s="91">
+      <c r="N18" s="75">
         <v>189</v>
       </c>
-      <c r="O18" s="28">
+      <c r="O18" s="19">
         <v>201</v>
       </c>
-      <c r="P18" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="165">
+      <c r="P18" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="149">
         <v>46321</v>
       </c>
-      <c r="S18" s="163"/>
+      <c r="S18" s="147"/>
+    </row>
+    <row r="19" spans="1:20" ht="110">
+      <c r="A19" s="19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="162" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="187">
+        <v>46286</v>
+      </c>
+      <c r="F19" s="19">
+        <f t="shared" ref="F19" ca="1" si="1">TODAY()-E19</f>
+        <v>38</v>
+      </c>
+      <c r="G19" s="19">
+        <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
+        <v>16</v>
+      </c>
+      <c r="H19" s="19">
+        <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
+        <v>13</v>
+      </c>
+      <c r="I19" s="19" t="str">
+        <f>TRIM(DATE(2026,10,23)-DATE(2026,10,22))</f>
+        <v>1</v>
+      </c>
+      <c r="J19" s="19">
+        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="19">
+        <f>DATE(2026,10,27)-DATE(2026,10,25)</f>
+        <v>2</v>
+      </c>
+      <c r="L19" s="19">
+        <f>DATE(2026,10,29)-DATE(2026,10,28)</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="19">
+        <v>7</v>
+      </c>
+      <c r="N19" s="19">
+        <v>100</v>
+      </c>
+      <c r="O19" s="19">
+        <v>80</v>
+      </c>
+      <c r="P19" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q19" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="R19" s="149">
+        <v>46324</v>
+      </c>
+      <c r="T19" t="s">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8740,299 +8459,315 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
     <col min="2" max="2" width="10.54296875" customWidth="1"/>
     <col min="3" max="3" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26.5" thickBot="1">
-      <c r="A1" s="96" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="97" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" s="94" t="s">
-        <v>152</v>
-      </c>
-      <c r="D1" s="92"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="85"/>
+      <c r="A1" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="81" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="76"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="32.5" customHeight="1" thickBot="1">
-      <c r="A2" s="101" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103" t="s">
-        <v>152</v>
-      </c>
-      <c r="D2" s="92"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="100"/>
-    </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1">
-      <c r="A3" s="93" t="s">
-        <v>149</v>
-      </c>
-      <c r="B3" s="180">
+      <c r="A2" s="85" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="86"/>
+      <c r="C2" s="87" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="76"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="84"/>
+    </row>
+    <row r="3" spans="1:11" ht="26.5" thickBot="1">
+      <c r="A3" s="77" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="164">
         <f>COUNTA(Table2[MPS ID])</f>
-        <v>35</v>
-      </c>
-      <c r="C3" s="95">
+        <v>34</v>
+      </c>
+      <c r="C3" s="79">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>
-        <v>24.515151515151516</v>
-      </c>
-      <c r="D3" s="92"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
+        <v>23.393939393939394</v>
+      </c>
+      <c r="D3" s="76"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1">
-      <c r="A4" s="98" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="127">
+      <c r="A4" s="82" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="111">
         <f>COUNTA(Delivered!C2:C18)</f>
         <v>17</v>
       </c>
-      <c r="C4" s="99">
+      <c r="C4" s="83">
         <f>AVERAGE(Table3[Total Avg. Aging Days])</f>
         <v>61.3125</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="181"/>
-      <c r="B5" s="181"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
+      <c r="A5" s="165"/>
+      <c r="B5" s="165"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="165"/>
     </row>
     <row r="6" spans="1:11" ht="36">
-      <c r="A6" s="184" t="s">
-        <v>220</v>
-      </c>
-      <c r="B6" s="185" t="s">
+      <c r="A6" s="168" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="185" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="185" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="185" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="185" t="s">
-        <v>207</v>
-      </c>
-      <c r="G6" s="185" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="185" t="s">
-        <v>225</v>
+      <c r="C6" s="169" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="169" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="169" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6" s="169" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" s="169" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="169" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" s="182">
+      <c r="A7" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="166">
         <f>Delivered!G2</f>
         <v>32</v>
       </c>
-      <c r="C7" s="182">
+      <c r="C7" s="166">
         <f>Delivered!H2</f>
         <v>11</v>
       </c>
-      <c r="D7" s="182">
+      <c r="D7" s="166">
         <f>Delivered!I2</f>
         <v>3</v>
       </c>
-      <c r="E7" s="182">
+      <c r="E7" s="166">
         <f>Delivered!J2</f>
         <v>6</v>
       </c>
-      <c r="F7" s="182">
+      <c r="F7" s="166">
         <f>Delivered!K2</f>
         <v>6</v>
       </c>
-      <c r="G7" s="182">
+      <c r="G7" s="166">
         <f>Delivered!L2</f>
         <v>5</v>
       </c>
-      <c r="H7" s="189">
+      <c r="H7" s="173">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8" s="183">
+      <c r="A8" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="167">
         <f>AVERAGE(Delivered!G3:G11)</f>
         <v>25</v>
       </c>
-      <c r="C8" s="183">
+      <c r="C8" s="167">
         <f>AVERAGE(Delivered!H3:H11)</f>
         <v>11.777777777777779</v>
       </c>
-      <c r="D8" s="183">
+      <c r="D8" s="167">
         <f>AVERAGE(Delivered!I3:I11)</f>
         <v>4.1111111111111107</v>
       </c>
-      <c r="E8" s="183">
+      <c r="E8" s="167">
         <f>AVERAGE(Delivered!J3:J11)</f>
         <v>6.8888888888888893</v>
       </c>
-      <c r="F8" s="183">
+      <c r="F8" s="167">
         <f>AVERAGE(Delivered!K3:K11)</f>
         <v>5.8888888888888893</v>
       </c>
-      <c r="G8" s="183">
+      <c r="G8" s="167">
         <f>AVERAGE(Delivered!L3:L11)</f>
         <v>6</v>
       </c>
-      <c r="H8" s="189">
+      <c r="H8" s="173">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="186" t="s">
-        <v>223</v>
-      </c>
-      <c r="B9" s="187">
+      <c r="A9" s="170" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="171">
         <f>AVERAGE(Delivered!G12:G21)</f>
-        <v>27.428571428571427</v>
-      </c>
-      <c r="C9" s="187">
+        <v>26</v>
+      </c>
+      <c r="C9" s="171">
         <f>AVERAGE(Delivered!H12:H21)</f>
-        <v>11.714285714285714</v>
-      </c>
-      <c r="D9" s="187">
+        <v>11.875</v>
+      </c>
+      <c r="D9" s="171">
         <f>AVERAGE(Delivered!I12:I21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="E9" s="187">
+      <c r="E9" s="171">
         <f>AVERAGE(Delivered!J12:J21)</f>
-        <v>4.1428571428571432</v>
-      </c>
-      <c r="F9" s="187">
+        <v>3.75</v>
+      </c>
+      <c r="F9" s="171">
         <f>AVERAGE(Delivered!K12:K21)</f>
-        <v>6.8571428571428568</v>
-      </c>
-      <c r="G9" s="187">
+        <v>6.25</v>
+      </c>
+      <c r="G9" s="171">
         <f>AVERAGE(Delivered!L12:L21)</f>
-        <v>4.5714285714285712</v>
-      </c>
-      <c r="H9" s="189">
+        <v>4.125</v>
+      </c>
+      <c r="H9" s="173">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29">
-      <c r="A10" s="188" t="s">
-        <v>224</v>
-      </c>
-      <c r="B10" s="189">
+      <c r="A10" s="172" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="173">
         <f>AVERAGE(B7:B9)</f>
-        <v>28.142857142857142</v>
-      </c>
-      <c r="C10" s="189">
+        <v>27.666666666666668</v>
+      </c>
+      <c r="C10" s="173">
         <f t="shared" ref="C10:G10" si="0">AVERAGE(C7:C9)</f>
-        <v>11.497354497354499</v>
-      </c>
-      <c r="D10" s="189">
+        <v>11.550925925925926</v>
+      </c>
+      <c r="D10" s="173">
         <f t="shared" si="0"/>
         <v>3.7513227513227512</v>
       </c>
-      <c r="E10" s="189">
+      <c r="E10" s="173">
         <f t="shared" si="0"/>
-        <v>5.6772486772486772</v>
-      </c>
-      <c r="F10" s="189">
+        <v>5.5462962962962967</v>
+      </c>
+      <c r="F10" s="173">
         <f t="shared" si="0"/>
-        <v>6.2486772486772493</v>
-      </c>
-      <c r="G10" s="189">
+        <v>6.0462962962962967</v>
+      </c>
+      <c r="G10" s="173">
         <f t="shared" si="0"/>
-        <v>5.1904761904761907</v>
-      </c>
-      <c r="H10" s="10"/>
+        <v>5.041666666666667</v>
+      </c>
+      <c r="H10" s="5"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="190" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="190">
+      <c r="A12" s="174" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="174">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="190" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="190">
+      <c r="A13" s="174" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="174">
         <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="10" t="s">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B17" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="186" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="10" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="186" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="10" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="186" t="s">
         <v>236</v>
-      </c>
-      <c r="B19" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="10">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9059,183 +8794,183 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="206" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="206"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
+      <c r="B3" s="188" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="188"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="66" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="66">
+      <c r="B4" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="50">
         <v>15</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="73" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="74" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
+      <c r="B5" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="75">
+      <c r="B6" s="59">
         <v>46235</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="60">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</f>
         <v>1</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="75">
+      <c r="B7" s="59">
         <v>46266</v>
       </c>
-      <c r="C7" s="76">
+      <c r="C7" s="60">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B7,Delivered!$R:$R,"&lt;"&amp;EDATE(B7,1))</f>
         <v>9</v>
       </c>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="75">
+      <c r="B8" s="59">
         <v>46296</v>
       </c>
-      <c r="C8" s="76">
+      <c r="C8" s="60">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B8,Delivered!$R:$R,"&lt;"&amp;EDATE(B8,1))</f>
-        <v>7</v>
-      </c>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
+        <v>8</v>
+      </c>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="75">
+      <c r="B9" s="59">
         <v>46327</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="60">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B9,Delivered!$R:$R,"&lt;"&amp;EDATE(B9,1))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="77">
+      <c r="B10" s="61">
         <v>46357</v>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="62">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B10,Delivered!$R:$R,"&lt;"&amp;EDATE(B10,1))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="5:10">
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9252,1351 +8987,672 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:T52"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
     <col min="2" max="2" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1" outlineLevel="2"/>
     <col min="4" max="4" width="14.54296875" customWidth="1" outlineLevel="2"/>
-    <col min="5" max="5" width="22.7265625" style="59" bestFit="1" customWidth="1" outlineLevel="2"/>
+    <col min="5" max="5" width="22.7265625" style="43" bestFit="1" customWidth="1" outlineLevel="2"/>
     <col min="6" max="6" width="23.08984375" customWidth="1" outlineLevel="2"/>
     <col min="8" max="8" width="21.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:20">
+      <c r="C1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="18" customFormat="1" ht="120">
+      <c r="A2" s="36">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="101" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="26">
+        <v>46286</v>
+      </c>
+      <c r="F2" s="24">
+        <f ca="1">TODAY()-E2</f>
+        <v>38</v>
+      </c>
+      <c r="G2" s="24">
+        <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
+        <v>16</v>
+      </c>
+      <c r="H2" s="91">
+        <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
+        <v>13</v>
+      </c>
+      <c r="I2" s="91" t="str">
+        <f>TRIM(DATE(2026,10,23)-DATE(2026,10,22))</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="91">
+        <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="91">
+        <f>DATE(2026,10,27)-DATE(2026,10,25)</f>
+        <v>2</v>
+      </c>
+      <c r="L2" s="88">
+        <f>DATE(2026,10,29)-DATE(2026,10,28)</f>
+        <v>1</v>
+      </c>
+      <c r="M2" s="24">
+        <v>7</v>
+      </c>
+      <c r="N2" s="24">
+        <v>100</v>
+      </c>
+      <c r="O2" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="T2" s="158"/>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="5"/>
+      <c r="C17" s="106" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="107">
+        <f>COUNTA(D20:D52)</f>
+        <v>33</v>
+      </c>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="2:11" ht="15" thickBot="1">
+      <c r="B18" s="5"/>
+      <c r="C18" s="108" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="109">
+        <v>17</v>
+      </c>
+      <c r="E18" s="109" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="15" thickBot="1">
+      <c r="B19" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="105" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="10">
+        <v>1</v>
+      </c>
+      <c r="C20" s="113" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="112" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="115">
+        <v>64</v>
+      </c>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="118">
+        <v>40</v>
+      </c>
+      <c r="F21" s="17"/>
+    </row>
+    <row r="22" spans="2:11" ht="45.5" customHeight="1">
+      <c r="B22" s="10">
+        <v>3</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="24">
+        <v>39</v>
+      </c>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" s="10">
+        <v>4</v>
+      </c>
+      <c r="C23" s="101" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="122" t="s">
+        <v>164</v>
+      </c>
+      <c r="E23" s="117">
+        <v>39</v>
+      </c>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="10">
+        <v>5</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="24">
+        <v>39</v>
+      </c>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="2:11" ht="29">
+      <c r="B25" s="10">
+        <v>6</v>
+      </c>
+      <c r="C25" s="101" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="116">
+        <v>36</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="156" t="s">
+        <v>190</v>
+      </c>
+      <c r="I25" s="156">
+        <v>30</v>
+      </c>
+      <c r="J25" s="156" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25" s="156" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="29">
+      <c r="B26" s="10">
+        <v>7</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="24">
+        <v>34</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="156" t="s">
+        <v>190</v>
+      </c>
+      <c r="I26" s="156">
+        <v>46</v>
+      </c>
+      <c r="J26" s="156" t="s">
+        <v>191</v>
+      </c>
+      <c r="K26" s="156" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="29">
+      <c r="B27" s="10">
+        <v>8</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="24">
+        <v>34</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="156" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="156">
+        <v>58</v>
+      </c>
+      <c r="J27" s="156" t="s">
+        <v>191</v>
+      </c>
+      <c r="K27" s="156" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="10">
+        <v>9</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="24">
+        <v>33</v>
+      </c>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="10">
+        <v>10</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="24">
+        <v>31</v>
+      </c>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="10">
+        <v>11</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="118">
+        <v>31</v>
+      </c>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="10">
+        <v>12</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="118">
+        <v>31</v>
+      </c>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="10">
+        <v>13</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="3">
+        <v>30</v>
+      </c>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="10">
+        <v>14</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="24">
+        <v>29</v>
+      </c>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="2:6" ht="28.5">
+      <c r="B34" s="10">
+        <v>15</v>
+      </c>
+      <c r="C34" s="142" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" s="143" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="118">
+        <v>28</v>
+      </c>
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="10">
+        <v>16</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="24">
+        <v>27</v>
+      </c>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="10">
+        <v>17</v>
+      </c>
+      <c r="C36" s="142" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="118">
+        <v>27</v>
+      </c>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="10">
+        <v>18</v>
+      </c>
+      <c r="C37" s="142" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="118">
+        <v>27</v>
+      </c>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="10">
+        <v>19</v>
+      </c>
+      <c r="C38" s="144" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="3">
+        <v>20</v>
+      </c>
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="10">
+        <v>20</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="10">
+        <v>20</v>
+      </c>
+      <c r="F39" s="5"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="10">
+        <v>21</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="118">
+        <v>15</v>
+      </c>
+      <c r="F40" s="5"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="10">
+        <v>22</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="10">
+        <v>15</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="10">
+        <v>23</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="10">
+        <v>13</v>
+      </c>
+      <c r="F42" s="5"/>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="10">
+        <v>24</v>
+      </c>
+      <c r="C43" s="142" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="10">
+        <v>10</v>
+      </c>
+      <c r="F43" s="5"/>
+    </row>
+    <row r="44" spans="2:6" ht="28">
+      <c r="B44" s="10">
+        <v>25</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" s="10">
+        <v>10</v>
+      </c>
+      <c r="F44" s="5"/>
+    </row>
+    <row r="45" spans="2:6" ht="28">
+      <c r="B45" s="10">
+        <v>26</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="10">
+        <v>10</v>
+      </c>
+      <c r="F45" s="5"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="10">
+        <v>27</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="10">
+        <v>6</v>
+      </c>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="10">
+        <v>28</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="10">
+        <v>6</v>
+      </c>
+      <c r="F47" s="5"/>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" s="10">
+        <v>29</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="10">
+        <v>6</v>
+      </c>
+      <c r="F48" s="5"/>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="10">
+        <v>30</v>
+      </c>
+      <c r="C49" s="157" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="10">
+        <v>1</v>
+      </c>
+      <c r="F49" s="5"/>
+    </row>
+    <row r="50" spans="2:6" ht="29">
+      <c r="B50" s="10">
+        <v>31</v>
+      </c>
+      <c r="C50" s="157" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="10">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="16">
-        <f>DATE(2026,8,27)-DATE(2026,8,3)</f>
+      <c r="F50" s="5"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="10">
+        <v>32</v>
+      </c>
+      <c r="C51" s="157" t="s">
+        <v>200</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="16">
-        <f>DATE(2026,9,3)-DATE(2026,8,27)</f>
-        <v>7</v>
-      </c>
-      <c r="E2" s="16">
-        <f>DATE(2026,9,10)-DATE(2026,9,3)</f>
-        <v>7</v>
-      </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H2" s="18" t="str">
-        <f>IF(SUM(C2:F2)=0, "Not Started", IF(SUM(C2:F2)&lt;=75, "On Track. "&amp;(75-SUM(C2:F2))&amp;" days buffer", "Recover "&amp;(SUM(C2:F2)-75)&amp;" days!"))</f>
-        <v>On Track. 37 days buffer</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="16">
-        <f>DATE(2026,8,28)-DATE(2026,8,5)</f>
-        <v>23</v>
-      </c>
-      <c r="D3" s="16">
-        <f>DATE(2026,9,8)-DATE(2026,8,29)</f>
-        <v>10</v>
-      </c>
-      <c r="E3" s="16">
-        <f>DATE(2026,9,12)-DATE(2026,9,8)</f>
-        <v>4</v>
-      </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H3" s="18" t="str">
-        <f>IF(SUM(C3:F3)=0, "Not Started", IF(SUM(C3:F3)&lt;=75, "On Track. "&amp;(75-SUM(C3:F3))&amp;" days buffer", "Recover "&amp;(SUM(C3:F3)-75)&amp;" days!"))</f>
-        <v>On Track. 38 days buffer</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="16">
-        <f>DATE(2026,8,25)-DATE(2026,8,17)</f>
-        <v>8</v>
-      </c>
-      <c r="D4" s="16">
-        <f>DATE(2026,9,8)-DATE(2026,8,27)</f>
-        <v>12</v>
-      </c>
-      <c r="E4" s="16">
-        <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
-        <v>6</v>
-      </c>
-      <c r="F4" s="4">
-        <f>DATE(2026,9,22)-DATE(2026,9,20)</f>
-        <v>2</v>
-      </c>
-      <c r="G4" s="51">
-        <f>DATE(2026,9,23)-DATE(2026,7,27)</f>
-        <v>58</v>
-      </c>
-      <c r="H4" s="18" t="str">
-        <f>IF(SUM(C4:F4)=0, "Not Started", IF(SUM(C4:F4)&lt;=75, "On Track. "&amp;(75-SUM(C4:F4))&amp;" days buffer", "Recover "&amp;(G4-75)&amp;" days!"))</f>
-        <v>On Track. 47 days buffer</v>
-      </c>
-      <c r="I4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="44">
-        <f>DATE(2026,9,5)-DATE(2026,8,24)</f>
-        <v>12</v>
-      </c>
-      <c r="D5" s="44">
-        <f>DATE(2026,9,9)-DATE(2026,9,5)</f>
-        <v>4</v>
-      </c>
-      <c r="E5" s="44">
-        <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
-        <v>6</v>
-      </c>
-      <c r="F5" s="44">
-        <f>DATE(2026,9,20)-DATE(2026,9,17)</f>
-        <v>3</v>
-      </c>
-      <c r="G5" s="45">
-        <f>DATE(2026,9,21)-DATE(2026,7,31)</f>
-        <v>52</v>
-      </c>
-      <c r="H5" s="18" t="str">
-        <f t="shared" ref="H5:H21" si="0">IF(SUM(C5:F5)=0, "Not Started", IF(SUM(C5:F5)&lt;=75, "On Track. "&amp;(75-SUM(C5:F5))&amp;" days buffer", "Recover "&amp;(SUM(C5:F5)-75)&amp;" days!"))</f>
-        <v>On Track. 50 days buffer</v>
-      </c>
-      <c r="I5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="16">
-        <f>DATE(2026,9,11)-DATE(2026,8,27)</f>
-        <v>15</v>
-      </c>
-      <c r="D6" s="7">
-        <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
-        <v>1</v>
-      </c>
-      <c r="E6" s="44">
-        <f>DATE(2026,9,14)-DATE(2026,9,8)</f>
-        <v>6</v>
-      </c>
-      <c r="F6" s="44">
-        <f>DATE(2026,9,26)-DATE(2026,9,22)</f>
-        <v>4</v>
-      </c>
-      <c r="G6" s="51">
-        <f>DATE(2026,9,25)-DATE(2026,8,12)</f>
-        <v>44</v>
-      </c>
-      <c r="H6" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>On Track. 49 days buffer</v>
-      </c>
-      <c r="I6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="16">
-        <f>DATE(2026,9,14)-DATE(2026,8,31)</f>
-        <v>14</v>
-      </c>
-      <c r="D7" s="7">
-        <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
-        <v>1</v>
-      </c>
-      <c r="E7" s="7">
-        <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
-        <v>6</v>
-      </c>
-      <c r="F7" s="7">
-        <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
-        <v>6</v>
-      </c>
-      <c r="G7" s="51">
-        <f>DATE(2026,9,26)-DATE(2026,8,10)</f>
-        <v>47</v>
-      </c>
-      <c r="H7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>On Track. 48 days buffer</v>
-      </c>
-      <c r="I7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="16">
-        <f>DATE(2026,9,17)-DATE(2026,9,12)</f>
-        <v>5</v>
-      </c>
-      <c r="D8" s="7">
-        <f>DATE(2026,9,17)-DATE(2026,9,17)</f>
+      <c r="E51" s="10">
         <v>0</v>
       </c>
-      <c r="E8" s="16">
-        <f>DATE(2026,9,22)-DATE(2026,9,18)</f>
-        <v>4</v>
-      </c>
-      <c r="F8" s="5">
-        <f ca="1">TODAY()-DATE(2026,9,25)</f>
-        <v>34</v>
-      </c>
-      <c r="G8" s="5" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H8" s="18" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>On Track. 32 days buffer</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="16" t="str">
-        <f>TRIM(DATE(2026,9,17)-DATE(2026,9,12))</f>
-        <v>5</v>
-      </c>
-      <c r="D9" s="16">
-        <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>42</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H9" s="18" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>On Track. 33 days buffer</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="16" t="str">
-        <f>TRIM(DATE(2026,9,17)-DATE(2026,9,12))</f>
-        <v>5</v>
-      </c>
-      <c r="D10" s="16">
-        <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>42</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H10" s="18" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>On Track. 33 days buffer</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="16" t="str">
-        <f>TRIM(DATE(2026,9,14)-DATE(2026,9,9))</f>
-        <v>5</v>
-      </c>
-      <c r="D11" s="7">
-        <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
-        <v>1</v>
-      </c>
-      <c r="E11" s="7">
-        <f ca="1">TODAY()-DATE(2026,9,16)</f>
-        <v>43</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H11" s="18" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>On Track. 31 days buffer</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H12" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="8">
-        <v>12</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="8">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H14" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="8">
-        <v>14</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H15" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="8">
-        <v>15</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H16" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="8">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H17" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="8">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H18" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="8">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H19" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="8">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H20" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="8">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H21" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="8">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H22" s="18"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="8">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H23" s="18"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="8">
-        <v>23</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="F51" s="5"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="10">
         <v>33</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H24" s="18"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="8">
+      <c r="C52" s="157" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="8" t="e">
-        <f ca="1">TODAY()-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H25" s="18"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="8">
-        <v>25</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="18"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="8">
-        <v>26</v>
-      </c>
-      <c r="B27" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="8">
-        <v>27</v>
-      </c>
-      <c r="B28" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="10"/>
-      <c r="C46" s="122" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" s="123">
-        <f>COUNTA(D49:D81)</f>
-        <v>33</v>
-      </c>
-      <c r="E46" s="18"/>
-    </row>
-    <row r="47" spans="2:6" ht="15" thickBot="1">
-      <c r="B47" s="10"/>
-      <c r="C47" s="124" t="s">
-        <v>179</v>
-      </c>
-      <c r="D47" s="125">
-        <v>17</v>
-      </c>
-      <c r="E47" s="125" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="15" thickBot="1">
-      <c r="B48" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="121" t="s">
-        <v>46</v>
-      </c>
-      <c r="F48" s="130" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
-      <c r="B49" s="18">
-        <v>1</v>
-      </c>
-      <c r="C49" s="129" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="128" t="s">
-        <v>181</v>
-      </c>
-      <c r="E49" s="131">
-        <v>64</v>
-      </c>
-      <c r="F49" s="10"/>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50" s="18">
-        <v>2</v>
-      </c>
-      <c r="C50" s="117" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E50" s="134">
-        <v>40</v>
-      </c>
-      <c r="F50" s="26"/>
-    </row>
-    <row r="51" spans="2:11" ht="45.5" customHeight="1">
-      <c r="B51" s="18">
-        <v>3</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" s="33">
-        <v>39</v>
-      </c>
-      <c r="F51" s="10"/>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="18">
-        <v>4</v>
-      </c>
-      <c r="C52" s="117" t="s">
-        <v>176</v>
-      </c>
-      <c r="D52" s="138" t="s">
-        <v>181</v>
-      </c>
-      <c r="E52" s="133">
-        <v>39</v>
-      </c>
-      <c r="F52" s="10"/>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="18">
-        <v>5</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="D53" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E53" s="33">
-        <v>39</v>
-      </c>
-      <c r="F53" s="10"/>
-    </row>
-    <row r="54" spans="2:11" ht="29">
-      <c r="B54" s="18">
-        <v>6</v>
-      </c>
-      <c r="C54" s="117" t="s">
-        <v>34</v>
-      </c>
-      <c r="D54" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E54" s="132">
-        <v>36</v>
-      </c>
-      <c r="F54" s="10"/>
-      <c r="G54" s="87" t="s">
-        <v>112</v>
-      </c>
-      <c r="H54" s="172" t="s">
-        <v>208</v>
-      </c>
-      <c r="I54" s="172">
-        <v>30</v>
-      </c>
-      <c r="J54" s="172" t="s">
-        <v>209</v>
-      </c>
-      <c r="K54" s="172" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" ht="29">
-      <c r="B55" s="18">
-        <v>7</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="D55" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" s="33">
-        <v>34</v>
-      </c>
-      <c r="F55" s="10"/>
-      <c r="G55" s="87" t="s">
-        <v>112</v>
-      </c>
-      <c r="H55" s="172" t="s">
-        <v>208</v>
-      </c>
-      <c r="I55" s="172">
-        <v>46</v>
-      </c>
-      <c r="J55" s="172" t="s">
-        <v>209</v>
-      </c>
-      <c r="K55" s="172" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" ht="29">
-      <c r="B56" s="18">
-        <v>8</v>
-      </c>
-      <c r="C56" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="D56" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E56" s="33">
-        <v>34</v>
-      </c>
-      <c r="F56" s="10"/>
-      <c r="G56" s="87" t="s">
-        <v>112</v>
-      </c>
-      <c r="H56" s="172" t="s">
-        <v>211</v>
-      </c>
-      <c r="I56" s="172">
-        <v>58</v>
-      </c>
-      <c r="J56" s="172" t="s">
-        <v>209</v>
-      </c>
-      <c r="K56" s="172" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="18">
-        <v>9</v>
-      </c>
-      <c r="C57" s="57" t="s">
-        <v>177</v>
-      </c>
-      <c r="D57" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="E57" s="33">
-        <v>33</v>
-      </c>
-      <c r="F57" s="10"/>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="18">
-        <v>10</v>
-      </c>
-      <c r="C58" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="D58" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="E58" s="33">
-        <v>31</v>
-      </c>
-      <c r="F58" s="10"/>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="18">
-        <v>11</v>
-      </c>
-      <c r="C59" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="D59" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="E59" s="134">
-        <v>31</v>
-      </c>
-      <c r="F59" s="10"/>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="18">
-        <v>12</v>
-      </c>
-      <c r="C60" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E60" s="134">
-        <v>31</v>
-      </c>
-      <c r="F60" s="10"/>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="18">
-        <v>13</v>
-      </c>
-      <c r="C61" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="D61" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E61" s="8">
-        <v>30</v>
-      </c>
-      <c r="F61" s="10"/>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="18">
-        <v>14</v>
-      </c>
-      <c r="C62" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D62" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="E62" s="33">
-        <v>29</v>
-      </c>
-      <c r="F62" s="10"/>
-    </row>
-    <row r="63" spans="2:11" ht="28.5">
-      <c r="B63" s="18">
-        <v>15</v>
-      </c>
-      <c r="C63" s="158" t="s">
-        <v>114</v>
-      </c>
-      <c r="D63" s="159" t="s">
-        <v>19</v>
-      </c>
-      <c r="E63" s="134">
-        <v>28</v>
-      </c>
-      <c r="F63" s="10"/>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="18">
-        <v>16</v>
-      </c>
-      <c r="C64" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E64" s="33">
-        <v>27</v>
-      </c>
-      <c r="F64" s="10"/>
-    </row>
-    <row r="65" spans="2:6">
-      <c r="B65" s="18">
-        <v>17</v>
-      </c>
-      <c r="C65" s="158" t="s">
-        <v>106</v>
-      </c>
-      <c r="D65" s="161" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65" s="134">
-        <v>27</v>
-      </c>
-      <c r="F65" s="10"/>
-    </row>
-    <row r="66" spans="2:6">
-      <c r="B66" s="18">
-        <v>18</v>
-      </c>
-      <c r="C66" s="158" t="s">
-        <v>115</v>
-      </c>
-      <c r="D66" s="161" t="s">
-        <v>19</v>
-      </c>
-      <c r="E66" s="134">
-        <v>27</v>
-      </c>
-      <c r="F66" s="10"/>
-    </row>
-    <row r="67" spans="2:6">
-      <c r="B67" s="18">
-        <v>19</v>
-      </c>
-      <c r="C67" s="160" t="s">
-        <v>157</v>
-      </c>
-      <c r="D67" s="161" t="s">
-        <v>19</v>
-      </c>
-      <c r="E67" s="8">
-        <v>20</v>
-      </c>
-      <c r="F67" s="10"/>
-    </row>
-    <row r="68" spans="2:6">
-      <c r="B68" s="18">
-        <v>20</v>
-      </c>
-      <c r="C68" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E68" s="18">
-        <v>20</v>
-      </c>
-      <c r="F68" s="10"/>
-    </row>
-    <row r="69" spans="2:6">
-      <c r="B69" s="18">
-        <v>21</v>
-      </c>
-      <c r="C69" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E69" s="134">
-        <v>15</v>
-      </c>
-      <c r="F69" s="10"/>
-    </row>
-    <row r="70" spans="2:6">
-      <c r="B70" s="18">
-        <v>22</v>
-      </c>
-      <c r="C70" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E70" s="18">
-        <v>15</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6">
-      <c r="B71" s="18">
-        <v>23</v>
-      </c>
-      <c r="C71" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E71" s="18">
-        <v>13</v>
-      </c>
-      <c r="F71" s="10"/>
-    </row>
-    <row r="72" spans="2:6">
-      <c r="B72" s="18">
-        <v>24</v>
-      </c>
-      <c r="C72" s="158" t="s">
-        <v>140</v>
-      </c>
-      <c r="D72" s="161" t="s">
-        <v>19</v>
-      </c>
-      <c r="E72" s="18">
-        <v>10</v>
-      </c>
-      <c r="F72" s="10"/>
-    </row>
-    <row r="73" spans="2:6" ht="28">
-      <c r="B73" s="18">
-        <v>25</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E73" s="18">
-        <v>10</v>
-      </c>
-      <c r="F73" s="10"/>
-    </row>
-    <row r="74" spans="2:6" ht="28">
-      <c r="B74" s="18">
-        <v>26</v>
-      </c>
-      <c r="C74" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E74" s="18">
-        <v>10</v>
-      </c>
-      <c r="F74" s="10"/>
-    </row>
-    <row r="75" spans="2:6">
-      <c r="B75" s="18">
-        <v>27</v>
-      </c>
-      <c r="C75" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E75" s="18">
-        <v>6</v>
-      </c>
-      <c r="F75" s="10"/>
-    </row>
-    <row r="76" spans="2:6">
-      <c r="B76" s="18">
-        <v>28</v>
-      </c>
-      <c r="C76" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E76" s="18">
-        <v>6</v>
-      </c>
-      <c r="F76" s="10"/>
-    </row>
-    <row r="77" spans="2:6">
-      <c r="B77" s="18">
-        <v>29</v>
-      </c>
-      <c r="C77" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E77" s="18">
-        <v>6</v>
-      </c>
-      <c r="F77" s="10"/>
-    </row>
-    <row r="78" spans="2:6">
-      <c r="B78" s="18">
-        <v>30</v>
-      </c>
-      <c r="C78" s="173" t="s">
-        <v>213</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E78" s="18">
-        <v>1</v>
-      </c>
-      <c r="F78" s="10"/>
-    </row>
-    <row r="79" spans="2:6" ht="29">
-      <c r="B79" s="18">
-        <v>31</v>
-      </c>
-      <c r="C79" s="173" t="s">
-        <v>214</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E79" s="18">
+      <c r="E52" s="10">
         <v>0</v>
       </c>
-      <c r="F79" s="10"/>
-    </row>
-    <row r="80" spans="2:6">
-      <c r="B80" s="18">
-        <v>32</v>
-      </c>
-      <c r="C80" s="173" t="s">
-        <v>218</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E80" s="18">
-        <v>0</v>
-      </c>
-      <c r="F80" s="10"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="18">
-        <v>33</v>
-      </c>
-      <c r="C81" s="173" t="s">
-        <v>216</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E81" s="18">
-        <v>0</v>
-      </c>
-      <c r="F81" s="10"/>
+      <c r="F52" s="5"/>
     </row>
   </sheetData>
   <sortState ref="C49:E81">
     <sortCondition descending="1" ref="E49:E81"/>
   </sortState>
-  <conditionalFormatting sqref="C2:C3 C5:C26">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="num" val="10"/>
-        <cfvo type="num" val="30"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3 C5:C26">
-    <cfRule type="cellIs" dxfId="20" priority="33" operator="between">
-      <formula>0</formula>
-      <formula>10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8 D11:D26">
-    <cfRule type="cellIs" dxfId="19" priority="29" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="30" operator="lessThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
-    <cfRule type="cellIs" dxfId="17" priority="27" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="28" operator="lessThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4 F8:F26">
-    <cfRule type="cellIs" dxfId="15" priority="25" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
-    <cfRule type="cellIs" dxfId="13" priority="23" operator="greaterThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="24" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="11" priority="21" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="22" operator="lessThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="9" priority="19" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="7" priority="17" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
-      <formula>0</formula>
-      <formula>25</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
-      <formula>25</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
-      <formula>7</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -4758,6 +4758,13 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
+  <autoFilter ref="A1:S17">
+    <filterColumn colId="17">
+      <filters>
+        <dateGroupItem year="2026" month="10" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="19">
     <tableColumn id="1" name="S. no" dataDxfId="28"/>
     <tableColumn id="2" name="Book ID" dataDxfId="27"/>
@@ -7312,7 +7319,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="60">
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="60" hidden="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -7368,7 +7375,7 @@
       </c>
       <c r="S2" s="48"/>
     </row>
-    <row r="3" spans="1:19" ht="60">
+    <row r="3" spans="1:19" ht="60" hidden="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -7430,7 +7437,7 @@
       </c>
       <c r="S3" s="48"/>
     </row>
-    <row r="4" spans="1:19" ht="60">
+    <row r="4" spans="1:19" ht="60" hidden="1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -7491,7 +7498,7 @@
       </c>
       <c r="S4" s="34"/>
     </row>
-    <row r="5" spans="1:19" ht="60">
+    <row r="5" spans="1:19" ht="60" hidden="1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -7553,7 +7560,7 @@
       </c>
       <c r="S5" s="34"/>
     </row>
-    <row r="6" spans="1:19" ht="60">
+    <row r="6" spans="1:19" ht="60" hidden="1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -7615,7 +7622,7 @@
       </c>
       <c r="S6" s="34"/>
     </row>
-    <row r="7" spans="1:19" s="18" customFormat="1" ht="60">
+    <row r="7" spans="1:19" s="18" customFormat="1" ht="60" hidden="1">
       <c r="A7" s="19">
         <v>6</v>
       </c>
@@ -7677,7 +7684,7 @@
       </c>
       <c r="S7" s="17"/>
     </row>
-    <row r="8" spans="1:19" s="18" customFormat="1" ht="69" customHeight="1" thickBot="1">
+    <row r="8" spans="1:19" s="18" customFormat="1" ht="69" hidden="1" customHeight="1" thickBot="1">
       <c r="A8" s="19">
         <v>7</v>
       </c>
@@ -7741,7 +7748,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="60">
+    <row r="9" spans="1:19" ht="60" hidden="1">
       <c r="A9" s="19">
         <f t="shared" ref="A9:A19" si="0">ROW()-1</f>
         <v>8</v>
@@ -7806,7 +7813,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="18" customFormat="1" ht="60">
+    <row r="10" spans="1:19" s="18" customFormat="1" ht="60" hidden="1">
       <c r="A10" s="19">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -7871,7 +7878,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="18" customFormat="1" ht="130.5">
+    <row r="11" spans="1:19" s="18" customFormat="1" ht="130.5" hidden="1">
       <c r="A11" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -8432,7 +8439,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="19">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P19" s="27" t="s">
         <v>59</v>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="8" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="254">
   <si>
     <t>S. no</t>
   </si>
@@ -669,9 +669,6 @@
     <t>28 Chaps-Rev.delivered, 3 Part in Eproof, FM-recept error</t>
   </si>
   <si>
-    <t>All in revises</t>
-  </si>
-  <si>
     <t>S200Login</t>
   </si>
   <si>
@@ -704,14 +701,6 @@
     <t>etSoc-Vol9-8771159</t>
   </si>
   <si>
-    <t>S200 - 
-Login : 36 Chapters;
-PE : 33 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>Zi,-PIC Yunlong 8770448</t>
   </si>
   <si>
@@ -781,9 +770,6 @@
     <t>697730_1_En</t>
   </si>
   <si>
-    <t>Hameed, Alaa Ali</t>
-  </si>
-  <si>
     <t>S50</t>
   </si>
   <si>
@@ -808,59 +794,13 @@
     <t>Delivered on 28th- Will move to S600 today</t>
   </si>
   <si>
-    <t>16 chaps in Revises</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 05 Chapters;
-CE : 25 Chapters;
-Comp : 06 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>16 Chaps in Revises.</t>
   </si>
   <si>
-    <t>S200 - 
-Login : 01 Chapters;
-PE : 126 Chapters;
-CE : 02 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 00 Chapters;
-CE : 01 Chapters;
-Comp : 47 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 00 Chapters;
-PE : 17 Chapters;
-CE : 23 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
-    <t>S200 - 
-Login : 03 Chapters;
-PE : 53 Chapters;
-CE : 00 Chapters;
-Comp : 00 Chapters;
-Online Delivery : 00 Chapters</t>
-  </si>
-  <si>
     <t>González, Carina-8770441</t>
   </si>
   <si>
     <t>703158_1_En</t>
-  </si>
-  <si>
-    <t>Camara, Moctar</t>
   </si>
   <si>
     <t>14 Books</t>
@@ -918,21 +858,95 @@
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
+    <t>Delivered titles</t>
+  </si>
+  <si>
+    <t>Remarks2</t>
+  </si>
+  <si>
+    <t>Diouf-SAE-8770492 Camara, Moctar-</t>
+  </si>
+  <si>
+    <t>Epub to vendor</t>
+  </si>
+  <si>
+    <t>08 Chap in revises</t>
+  </si>
+  <si>
+    <t>18 chaps in Revises</t>
+  </si>
+  <si>
     <t>S200 - 
 Login : 00 Chapters;
-PE : 69 Chapters;
+PE : 03 Chapters;
+CE : 09 Chapters;
+Comp : 24 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>33 chap in Revises. Rest with author</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 121 Chapters;
+CE : 14 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 00 Chapters;
+CE : 01 Chapters;
+Comp : 21 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 00 Chapters;
+CE : 04 Chapters;
+Comp : 36 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 01 Chapters;
+PE : 55 Chapters;
 CE : 00 Chapters;
 Comp : 00 Chapters;
 Online Delivery : 00 Chapters</t>
   </si>
   <si>
-    <t>30 chap in Revises</t>
-  </si>
-  <si>
-    <t>Delivered titles</t>
-  </si>
-  <si>
-    <t>Remarks2</t>
+    <t>S200 - 
+Login : 65 Chapters;
+PE : 05 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 00 Chapters;
+PE : 70 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>S200 - 
+Login : 26 Chapters;
+PE : 00 Chapters;
+CE : 00 Chapters;
+Comp : 00 Chapters;
+Online Delivery : 00 Chapters</t>
+  </si>
+  <si>
+    <t>Hameed-8770635, Alaa Ali</t>
+  </si>
+  <si>
+    <t>Ventura, Michele Della</t>
   </si>
 </sst>
 </file>
@@ -943,7 +957,7 @@
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1138,6 +1152,16 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Display"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1492,7 +1516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1660,18 +1684,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1946,9 +1958,6 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2029,14 +2038,74 @@
     <xf numFmtId="15" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="61">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2055,24 +2124,34 @@
       </font>
       <numFmt numFmtId="164" formatCode="0;[Red]0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="22" formatCode="mmm/yy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -2082,6 +2161,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -4436,7 +4521,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:H12" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -4645,6 +4730,9 @@
     <dataField name="Count of S650 TAT" fld="11" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
+    <format dxfId="60">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
     <format dxfId="59">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
@@ -4652,9 +4740,6 @@
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
     <format dxfId="57">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
-    </format>
-    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4663,7 +4748,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4672,7 +4757,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4681,7 +4766,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4690,7 +4775,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4702,7 +4787,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="3">
           <reference field="2" count="1" selected="0">
@@ -4728,29 +4813,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T35" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
-  <autoFilter ref="A1:T35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:T36" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+  <autoFilter ref="A1:T36"/>
   <tableColumns count="20">
-    <tableColumn id="1" name="S. no" dataDxfId="48"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="47"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="46"/>
-    <tableColumn id="4" name="Stage" dataDxfId="45"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="44"/>
-    <tableColumn id="6" name="Current TAT (S50 onward)" dataDxfId="43"/>
-    <tableColumn id="7" name="S200 TAT" dataDxfId="42"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="41"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="40"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="39"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="38"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="37"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="36"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="35"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="34"/>
-    <tableColumn id="16" name="Status - 300" dataDxfId="33"/>
-    <tableColumn id="17" name="Remarks" dataDxfId="32"/>
-    <tableColumn id="18" name="Column1" dataDxfId="31"/>
-    <tableColumn id="19" name="Plateform" dataDxfId="30"/>
-    <tableColumn id="20" name="Column2" dataDxfId="29"/>
+    <tableColumn id="1" name="S. no" dataDxfId="49"/>
+    <tableColumn id="2" name="Book ID" dataDxfId="48"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="47"/>
+    <tableColumn id="4" name="Stage" dataDxfId="46"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="45"/>
+    <tableColumn id="6" name="Current TAT (S50 onward)" dataDxfId="44"/>
+    <tableColumn id="7" name="S200 TAT" dataDxfId="43"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="42"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="41"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="40"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="39"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="38"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="37"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="36"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="35"/>
+    <tableColumn id="16" name="Status - 300" dataDxfId="34"/>
+    <tableColumn id="17" name="Remarks" dataDxfId="33"/>
+    <tableColumn id="18" name="Column1" dataDxfId="32"/>
+    <tableColumn id="19" name="Plateform" dataDxfId="31"/>
+    <tableColumn id="20" name="Column2" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4758,40 +4843,35 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:S17" totalsRowShown="0">
-  <autoFilter ref="A1:S17">
-    <filterColumn colId="17">
-      <filters>
-        <dateGroupItem year="2026" month="10" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="19">
-    <tableColumn id="1" name="S. no" dataDxfId="28"/>
-    <tableColumn id="2" name="Book ID" dataDxfId="27"/>
-    <tableColumn id="3" name="MPS ID" dataDxfId="26"/>
-    <tableColumn id="4" name="Stage" dataDxfId="25"/>
-    <tableColumn id="5" name="Received Date (S50)" dataDxfId="24"/>
-    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="23"/>
-    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="22"/>
-    <tableColumn id="8" name="S300A TAT" dataDxfId="21"/>
-    <tableColumn id="9" name="S300 TAT" dataDxfId="20"/>
-    <tableColumn id="10" name="S600 TAT" dataDxfId="19"/>
-    <tableColumn id="11" name="S650A TAT" dataDxfId="18"/>
-    <tableColumn id="12" name="S650 TAT" dataDxfId="17"/>
-    <tableColumn id="13" name="Total Chapters" dataDxfId="16"/>
-    <tableColumn id="14" name="MS Pages" dataDxfId="15"/>
-    <tableColumn id="19" name="TS Pages" dataDxfId="14"/>
-    <tableColumn id="15" name="Status - S200" dataDxfId="13"/>
-    <tableColumn id="16" name="Remarks" dataDxfId="12"/>
-    <tableColumn id="17" name="Delivered Date " dataDxfId="11"/>
-    <tableColumn id="18" name="Remarks2" dataDxfId="10"/>
+    <tableColumn id="1" name="S. no" dataDxfId="29">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" name="Book ID" dataDxfId="28"/>
+    <tableColumn id="3" name="MPS ID" dataDxfId="27"/>
+    <tableColumn id="4" name="Stage" dataDxfId="26"/>
+    <tableColumn id="5" name="Received Date (S50)" dataDxfId="25"/>
+    <tableColumn id="6" name="Total Avg. Aging Days" dataDxfId="24"/>
+    <tableColumn id="7" name="Total Avg.Aging Days in S200" dataDxfId="23"/>
+    <tableColumn id="8" name="S300A TAT" dataDxfId="22"/>
+    <tableColumn id="9" name="S300 TAT" dataDxfId="21"/>
+    <tableColumn id="10" name="S600 TAT" dataDxfId="20"/>
+    <tableColumn id="11" name="S650A TAT" dataDxfId="19"/>
+    <tableColumn id="12" name="S650 TAT" dataDxfId="18"/>
+    <tableColumn id="13" name="Total Chapters" dataDxfId="17"/>
+    <tableColumn id="14" name="MS Pages" dataDxfId="16"/>
+    <tableColumn id="19" name="TS Pages" dataDxfId="15"/>
+    <tableColumn id="15" name="Status - S200" dataDxfId="14"/>
+    <tableColumn id="16" name="Remarks" dataDxfId="13"/>
+    <tableColumn id="17" name="Delivered Date " dataDxfId="12"/>
+    <tableColumn id="18" name="Remarks2" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C4" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="1" name="DESCriptions"/>
@@ -4803,12 +4883,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:C10" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
-  <autoFilter ref="B5:C10"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="Month" dataDxfId="1"/>
-    <tableColumn id="2" name="No of titles delivered" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B5:D10" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+  <autoFilter ref="B5:D10"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Month" dataDxfId="2"/>
+    <tableColumn id="2" name="No of titles delivered" dataDxfId="1">
       <calculatedColumnFormula>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" name="TS Pages" dataDxfId="0">
+      <calculatedColumnFormula>SUM(Delivered!O10:O17)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5093,18 +5176,18 @@
   <sheetData>
     <row r="3" spans="1:8">
       <c r="C3"/>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="69" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="156" t="s">
         <v>40</v>
       </c>
       <c r="D4" t="s">
@@ -5133,17 +5216,17 @@
       <c r="C5">
         <v>32</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="70">
         <v>1</v>
       </c>
-      <c r="E5" s="74">
+      <c r="E5" s="70">
         <v>1</v>
       </c>
-      <c r="F5" s="74">
+      <c r="F5" s="70">
         <v>1</v>
       </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
@@ -5155,19 +5238,19 @@
       <c r="C6">
         <v>32</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="70">
         <v>1</v>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="70">
         <v>1</v>
       </c>
-      <c r="F6" s="74">
+      <c r="F6" s="70">
         <v>1</v>
       </c>
-      <c r="G6" s="74">
+      <c r="G6" s="70">
         <v>1</v>
       </c>
-      <c r="H6" s="74"/>
+      <c r="H6" s="70"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
@@ -5179,17 +5262,17 @@
       <c r="C7">
         <v>32</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="70">
         <v>1</v>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="70">
         <v>1</v>
       </c>
-      <c r="F7" s="74">
+      <c r="F7" s="70">
         <v>1</v>
       </c>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
@@ -5201,17 +5284,17 @@
       <c r="C8">
         <v>35</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="70">
         <v>1</v>
       </c>
-      <c r="E8" s="74">
+      <c r="E8" s="70">
         <v>1</v>
       </c>
-      <c r="F8" s="74">
+      <c r="F8" s="70">
         <v>1</v>
       </c>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
@@ -5223,17 +5306,17 @@
       <c r="C9">
         <v>40</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="70">
         <v>1</v>
       </c>
-      <c r="E9" s="74">
+      <c r="E9" s="70">
         <v>1</v>
       </c>
-      <c r="F9" s="74">
+      <c r="F9" s="70">
         <v>1</v>
       </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
@@ -5245,19 +5328,19 @@
       <c r="C10">
         <v>40</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="70">
         <v>1</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E10" s="70">
         <v>1</v>
       </c>
-      <c r="F10" s="74">
+      <c r="F10" s="70">
         <v>1</v>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="70">
         <v>1</v>
       </c>
-      <c r="H10" s="74"/>
+      <c r="H10" s="70"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
@@ -5269,36 +5352,36 @@
       <c r="C11">
         <v>34</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="70">
         <v>1</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="70">
         <v>1</v>
       </c>
-      <c r="F11" s="74">
+      <c r="F11" s="70">
         <v>1</v>
       </c>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>125</v>
       </c>
       <c r="C12"/>
-      <c r="D12" s="74">
+      <c r="D12" s="70">
         <v>7</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="70">
         <v>7</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F12" s="70">
         <v>7</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="70">
         <v>2</v>
       </c>
-      <c r="H12" s="74"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" spans="1:8">
       <c r="C13"/>
@@ -5397,7 +5480,7 @@
     <col min="3" max="3" width="21.453125" style="53" customWidth="1"/>
     <col min="4" max="4" width="13.6328125" style="39" customWidth="1"/>
     <col min="5" max="5" width="18.81640625" style="39" customWidth="1"/>
-    <col min="6" max="6" width="23.90625" style="185" customWidth="1"/>
+    <col min="6" max="6" width="23.90625" style="180" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="39" customWidth="1"/>
     <col min="8" max="8" width="10" style="18" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="8.7265625" style="18" bestFit="1" customWidth="1"/>
@@ -5405,9 +5488,9 @@
     <col min="12" max="12" width="8.7265625" style="18" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.08984375" style="39" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.6328125" style="35" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.54296875" style="97" customWidth="1"/>
-    <col min="16" max="16" width="16" style="97" customWidth="1"/>
-    <col min="17" max="17" width="15.81640625" style="97" customWidth="1"/>
+    <col min="15" max="15" width="19.54296875" style="93" customWidth="1"/>
+    <col min="16" max="16" width="16" style="93" customWidth="1"/>
+    <col min="17" max="17" width="15.81640625" style="93" customWidth="1"/>
     <col min="18" max="18" width="19.26953125" style="17" customWidth="1"/>
     <col min="19" max="19" width="15.81640625" style="17"/>
     <col min="20" max="16384" width="15.81640625" style="18"/>
@@ -5471,8 +5554,8 @@
       <c r="S1" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="T1" s="184" t="s">
-        <v>219</v>
+      <c r="T1" s="179" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="240">
@@ -5483,18 +5566,18 @@
       <c r="B2" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="96" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E2" s="37">
         <v>46258</v>
       </c>
-      <c r="F2" s="72">
+      <c r="F2" s="68">
         <f t="shared" ref="F2:F12" ca="1" si="1">TODAY()-E2</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="36">
         <f>DATE(2026,9,19)-DATE(2026,8,24)</f>
@@ -5510,11 +5593,11 @@
       </c>
       <c r="J2" s="24">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" s="24">
         <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="24"/>
       <c r="M2" s="24">
@@ -5523,22 +5606,22 @@
       <c r="N2" s="24">
         <v>500</v>
       </c>
-      <c r="O2" s="96" t="s">
+      <c r="O2" s="92" t="s">
         <v>59</v>
       </c>
       <c r="P2" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="Q2" s="132" t="s">
+      <c r="Q2" s="128" t="s">
         <v>176</v>
       </c>
-      <c r="R2" s="89" t="s">
+      <c r="R2" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="89" t="s">
+      <c r="S2" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T2" s="183"/>
+      <c r="T2" s="178"/>
     </row>
     <row r="3" spans="1:20" ht="60">
       <c r="A3" s="36">
@@ -5548,34 +5631,34 @@
       <c r="B3" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="180" t="s">
+      <c r="C3" s="175" t="s">
         <v>153</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="E3" s="26">
         <v>46291</v>
       </c>
       <c r="F3" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="24">
         <f>DATE(2026,10,10)-DATE(2026,9,26)</f>
         <v>14</v>
       </c>
-      <c r="H3" s="88">
+      <c r="H3" s="84">
         <f>DATE(2026,10,24)-DATE(2026,10,10)</f>
         <v>14</v>
       </c>
-      <c r="I3" s="88">
+      <c r="I3" s="84">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
       <c r="J3" s="38">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -5585,22 +5668,22 @@
       <c r="N3" s="24">
         <v>200</v>
       </c>
-      <c r="O3" s="96" t="s">
+      <c r="O3" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="95" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q3" s="133" t="s">
+      <c r="P3" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q3" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="R3" s="139" t="s">
+      <c r="R3" s="135" t="s">
         <v>85</v>
       </c>
-      <c r="S3" s="89" t="s">
+      <c r="S3" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T3" s="158"/>
+      <c r="T3" s="154"/>
     </row>
     <row r="4" spans="1:20" ht="60">
       <c r="A4" s="36">
@@ -5610,7 +5693,7 @@
       <c r="B4" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="179" t="s">
+      <c r="C4" s="174" t="s">
         <v>154</v>
       </c>
       <c r="D4" s="42" t="s">
@@ -5621,44 +5704,44 @@
       </c>
       <c r="F4" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="24">
         <f>DATE(2026,10,12)-DATE(2026,9,26)</f>
         <v>16</v>
       </c>
-      <c r="H4" s="88">
+      <c r="H4" s="84">
         <f>DATE(2026,10,22)-DATE(2026,10,12)</f>
         <v>10</v>
       </c>
-      <c r="I4" s="88">
+      <c r="I4" s="84">
         <f>DATE(2026,10,28)-DATE(2026,10,23)</f>
         <v>5</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="84">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>1</v>
-      </c>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
+        <v>2</v>
+      </c>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
       <c r="M4" s="24">
         <v>15</v>
       </c>
       <c r="N4" s="24">
         <v>200</v>
       </c>
-      <c r="O4" s="96" t="s">
+      <c r="O4" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="133" t="s">
+      <c r="P4" s="91"/>
+      <c r="Q4" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="89"/>
-      <c r="S4" s="89" t="s">
+      <c r="R4" s="85"/>
+      <c r="S4" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T4" s="158"/>
+      <c r="T4" s="154"/>
     </row>
     <row r="5" spans="1:20" ht="60">
       <c r="A5" s="36">
@@ -5679,7 +5762,7 @@
       </c>
       <c r="F5" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" s="52">
         <f>DATE(2026,10,8)-DATE(2026,9,23)</f>
@@ -5695,7 +5778,7 @@
       </c>
       <c r="J5" s="38">
         <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="38"/>
       <c r="L5" s="38"/>
@@ -5705,20 +5788,22 @@
       <c r="N5" s="24">
         <v>280</v>
       </c>
-      <c r="O5" s="96" t="s">
+      <c r="O5" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P5" s="95"/>
-      <c r="Q5" s="133" t="s">
+      <c r="P5" s="91" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q5" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="R5" s="89" t="s">
+      <c r="R5" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="S5" s="89" t="s">
+      <c r="S5" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T5" s="158"/>
+      <c r="T5" s="154"/>
     </row>
     <row r="6" spans="1:20" ht="60">
       <c r="A6" s="36">
@@ -5728,69 +5813,72 @@
       <c r="B6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="179" t="s">
+      <c r="C6" s="174" t="s">
         <v>156</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="E6" s="26">
         <v>46288</v>
       </c>
       <c r="F6" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="G6" s="175">
+        <v>37</v>
+      </c>
+      <c r="G6" s="170">
         <f>DATE(2026,10,14)-DATE(2026,10,2)</f>
         <v>12</v>
       </c>
-      <c r="H6" s="88">
+      <c r="H6" s="84">
         <f>DATE(2026,10,27)-DATE(2026,10,14)</f>
         <v>13</v>
       </c>
-      <c r="I6" s="88">
+      <c r="I6" s="84">
         <f>DATE(2026,10,28)-DATE(2026,10,28)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
+      <c r="J6" s="84">
+        <f ca="1">TODAY()-DATE(2026,10,29)</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
       <c r="M6" s="24">
         <v>25</v>
       </c>
       <c r="N6" s="24">
         <v>240</v>
       </c>
-      <c r="O6" s="96" t="s">
+      <c r="O6" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q6" s="133" t="s">
+      <c r="P6" s="91" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q6" s="129" t="s">
         <v>137</v>
       </c>
-      <c r="R6" s="140" t="s">
+      <c r="R6" s="136" t="s">
         <v>169</v>
       </c>
-      <c r="S6" s="89" t="s">
+      <c r="S6" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T6" s="158"/>
+      <c r="T6" s="154"/>
     </row>
     <row r="7" spans="1:20" ht="60">
       <c r="A7" s="36">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="183" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="184" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="185" t="s">
         <v>120</v>
       </c>
       <c r="E7" s="26">
@@ -5798,7 +5886,7 @@
       </c>
       <c r="F7" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="24">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
@@ -5808,11 +5896,14 @@
         <f>DATE(2026,10,24)-DATE(2026,10,8)</f>
         <v>16</v>
       </c>
-      <c r="I7" s="130">
+      <c r="I7" s="126">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
-      <c r="J7" s="17"/>
+      <c r="J7" s="38">
+        <f ca="1">TODAY()-DATE(2026,10,29)</f>
+        <v>1</v>
+      </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="24">
@@ -5821,90 +5912,90 @@
       <c r="N7" s="24">
         <v>244</v>
       </c>
-      <c r="O7" s="96" t="s">
+      <c r="O7" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P7" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q7" s="133" t="s">
+      <c r="P7" s="91" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q7" s="129" t="s">
         <v>111</v>
       </c>
-      <c r="R7" s="89" t="s">
+      <c r="R7" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="S7" s="89" t="s">
+      <c r="S7" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T7" s="158"/>
-    </row>
-    <row r="8" spans="1:20" s="129" customFormat="1" ht="60">
-      <c r="A8" s="122">
+      <c r="T7" s="154"/>
+    </row>
+    <row r="8" spans="1:20" s="125" customFormat="1" ht="60">
+      <c r="A8" s="118">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="97" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="122" t="s">
-        <v>189</v>
-      </c>
-      <c r="E8" s="124">
+      <c r="D8" s="118" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="120">
         <v>46283</v>
       </c>
-      <c r="F8" s="122">
+      <c r="F8" s="118">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="G8" s="122">
+        <v>42</v>
+      </c>
+      <c r="G8" s="118">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H8" s="125">
+      <c r="H8" s="121">
         <f>DATE(2026,10,19)-DATE(2026,10,12)</f>
         <v>7</v>
       </c>
-      <c r="I8" s="125">
+      <c r="I8" s="121">
         <f ca="1">TODAY()-DATE(2026,10,20)</f>
-        <v>9</v>
-      </c>
-      <c r="J8" s="125">
+        <v>10</v>
+      </c>
+      <c r="J8" s="121">
         <f>DATE(2026,10,26)-DATE(2026,10,22)</f>
         <v>4</v>
       </c>
-      <c r="K8" s="125">
+      <c r="K8" s="121">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="126"/>
-      <c r="M8" s="122">
+        <v>1</v>
+      </c>
+      <c r="L8" s="122"/>
+      <c r="M8" s="118">
         <v>9</v>
       </c>
-      <c r="N8" s="122">
+      <c r="N8" s="118">
         <v>100</v>
       </c>
-      <c r="O8" s="127" t="s">
+      <c r="O8" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="128"/>
-      <c r="Q8" s="134" t="s">
+      <c r="P8" s="124"/>
+      <c r="Q8" s="130" t="s">
         <v>63</v>
       </c>
-      <c r="R8" s="126"/>
-      <c r="S8" s="126" t="s">
+      <c r="R8" s="122"/>
+      <c r="S8" s="122" t="s">
         <v>151</v>
       </c>
-      <c r="T8" s="158"/>
+      <c r="T8" s="154"/>
     </row>
     <row r="9" spans="1:20" ht="60">
       <c r="A9" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="66" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="25" t="s">
@@ -5918,7 +6009,7 @@
       </c>
       <c r="F9" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="24">
         <f>DATE(2026,10,9)-DATE(2026,9,21)</f>
@@ -5928,34 +6019,34 @@
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I9" s="130">
+      <c r="I9" s="126">
         <f>DATE(2026,10,28)-DATE(2026,10,25)</f>
         <v>3</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="84">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>1</v>
-      </c>
-      <c r="K9" s="89"/>
-      <c r="L9" s="89"/>
+        <v>2</v>
+      </c>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
       <c r="M9" s="24">
         <v>13</v>
       </c>
       <c r="N9" s="24">
         <v>120</v>
       </c>
-      <c r="O9" s="96" t="s">
+      <c r="O9" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P9" s="95"/>
-      <c r="Q9" s="133" t="s">
+      <c r="P9" s="91"/>
+      <c r="Q9" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="R9" s="89"/>
-      <c r="S9" s="89" t="s">
+      <c r="R9" s="85"/>
+      <c r="S9" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T9" s="158"/>
+      <c r="T9" s="154"/>
     </row>
     <row r="10" spans="1:20" ht="60">
       <c r="A10" s="36">
@@ -5965,7 +6056,7 @@
       <c r="B10" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="180" t="s">
+      <c r="C10" s="175" t="s">
         <v>160</v>
       </c>
       <c r="D10" s="42" t="s">
@@ -5976,7 +6067,7 @@
       </c>
       <c r="F10" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="38">
         <f>DATE(2026,10,11)-DATE(2026,9,25)</f>
@@ -5986,35 +6077,35 @@
         <f>DATE(2026,10,24)-DATE(2026,10,12)</f>
         <v>12</v>
       </c>
-      <c r="I10" s="130">
+      <c r="I10" s="126">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>4</v>
-      </c>
-      <c r="J10" s="89"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
+        <v>5</v>
+      </c>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
       <c r="M10" s="24">
         <v>37</v>
       </c>
       <c r="N10" s="24">
         <v>200</v>
       </c>
-      <c r="O10" s="96" t="s">
+      <c r="O10" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P10" s="95" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q10" s="133" t="s">
+      <c r="P10" s="91" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q10" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="R10" s="139" t="s">
+      <c r="R10" s="135" t="s">
         <v>85</v>
       </c>
-      <c r="S10" s="89" t="s">
+      <c r="S10" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T10" s="158"/>
+      <c r="T10" s="154"/>
     </row>
     <row r="11" spans="1:20" ht="60">
       <c r="A11" s="36">
@@ -6024,7 +6115,7 @@
       <c r="B11" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="174" t="s">
         <v>161</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -6035,53 +6126,53 @@
       </c>
       <c r="F11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="G11" s="88">
+        <v>30</v>
+      </c>
+      <c r="G11" s="84">
         <f>DATE(2026,10,27)-DATE(2026,10,12)</f>
         <v>15</v>
       </c>
-      <c r="H11" s="88">
+      <c r="H11" s="84">
         <f>DATE(2026,10,28)-DATE(2026,10,28)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="88">
+      <c r="I11" s="84">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="89"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="89"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
       <c r="M11" s="24">
         <v>78</v>
       </c>
       <c r="N11" s="24">
         <v>750</v>
       </c>
-      <c r="O11" s="96" t="s">
-        <v>209</v>
-      </c>
-      <c r="P11" s="95" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q11" s="133" t="s">
+      <c r="O11" s="92" t="s">
+        <v>207</v>
+      </c>
+      <c r="P11" s="91" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q11" s="129" t="s">
         <v>148</v>
       </c>
-      <c r="R11" s="89"/>
-      <c r="S11" s="89" t="s">
+      <c r="R11" s="85"/>
+      <c r="S11" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T11" s="158"/>
+      <c r="T11" s="154"/>
     </row>
     <row r="12" spans="1:20" ht="130.5">
       <c r="A12" s="36">
-        <f t="shared" ref="A12:A34" si="3">ROW()-1</f>
+        <f t="shared" ref="A12:A36" si="3">ROW()-1</f>
         <v>11</v>
       </c>
       <c r="B12" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="179" t="s">
+      <c r="C12" s="174" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="24" t="s">
@@ -6092,106 +6183,106 @@
       </c>
       <c r="F12" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="G12" s="88">
+        <v>32</v>
+      </c>
+      <c r="G12" s="84">
         <f>DATE(2026,10,21)-DATE(2026,9,30)</f>
         <v>21</v>
       </c>
-      <c r="H12" s="88">
+      <c r="H12" s="84">
         <f>DATE(2026,10,28)-DATE(2026,10,26)</f>
         <v>2</v>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="84">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="89"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
+        <v>1</v>
+      </c>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
       <c r="M12" s="24">
         <v>81</v>
       </c>
       <c r="N12" s="24">
         <v>600</v>
       </c>
-      <c r="O12" s="96" t="s">
+      <c r="O12" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="95" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q12" s="133" t="s">
+      <c r="P12" s="91" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q12" s="129" t="s">
         <v>66</v>
       </c>
-      <c r="R12" s="89" t="s">
-        <v>238</v>
-      </c>
-      <c r="S12" s="89" t="s">
+      <c r="R12" s="85" t="s">
+        <v>228</v>
+      </c>
+      <c r="S12" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T12" s="158"/>
+      <c r="T12" s="154"/>
     </row>
     <row r="13" spans="1:20" ht="60">
       <c r="A13" s="36">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="B13" s="71" t="s">
+      <c r="B13" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="97" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E13" s="26">
         <v>46282</v>
       </c>
       <c r="F13" s="24">
         <f ca="1">TODAY()-DATE(2026,9,17)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="24">
         <f>DATE(2026,10,6)-DATE(2026,9,17)</f>
         <v>19</v>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="84">
         <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
         <v>13</v>
       </c>
-      <c r="I13" s="88">
+      <c r="I13" s="84">
         <f>DATE(2026,10,22)-DATE(2026,10,21)</f>
         <v>1</v>
       </c>
-      <c r="J13" s="121">
+      <c r="J13" s="117">
         <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
         <v>1</v>
       </c>
-      <c r="K13" s="91">
+      <c r="K13" s="87">
         <f ca="1">TODAY()-DATE(2026,10,26)</f>
-        <v>3</v>
-      </c>
-      <c r="L13" s="92"/>
+        <v>4</v>
+      </c>
+      <c r="L13" s="88"/>
       <c r="M13" s="24">
         <v>41</v>
       </c>
       <c r="N13" s="24">
         <v>500</v>
       </c>
-      <c r="O13" s="96" t="s">
+      <c r="O13" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P13" s="95"/>
-      <c r="Q13" s="135" t="s">
+      <c r="P13" s="91"/>
+      <c r="Q13" s="131" t="s">
         <v>66</v>
       </c>
-      <c r="R13" s="89"/>
-      <c r="S13" s="89" t="s">
+      <c r="R13" s="85"/>
+      <c r="S13" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T13" s="158"/>
+      <c r="T13" s="154"/>
     </row>
     <row r="14" spans="1:20" ht="60">
       <c r="A14" s="36">
@@ -6201,7 +6292,7 @@
       <c r="B14" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="179" t="s">
+      <c r="C14" s="174" t="s">
         <v>97</v>
       </c>
       <c r="D14" s="24" t="s">
@@ -6212,37 +6303,37 @@
       </c>
       <c r="F14" s="33">
         <f ca="1">TODAY()-E14</f>
-        <v>30</v>
-      </c>
-      <c r="G14" s="88">
+        <v>31</v>
+      </c>
+      <c r="G14" s="84">
         <f ca="1">TODAY()-DATE(2026,10,3)</f>
-        <v>26</v>
-      </c>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="89"/>
+        <v>27</v>
+      </c>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
       <c r="M14" s="24">
         <v>36</v>
       </c>
       <c r="N14" s="24">
         <v>500</v>
       </c>
-      <c r="O14" s="96" t="s">
-        <v>223</v>
-      </c>
-      <c r="P14" s="95" t="s">
+      <c r="O14" s="92" t="s">
+        <v>243</v>
+      </c>
+      <c r="P14" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="Q14" s="133" t="s">
-        <v>239</v>
-      </c>
-      <c r="R14" s="89"/>
-      <c r="S14" s="89" t="s">
+      <c r="Q14" s="129" t="s">
+        <v>229</v>
+      </c>
+      <c r="R14" s="85"/>
+      <c r="S14" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="T14" s="158"/>
+      <c r="T14" s="154"/>
     </row>
     <row r="15" spans="1:20" ht="60">
       <c r="A15" s="36">
@@ -6252,7 +6343,7 @@
       <c r="B15" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="179" t="s">
+      <c r="C15" s="174" t="s">
         <v>83</v>
       </c>
       <c r="D15" s="24" t="s">
@@ -6263,38 +6354,38 @@
       </c>
       <c r="F15" s="24">
         <f ca="1">TODAY()-E15</f>
-        <v>32</v>
-      </c>
-      <c r="G15" s="88">
+        <v>33</v>
+      </c>
+      <c r="G15" s="84">
         <f>DATE(2026,10,27)-DATE(2026,9,28)</f>
         <v>29</v>
       </c>
-      <c r="H15" s="88">
-        <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>1</v>
-      </c>
-      <c r="I15" s="88"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
+      <c r="H15" s="84">
+        <f ca="1">TODAY()-DATE(2026,10,27)</f>
+        <v>3</v>
+      </c>
+      <c r="I15" s="84"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
       <c r="M15" s="24">
         <v>31</v>
       </c>
-      <c r="N15" s="88">
+      <c r="N15" s="84">
         <v>500</v>
       </c>
-      <c r="O15" s="96" t="s">
-        <v>210</v>
-      </c>
-      <c r="P15" s="95" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q15" s="133"/>
-      <c r="R15" s="89"/>
-      <c r="S15" s="89" t="s">
+      <c r="O15" s="92" t="s">
+        <v>208</v>
+      </c>
+      <c r="P15" s="91" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="85"/>
+      <c r="S15" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T15" s="158"/>
+      <c r="T15" s="154"/>
     </row>
     <row r="16" spans="1:20" ht="60">
       <c r="A16" s="36">
@@ -6315,41 +6406,41 @@
       </c>
       <c r="F16" s="24">
         <f ca="1">TODAY()-E16</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" s="36">
         <f>DATE(2026,10,22)-DATE(2026,9,28)</f>
         <v>24</v>
       </c>
-      <c r="H16" s="88">
+      <c r="H16" s="84">
         <f>DATE(2026,10,27)-DATE(2026,10,22)</f>
         <v>5</v>
       </c>
-      <c r="I16" s="88">
+      <c r="I16" s="84">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>1</v>
-      </c>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
-      <c r="L16" s="89"/>
+        <v>2</v>
+      </c>
+      <c r="J16" s="85"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
       <c r="M16" s="24">
         <v>28</v>
       </c>
-      <c r="N16" s="88">
+      <c r="N16" s="84">
         <v>350</v>
       </c>
-      <c r="O16" s="99" t="s">
+      <c r="O16" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="98" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q16" s="135"/>
-      <c r="R16" s="89"/>
-      <c r="S16" s="89" t="s">
+      <c r="P16" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q16" s="131"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T16" s="158"/>
+      <c r="T16" s="154"/>
     </row>
     <row r="17" spans="1:20" ht="60">
       <c r="A17" s="36">
@@ -6359,7 +6450,7 @@
       <c r="B17" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="182" t="s">
+      <c r="C17" s="177" t="s">
         <v>140</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -6370,48 +6461,48 @@
       </c>
       <c r="F17" s="24">
         <f ca="1">TODAY()-E17</f>
-        <v>22</v>
-      </c>
-      <c r="G17" s="71">
+        <v>23</v>
+      </c>
+      <c r="G17" s="67">
         <f ca="1">TODAY()-DATE(2026,10,21)</f>
-        <v>8</v>
-      </c>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="89"/>
-      <c r="L17" s="89"/>
+        <v>9</v>
+      </c>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
       <c r="M17" s="24">
         <f>129+6</f>
         <v>135</v>
       </c>
-      <c r="N17" s="88">
+      <c r="N17" s="84">
         <v>1500</v>
       </c>
-      <c r="O17" s="99" t="s">
-        <v>225</v>
-      </c>
-      <c r="P17" s="95" t="s">
+      <c r="O17" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="Q17" s="136" t="s">
+      <c r="P17" s="91" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q17" s="132" t="s">
         <v>170</v>
       </c>
-      <c r="R17" s="89"/>
-      <c r="S17" s="89" t="s">
+      <c r="R17" s="85"/>
+      <c r="S17" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="T17" s="158"/>
+      <c r="T17" s="154"/>
     </row>
     <row r="18" spans="1:20" ht="33.5" customHeight="1">
       <c r="A18" s="36">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="B18" s="141" t="s">
+      <c r="B18" s="137" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="181" t="s">
+      <c r="C18" s="176" t="s">
         <v>91</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -6422,45 +6513,45 @@
       </c>
       <c r="F18" s="24">
         <f ca="1">TODAY()-E18</f>
-        <v>29</v>
-      </c>
-      <c r="G18" s="88">
+        <v>30</v>
+      </c>
+      <c r="G18" s="84">
         <f ca="1">TODAY()-DATE(2026,10,13)</f>
-        <v>16</v>
-      </c>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
+        <v>17</v>
+      </c>
+      <c r="H18" s="85"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
       <c r="M18" s="24">
         <v>48</v>
       </c>
-      <c r="N18" s="88">
+      <c r="N18" s="84">
         <v>550</v>
       </c>
-      <c r="O18" s="96" t="s">
-        <v>226</v>
-      </c>
-      <c r="P18" s="95" t="s">
+      <c r="O18" s="92" t="s">
+        <v>246</v>
+      </c>
+      <c r="P18" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="Q18" s="133"/>
-      <c r="R18" s="89"/>
-      <c r="S18" s="89" t="s">
+      <c r="Q18" s="129"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="T18" s="158"/>
+      <c r="T18" s="154"/>
     </row>
     <row r="19" spans="1:20" ht="60">
       <c r="A19" s="36">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="179" t="s">
+      <c r="C19" s="174" t="s">
         <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -6471,42 +6562,42 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" ref="F19" ca="1" si="4">TODAY()-E19</f>
-        <v>29</v>
-      </c>
-      <c r="G19" s="88">
+        <v>30</v>
+      </c>
+      <c r="G19" s="84">
         <f ca="1">TODAY()-DATE(2026,10,12)</f>
-        <v>17</v>
-      </c>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="89"/>
+        <v>18</v>
+      </c>
+      <c r="H19" s="85"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
       <c r="M19" s="24">
         <v>40</v>
       </c>
-      <c r="N19" s="88">
+      <c r="N19" s="84">
         <v>450</v>
       </c>
-      <c r="O19" s="96" t="s">
-        <v>227</v>
-      </c>
-      <c r="P19" s="95"/>
-      <c r="Q19" s="133" t="s">
+      <c r="O19" s="92" t="s">
+        <v>247</v>
+      </c>
+      <c r="P19" s="91"/>
+      <c r="Q19" s="129" t="s">
         <v>152</v>
       </c>
-      <c r="R19" s="89"/>
-      <c r="S19" s="89" t="s">
+      <c r="R19" s="85"/>
+      <c r="S19" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T19" s="158"/>
+      <c r="T19" s="154"/>
     </row>
     <row r="20" spans="1:20" ht="127">
       <c r="A20" s="36">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="67" t="s">
         <v>99</v>
       </c>
       <c r="C20" s="25" t="s">
@@ -6520,46 +6611,46 @@
       </c>
       <c r="F20" s="3">
         <f ca="1">TODAY()-E20</f>
-        <v>17</v>
-      </c>
-      <c r="G20" s="88">
+        <v>18</v>
+      </c>
+      <c r="G20" s="84">
         <f ca="1">TODAY()-DATE(2026,10,28)</f>
-        <v>1</v>
-      </c>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
+        <v>2</v>
+      </c>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
       <c r="M20" s="24">
         <v>31</v>
       </c>
-      <c r="N20" s="88">
+      <c r="N20" s="84">
         <v>350</v>
       </c>
-      <c r="O20" s="96" t="s">
-        <v>241</v>
-      </c>
-      <c r="P20" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q20" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="R20" s="89" t="s">
-        <v>243</v>
-      </c>
-      <c r="S20" s="89" t="s">
+      <c r="O20" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="P20" s="91" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q20" s="129" t="s">
+        <v>230</v>
+      </c>
+      <c r="R20" s="85" t="s">
+        <v>233</v>
+      </c>
+      <c r="S20" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T20" s="158"/>
+      <c r="T20" s="154"/>
     </row>
     <row r="21" spans="1:20" ht="60">
       <c r="A21" s="36">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="67" t="s">
         <v>109</v>
       </c>
       <c r="C21" s="25" t="s">
@@ -6571,45 +6662,45 @@
       <c r="E21" s="26">
         <v>46307</v>
       </c>
-      <c r="F21" s="91">
+      <c r="F21" s="87">
         <f ca="1">TODAY()-E21</f>
-        <v>17</v>
-      </c>
-      <c r="G21" s="88">
+        <v>18</v>
+      </c>
+      <c r="G21" s="84">
         <f ca="1">TODAY()-DATE(2026,10,19)</f>
-        <v>10</v>
-      </c>
-      <c r="H21" s="152"/>
-      <c r="I21" s="152"/>
-      <c r="J21" s="152"/>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
+        <v>11</v>
+      </c>
+      <c r="H21" s="148"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="148"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
       <c r="M21" s="24">
         <v>28</v>
       </c>
-      <c r="N21" s="88">
+      <c r="N21" s="84">
         <v>500</v>
       </c>
-      <c r="O21" s="96" t="s">
+      <c r="O21" s="92" t="s">
         <v>168</v>
       </c>
-      <c r="P21" s="95"/>
-      <c r="Q21" s="137"/>
-      <c r="R21" s="89"/>
-      <c r="S21" s="89" t="s">
+      <c r="P21" s="91"/>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T21" s="158"/>
+      <c r="T21" s="154"/>
     </row>
     <row r="22" spans="1:20" ht="60">
       <c r="A22" s="36">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="179" t="s">
+      <c r="C22" s="174" t="s">
         <v>93</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -6618,40 +6709,40 @@
       <c r="E22" s="4">
         <v>46302</v>
       </c>
-      <c r="F22" s="153">
+      <c r="F22" s="149">
         <f ca="1">TODAY()-E22</f>
-        <v>22</v>
-      </c>
-      <c r="G22" s="88" t="str">
+        <v>23</v>
+      </c>
+      <c r="G22" s="84" t="str">
         <f ca="1">TRIM(TODAY()-DATE(2026,10,19))</f>
-        <v>10</v>
-      </c>
-      <c r="H22" s="152"/>
-      <c r="I22" s="152"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
+        <v>11</v>
+      </c>
+      <c r="H22" s="148"/>
+      <c r="I22" s="148"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
       <c r="M22" s="24">
         <v>36</v>
       </c>
-      <c r="N22" s="88">
+      <c r="N22" s="84">
         <v>450</v>
       </c>
-      <c r="O22" s="96" t="s">
-        <v>211</v>
-      </c>
-      <c r="P22" s="95"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="89"/>
-      <c r="T22" s="158"/>
+      <c r="O22" s="92" t="s">
+        <v>209</v>
+      </c>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="133"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="85"/>
+      <c r="T22" s="154"/>
     </row>
     <row r="23" spans="1:20" ht="60">
       <c r="A23" s="36">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="B23" s="154" t="s">
+      <c r="B23" s="150" t="s">
         <v>112</v>
       </c>
       <c r="C23" s="25" t="s">
@@ -6660,45 +6751,45 @@
       <c r="D23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="131">
+      <c r="E23" s="127">
         <v>46309</v>
       </c>
-      <c r="F23" s="153">
+      <c r="F23" s="149">
         <f ca="1">TODAY()-E23</f>
-        <v>15</v>
-      </c>
-      <c r="G23" s="88">
+        <v>16</v>
+      </c>
+      <c r="G23" s="84">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>7</v>
-      </c>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="89"/>
+        <v>8</v>
+      </c>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
       <c r="M23" s="24">
         <v>42</v>
       </c>
-      <c r="N23" s="88">
+      <c r="N23" s="84">
         <v>500</v>
       </c>
-      <c r="O23" s="96" t="s">
-        <v>186</v>
-      </c>
-      <c r="P23" s="95"/>
-      <c r="Q23" s="133"/>
-      <c r="R23" s="89"/>
-      <c r="S23" s="89" t="s">
+      <c r="O23" s="92" t="s">
+        <v>185</v>
+      </c>
+      <c r="P23" s="91"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="85"/>
+      <c r="S23" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T23" s="158"/>
+      <c r="T23" s="154"/>
     </row>
     <row r="24" spans="1:20" ht="60">
       <c r="A24" s="36">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="B24" s="154" t="s">
+      <c r="B24" s="150" t="s">
         <v>122</v>
       </c>
       <c r="C24" s="25" t="s">
@@ -6707,45 +6798,45 @@
       <c r="D24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="131">
+      <c r="E24" s="127">
         <v>46312</v>
       </c>
-      <c r="F24" s="153">
+      <c r="F24" s="149">
         <f ca="1">TODAY()-E24</f>
-        <v>12</v>
-      </c>
-      <c r="G24" s="88">
+        <v>13</v>
+      </c>
+      <c r="G24" s="84">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>7</v>
-      </c>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="88">
+        <v>8</v>
+      </c>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="84">
         <v>23</v>
       </c>
-      <c r="N24" s="88">
+      <c r="N24" s="84">
         <v>350</v>
       </c>
-      <c r="O24" s="96" t="s">
+      <c r="O24" s="92" t="s">
         <v>182</v>
       </c>
-      <c r="P24" s="95"/>
-      <c r="Q24" s="133"/>
-      <c r="R24" s="89"/>
-      <c r="S24" s="89" t="s">
+      <c r="P24" s="91"/>
+      <c r="Q24" s="129"/>
+      <c r="R24" s="85"/>
+      <c r="S24" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T24" s="158"/>
+      <c r="T24" s="154"/>
     </row>
     <row r="25" spans="1:20" ht="60">
       <c r="A25" s="36">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="B25" s="155" t="s">
+      <c r="B25" s="151" t="s">
         <v>139</v>
       </c>
       <c r="C25" s="25" t="s">
@@ -6754,47 +6845,47 @@
       <c r="D25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="131">
+      <c r="E25" s="127">
         <v>46312</v>
       </c>
-      <c r="F25" s="153">
+      <c r="F25" s="149">
         <f t="shared" ref="F25" ca="1" si="5">TODAY()-E25</f>
-        <v>12</v>
-      </c>
-      <c r="G25" s="88">
+        <v>13</v>
+      </c>
+      <c r="G25" s="84">
         <f ca="1">TODAY()-DATE(2026,10,27)</f>
-        <v>2</v>
-      </c>
-      <c r="H25" s="89"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="89"/>
-      <c r="K25" s="89"/>
-      <c r="L25" s="89"/>
+        <v>3</v>
+      </c>
+      <c r="H25" s="85"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
       <c r="M25" s="24">
         <v>56</v>
       </c>
-      <c r="N25" s="88">
+      <c r="N25" s="84">
         <v>300</v>
       </c>
-      <c r="O25" s="96" t="s">
-        <v>228</v>
-      </c>
-      <c r="P25" s="95" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q25" s="138"/>
-      <c r="R25" s="89"/>
-      <c r="S25" s="89" t="s">
+      <c r="O25" s="92" t="s">
+        <v>248</v>
+      </c>
+      <c r="P25" s="91" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q25" s="134"/>
+      <c r="R25" s="85"/>
+      <c r="S25" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="T25" s="158"/>
+      <c r="T25" s="154"/>
     </row>
     <row r="26" spans="1:20" ht="60">
       <c r="A26" s="36">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="B26" s="103" t="s">
+      <c r="B26" s="99" t="s">
         <v>142</v>
       </c>
       <c r="C26" s="25" t="s">
@@ -6803,46 +6894,46 @@
       <c r="D26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="131">
+      <c r="E26" s="127">
         <v>46316</v>
       </c>
-      <c r="F26" s="153">
-        <f t="shared" ref="F26:F34" ca="1" si="6">TODAY()-E26</f>
-        <v>8</v>
-      </c>
-      <c r="G26" s="88" t="str">
+      <c r="F26" s="149">
+        <f t="shared" ref="F26:F35" ca="1" si="6">TODAY()-E26</f>
+        <v>9</v>
+      </c>
+      <c r="G26" s="84" t="str">
         <f ca="1">TRIM(TODAY()-DATE(2026,10,26))</f>
-        <v>3</v>
-      </c>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="102"/>
+        <v>4</v>
+      </c>
+      <c r="H26" s="85"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="85"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="98"/>
       <c r="M26" s="24">
         <f>8+109</f>
         <v>117</v>
       </c>
-      <c r="N26" s="88">
+      <c r="N26" s="84">
         <v>350</v>
       </c>
-      <c r="O26" s="96" t="s">
-        <v>246</v>
-      </c>
-      <c r="P26" s="94"/>
-      <c r="Q26" s="138"/>
-      <c r="R26" s="89"/>
-      <c r="S26" s="89" t="s">
+      <c r="O26" s="92" t="s">
+        <v>236</v>
+      </c>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="134"/>
+      <c r="R26" s="85"/>
+      <c r="S26" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T26" s="158"/>
+      <c r="T26" s="154"/>
     </row>
     <row r="27" spans="1:20" ht="60">
       <c r="A27" s="36">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="B27" s="103" t="s">
+      <c r="B27" s="99" t="s">
         <v>144</v>
       </c>
       <c r="C27" s="25" t="s">
@@ -6851,45 +6942,46 @@
       <c r="D27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="131">
+      <c r="E27" s="127">
         <v>46316</v>
       </c>
-      <c r="F27" s="153">
+      <c r="F27" s="149">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="G27" s="88">
+        <v>9</v>
+      </c>
+      <c r="G27" s="84">
         <f ca="1">TODAY()-DATE(2026,10,25)</f>
-        <v>4</v>
-      </c>
-      <c r="H27" s="152"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="89"/>
-      <c r="K27" s="89"/>
-      <c r="L27" s="102"/>
+        <v>5</v>
+      </c>
+      <c r="H27" s="148"/>
+      <c r="I27" s="148"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="98"/>
       <c r="M27" s="24">
-        <v>69</v>
-      </c>
-      <c r="N27" s="88">
+        <f>1+69</f>
+        <v>70</v>
+      </c>
+      <c r="N27" s="84">
         <v>400</v>
       </c>
-      <c r="O27" s="96" t="s">
-        <v>194</v>
-      </c>
-      <c r="P27" s="95"/>
-      <c r="Q27" s="138"/>
-      <c r="R27" s="89"/>
-      <c r="S27" s="89" t="s">
+      <c r="O27" s="92" t="s">
+        <v>249</v>
+      </c>
+      <c r="P27" s="91"/>
+      <c r="Q27" s="134"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="T27" s="158"/>
+      <c r="T27" s="154"/>
     </row>
     <row r="28" spans="1:20" ht="60">
       <c r="A28" s="36">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="B28" s="103" t="s">
+      <c r="B28" s="99" t="s">
         <v>149</v>
       </c>
       <c r="C28" s="25" t="s">
@@ -6898,331 +6990,373 @@
       <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="131">
+      <c r="E28" s="127">
         <v>46312</v>
       </c>
-      <c r="F28" s="153">
+      <c r="F28" s="149">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="G28" s="88">
+        <v>13</v>
+      </c>
+      <c r="G28" s="84">
         <f ca="1">TODAY()-DATE(2026,10,22)</f>
-        <v>7</v>
-      </c>
-      <c r="H28" s="152"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="152"/>
-      <c r="K28" s="176"/>
-      <c r="L28" s="176"/>
+        <v>8</v>
+      </c>
+      <c r="H28" s="148"/>
+      <c r="I28" s="171"/>
+      <c r="J28" s="148"/>
+      <c r="K28" s="171"/>
+      <c r="L28" s="171"/>
       <c r="M28" s="24">
+        <f>4+29</f>
         <v>33</v>
       </c>
-      <c r="N28" s="88">
+      <c r="N28" s="84">
         <v>450</v>
       </c>
-      <c r="O28" s="96" t="s">
-        <v>247</v>
-      </c>
-      <c r="P28" s="94"/>
-      <c r="Q28" s="138"/>
-      <c r="R28" s="89"/>
-      <c r="S28" s="89" t="s">
+      <c r="O28" s="92" t="s">
+        <v>250</v>
+      </c>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="134"/>
+      <c r="R28" s="85"/>
+      <c r="S28" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T28" s="158"/>
+      <c r="T28" s="154"/>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="24">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="B29" s="103" t="s">
+      <c r="B29" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="172" t="s">
         <v>175</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E29" s="131">
+        <v>211</v>
+      </c>
+      <c r="E29" s="127">
         <v>46323</v>
       </c>
-      <c r="F29" s="153">
+      <c r="F29" s="149">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G29" s="88"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="102"/>
-      <c r="L29" s="102"/>
+        <v>2</v>
+      </c>
+      <c r="G29" s="84"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
+      <c r="L29" s="98"/>
       <c r="M29" s="24">
         <v>21</v>
       </c>
-      <c r="N29" s="90">
+      <c r="N29" s="86">
         <v>150</v>
       </c>
-      <c r="O29" s="94"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="94"/>
-      <c r="R29" s="89"/>
-      <c r="S29" s="89" t="s">
+      <c r="O29" s="90"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="85"/>
+      <c r="S29" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T29" s="158"/>
+      <c r="T29" s="154"/>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="24">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
-      <c r="B30" s="177" t="s">
-        <v>187</v>
-      </c>
-      <c r="C30" s="177" t="s">
-        <v>195</v>
+      <c r="B30" s="172" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="172" t="s">
+        <v>193</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E30" s="131">
+        <v>211</v>
+      </c>
+      <c r="E30" s="127">
         <v>46321</v>
       </c>
-      <c r="F30" s="153">
+      <c r="F30" s="149">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="G30" s="88"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="102"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="102"/>
+        <v>4</v>
+      </c>
+      <c r="G30" s="84"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="98"/>
       <c r="M30" s="24">
         <v>12</v>
       </c>
-      <c r="N30" s="90">
+      <c r="N30" s="86">
         <v>150</v>
       </c>
-      <c r="O30" s="94"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="89"/>
-      <c r="S30" s="89" t="s">
+      <c r="O30" s="90"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="85"/>
+      <c r="S30" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T30" s="158"/>
-    </row>
-    <row r="31" spans="1:20" ht="29">
+      <c r="T30" s="154"/>
+    </row>
+    <row r="31" spans="1:20" ht="60">
       <c r="A31" s="24">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="B31" s="177" t="s">
-        <v>188</v>
-      </c>
-      <c r="C31" s="177" t="s">
-        <v>196</v>
+      <c r="B31" s="172" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" s="172" t="s">
+        <v>194</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="131">
+      <c r="E31" s="127">
         <v>46322</v>
       </c>
-      <c r="F31" s="153">
+      <c r="F31" s="149">
         <f t="shared" ca="1" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="G31" s="88">
+        <v>3</v>
+      </c>
+      <c r="G31" s="84">
         <f ca="1">TODAY()-DATE(2026,10,29)</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="89"/>
-      <c r="I31" s="102"/>
-      <c r="J31" s="102"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="102"/>
+        <v>1</v>
+      </c>
+      <c r="H31" s="85"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
       <c r="M31" s="24">
         <v>26</v>
       </c>
-      <c r="N31" s="90">
+      <c r="N31" s="86">
         <v>450</v>
       </c>
-      <c r="O31" s="94"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="94"/>
-      <c r="R31" s="89"/>
-      <c r="S31" s="89" t="s">
+      <c r="O31" s="92" t="s">
+        <v>251</v>
+      </c>
+      <c r="P31" s="90"/>
+      <c r="Q31" s="90"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T31" s="158"/>
-    </row>
-    <row r="32" spans="1:20" ht="28">
+      <c r="T31" s="154"/>
+    </row>
+    <row r="32" spans="1:20" ht="29">
       <c r="A32" s="24">
         <f t="shared" si="3"/>
         <v>31</v>
       </c>
-      <c r="B32" s="160" t="s">
-        <v>199</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>229</v>
+      <c r="B32" s="155" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="173" t="s">
+        <v>220</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E32" s="131">
+        <v>211</v>
+      </c>
+      <c r="E32" s="127">
         <v>46322</v>
       </c>
-      <c r="F32" s="153">
+      <c r="F32" s="149">
         <f t="shared" ca="1" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="G32" s="88"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="102"/>
-      <c r="J32" s="102"/>
-      <c r="K32" s="102"/>
-      <c r="L32" s="102"/>
+        <v>3</v>
+      </c>
+      <c r="G32" s="84"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
       <c r="M32" s="24">
         <v>16</v>
       </c>
-      <c r="N32" s="90">
+      <c r="N32" s="86">
         <v>200</v>
       </c>
-      <c r="O32" s="158"/>
-      <c r="P32" s="158"/>
-      <c r="Q32" s="158"/>
-      <c r="R32" s="89"/>
-      <c r="S32" s="89" t="s">
+      <c r="O32" s="154"/>
+      <c r="P32" s="154"/>
+      <c r="Q32" s="154"/>
+      <c r="R32" s="85"/>
+      <c r="S32" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T32" s="158"/>
+      <c r="T32" s="154"/>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" s="24">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="B33" s="178" t="s">
-        <v>197</v>
-      </c>
-      <c r="C33" s="178" t="s">
-        <v>198</v>
+      <c r="B33" s="173" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="173" t="s">
+        <v>196</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="131">
+      <c r="E33" s="127">
         <v>46323</v>
       </c>
-      <c r="F33" s="153">
+      <c r="F33" s="149">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G33" s="88"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="102"/>
-      <c r="J33" s="102"/>
-      <c r="K33" s="102"/>
-      <c r="L33" s="102"/>
+        <v>2</v>
+      </c>
+      <c r="G33" s="84"/>
+      <c r="H33" s="85"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
       <c r="M33" s="24">
         <v>17</v>
       </c>
-      <c r="N33" s="90">
+      <c r="N33" s="86">
         <v>600</v>
       </c>
-      <c r="O33" s="158"/>
-      <c r="P33" s="158"/>
-      <c r="Q33" s="158"/>
-      <c r="R33" s="89"/>
-      <c r="S33" s="89" t="s">
-        <v>237</v>
-      </c>
-      <c r="T33" s="158" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="O33" s="154"/>
+      <c r="P33" s="154"/>
+      <c r="Q33" s="154"/>
+      <c r="R33" s="85"/>
+      <c r="S33" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="T33" s="154" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="29">
       <c r="A34" s="24">
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="B34" s="160" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>213</v>
+      <c r="B34" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" s="173" t="s">
+        <v>252</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="131">
+      <c r="E34" s="127">
         <v>46323</v>
       </c>
-      <c r="F34" s="153">
+      <c r="F34" s="149">
+        <f t="shared" ca="1" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="84"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="24">
+        <v>74</v>
+      </c>
+      <c r="N34" s="86">
+        <v>700</v>
+      </c>
+      <c r="O34" s="154"/>
+      <c r="P34" s="154"/>
+      <c r="Q34" s="154"/>
+      <c r="R34" s="85"/>
+      <c r="S34" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="T34" s="154" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="29">
+      <c r="A35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="195" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="195" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="127">
+        <v>46324</v>
+      </c>
+      <c r="F35" s="149">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102"/>
-      <c r="M34" s="24">
-        <v>74</v>
-      </c>
-      <c r="N34" s="90">
-        <v>700</v>
-      </c>
-      <c r="O34" s="158"/>
-      <c r="P34" s="158"/>
-      <c r="Q34" s="158"/>
-      <c r="R34" s="89"/>
-      <c r="S34" s="89" t="s">
-        <v>237</v>
-      </c>
-      <c r="T34" s="158" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="24">
+      <c r="G35" s="84"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="98"/>
+      <c r="J35" s="98"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="24">
+        <v>24</v>
+      </c>
+      <c r="N35" s="86">
+        <v>500</v>
+      </c>
+      <c r="O35" s="154"/>
+      <c r="P35" s="154"/>
+      <c r="Q35" s="154"/>
+      <c r="R35" s="85"/>
+      <c r="S35" s="85"/>
+      <c r="T35" s="154"/>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" s="24">
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="B35" s="160" t="s">
-        <v>230</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="B36" s="195" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36" s="195" t="s">
+        <v>253</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="88"/>
-      <c r="F35" s="152"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="102"/>
-      <c r="J35" s="102"/>
-      <c r="K35" s="102"/>
-      <c r="L35" s="102"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="90"/>
-      <c r="O35" s="158"/>
-      <c r="P35" s="158"/>
-      <c r="Q35" s="158"/>
-      <c r="R35" s="89"/>
-      <c r="S35" s="89"/>
-      <c r="T35" s="158"/>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="R36" s="159"/>
-      <c r="S36" s="159"/>
+      <c r="E36" s="127">
+        <v>46325</v>
+      </c>
+      <c r="F36" s="148"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="98"/>
+      <c r="J36" s="98"/>
+      <c r="K36" s="98"/>
+      <c r="L36" s="98"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="86"/>
+      <c r="O36" s="194"/>
+      <c r="P36" s="194"/>
+      <c r="Q36" s="194"/>
+      <c r="R36" s="88"/>
+      <c r="S36" s="88"/>
+      <c r="T36" s="194"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7236,7 +7370,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
@@ -7273,37 +7407,37 @@
       <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="119" t="s">
+      <c r="E1" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="120" t="s">
+      <c r="F1" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="120" t="s">
+      <c r="G1" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="120" t="s">
+      <c r="H1" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="120" t="s">
+      <c r="J1" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="120" t="s">
+      <c r="K1" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="119" t="s">
+      <c r="L1" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="120" t="s">
+      <c r="M1" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="120" t="s">
+      <c r="N1" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="O1" s="120" t="s">
+      <c r="O1" s="116" t="s">
         <v>48</v>
       </c>
       <c r="P1" s="14" t="s">
@@ -7316,11 +7450,12 @@
         <v>102</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="60" hidden="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="60">
       <c r="A2" s="1">
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="31" t="s">
@@ -7375,8 +7510,9 @@
       </c>
       <c r="S2" s="48"/>
     </row>
-    <row r="3" spans="1:19" ht="60" hidden="1">
+    <row r="3" spans="1:19" ht="60">
       <c r="A3" s="1">
+        <f t="shared" ref="A3:A17" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -7437,8 +7573,9 @@
       </c>
       <c r="S3" s="48"/>
     </row>
-    <row r="4" spans="1:19" ht="60" hidden="1">
+    <row r="4" spans="1:19" ht="60">
       <c r="A4" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="31" t="s">
@@ -7498,8 +7635,9 @@
       </c>
       <c r="S4" s="34"/>
     </row>
-    <row r="5" spans="1:19" ht="60" hidden="1">
+    <row r="5" spans="1:19" ht="60">
       <c r="A5" s="1">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="31" t="s">
@@ -7560,8 +7698,9 @@
       </c>
       <c r="S5" s="34"/>
     </row>
-    <row r="6" spans="1:19" ht="60" hidden="1">
+    <row r="6" spans="1:19" ht="60">
       <c r="A6" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="31" t="s">
@@ -7622,8 +7761,9 @@
       </c>
       <c r="S6" s="34"/>
     </row>
-    <row r="7" spans="1:19" s="18" customFormat="1" ht="60" hidden="1">
-      <c r="A7" s="19">
+    <row r="7" spans="1:19" s="18" customFormat="1" ht="60">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="31" t="s">
@@ -7684,8 +7824,9 @@
       </c>
       <c r="S7" s="17"/>
     </row>
-    <row r="8" spans="1:19" s="18" customFormat="1" ht="69" hidden="1" customHeight="1" thickBot="1">
-      <c r="A8" s="19">
+    <row r="8" spans="1:19" s="18" customFormat="1" ht="69" customHeight="1" thickBot="1">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
@@ -7748,9 +7889,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="60" hidden="1">
-      <c r="A9" s="19">
-        <f t="shared" ref="A9:A19" si="0">ROW()-1</f>
+    <row r="9" spans="1:19" ht="60">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="22" t="s">
@@ -7765,34 +7906,34 @@
       <c r="E9" s="8">
         <v>46244</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="71">
         <v>47</v>
       </c>
-      <c r="G9" s="75">
+      <c r="G9" s="71">
         <f>DATE(2026,8,31)-DATE(2026,8,12)</f>
         <v>19</v>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="71">
         <f>DATE(2026,9,14)-DATE(2026,8,31)</f>
         <v>14</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="71">
         <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
         <v>1</v>
       </c>
-      <c r="J9" s="75">
+      <c r="J9" s="71">
         <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
         <v>6</v>
       </c>
-      <c r="K9" s="75">
+      <c r="K9" s="71">
         <f>DATE(2026,9,23)-DATE(2026,9,22)</f>
         <v>1</v>
       </c>
-      <c r="L9" s="75">
+      <c r="L9" s="71">
         <f>DATE(2026,9,23)-DATE(2026,9,17)</f>
         <v>6</v>
       </c>
-      <c r="M9" s="75">
+      <c r="M9" s="71">
         <v>64</v>
       </c>
       <c r="N9" s="9">
@@ -7813,8 +7954,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="18" customFormat="1" ht="60" hidden="1">
-      <c r="A10" s="19">
+    <row r="10" spans="1:19" s="18" customFormat="1" ht="60">
+      <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -7830,34 +7971,34 @@
       <c r="E10" s="8">
         <v>46246</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="71">
         <v>44</v>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="71">
         <f>DATE(2026,8,27)-DATE(2026,8,12)</f>
         <v>15</v>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="71">
         <f>DATE(2026,9,11)-DATE(2026,8,27)</f>
         <v>15</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="71">
         <f>DATE(2026,9,16)-DATE(2026,9,14)</f>
         <v>2</v>
       </c>
-      <c r="J10" s="75">
+      <c r="J10" s="71">
         <f>DATE(2026,9,22)-DATE(2026,9,16)</f>
         <v>6</v>
       </c>
-      <c r="K10" s="75">
+      <c r="K10" s="71">
         <f>DATE(2026,9,23)-DATE(2026,9,22)</f>
         <v>1</v>
       </c>
-      <c r="L10" s="75">
+      <c r="L10" s="71">
         <f>DATE(2026,9,25)-DATE(2026,9,23)</f>
         <v>2</v>
       </c>
-      <c r="M10" s="75">
+      <c r="M10" s="71">
         <v>55</v>
       </c>
       <c r="N10" s="9">
@@ -7878,8 +8019,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="18" customFormat="1" ht="130.5" hidden="1">
-      <c r="A11" s="19">
+    <row r="11" spans="1:19" s="18" customFormat="1" ht="130.5">
+      <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -7895,35 +8036,35 @@
       <c r="E11" s="8">
         <v>46258</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="71">
         <f>DATE(2026,9,30)-DATE(2026,8,24)</f>
         <v>37</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="71">
         <f>DATE(2026,9,9)-DATE(2026,8,24)</f>
         <v>16</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="71">
         <f>DATE(2026,9,14)-DATE(2026,9,9)</f>
         <v>5</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="71">
         <f>DATE(2026,9,15)-DATE(2026,9,14)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="71">
         <f>DATE(2026,9,23)-DATE(2026,9,16)</f>
         <v>7</v>
       </c>
-      <c r="K11" s="75">
+      <c r="K11" s="71">
         <f>DATE(2026,9,23)-DATE(2026,9,23)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="75">
+      <c r="L11" s="71">
         <f>DATE(2026,9,30)-DATE(2026,9,23)</f>
         <v>7</v>
       </c>
-      <c r="M11" s="75">
+      <c r="M11" s="71">
         <v>60</v>
       </c>
       <c r="N11" s="9">
@@ -7945,7 +8086,7 @@
       </c>
     </row>
     <row r="12" spans="1:19" s="18" customFormat="1" ht="116">
-      <c r="A12" s="19">
+      <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -7961,35 +8102,35 @@
       <c r="E12" s="8">
         <v>46252</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="71">
         <f>DATE(2026,10,3)-DATE(2026,8,18)</f>
         <v>46</v>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="71">
         <f>DATE(2026,9,14)-DATE(2026,8,18)</f>
         <v>27</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="71">
         <f>DATE(2026,9,18)-DATE(2026,9,14)</f>
         <v>4</v>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="71">
         <f>DATE(2026,9,22)-DATE(2026,9,18)</f>
         <v>4</v>
       </c>
-      <c r="J12" s="75">
+      <c r="J12" s="71">
         <f>DATE(2026,9,26)-DATE(2026,9,22)</f>
         <v>4</v>
       </c>
-      <c r="K12" s="75">
+      <c r="K12" s="71">
         <f>DATE(2026,9,29)-DATE(2026,9,26)</f>
         <v>3</v>
       </c>
-      <c r="L12" s="75">
+      <c r="L12" s="71">
         <f>DATE(2026,10,1)-DATE(2026,9,29)</f>
         <v>2</v>
       </c>
-      <c r="M12" s="75">
+      <c r="M12" s="71">
         <v>25</v>
       </c>
       <c r="N12" s="9">
@@ -8011,7 +8152,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" s="18" customFormat="1" ht="60">
-      <c r="A13" s="19">
+      <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -8027,34 +8168,34 @@
       <c r="E13" s="8">
         <v>46254</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="71">
         <f>DATE(2026,10,1)-DATE(2026,8,20)</f>
         <v>42</v>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="71">
         <f>DATE(2026,9,14)-DATE(2026,8,20)</f>
         <v>25</v>
       </c>
-      <c r="H13" s="75">
+      <c r="H13" s="71">
         <f>DATE(2026,9,17)-DATE(2026,9,12)</f>
         <v>5</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="71">
         <f>DATE(2026,9,24)-DATE(2026,9,22)</f>
         <v>2</v>
       </c>
-      <c r="J13" s="75">
+      <c r="J13" s="71">
         <f>DATE(2026,9,24)-DATE(2026,9,24)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="75">
+      <c r="K13" s="71">
         <f>DATE(2026,9,25)-DATE(2026,9,24)</f>
         <v>1</v>
       </c>
-      <c r="L13" s="75">
+      <c r="L13" s="71">
         <v>8</v>
       </c>
-      <c r="M13" s="75">
+      <c r="M13" s="71">
         <v>25</v>
       </c>
       <c r="N13" s="9">
@@ -8076,7 +8217,7 @@
       </c>
     </row>
     <row r="14" spans="1:19" s="18" customFormat="1" ht="60">
-      <c r="A14" s="19">
+      <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -8092,35 +8233,35 @@
       <c r="E14" s="8">
         <v>46259</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="71">
         <f>DATE(2026,10,1)-DATE(2026,8,25)</f>
         <v>37</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="71">
         <f>DATE(2026,9,12)-DATE(2026,8,24)</f>
         <v>19</v>
       </c>
-      <c r="H14" s="75">
+      <c r="H14" s="71">
         <f>DATE(2026,9,17)-DATE(2026,9,12)</f>
         <v>5</v>
       </c>
-      <c r="I14" s="75">
+      <c r="I14" s="71">
         <f>DATE(2026,9,17)-DATE(2026,9,17)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="75">
+      <c r="J14" s="71">
         <f>DATE(2026,9,22)-DATE(2026,9,18)</f>
         <v>4</v>
       </c>
-      <c r="K14" s="75">
+      <c r="K14" s="71">
         <f>DATE(2026,9,24)-DATE(2026,9,22)</f>
         <v>2</v>
       </c>
-      <c r="L14" s="75">
+      <c r="L14" s="71">
         <f>DATE(2026,9,30)-DATE(2026,9,25)</f>
         <v>5</v>
       </c>
-      <c r="M14" s="75">
+      <c r="M14" s="71">
         <v>35</v>
       </c>
       <c r="N14" s="9">
@@ -8142,7 +8283,7 @@
       </c>
     </row>
     <row r="15" spans="1:19" s="18" customFormat="1" ht="60">
-      <c r="A15" s="19">
+      <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -8155,7 +8296,7 @@
       <c r="D15" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="150">
+      <c r="E15" s="146">
         <v>46204</v>
       </c>
       <c r="F15" s="32">
@@ -8199,13 +8340,13 @@
       <c r="P15" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="Q15" s="146"/>
-      <c r="R15" s="148">
+      <c r="Q15" s="142"/>
+      <c r="R15" s="144">
         <v>46301</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="60">
-      <c r="A16" s="19">
+      <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -8218,32 +8359,32 @@
       <c r="D16" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="150">
+      <c r="E16" s="146">
         <v>46204</v>
       </c>
       <c r="F16" s="32">
         <f>DATE(2026,10,12)-E16</f>
         <v>103</v>
       </c>
-      <c r="G16" s="75">
+      <c r="G16" s="71">
         <v>35</v>
       </c>
-      <c r="H16" s="75">
+      <c r="H16" s="71">
         <v>23</v>
       </c>
-      <c r="I16" s="75">
+      <c r="I16" s="71">
         <v>10</v>
       </c>
-      <c r="J16" s="75">
+      <c r="J16" s="71">
         <v>4</v>
       </c>
-      <c r="K16" s="75">
+      <c r="K16" s="71">
         <v>18</v>
       </c>
-      <c r="L16" s="75">
+      <c r="L16" s="71">
         <v>5</v>
       </c>
-      <c r="M16" s="75">
+      <c r="M16" s="71">
         <v>6</v>
       </c>
       <c r="N16" s="9">
@@ -8252,17 +8393,17 @@
       <c r="O16" s="9">
         <v>333</v>
       </c>
-      <c r="P16" s="110" t="s">
+      <c r="P16" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="Q16" s="146"/>
-      <c r="R16" s="148">
+      <c r="Q16" s="142"/>
+      <c r="R16" s="144">
         <v>46307</v>
       </c>
-      <c r="S16" s="104"/>
-    </row>
-    <row r="17" spans="1:20" ht="60">
-      <c r="A17" s="19">
+      <c r="S16" s="100"/>
+    </row>
+    <row r="17" spans="1:19" ht="60">
+      <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -8275,38 +8416,38 @@
       <c r="D17" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="150">
+      <c r="E17" s="146">
         <v>46265</v>
       </c>
       <c r="F17" s="32">
         <f>DATE(2026,10,14)-E17</f>
         <v>44</v>
       </c>
-      <c r="G17" s="75">
+      <c r="G17" s="71">
         <f>DATE(2026,9,24)-DATE(2026,8,24)</f>
         <v>31</v>
       </c>
-      <c r="H17" s="75">
+      <c r="H17" s="71">
         <f>DATE(2026,9,30)-DATE(2026,9,24)</f>
         <v>6</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="71">
         <f>DATE(2026,10,3)-DATE(2026,10,1)</f>
         <v>2</v>
       </c>
-      <c r="J17" s="75">
+      <c r="J17" s="71">
         <f>DATE(2026,10,7)-DATE(2026,10,4)</f>
         <v>3</v>
       </c>
-      <c r="K17" s="75">
+      <c r="K17" s="71">
         <f>DATE(2026,10,10)-DATE(2026,10,7)</f>
         <v>3</v>
       </c>
-      <c r="L17" s="75">
+      <c r="L17" s="71">
         <f>DATE(2026,10,14)-DATE(2026,10,10)</f>
         <v>4</v>
       </c>
-      <c r="M17" s="75">
+      <c r="M17" s="71">
         <v>25</v>
       </c>
       <c r="N17" s="9">
@@ -8319,29 +8460,29 @@
         <v>59</v>
       </c>
       <c r="Q17" s="22"/>
-      <c r="R17" s="148">
+      <c r="R17" s="144">
         <v>46309</v>
       </c>
-      <c r="S17" s="93"/>
-    </row>
-    <row r="18" spans="1:20" s="35" customFormat="1" ht="60">
+      <c r="S17" s="89"/>
+    </row>
+    <row r="18" spans="1:19" ht="60">
       <c r="A18" s="19">
         <f>ROW()-1</f>
         <v>17</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="162" t="s">
+      <c r="C18" s="157" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="163" t="s">
+      <c r="D18" s="158" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="150">
+      <c r="E18" s="146">
         <v>46269</v>
       </c>
-      <c r="F18" s="151">
+      <c r="F18" s="147">
         <f>DATE(2026,10,26)-E18</f>
         <v>52</v>
       </c>
@@ -8349,7 +8490,7 @@
         <f>DATE(2026,9,26)-DATE(2026,9,4)</f>
         <v>22</v>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="71">
         <f>DATE(2026,10,11)-DATE(2026,9,26)</f>
         <v>15</v>
       </c>
@@ -8357,7 +8498,7 @@
         <f>DATE(2026,10,16)-DATE(2026,10,12)</f>
         <v>4</v>
       </c>
-      <c r="J18" s="75">
+      <c r="J18" s="71">
         <f>DATE(2026,10,23)-DATE(2026,10,16)</f>
         <v>7</v>
       </c>
@@ -8365,14 +8506,14 @@
         <f>DATE(2026,10,26)-DATE(2026,10,23)</f>
         <v>3</v>
       </c>
-      <c r="L18" s="75">
+      <c r="L18" s="71">
         <f>DATE(2026,10,27)-DATE(2026,10,26)</f>
         <v>1</v>
       </c>
       <c r="M18" s="19">
         <v>14</v>
       </c>
-      <c r="N18" s="75">
+      <c r="N18" s="71">
         <v>189</v>
       </c>
       <c r="O18" s="19">
@@ -8382,31 +8523,31 @@
         <v>59</v>
       </c>
       <c r="Q18" s="19"/>
-      <c r="R18" s="149">
+      <c r="R18" s="145">
         <v>46321</v>
       </c>
-      <c r="S18" s="147"/>
-    </row>
-    <row r="19" spans="1:20" ht="110">
+      <c r="S18" s="143"/>
+    </row>
+    <row r="19" spans="1:19" ht="110">
       <c r="A19" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A19" si="1">ROW()-1</f>
         <v>18</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="162" t="s">
+      <c r="C19" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="162" t="s">
+      <c r="D19" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="187">
+      <c r="E19" s="182">
         <v>46286</v>
       </c>
       <c r="F19" s="19">
-        <f t="shared" ref="F19" ca="1" si="1">TODAY()-E19</f>
-        <v>38</v>
+        <f t="shared" ref="F19" ca="1" si="2">TODAY()-E19</f>
+        <v>39</v>
       </c>
       <c r="G19" s="19">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
@@ -8447,11 +8588,8 @@
       <c r="Q19" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="R19" s="149">
+      <c r="R19" s="145">
         <v>46324</v>
-      </c>
-      <c r="T19" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -8475,241 +8613,241 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26.5" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="78" t="s">
+      <c r="C1" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="76"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="69"/>
+      <c r="D1" s="72"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:11" ht="32.5" customHeight="1" thickBot="1">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="87" t="s">
+      <c r="B2" s="82"/>
+      <c r="C2" s="83" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="84"/>
+      <c r="D2" s="72"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="80"/>
     </row>
     <row r="3" spans="1:11" ht="26.5" thickBot="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="164">
+      <c r="B3" s="159">
         <f>COUNTA(Table2[MPS ID])</f>
-        <v>34</v>
-      </c>
-      <c r="C3" s="79">
+        <v>35</v>
+      </c>
+      <c r="C3" s="75">
         <f ca="1">AVERAGE(Table2[Current TAT (S50 onward)])</f>
-        <v>23.393939393939394</v>
-      </c>
-      <c r="D3" s="76"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
+        <v>23.705882352941178</v>
+      </c>
+      <c r="D3" s="72"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="111">
+      <c r="B4" s="107">
         <f>COUNTA(Delivered!C2:C18)</f>
         <v>17</v>
       </c>
-      <c r="C4" s="83">
+      <c r="C4" s="79">
         <f>AVERAGE(Table3[Total Avg. Aging Days])</f>
         <v>61.3125</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="165"/>
-      <c r="B5" s="165"/>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
+      <c r="A5" s="160"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="160"/>
     </row>
     <row r="6" spans="1:11" ht="36">
-      <c r="A6" s="168" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="169" t="s">
+      <c r="A6" s="163" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="164" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="169" t="s">
+      <c r="C6" s="164" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="169" t="s">
+      <c r="D6" s="164" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="169" t="s">
+      <c r="E6" s="164" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="169" t="s">
-        <v>189</v>
-      </c>
-      <c r="G6" s="169" t="s">
+      <c r="F6" s="164" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="164" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="169" t="s">
-        <v>206</v>
+      <c r="H6" s="164" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="166">
+        <v>201</v>
+      </c>
+      <c r="B7" s="161">
         <f>Delivered!G2</f>
         <v>32</v>
       </c>
-      <c r="C7" s="166">
+      <c r="C7" s="161">
         <f>Delivered!H2</f>
         <v>11</v>
       </c>
-      <c r="D7" s="166">
+      <c r="D7" s="161">
         <f>Delivered!I2</f>
         <v>3</v>
       </c>
-      <c r="E7" s="166">
+      <c r="E7" s="161">
         <f>Delivered!J2</f>
         <v>6</v>
       </c>
-      <c r="F7" s="166">
+      <c r="F7" s="161">
         <f>Delivered!K2</f>
         <v>6</v>
       </c>
-      <c r="G7" s="166">
+      <c r="G7" s="161">
         <f>Delivered!L2</f>
         <v>5</v>
       </c>
-      <c r="H7" s="173">
+      <c r="H7" s="168">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="167">
+        <v>200</v>
+      </c>
+      <c r="B8" s="162">
         <f>AVERAGE(Delivered!G3:G11)</f>
         <v>25</v>
       </c>
-      <c r="C8" s="167">
+      <c r="C8" s="162">
         <f>AVERAGE(Delivered!H3:H11)</f>
         <v>11.777777777777779</v>
       </c>
-      <c r="D8" s="167">
+      <c r="D8" s="162">
         <f>AVERAGE(Delivered!I3:I11)</f>
         <v>4.1111111111111107</v>
       </c>
-      <c r="E8" s="167">
+      <c r="E8" s="162">
         <f>AVERAGE(Delivered!J3:J11)</f>
         <v>6.8888888888888893</v>
       </c>
-      <c r="F8" s="167">
+      <c r="F8" s="162">
         <f>AVERAGE(Delivered!K3:K11)</f>
         <v>5.8888888888888893</v>
       </c>
-      <c r="G8" s="167">
+      <c r="G8" s="162">
         <f>AVERAGE(Delivered!L3:L11)</f>
         <v>6</v>
       </c>
-      <c r="H8" s="173">
+      <c r="H8" s="168">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="170" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="171">
+      <c r="A9" s="165" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="166">
         <f>AVERAGE(Delivered!G12:G21)</f>
         <v>26</v>
       </c>
-      <c r="C9" s="171">
+      <c r="C9" s="166">
         <f>AVERAGE(Delivered!H12:H21)</f>
         <v>11.875</v>
       </c>
-      <c r="D9" s="171">
+      <c r="D9" s="166">
         <f>AVERAGE(Delivered!I12:I21)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="E9" s="171">
+      <c r="E9" s="166">
         <f>AVERAGE(Delivered!J12:J21)</f>
         <v>3.75</v>
       </c>
-      <c r="F9" s="171">
+      <c r="F9" s="166">
         <f>AVERAGE(Delivered!K12:K21)</f>
         <v>6.25</v>
       </c>
-      <c r="G9" s="171">
+      <c r="G9" s="166">
         <f>AVERAGE(Delivered!L12:L21)</f>
         <v>4.125</v>
       </c>
-      <c r="H9" s="173">
+      <c r="H9" s="168">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29">
-      <c r="A10" s="172" t="s">
-        <v>205</v>
-      </c>
-      <c r="B10" s="173">
+      <c r="A10" s="167" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="168">
         <f>AVERAGE(B7:B9)</f>
         <v>27.666666666666668</v>
       </c>
-      <c r="C10" s="173">
+      <c r="C10" s="168">
         <f t="shared" ref="C10:G10" si="0">AVERAGE(C7:C9)</f>
         <v>11.550925925925926</v>
       </c>
-      <c r="D10" s="173">
+      <c r="D10" s="168">
         <f t="shared" si="0"/>
         <v>3.7513227513227512</v>
       </c>
-      <c r="E10" s="173">
+      <c r="E10" s="168">
         <f t="shared" si="0"/>
         <v>5.5462962962962967</v>
       </c>
-      <c r="F10" s="173">
+      <c r="F10" s="168">
         <f t="shared" si="0"/>
         <v>6.0462962962962967</v>
       </c>
-      <c r="G10" s="173">
+      <c r="G10" s="168">
         <f t="shared" si="0"/>
         <v>5.041666666666667</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="174" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="174">
+      <c r="A12" s="169" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="169">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="174" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="174">
+      <c r="A13" s="169" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="169">
         <v>103</v>
       </c>
     </row>
@@ -8718,15 +8856,15 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B16" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8734,7 +8872,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -8742,7 +8880,7 @@
         <v>62</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -8750,31 +8888,31 @@
         <v>120</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="186" t="s">
-        <v>234</v>
+      <c r="B20" s="181" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="186" t="s">
-        <v>235</v>
+        <v>212</v>
+      </c>
+      <c r="B21" s="181" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="186" t="s">
-        <v>236</v>
+      <c r="B22" s="181" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -8801,38 +8939,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="192" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="188"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="193"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="50" t="s">
         <v>100</v>
       </c>
       <c r="C4" s="50">
-        <v>15</v>
-      </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
+        <f>SUM(Table1[No of titles delivered])</f>
+        <v>18</v>
+      </c>
+      <c r="E4" s="59"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="57" t="s">
@@ -8841,150 +8981,175 @@
       <c r="C5" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
+      <c r="D5" s="186" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="59">
+      <c r="B6" s="187">
         <v>46235</v>
       </c>
-      <c r="C6" s="60">
+      <c r="C6" s="188">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B6,Delivered!$R:$R,"&lt;"&amp;EDATE(B6,1))</f>
         <v>1</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
+      <c r="D6" s="161">
+        <f>Delivered!O2</f>
+        <v>385</v>
+      </c>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="59">
+      <c r="B7" s="187">
         <v>46266</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="188">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B7,Delivered!$R:$R,"&lt;"&amp;EDATE(B7,1))</f>
         <v>9</v>
       </c>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
+      <c r="D7" s="161">
+        <f>SUM(Delivered!O3:O11)</f>
+        <v>5975</v>
+      </c>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="59">
+      <c r="B8" s="187">
         <v>46296</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="188">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B8,Delivered!$R:$R,"&lt;"&amp;EDATE(B8,1))</f>
         <v>8</v>
       </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
+      <c r="D8" s="161">
+        <f>SUM(Delivered!O12:O19)</f>
+        <v>2404</v>
+      </c>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="59">
+      <c r="B9" s="187">
         <v>46327</v>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="188">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B9,Delivered!$R:$R,"&lt;"&amp;EDATE(B9,1))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
+      <c r="D9" s="161">
+        <v>0</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="61">
+      <c r="B10" s="189">
         <v>46357</v>
       </c>
-      <c r="C10" s="62">
+      <c r="C10" s="190">
         <f>COUNTIFS(Delivered!$R:$R,"&gt;="&amp;B10,Delivered!$R:$R,"&lt;"&amp;EDATE(B10,1))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
+      <c r="D10" s="191">
+        <f>SUM(D6:D9)</f>
+        <v>8764</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
     </row>
     <row r="17" spans="5:10">
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="63"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D6:D7 D9:D10" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -9008,17 +9173,17 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="C1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="18" customFormat="1" ht="120">
       <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="97" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="24" t="s">
@@ -9029,29 +9194,29 @@
       </c>
       <c r="F2" s="24">
         <f ca="1">TODAY()-E2</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="24">
         <f>DATE(2026,10,7)-DATE(2026,9,21)</f>
         <v>16</v>
       </c>
-      <c r="H2" s="91">
+      <c r="H2" s="87">
         <f>DATE(2026,10,21)-DATE(2026,10,8)</f>
         <v>13</v>
       </c>
-      <c r="I2" s="91" t="str">
+      <c r="I2" s="87" t="str">
         <f>TRIM(DATE(2026,10,23)-DATE(2026,10,22))</f>
         <v>1</v>
       </c>
-      <c r="J2" s="91">
+      <c r="J2" s="87">
         <f>DATE(2026,10,24)-DATE(2026,10,23)</f>
         <v>1</v>
       </c>
-      <c r="K2" s="91">
+      <c r="K2" s="87">
         <f>DATE(2026,10,27)-DATE(2026,10,25)</f>
         <v>2</v>
       </c>
-      <c r="L2" s="88">
+      <c r="L2" s="84">
         <f>DATE(2026,10,29)-DATE(2026,10,28)</f>
         <v>1</v>
       </c>
@@ -9061,25 +9226,25 @@
       <c r="N2" s="24">
         <v>100</v>
       </c>
-      <c r="O2" s="96" t="s">
+      <c r="O2" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="133" t="s">
+      <c r="P2" s="91"/>
+      <c r="Q2" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89" t="s">
+      <c r="R2" s="85"/>
+      <c r="S2" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="T2" s="158"/>
+      <c r="T2" s="154"/>
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="5"/>
-      <c r="C17" s="106" t="s">
+      <c r="C17" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="107">
+      <c r="D17" s="103">
         <f>COUNTA(D20:D52)</f>
         <v>33</v>
       </c>
@@ -9087,13 +9252,13 @@
     </row>
     <row r="18" spans="2:11" ht="15" thickBot="1">
       <c r="B18" s="5"/>
-      <c r="C18" s="108" t="s">
+      <c r="C18" s="104" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="109">
+      <c r="D18" s="105">
         <v>17</v>
       </c>
-      <c r="E18" s="109" t="s">
+      <c r="E18" s="105" t="s">
         <v>163</v>
       </c>
     </row>
@@ -9107,10 +9272,10 @@
       <c r="D19" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="105" t="s">
+      <c r="E19" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="114" t="s">
+      <c r="F19" s="110" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9118,13 +9283,13 @@
       <c r="B20" s="10">
         <v>1</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="112" t="s">
+      <c r="D20" s="108" t="s">
         <v>164</v>
       </c>
-      <c r="E20" s="115">
+      <c r="E20" s="111">
         <v>64</v>
       </c>
       <c r="F20" s="5"/>
@@ -9133,13 +9298,13 @@
       <c r="B21" s="10">
         <v>2</v>
       </c>
-      <c r="C21" s="101" t="s">
+      <c r="C21" s="97" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="118">
+        <v>188</v>
+      </c>
+      <c r="E21" s="114">
         <v>40</v>
       </c>
       <c r="F21" s="17"/>
@@ -9163,13 +9328,13 @@
       <c r="B23" s="10">
         <v>4</v>
       </c>
-      <c r="C23" s="101" t="s">
+      <c r="C23" s="97" t="s">
         <v>159</v>
       </c>
-      <c r="D23" s="122" t="s">
+      <c r="D23" s="118" t="s">
         <v>164</v>
       </c>
-      <c r="E23" s="117">
+      <c r="E23" s="113">
         <v>39</v>
       </c>
       <c r="F23" s="5"/>
@@ -9193,30 +9358,30 @@
       <c r="B25" s="10">
         <v>6</v>
       </c>
-      <c r="C25" s="101" t="s">
+      <c r="C25" s="97" t="s">
         <v>34</v>
       </c>
       <c r="D25" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="112">
+        <v>36</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="152" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="116">
-        <v>36</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" s="156" t="s">
+      <c r="I25" s="152">
+        <v>30</v>
+      </c>
+      <c r="J25" s="152" t="s">
         <v>190</v>
       </c>
-      <c r="I25" s="156">
-        <v>30</v>
-      </c>
-      <c r="J25" s="156" t="s">
+      <c r="K25" s="152" t="s">
         <v>191</v>
-      </c>
-      <c r="K25" s="156" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="29">
@@ -9233,20 +9398,20 @@
         <v>34</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="71" t="s">
+      <c r="G26" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="156" t="s">
+      <c r="H26" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="I26" s="152">
+        <v>46</v>
+      </c>
+      <c r="J26" s="152" t="s">
         <v>190</v>
       </c>
-      <c r="I26" s="156">
-        <v>46</v>
-      </c>
-      <c r="J26" s="156" t="s">
+      <c r="K26" s="152" t="s">
         <v>191</v>
-      </c>
-      <c r="K26" s="156" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="29">
@@ -9263,20 +9428,20 @@
         <v>34</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="71" t="s">
+      <c r="G27" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="H27" s="156" t="s">
-        <v>193</v>
-      </c>
-      <c r="I27" s="156">
+      <c r="H27" s="152" t="s">
+        <v>192</v>
+      </c>
+      <c r="I27" s="152">
         <v>58</v>
       </c>
-      <c r="J27" s="156" t="s">
+      <c r="J27" s="152" t="s">
+        <v>190</v>
+      </c>
+      <c r="K27" s="152" t="s">
         <v>191</v>
-      </c>
-      <c r="K27" s="156" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -9319,7 +9484,7 @@
       <c r="D30" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="118">
+      <c r="E30" s="114">
         <v>31</v>
       </c>
       <c r="F30" s="5"/>
@@ -9334,7 +9499,7 @@
       <c r="D31" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="118">
+      <c r="E31" s="114">
         <v>31</v>
       </c>
       <c r="F31" s="5"/>
@@ -9373,13 +9538,13 @@
       <c r="B34" s="10">
         <v>15</v>
       </c>
-      <c r="C34" s="142" t="s">
+      <c r="C34" s="138" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="143" t="s">
+      <c r="D34" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="118">
+      <c r="E34" s="114">
         <v>28</v>
       </c>
       <c r="F34" s="5"/>
@@ -9403,13 +9568,13 @@
       <c r="B36" s="10">
         <v>17</v>
       </c>
-      <c r="C36" s="142" t="s">
+      <c r="C36" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="145" t="s">
+      <c r="D36" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="118">
+      <c r="E36" s="114">
         <v>27</v>
       </c>
       <c r="F36" s="5"/>
@@ -9418,13 +9583,13 @@
       <c r="B37" s="10">
         <v>18</v>
       </c>
-      <c r="C37" s="142" t="s">
+      <c r="C37" s="138" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="145" t="s">
+      <c r="D37" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="118">
+      <c r="E37" s="114">
         <v>27</v>
       </c>
       <c r="F37" s="5"/>
@@ -9433,10 +9598,10 @@
       <c r="B38" s="10">
         <v>19</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="140" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="145" t="s">
+      <c r="D38" s="141" t="s">
         <v>19</v>
       </c>
       <c r="E38" s="3">
@@ -9467,9 +9632,9 @@
         <v>119</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E40" s="118">
+        <v>184</v>
+      </c>
+      <c r="E40" s="114">
         <v>15</v>
       </c>
       <c r="F40" s="5"/>
@@ -9510,10 +9675,10 @@
       <c r="B43" s="10">
         <v>24</v>
       </c>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="138" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="145" t="s">
+      <c r="D43" s="141" t="s">
         <v>19</v>
       </c>
       <c r="E43" s="10">
@@ -9600,8 +9765,8 @@
       <c r="B49" s="10">
         <v>30</v>
       </c>
-      <c r="C49" s="157" t="s">
-        <v>195</v>
+      <c r="C49" s="153" t="s">
+        <v>193</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>24</v>
@@ -9615,8 +9780,8 @@
       <c r="B50" s="10">
         <v>31</v>
       </c>
-      <c r="C50" s="157" t="s">
-        <v>196</v>
+      <c r="C50" s="153" t="s">
+        <v>194</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>24</v>
@@ -9630,8 +9795,8 @@
       <c r="B51" s="10">
         <v>32</v>
       </c>
-      <c r="C51" s="157" t="s">
-        <v>200</v>
+      <c r="C51" s="153" t="s">
+        <v>198</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>24</v>
@@ -9645,8 +9810,8 @@
       <c r="B52" s="10">
         <v>33</v>
       </c>
-      <c r="C52" s="157" t="s">
-        <v>198</v>
+      <c r="C52" s="153" t="s">
+        <v>196</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>24</v>
